--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54299EB2-44E9-40A5-8B62-8E624773A0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C9F68F-8E34-4205-B306-5067B27713E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13680" yWindow="0" windowWidth="15225" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="613">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -124,18 +124,6 @@
     <t>Michelangelo</t>
   </si>
   <si>
-    <t>Girolamo</t>
-  </si>
-  <si>
-    <t>Danese</t>
-  </si>
-  <si>
-    <t>Benvenuto</t>
-  </si>
-  <si>
-    <t>Michel</t>
-  </si>
-  <si>
     <t>Francesco</t>
   </si>
   <si>
@@ -271,27 +259,6 @@
     <t>BOLOGNE</t>
   </si>
   <si>
-    <t>BONTEMPS</t>
-  </si>
-  <si>
-    <t>BRÜGGEMANN</t>
-  </si>
-  <si>
-    <t>BUONARROTI</t>
-  </si>
-  <si>
-    <t>CAMPAGNA</t>
-  </si>
-  <si>
-    <t>CATTANEO</t>
-  </si>
-  <si>
-    <t>CELLINI</t>
-  </si>
-  <si>
-    <t>COLOMBE</t>
-  </si>
-  <si>
     <t>da SANGALLO</t>
   </si>
   <si>
@@ -442,27 +409,6 @@
     <t>1579-1583</t>
   </si>
   <si>
-    <t>1550-1556</t>
-  </si>
-  <si>
-    <t>1514-1521</t>
-  </si>
-  <si>
-    <t>1501-1504</t>
-  </si>
-  <si>
-    <t>1593-1596</t>
-  </si>
-  <si>
-    <t>1563 environ</t>
-  </si>
-  <si>
-    <t>1545-1554</t>
-  </si>
-  <si>
-    <t>1500</t>
-  </si>
-  <si>
     <t>1526</t>
   </si>
   <si>
@@ -694,18 +640,6 @@
     <t>Basilique Saint-Denis</t>
   </si>
   <si>
-    <t>Cathédrale de Schleswig</t>
-  </si>
-  <si>
-    <t>Les galeries de l'Académie</t>
-  </si>
-  <si>
-    <t>Basilique San Francesco della Vigna</t>
-  </si>
-  <si>
-    <t>Église de la Madonna dell'Orto</t>
-  </si>
-  <si>
     <t>Musée du Louvre</t>
   </si>
   <si>
@@ -817,9 +751,6 @@
     <t>Église San Zaccaria</t>
   </si>
   <si>
-    <t>"Atlas soutenant le monde"</t>
-  </si>
-  <si>
     <t>"Portail de la cour Henri IV"</t>
   </si>
   <si>
@@ -835,30 +766,6 @@
     <t>"Reliefs du chœur (avec Alonso Berruguete)"</t>
   </si>
   <si>
-    <t>"L'Enlèvement des Sabines"</t>
-  </si>
-  <si>
-    <t>"Monument du cœur de François Ier"</t>
-  </si>
-  <si>
-    <t>"Le Retable de Bordesholm"</t>
-  </si>
-  <si>
-    <t>"David"</t>
-  </si>
-  <si>
-    <t>"Maître-autel"</t>
-  </si>
-  <si>
-    <t>"Tombeau de Gasparo Contarini"</t>
-  </si>
-  <si>
-    <t>"Persée tenant la tête de Méduse"</t>
-  </si>
-  <si>
-    <t>"Vierge à l'enfant"</t>
-  </si>
-  <si>
     <t>"La Metterza (Sainte Anne, la Vierge et l'Enfant)"</t>
   </si>
   <si>
@@ -871,9 +778,6 @@
     <t>"Le Duel allégorique entre Albrecht Dürer et Apelle"</t>
   </si>
   <si>
-    <t>"L'Enterrement du Christ"</t>
-  </si>
-  <si>
     <t>"L'Enlèvement d'Hélène par Pâris."</t>
   </si>
   <si>
@@ -1012,30 +916,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7d/Choir_stall_of_Cathedral_of_Toledo_06.jpg/960px-Choir_stall_of_Cathedral_of_Toledo_06.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Giambologna_raptodasabina.jpg/1280px-Giambologna_raptodasabina.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1a/Basilique_Saint-Denis_Francois_Ier_monument_coeur.jpg/1280px-Basilique_Saint-Denis_Francois_Ier_monument_coeur.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/00_2516_Schleswig_%28Schleswig-Holstein%2C_Germany%29_-_Sankt-Petri-Dom.jpg/960px-00_2516_Schleswig_%28Schleswig-Holstein%2C_Germany%29_-_Sankt-Petri-Dom.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/San_Francesco_della_Vigna_%28Venice%29_-_Choir_-_Main_altar.jpg/1280px-San_Francesco_della_Vigna_%28Venice%29_-_Choir_-_Main_altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3b/Madonna_dell%27Orto_%28Venice%29_-_Chapel_Contarini_-_Gasparo_Contarini_%281483-1542%29_by_Danese_Cattaneo_%28ca_1563%29.jpg/1280px-Madonna_dell%27Orto_%28Venice%29_-_Chapel_Contarini_-_Gasparo_Contarini_%281483-1542%29_by_Danese_Cattaneo_%28ca_1563%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c0/Perseus_Cellini_Loggia_dei_Lanzi_2005_09_13.jpg/1280px-Perseus_Cellini_Loggia_dei_Lanzi_2005_09_13.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/02/La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg/960px-La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/43/Sant%27Anna%2C_la_Madonna_e_il_Bambino_di_Francesco_da_Sangallo_%281526_circa%29%2C2.JPG/1280px-Sant%27Anna%2C_la_Madonna_e_il_Bambino_di_Francesco_da_Sangallo_%281526_circa%29%2C2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1180,9 +1060,6 @@
     <t>Bois polychrome doré</t>
   </si>
   <si>
-    <t>Bois de chêne polychrome</t>
-  </si>
-  <si>
     <t>Bois polychrome</t>
   </si>
   <si>
@@ -1228,18 +1105,6 @@
     <t>100 cm environ</t>
   </si>
   <si>
-    <t>410 cm environ</t>
-  </si>
-  <si>
-    <t>517 cm</t>
-  </si>
-  <si>
-    <t>519 cm environ</t>
-  </si>
-  <si>
-    <t>90 cm environ</t>
-  </si>
-  <si>
     <t>195 cm environ</t>
   </si>
   <si>
@@ -1607,6 +1472,393 @@
   </si>
   <si>
     <t>Michel Ange</t>
+  </si>
+  <si>
+    <t>Atlas soutenant le monde</t>
+  </si>
+  <si>
+    <t>Atlante che sorregge il mondo</t>
+  </si>
+  <si>
+    <t>Statue</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Hercule terrassant l'Hydre</t>
+  </si>
+  <si>
+    <t>Ercole uccide l'idra</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/94/Hercules_Slaying_the_Hydra_by_Tiziano_Aspetti.JPG/960px-Hercules_Slaying_the_Hydra_by_Tiziano_Aspetti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>vers 1590</t>
+  </si>
+  <si>
+    <t>Église de San Francesco della Vigna</t>
+  </si>
+  <si>
+    <t>Façade (niches)</t>
+  </si>
+  <si>
+    <t>Moïse</t>
+  </si>
+  <si>
+    <t>Mosè</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue monumentale</t>
+  </si>
+  <si>
+    <t>Saint Paul</t>
+  </si>
+  <si>
+    <t>San Paolo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1592</t>
+  </si>
+  <si>
+    <t>Basilique Saint-Antoine</t>
+  </si>
+  <si>
+    <t>Chapelle de Saint Antoine</t>
+  </si>
+  <si>
+    <t>Le Martyre de saint Daniel</t>
+  </si>
+  <si>
+    <t>Martirio di san Daniele</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2d/Martyrdom_of_St._Daniel_of_Padua_MET_DP-1370-001.jpg/1280px-Martyrdom_of_St._Daniel_of_Padua_MET_DP-1370-001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bas-relief</t>
+  </si>
+  <si>
+    <t>vers 1600</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Marte</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bf/Mars_as_Contemporary_Warrior_MET_DP248150.jpg/960px-Mars_as_Contemporary_Warrior_MET_DP248150.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statuette</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>L'Enlèvement des Sabines</t>
+  </si>
+  <si>
+    <t>Ratto delle sabine</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Giambologna_raptodasabina.jpg/1280px-Giambologna_raptodasabina.jpg</t>
+  </si>
+  <si>
+    <t>410 cm</t>
+  </si>
+  <si>
+    <t>1564-1566</t>
+  </si>
+  <si>
+    <t>Bologne</t>
+  </si>
+  <si>
+    <t>Piazza del Nettuno</t>
+  </si>
+  <si>
+    <t>Fontaine de Neptune</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Fontaine monumentale</t>
+  </si>
+  <si>
+    <t>320 cm (Neptune)</t>
+  </si>
+  <si>
+    <t>1580</t>
+  </si>
+  <si>
+    <t>Mercure volant</t>
+  </si>
+  <si>
+    <t>Mercurio volante</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg/500px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>180 cm</t>
+  </si>
+  <si>
+    <t>Vaglia</t>
+  </si>
+  <si>
+    <t>Villa Medicea di Pratolino</t>
+  </si>
+  <si>
+    <t>Colosse de l'Apennin</t>
+  </si>
+  <si>
+    <t>Colosso dell'Appennino</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/da/Appennino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Statue colossale</t>
+  </si>
+  <si>
+    <t>Pierre et brique, stuc</t>
+  </si>
+  <si>
+    <t>1400 cm</t>
+  </si>
+  <si>
+    <t>1594</t>
+  </si>
+  <si>
+    <t>Statue équestre de Cosme Ier de Médicis</t>
+  </si>
+  <si>
+    <t>Monumento equestre a Cosimo I de' Medici</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue équestre</t>
+  </si>
+  <si>
+    <t>450 cm</t>
+  </si>
+  <si>
+    <t>1567-1570</t>
+  </si>
+  <si>
+    <t>Florence triomphant de Pise</t>
+  </si>
+  <si>
+    <t>Firenze vittoriosa su Pisa</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Groupe sculpté</t>
+  </si>
+  <si>
+    <t>260 cm</t>
+  </si>
+  <si>
+    <t>1560-1562</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/2/2d/Michelangelo_Bacchus.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>203 cm</t>
+  </si>
+  <si>
+    <t>1595-1600</t>
+  </si>
+  <si>
+    <t>Hercule et le Centaure Nessus</t>
+  </si>
+  <si>
+    <t>Ercole e il centauro Nesso</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9a/Herakles_Nessos_Loggia_dei_Lanzi_2005_09_13.jpg/960px-Herakles_Nessos_Loggia_dei_Lanzi_2005_09_13.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>269 cm</t>
+  </si>
+  <si>
+    <t>Mercure enlevant Psyché</t>
+  </si>
+  <si>
+    <t>Mercurius raapt Psyche op</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>1596-1599</t>
+  </si>
+  <si>
+    <t>Maximilianstraße</t>
+  </si>
+  <si>
+    <t>Fontaine de Mercure</t>
+  </si>
+  <si>
+    <t>Merkurbrunnen</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/5e/Augsburg_Mattes_2013-05-01_%2846%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>1597-1600</t>
+  </si>
+  <si>
+    <t>Fontaine d'Hercule</t>
+  </si>
+  <si>
+    <t>Herkulesbrunnen</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/55/Herkulesbrunnen_von_Adriaen_de_Vries%3B_Augsburg.JPG/960px-Herkulesbrunnen_von_Adriaen_de_Vries%3B_Augsburg.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1603</t>
+  </si>
+  <si>
+    <t>Buste de l'empereur Rodolphe II</t>
+  </si>
+  <si>
+    <t>Büste Kaiser Rudolfs II.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Kaiser_Rudolf_II._%28de_Vries_1603%29.jpg/960px-Kaiser_Rudolf_II._%28de_Vries_1603%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Buste</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>L'Enterrement du Christ</t>
+  </si>
+  <si>
+    <t>El Santo Entierro</t>
+  </si>
+  <si>
+    <t>1550-1560</t>
+  </si>
+  <si>
+    <t>Saint Jean-Baptiste</t>
+  </si>
+  <si>
+    <t>San Juan Bautista</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ee/Valladolid_museo_escultura_San_Juan_Juan_de_Juni_ni.JPG/960px-Valladolid_museo_escultura_San_Juan_Juan_de_Juni_ni.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1556</t>
+  </si>
+  <si>
+    <t>Medina de Rioseco</t>
+  </si>
+  <si>
+    <t>Église de Santa María de Mediavilla</t>
+  </si>
+  <si>
+    <t>Chapelle des Benavente</t>
+  </si>
+  <si>
+    <t>Retable de la chapelle des Benavente</t>
+  </si>
+  <si>
+    <t>Retablo de la capilla de los Benavente</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/Medina_de_Rioseco_-_Santa_Maria_de_Mediavilla1.jpg/960px-Medina_de_Rioseco_-_Santa_Maria_de_Mediavilla1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Terre cuite polychrome</t>
+  </si>
+  <si>
+    <t>1571</t>
+  </si>
+  <si>
+    <t>Cathédrale de Valladolid</t>
+  </si>
+  <si>
+    <t>Retable majeur (Retablo mayor)</t>
+  </si>
+  <si>
+    <t>Retablo mayor de la Catedral de Valladolid</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/Valladolid_catedral_retablo_02_lou.jpg/960px-Valladolid_catedral_retablo_02_lou.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bois polychrome et doré</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>1551</t>
+  </si>
+  <si>
+    <t>Segovie</t>
+  </si>
+  <si>
+    <t>Cathédrale de Ségovie</t>
+  </si>
+  <si>
+    <t>Chapelle de la Piedad</t>
+  </si>
+  <si>
+    <t>La Déploration du Christ (El Entierro de Cristo)</t>
+  </si>
+  <si>
+    <t>El Santo Entierro / La Piedad</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Retablo_del_Santo_Entierro%2C_Juan_de_Juni.jpg/960px-Retablo_del_Santo_Entierro%2C_Juan_de_Juni.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Groupe sculptural</t>
+  </si>
+  <si>
+    <t>Musée Diocésain et Cathédralice</t>
+  </si>
+  <si>
+    <t>La Vierge des Douleurs (Virgen de las Angustias)</t>
+  </si>
+  <si>
+    <t>Virgen de las Angustias</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/70/Virgen-de-las-Angustias.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>125</t>
   </si>
 </sst>
 </file>
@@ -2024,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y82"/>
+  <dimension ref="A1:Y96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2197,40 +2449,40 @@
         <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>414</v>
+        <v>369</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>415</v>
+        <v>370</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="S3" s="2">
         <v>560</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -2238,40 +2490,40 @@
         <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>419</v>
+        <v>374</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>420</v>
+        <v>375</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>421</v>
+        <v>376</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>422</v>
+        <v>377</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -2279,40 +2531,40 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>423</v>
+        <v>378</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>424</v>
+        <v>379</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>425</v>
+        <v>380</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>426</v>
+        <v>381</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>427</v>
+        <v>382</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="S5" s="2">
         <v>262</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -2320,40 +2572,40 @@
         <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>428</v>
+        <v>383</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>424</v>
+        <v>379</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>431</v>
+        <v>386</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="S6" s="2">
         <v>139</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -2361,37 +2613,37 @@
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>433</v>
+        <v>388</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>434</v>
+        <v>389</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>436</v>
+        <v>391</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>437</v>
+        <v>392</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -2399,37 +2651,37 @@
         <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>438</v>
+        <v>393</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>439</v>
+        <v>394</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>440</v>
+        <v>395</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>441</v>
+        <v>396</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>443</v>
+        <v>398</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -2437,37 +2689,37 @@
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>446</v>
+        <v>401</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -2475,40 +2727,40 @@
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>449</v>
+        <v>404</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>417</v>
+        <v>372</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>451</v>
+        <v>406</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>452</v>
+        <v>407</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>453</v>
+        <v>408</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -2516,289 +2768,290 @@
         <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>265</v>
+        <v>484</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>485</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>324</v>
+        <v>292</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="V11" s="6">
-        <v>2</v>
+        <v>343</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>487</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>266</v>
+        <v>488</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>325</v>
+        <v>490</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V12" s="7">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>487</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>134</v>
+        <v>491</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>215</v>
+        <v>492</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="V13" s="5" t="s">
-        <v>456</v>
+        <v>343</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>487</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>424</v>
+        <v>492</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>463</v>
+        <v>498</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>464</v>
+        <v>499</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>465</v>
+        <v>500</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="V14" s="5" t="s">
-        <v>456</v>
+        <v>343</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>487</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>188</v>
+        <v>372</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>218</v>
+        <v>502</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>469</v>
+        <v>504</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>470</v>
+        <v>505</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>471</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="M15" s="4"/>
       <c r="Q15" s="2" t="s">
-        <v>460</v>
+        <v>507</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>456</v>
+        <v>343</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>487</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>473</v>
+        <v>508</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>439</v>
+        <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>474</v>
+        <v>509</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>510</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="S16" s="2">
-        <v>78</v>
-      </c>
-      <c r="T16" s="2">
-        <v>75</v>
-      </c>
-      <c r="V16" s="5" t="s">
-        <v>456</v>
+        <v>511</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>487</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>478</v>
+        <v>199</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>480</v>
+        <v>243</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>460</v>
+        <v>293</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="V17" s="5" t="s">
-        <v>456</v>
+        <v>31</v>
+      </c>
+      <c r="V17" s="7">
+        <v>3</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -2806,46 +3059,46 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>483</v>
+        <v>123</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>485</v>
+        <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>486</v>
+        <v>412</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>487</v>
+        <v>413</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>488</v>
+        <v>294</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>414</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="V18" s="5" t="s">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -2853,333 +3106,330 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>134</v>
+        <v>417</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>215</v>
+        <v>379</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>267</v>
+        <v>418</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>419</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>326</v>
+        <v>420</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="V19" s="5">
-        <v>1</v>
+        <v>421</v>
+      </c>
+      <c r="V19" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>135</v>
+        <v>422</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>218</v>
+        <v>200</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>268</v>
+        <v>424</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>327</v>
+        <v>426</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="V20" s="7">
-        <v>3</v>
+        <v>427</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>136</v>
+        <v>428</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>219</v>
+        <v>394</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>269</v>
+        <v>429</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="V21" s="7">
-        <v>3</v>
+        <v>430</v>
+      </c>
+      <c r="S21" s="2">
+        <v>78</v>
+      </c>
+      <c r="T21" s="2">
+        <v>75</v>
+      </c>
+      <c r="V21" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>137</v>
+        <v>431</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>220</v>
+        <v>432</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>433</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>490</v>
+        <v>434</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>491</v>
+        <v>435</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>492</v>
+        <v>436</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>493</v>
+        <v>415</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="V22" s="6">
-        <v>2</v>
+        <v>344</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="V22" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>137</v>
+        <v>438</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>220</v>
+        <v>439</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>440</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>494</v>
+        <v>441</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>495</v>
+        <v>442</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>497</v>
+        <v>443</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>387</v>
+        <v>344</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="V23" s="6">
-        <v>2</v>
+        <v>444</v>
+      </c>
+      <c r="V23" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>501</v>
+        <v>170</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>503</v>
+        <v>197</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>505</v>
+        <v>244</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>507</v>
+        <v>294</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="V24" s="6">
-        <v>2</v>
+        <v>344</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="V24" s="5">
+        <v>1</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>509</v>
+        <v>124</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>501</v>
+        <v>170</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>511</v>
+        <v>200</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>513</v>
+        <v>245</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>515</v>
+        <v>295</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="V25" s="6">
-        <v>2</v>
+        <v>343</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V25" s="7">
+        <v>3</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>190</v>
+        <v>125</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>518</v>
+        <v>246</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>460</v>
+        <v>296</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="T26" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="V26" s="6">
-        <v>2</v>
+        <v>345</v>
+      </c>
+      <c r="V26" s="7">
+        <v>3</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -3187,31 +3437,31 @@
         <v>28</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>522</v>
+        <v>126</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>523</v>
+        <v>172</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>524</v>
+        <v>202</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>525</v>
+        <v>445</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>526</v>
+        <v>446</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>527</v>
+        <v>447</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>493</v>
+        <v>448</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>385</v>
+        <v>345</v>
       </c>
       <c r="V27" s="6">
         <v>2</v>
@@ -3220,1361 +3470,1588 @@
         <v>28</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>138</v>
+        <v>126</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>270</v>
+        <v>449</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>329</v>
+        <v>451</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="V28" s="7">
-        <v>3</v>
+        <v>346</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="V28" s="6">
+        <v>2</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>139</v>
+        <v>455</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>188</v>
+        <v>456</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>222</v>
+        <v>457</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>271</v>
+        <v>459</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>330</v>
+        <v>461</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="V29" s="5">
-        <v>1</v>
+        <v>463</v>
+      </c>
+      <c r="V29" s="6">
+        <v>2</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>140</v>
+        <v>464</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>191</v>
+        <v>456</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>223</v>
+        <v>465</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>466</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>272</v>
+        <v>467</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>468</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>331</v>
+        <v>469</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>470</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="V30" s="7">
-        <v>3</v>
+        <v>471</v>
+      </c>
+      <c r="V30" s="6">
+        <v>2</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>273</v>
+        <v>472</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>473</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>332</v>
+        <v>474</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="V31" s="7">
-        <v>3</v>
+        <v>346</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="V31" s="6">
+        <v>2</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>142</v>
+        <v>477</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>188</v>
+        <v>478</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>225</v>
+        <v>479</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>274</v>
+        <v>480</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>481</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>333</v>
+        <v>482</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S32" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="V32" s="7">
-        <v>3</v>
+        <v>345</v>
+      </c>
+      <c r="V32" s="6">
+        <v>2</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>334</v>
+        <v>297</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>382</v>
+        <v>345</v>
       </c>
       <c r="V33" s="7">
         <v>3</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>276</v>
+        <v>514</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>515</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>335</v>
+        <v>516</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="V34" s="7">
-        <v>3</v>
+        <v>344</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="V34" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>145</v>
+        <v>518</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>188</v>
+        <v>519</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>222</v>
+        <v>520</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>277</v>
+        <v>521</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>370</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>336</v>
+        <v>522</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>523</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="V35" s="5">
-        <v>1</v>
+        <v>524</v>
+      </c>
+      <c r="V35" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>146</v>
+        <v>525</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>278</v>
+        <v>526</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>337</v>
+        <v>528</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="V36" s="7">
-        <v>3</v>
+        <v>529</v>
+      </c>
+      <c r="V36" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>530</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>229</v>
+        <v>531</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>279</v>
+        <v>532</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>533</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>338</v>
+        <v>534</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>535</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>384</v>
+        <v>536</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="V37" s="7">
-        <v>3</v>
+        <v>537</v>
+      </c>
+      <c r="V37" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>148</v>
+        <v>538</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>280</v>
+        <v>539</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>540</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>339</v>
+        <v>541</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>542</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="V38" s="7">
-        <v>3</v>
+        <v>543</v>
+      </c>
+      <c r="V38" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>149</v>
+        <v>544</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>230</v>
+        <v>379</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>281</v>
+        <v>545</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>546</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>340</v>
+        <v>547</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="V39" s="7">
-        <v>3</v>
+        <v>549</v>
+      </c>
+      <c r="V39" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>150</v>
+        <v>550</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>231</v>
+        <v>379</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>282</v>
+        <v>418</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>419</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>341</v>
+        <v>551</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="V40" s="7">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="V40" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>151</v>
+        <v>553</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>283</v>
+        <v>554</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>555</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>342</v>
+        <v>556</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="V41" s="6">
-        <v>2</v>
+        <v>344</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="V41" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>343</v>
+        <v>298</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>408</v>
+        <v>361</v>
       </c>
       <c r="V42" s="7">
         <v>3</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="K43" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="R43" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="R43" s="2" t="s">
-        <v>31</v>
+      <c r="S43" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="V43" s="7">
         <v>3</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>345</v>
+        <v>300</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="V44" s="5">
-        <v>1</v>
+        <v>363</v>
+      </c>
+      <c r="V44" s="7">
+        <v>3</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>346</v>
+        <v>301</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>382</v>
+        <v>344</v>
       </c>
       <c r="V45" s="7">
         <v>3</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>288</v>
+        <v>578</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>579</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>347</v>
+        <v>302</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>388</v>
+        <v>346</v>
       </c>
       <c r="V46" s="6">
         <v>2</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>157</v>
+        <v>580</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>289</v>
+        <v>581</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>582</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>348</v>
+        <v>583</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="V47" s="7">
-        <v>3</v>
+        <v>346</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="V47" s="6">
+        <v>2</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>158</v>
+        <v>585</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>195</v>
+        <v>586</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>237</v>
+        <v>587</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>588</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>290</v>
+        <v>589</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>590</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>349</v>
+        <v>591</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="V48" s="7">
-        <v>3</v>
+        <v>592</v>
+      </c>
+      <c r="V48" s="6">
+        <v>2</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>159</v>
+        <v>593</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>238</v>
+        <v>594</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>350</v>
+        <v>595</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="V49" s="7">
-        <v>3</v>
+        <v>598</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="V49" s="6">
+        <v>2</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>157</v>
+        <v>600</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>601</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>239</v>
+        <v>602</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>292</v>
+        <v>604</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>605</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>351</v>
+        <v>606</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>607</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="S50" s="2" t="s">
-        <v>410</v>
+        <v>346</v>
       </c>
       <c r="V50" s="6">
         <v>2</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>160</v>
+        <v>378</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>240</v>
+        <v>608</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>293</v>
+        <v>609</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>610</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>352</v>
+        <v>611</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="V51" s="7">
-        <v>3</v>
+        <v>346</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="V51" s="6">
+        <v>2</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>353</v>
+        <v>303</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="V52" s="6">
-        <v>2</v>
+        <v>344</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="V52" s="7">
+        <v>3</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>295</v>
+        <v>253</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>354</v>
+        <v>304</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V53" s="5">
-        <v>1</v>
+      <c r="V53" s="7">
+        <v>3</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>296</v>
+        <v>558</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>559</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>355</v>
+        <v>305</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>415</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="V54" s="7">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="V54" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>164</v>
+        <v>561</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>244</v>
+        <v>562</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>297</v>
+        <v>563</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>564</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>356</v>
+        <v>565</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>523</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="S55" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="V55" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="V55" s="7">
-        <v>3</v>
-      </c>
       <c r="W55" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>165</v>
+        <v>567</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>228</v>
+        <v>562</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>298</v>
+        <v>568</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>569</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>357</v>
+        <v>570</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>523</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="V56" s="7">
-        <v>3</v>
+        <v>347</v>
+      </c>
+      <c r="V56" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>166</v>
+        <v>572</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>299</v>
+        <v>573</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>574</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>358</v>
+        <v>575</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>576</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V57" s="7">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="V57" s="5" t="s">
+        <v>411</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>359</v>
+        <v>305</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="V58" s="7">
-        <v>3</v>
+        <v>364</v>
+      </c>
+      <c r="V58" s="5">
+        <v>1</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>202</v>
+        <v>137</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>384</v>
+        <v>342</v>
       </c>
       <c r="V59" s="7">
         <v>3</v>
       </c>
       <c r="W59" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>361</v>
+        <v>307</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="V60" s="7">
-        <v>3</v>
+        <v>347</v>
+      </c>
+      <c r="V60" s="6">
+        <v>2</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>387</v>
+        <v>346</v>
       </c>
       <c r="V61" s="7">
         <v>3</v>
       </c>
       <c r="W61" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="V62" s="6">
-        <v>2</v>
+        <v>344</v>
+      </c>
+      <c r="V62" s="7">
+        <v>3</v>
       </c>
       <c r="W62" s="2" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>171</v>
+        <v>141</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="V63" s="6">
-        <v>2</v>
+        <v>348</v>
+      </c>
+      <c r="V63" s="7">
+        <v>3</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="K64" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="S64" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="R64" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="V64" s="7">
-        <v>3</v>
+      <c r="V64" s="6">
+        <v>2</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>366</v>
+        <v>312</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>395</v>
+        <v>350</v>
       </c>
       <c r="V65" s="7">
         <v>3</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="K66" s="4"/>
-      <c r="V66" s="5">
-        <v>1</v>
+      <c r="A66" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="V66" s="6">
+        <v>2</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>528</v>
+        <v>47</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
@@ -4582,627 +5059,1110 @@
         <v>30</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="E67" s="2" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>308</v>
+        <v>263</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>367</v>
+        <v>314</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="V67" s="7">
-        <v>3</v>
+        <v>31</v>
+      </c>
+      <c r="V67" s="5">
+        <v>1</v>
       </c>
       <c r="W67" s="2" t="s">
         <v>30</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>368</v>
+        <v>315</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="V68" s="7">
         <v>3</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>369</v>
+        <v>316</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>396</v>
+        <v>346</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="V69" s="7">
         <v>3</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>311</v>
+        <v>266</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="V70" s="5">
-        <v>1</v>
+        <v>343</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="V70" s="7">
+        <v>3</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>384</v>
+        <v>31</v>
       </c>
       <c r="V71" s="7">
         <v>3</v>
       </c>
       <c r="W71" s="2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="K72" s="4"/>
-      <c r="V72" s="6">
-        <v>2</v>
+      <c r="A72" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="V72" s="7">
+        <v>3</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>413</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>256</v>
+        <v>205</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>313</v>
+        <v>269</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>31</v>
+        <v>344</v>
       </c>
       <c r="V73" s="7">
         <v>3</v>
       </c>
       <c r="W73" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>314</v>
+        <v>270</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>397</v>
+        <v>347</v>
       </c>
       <c r="V74" s="7">
         <v>3</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>315</v>
+        <v>271</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>384</v>
+        <v>346</v>
       </c>
       <c r="V75" s="7">
         <v>3</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>316</v>
+        <v>272</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S76" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="V76" s="5">
-        <v>1</v>
+        <v>343</v>
+      </c>
+      <c r="V76" s="6">
+        <v>2</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>317</v>
+        <v>273</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>398</v>
+        <v>353</v>
       </c>
       <c r="V77" s="6">
         <v>2</v>
       </c>
       <c r="W77" s="2" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>183</v>
+        <v>154</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>318</v>
+        <v>274</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>377</v>
+        <v>325</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>409</v>
+        <v>343</v>
       </c>
       <c r="V78" s="7">
         <v>3</v>
       </c>
       <c r="W78" s="2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>378</v>
+        <v>326</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>410</v>
+        <v>354</v>
       </c>
       <c r="V79" s="7">
         <v>3</v>
       </c>
       <c r="W79" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="K80" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="V80" s="7">
-        <v>3</v>
+      <c r="K80" s="4"/>
+      <c r="V80" s="5">
+        <v>1</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>128</v>
+        <v>483</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>321</v>
+        <v>276</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="V81" s="7">
         <v>3</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>189</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>322</v>
+        <v>277</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="V82" s="6">
+        <v>344</v>
+      </c>
+      <c r="V82" s="7">
+        <v>3</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="R83" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="V83" s="7">
+        <v>3</v>
+      </c>
+      <c r="W83" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="X83" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="R84" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="V84" s="5">
+        <v>1</v>
+      </c>
+      <c r="W84" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X84" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="R85" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="V85" s="7">
+        <v>3</v>
+      </c>
+      <c r="W85" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X85" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="K86" s="4"/>
+      <c r="V86" s="6">
         <v>2</v>
       </c>
-      <c r="W82" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="X82" s="2" t="s">
-        <v>130</v>
+      <c r="X86" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V87" s="7">
+        <v>3</v>
+      </c>
+      <c r="W87" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X87" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="V88" s="7">
+        <v>3</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X88" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="V89" s="7">
+        <v>3</v>
+      </c>
+      <c r="W89" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X89" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="R90" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="S90" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="V90" s="5">
+        <v>1</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="R91" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="V91" s="6">
+        <v>2</v>
+      </c>
+      <c r="W91" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X91" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="V92" s="7">
+        <v>3</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S93" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="V93" s="7">
+        <v>3</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X93" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="R94" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S94" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="V94" s="7">
+        <v>3</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X94" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="V95" s="7">
+        <v>3</v>
+      </c>
+      <c r="W95" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="R96" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="V96" s="6">
+        <v>2</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X96" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="K19" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K20" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="K21" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="K28" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="K29" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="K30" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="K32" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="K33" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="K34" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K35" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="K36" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K37" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K38" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="K39" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K40" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K41" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="K42" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K43" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K44" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K45" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K46" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K47" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K48" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K49" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K50" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="K51" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="K52" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="K53" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="K54" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="K55" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="K56" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="K57" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="K58" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="K59" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="K60" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="K61" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="K62" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="K63" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="K64" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="K65" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="K67" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="K68" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="K69" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="K70" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="K71" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="K73" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K74" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="K75" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="K76" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="K77" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K78" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K79" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K80" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K81" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K82" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="K3" r:id="rId59" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
-    <hyperlink ref="K4" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
-    <hyperlink ref="K5" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
-    <hyperlink ref="K6" r:id="rId62" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
-    <hyperlink ref="K7" r:id="rId63" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
-    <hyperlink ref="K8" r:id="rId64" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
-    <hyperlink ref="K9" r:id="rId65" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
-    <hyperlink ref="K10" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
-    <hyperlink ref="K13" r:id="rId67" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
-    <hyperlink ref="K14" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
-    <hyperlink ref="K16" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
-    <hyperlink ref="K15" r:id="rId70" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
-    <hyperlink ref="K17" r:id="rId71" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
-    <hyperlink ref="M13" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
-    <hyperlink ref="K18" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
-    <hyperlink ref="K22" r:id="rId74" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
-    <hyperlink ref="K23" r:id="rId75" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
-    <hyperlink ref="M23" r:id="rId76" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
-    <hyperlink ref="K24" r:id="rId77" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
-    <hyperlink ref="K25" r:id="rId78" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
-    <hyperlink ref="K26" r:id="rId79" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
-    <hyperlink ref="K27" r:id="rId80" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
+    <hyperlink ref="K17" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K24" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K25" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K26" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="K33" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K42" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K43" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="K44" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K45" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K52" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K53" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K58" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K59" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K60" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K61" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K62" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K63" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K64" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="K65" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K66" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="K67" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="K68" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K69" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="K70" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K71" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K72" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K73" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="K74" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K75" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="K76" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K77" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="K78" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K79" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="K81" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K82" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K83" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K84" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="K85" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K87" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K88" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K89" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K90" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="K91" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K92" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K93" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K94" r:id="rId46" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K95" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K96" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K3" r:id="rId49" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
+    <hyperlink ref="K4" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
+    <hyperlink ref="K5" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
+    <hyperlink ref="K6" r:id="rId52" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
+    <hyperlink ref="K7" r:id="rId53" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
+    <hyperlink ref="K8" r:id="rId54" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
+    <hyperlink ref="K9" r:id="rId55" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
+    <hyperlink ref="K10" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
+    <hyperlink ref="K18" r:id="rId57" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
+    <hyperlink ref="K19" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
+    <hyperlink ref="K21" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
+    <hyperlink ref="K20" r:id="rId60" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
+    <hyperlink ref="K22" r:id="rId61" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
+    <hyperlink ref="M18" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
+    <hyperlink ref="K23" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
+    <hyperlink ref="K27" r:id="rId64" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
+    <hyperlink ref="K28" r:id="rId65" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
+    <hyperlink ref="M28" r:id="rId66" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
+    <hyperlink ref="K29" r:id="rId67" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
+    <hyperlink ref="K30" r:id="rId68" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
+    <hyperlink ref="K31" r:id="rId69" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
+    <hyperlink ref="K32" r:id="rId70" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
+    <hyperlink ref="K11" r:id="rId71" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
+    <hyperlink ref="K12" r:id="rId72" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
+    <hyperlink ref="K13" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
+    <hyperlink ref="K14" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
+    <hyperlink ref="K15" r:id="rId75" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
+    <hyperlink ref="K16" r:id="rId76" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
+    <hyperlink ref="K34" r:id="rId77" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
+    <hyperlink ref="K35" r:id="rId78" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
+    <hyperlink ref="K36" r:id="rId79" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
+    <hyperlink ref="K37" r:id="rId80" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
+    <hyperlink ref="K38" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
+    <hyperlink ref="K39" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
+    <hyperlink ref="K40" r:id="rId83" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
+    <hyperlink ref="K41" r:id="rId84" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
+    <hyperlink ref="K54" r:id="rId85" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
+    <hyperlink ref="K55" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
+    <hyperlink ref="M55" r:id="rId87" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
+    <hyperlink ref="K56" r:id="rId88" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
+    <hyperlink ref="M56" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
+    <hyperlink ref="K57" r:id="rId90" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
+    <hyperlink ref="K46" r:id="rId91" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
+    <hyperlink ref="K47" r:id="rId92" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
+    <hyperlink ref="K50" r:id="rId93" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
+    <hyperlink ref="M49" r:id="rId94" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
+    <hyperlink ref="K48" r:id="rId95" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
+    <hyperlink ref="K51" r:id="rId96" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C9F68F-8E34-4205-B306-5067B27713E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BF1CF5-4519-4E35-A27E-CEF3F09D8058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="649">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -859,9 +872,6 @@
     <t>"Tombeau de Philippe le Beau et Jeanne la Folle"</t>
   </si>
   <si>
-    <t>"Tombeau d'Henri II et Catherine de Médicis"</t>
-  </si>
-  <si>
     <t>"Gisant du connétable Anne de Montmorency"</t>
   </si>
   <si>
@@ -1859,6 +1869,117 @@
   </si>
   <si>
     <t>125</t>
+  </si>
+  <si>
+    <t>Gisants d'Henri II et Catherine de Médicis</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG/1280px-Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument conçu par Le Primatice pour la Rotonde des Valois, construction adjacente à La Basilique Saint Denis, aujourd'hui disparue.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a8/Tombeau_et_Monument_de_Henri_II_et_Catherine_de_M%C3%A9dicis%2C_Saint-Denis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Monument funéraire</t>
+  </si>
+  <si>
+    <t>Dalle funéraire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monument du cœur d'Henri II </t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ronde-bosse</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Vierge de douleur</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Modèle pour la Vierge de douleur actuellement à l'Eglise Saint Paul</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/00/Germain_pilon%2C_madonna_dolente%2C_1586%2C_01.JPG/960px-Germain_pilon%2C_madonna_dolente%2C_1586%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Terre cuite peinte</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Vers 1565</t>
+  </si>
+  <si>
+    <t>Le Christ ressuscité</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1583</t>
+  </si>
+  <si>
+    <t>Tombeau de Valentine Balbiani</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tombeau_Valentine_Balbiani_details_Pilon_LP397_MR1643.png/1280px-Tombeau_Valentine_Balbiani_details_Pilon_LP397_MR1643.png?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Valentine_Balbiani_Pilon_Louvre_MR1643.jpg/1280px-Valentine_Balbiani_Pilon_Louvre_MR1643.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>Tombeau du cardinal René de Birague</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Le Mans</t>
+  </si>
+  <si>
+    <t>Eglise Notre-Dame de la couture</t>
+  </si>
+  <si>
+    <t>Vierge à l'Enfant</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Germain_Pilon_Vierge_et_enfant.jpg/960px-Germain_Pilon_Vierge_et_enfant.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La statue a été placée dans un retable en pierre datant de 1533 avec deux statues de Saint Pierre et Saint Paul également attribuées à Germain Pilon</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/c5/Retable_Couture.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Vers 1570</t>
+  </si>
+  <si>
+    <t>Eglise Saint Paul</t>
+  </si>
+  <si>
+    <t>165</t>
   </si>
 </sst>
 </file>
@@ -1952,7 +2073,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1970,6 +2091,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2276,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y96"/>
+  <dimension ref="A1:Y104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="2" bestFit="1" customWidth="1"/>
@@ -2461,22 +2591,22 @@
         <v>197</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="S3" s="2">
         <v>560</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
@@ -2493,31 +2623,31 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="R4" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>377</v>
-      </c>
       <c r="V4" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
@@ -2534,31 +2664,31 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>382</v>
-      </c>
       <c r="R5" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S5" s="2">
         <v>262</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
@@ -2575,31 +2705,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>386</v>
-      </c>
       <c r="R6" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S6" s="2">
         <v>139</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
@@ -2616,28 +2746,28 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="R7" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="V7" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
@@ -2654,28 +2784,28 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="R8" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="R8" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="V8" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
@@ -2692,28 +2822,28 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="R9" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
@@ -2730,31 +2860,31 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="R10" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="V10" s="5" t="s">
         <v>410</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>411</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
@@ -2780,22 +2910,22 @@
         <v>198</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="V11" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V11" s="6" t="s">
-        <v>487</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
@@ -2821,22 +2951,22 @@
         <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>490</v>
-      </c>
       <c r="Q12" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="V12" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>487</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>23</v>
@@ -2853,34 +2983,34 @@
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="Q13" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>497</v>
-      </c>
       <c r="R13" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V13" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>23</v>
@@ -2897,34 +3027,34 @@
         <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="I14" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>500</v>
-      </c>
       <c r="Q14" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>23</v>
@@ -2941,35 +3071,35 @@
         <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>506</v>
       </c>
       <c r="M15" s="4"/>
       <c r="Q15" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>23</v>
@@ -2986,7 +3116,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>176</v>
@@ -2995,25 +3125,25 @@
         <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="Q16" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S16" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="R16" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="V16" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>23</v>
@@ -3039,7 +3169,7 @@
         <v>243</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>31</v>
@@ -3071,28 +3201,28 @@
         <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="M18" s="4" t="s">
+      <c r="Q18" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="V18" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
@@ -3109,34 +3239,34 @@
         <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="Q19" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="Q19" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>421</v>
-      </c>
       <c r="V19" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W19" s="2" t="s">
         <v>25</v>
@@ -3153,7 +3283,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>170</v>
@@ -3162,28 +3292,28 @@
         <v>200</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="Q20" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S20" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="Q20" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>427</v>
-      </c>
       <c r="V20" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>25</v>
@@ -3200,19 +3330,19 @@
         <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I21" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>430</v>
       </c>
       <c r="S21" s="2">
         <v>78</v>
@@ -3221,7 +3351,7 @@
         <v>75</v>
       </c>
       <c r="V21" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
@@ -3238,37 +3368,37 @@
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="Q22" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S22" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="Q22" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="V22" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>25</v>
@@ -3285,37 +3415,37 @@
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="Q23" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S23" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>444</v>
-      </c>
       <c r="V23" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>25</v>
@@ -3344,13 +3474,13 @@
         <v>244</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="V24" s="5">
         <v>1</v>
@@ -3382,13 +3512,13 @@
         <v>245</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V25" s="7">
         <v>3</v>
@@ -3417,10 +3547,10 @@
         <v>246</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V26" s="7">
         <v>3</v>
@@ -3449,19 +3579,19 @@
         <v>202</v>
       </c>
       <c r="I27" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="Q27" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="Q27" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="R27" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V27" s="6">
         <v>2</v>
@@ -3490,28 +3620,28 @@
         <v>202</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="M28" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="Q28" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="S28" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="Q28" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="S28" s="2" t="s">
+      <c r="T28" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="V28" s="6">
         <v>2</v>
@@ -3531,31 +3661,31 @@
         <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="Q29" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="V29" s="6">
         <v>2</v>
@@ -3575,31 +3705,31 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="Q30" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="V30" s="6">
         <v>2</v>
@@ -3628,25 +3758,25 @@
         <v>202</v>
       </c>
       <c r="I31" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="Q31" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="S31" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="Q31" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="S31" s="2" t="s">
+      <c r="T31" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="V31" s="6">
         <v>2</v>
@@ -3666,28 +3796,28 @@
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="K32" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="Q32" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V32" s="6">
         <v>2</v>
@@ -3716,10 +3846,10 @@
         <v>247</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="V33" s="7">
         <v>3</v>
@@ -3748,25 +3878,25 @@
         <v>204</v>
       </c>
       <c r="I34" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="Q34" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S34" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="Q34" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="V34" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -3783,34 +3913,34 @@
         <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="J35" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="K35" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="J35" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="K35" s="4" t="s">
+      <c r="Q35" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="R35" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="S35" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="R35" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>524</v>
-      </c>
       <c r="V35" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -3827,34 +3957,34 @@
         <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I36" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="Q36" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S36" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="Q36" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>529</v>
-      </c>
       <c r="V36" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -3874,31 +4004,31 @@
         <v>128</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="I37" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="J37" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="K37" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="Q37" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="R37" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="R37" s="2" t="s">
+      <c r="S37" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="S37" s="2" t="s">
-        <v>537</v>
-      </c>
       <c r="V37" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -3915,7 +4045,7 @@
         <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>170</v>
@@ -3924,25 +4054,25 @@
         <v>197</v>
       </c>
       <c r="I38" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="K38" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="Q38" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="R38" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S38" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="V38" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -3959,34 +4089,34 @@
         <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I39" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="K39" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="Q39" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="Q39" s="2" t="s">
+      <c r="R39" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S39" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="R39" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="V39" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4003,34 +4133,34 @@
         <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I40" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="J40" s="2" t="s">
-        <v>419</v>
-      </c>
       <c r="K40" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S40" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="Q40" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="V40" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4047,7 +4177,7 @@
         <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>170</v>
@@ -4056,25 +4186,25 @@
         <v>204</v>
       </c>
       <c r="I41" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="K41" s="4" t="s">
+      <c r="Q41" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S41" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="Q41" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S41" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="V41" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4100,13 +4230,13 @@
         <v>248</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="V42" s="7">
         <v>3</v>
@@ -4138,13 +4268,13 @@
         <v>249</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="V43" s="7">
         <v>3</v>
@@ -4176,13 +4306,13 @@
         <v>250</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V44" s="7">
         <v>3</v>
@@ -4214,10 +4344,10 @@
         <v>251</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V45" s="7">
         <v>3</v>
@@ -4246,19 +4376,19 @@
         <v>202</v>
       </c>
       <c r="I46" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="J46" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="J46" s="2" t="s">
-        <v>579</v>
-      </c>
       <c r="K46" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="V46" s="6">
         <v>2</v>
@@ -4278,7 +4408,7 @@
         <v>83</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>172</v>
@@ -4287,22 +4417,22 @@
         <v>202</v>
       </c>
       <c r="I47" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="K47" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="K47" s="4" t="s">
+      <c r="Q47" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="S47" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="V47" s="6">
         <v>2</v>
@@ -4322,31 +4452,31 @@
         <v>83</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="G48" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="J48" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="K48" s="4" t="s">
+      <c r="Q48" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="R48" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>592</v>
       </c>
       <c r="V48" s="6">
         <v>2</v>
@@ -4366,34 +4496,34 @@
         <v>83</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="I49" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="I49" s="2" t="s">
+      <c r="J49" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="K49" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="M49" s="4" t="s">
+      <c r="Q49" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="R49" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="Q49" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="R49" s="2" t="s">
+      <c r="S49" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="S49" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="T49" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="V49" s="6">
         <v>2</v>
@@ -4413,31 +4543,31 @@
         <v>83</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="G50" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="I50" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="J50" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="K50" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="K50" s="4" t="s">
+      <c r="Q50" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="Q50" s="2" t="s">
-        <v>607</v>
-      </c>
       <c r="R50" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="V50" s="6">
         <v>2</v>
@@ -4457,31 +4587,31 @@
         <v>83</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="J51" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="J51" s="2" t="s">
+      <c r="K51" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="K51" s="4" t="s">
+      <c r="Q51" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="S51" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="V51" s="6">
         <v>2</v>
@@ -4513,13 +4643,13 @@
         <v>252</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="V52" s="7">
         <v>3</v>
@@ -4548,7 +4678,7 @@
         <v>253</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>31</v>
@@ -4580,25 +4710,25 @@
         <v>206</v>
       </c>
       <c r="I54" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="J54" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="J54" s="2" t="s">
+      <c r="K54" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S54" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="K54" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R54" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S54" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="V54" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>39</v>
@@ -4615,34 +4745,34 @@
         <v>86</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="I55" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="J55" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="J55" s="2" t="s">
+      <c r="K55" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="K55" s="4" t="s">
+      <c r="M55" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="M55" s="4" t="s">
-        <v>566</v>
-      </c>
       <c r="Q55" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V55" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>39</v>
@@ -4659,34 +4789,34 @@
         <v>86</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I56" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="J56" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="K56" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="K56" s="4" t="s">
+      <c r="M56" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="M56" s="4" t="s">
-        <v>571</v>
-      </c>
       <c r="Q56" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V56" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W56" s="2" t="s">
         <v>39</v>
@@ -4703,7 +4833,7 @@
         <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>186</v>
@@ -4712,25 +4842,25 @@
         <v>227</v>
       </c>
       <c r="I57" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="J57" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="J57" s="2" t="s">
+      <c r="K57" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K57" s="4" t="s">
+      <c r="Q57" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="Q57" s="2" t="s">
+      <c r="R57" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S57" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="R57" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S57" s="2" t="s">
-        <v>577</v>
-      </c>
       <c r="V57" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="W57" s="2" t="s">
         <v>39</v>
@@ -4759,13 +4889,13 @@
         <v>254</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="V58" s="5">
         <v>1</v>
@@ -4794,10 +4924,10 @@
         <v>255</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="V59" s="7">
         <v>3</v>
@@ -4829,10 +4959,10 @@
         <v>256</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V60" s="6">
         <v>2</v>
@@ -4864,10 +4994,10 @@
         <v>257</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="V61" s="7">
         <v>3</v>
@@ -4899,10 +5029,10 @@
         <v>258</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V62" s="7">
         <v>3</v>
@@ -4934,10 +5064,10 @@
         <v>259</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="V63" s="7">
         <v>3</v>
@@ -4966,13 +5096,13 @@
         <v>260</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="V64" s="6">
         <v>2</v>
@@ -5004,10 +5134,10 @@
         <v>261</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V65" s="7">
         <v>3</v>
@@ -5039,10 +5169,10 @@
         <v>262</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V66" s="6">
         <v>2</v>
@@ -5074,7 +5204,7 @@
         <v>263</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>31</v>
@@ -5109,10 +5239,10 @@
         <v>264</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="V68" s="7">
         <v>3</v>
@@ -5144,13 +5274,13 @@
         <v>265</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="V69" s="7">
         <v>3</v>
@@ -5182,13 +5312,13 @@
         <v>266</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="V70" s="7">
         <v>3</v>
@@ -5217,7 +5347,7 @@
         <v>267</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R71" s="2" t="s">
         <v>31</v>
@@ -5252,13 +5382,13 @@
         <v>268</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V72" s="7">
         <v>3</v>
@@ -5290,10 +5420,10 @@
         <v>269</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V73" s="7">
         <v>3</v>
@@ -5325,10 +5455,10 @@
         <v>270</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="V74" s="7">
         <v>3</v>
@@ -5360,10 +5490,10 @@
         <v>271</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="V75" s="7">
         <v>3</v>
@@ -5395,10 +5525,10 @@
         <v>272</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V76" s="6">
         <v>2</v>
@@ -5427,10 +5557,10 @@
         <v>273</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="V77" s="6">
         <v>2</v>
@@ -5462,10 +5592,10 @@
         <v>274</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="V78" s="7">
         <v>3</v>
@@ -5497,10 +5627,10 @@
         <v>275</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="V79" s="7">
         <v>3</v>
@@ -5518,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
@@ -5541,10 +5671,10 @@
         <v>276</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V81" s="7">
         <v>3</v>
@@ -5576,10 +5706,10 @@
         <v>277</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="V82" s="7">
         <v>3</v>
@@ -5611,10 +5741,10 @@
         <v>278</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="V83" s="7">
         <v>3</v>
@@ -5626,7 +5756,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>60</v>
       </c>
@@ -5643,16 +5773,37 @@
         <v>205</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="K84" s="4" t="s">
-        <v>330</v>
+        <v>612</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="L84" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="M84" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="O84" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>617</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V84" s="5">
-        <v>1</v>
+        <v>341</v>
+      </c>
+      <c r="S84" s="3">
+        <v>450</v>
+      </c>
+      <c r="T84" s="3">
+        <v>350</v>
+      </c>
+      <c r="U84" s="3">
+        <v>250</v>
+      </c>
+      <c r="V84" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="W84" s="2" t="s">
         <v>60</v>
@@ -5661,406 +5812,800 @@
         <v>109</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>159</v>
+        <v>109</v>
+      </c>
+      <c r="C85" s="10">
+        <v>1583</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E85" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="L85" s="9"/>
+      <c r="M85" s="8"/>
+      <c r="O85" s="8"/>
+      <c r="Q85" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="R85" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S85" s="3"/>
+      <c r="T85" s="3"/>
+      <c r="U85" s="3"/>
+      <c r="V85" s="5">
+        <v>1</v>
+      </c>
+      <c r="W85" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X85" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="R85" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V85" s="7">
-        <v>3</v>
-      </c>
-      <c r="W85" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="X85" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="K86" s="4"/>
-      <c r="V86" s="6">
-        <v>2</v>
+      <c r="I86" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="K86" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="L86" s="9"/>
+      <c r="M86" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="O86" s="9"/>
+      <c r="Q86" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S86" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="W86" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>160</v>
+        <v>109</v>
+      </c>
+      <c r="C87" s="10">
+        <v>1586</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="K87" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="M87" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="O87" s="9"/>
+      <c r="Q87" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="S87" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="T87" s="3">
+        <v>120</v>
+      </c>
+      <c r="U87" s="3">
+        <v>81</v>
+      </c>
+      <c r="V87" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="W87" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X87" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="K88" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="L88" s="9"/>
+      <c r="M88" s="9"/>
+      <c r="O88" s="9"/>
+      <c r="Q88" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S88" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X88" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="L89" s="9"/>
+      <c r="M89" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="O89" s="9"/>
+      <c r="Q89" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S89" s="3">
+        <v>83</v>
+      </c>
+      <c r="T89" s="3">
         <v>191</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="R87" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V87" s="7">
-        <v>3</v>
-      </c>
-      <c r="W87" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X87" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K88" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="R88" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="V88" s="7">
-        <v>3</v>
-      </c>
-      <c r="W88" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="X88" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="R89" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V89" s="7">
-        <v>3</v>
+      <c r="U89" s="3">
+        <v>49</v>
+      </c>
+      <c r="V89" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>163</v>
+        <v>637</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>335</v>
+        <v>638</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="L90" s="9"/>
+      <c r="M90" s="9"/>
+      <c r="O90" s="9"/>
+      <c r="Q90" s="2" t="s">
+        <v>469</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S90" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="V90" s="5">
+        <v>342</v>
+      </c>
+      <c r="S90" s="3">
+        <v>140</v>
+      </c>
+      <c r="T90" s="3">
+        <v>210</v>
+      </c>
+      <c r="U90" s="3">
+        <v>80</v>
+      </c>
+      <c r="V90" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C91" s="10">
+        <v>1570</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="K91" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M91" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="O91" s="9"/>
+      <c r="Q91" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="R91" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S91" s="3">
+        <v>96</v>
+      </c>
+      <c r="T91" s="3">
+        <v>25</v>
+      </c>
+      <c r="U91" s="3">
+        <v>18</v>
+      </c>
+      <c r="V91" s="5">
         <v>1</v>
       </c>
-      <c r="W90" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="X90" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="R91" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="V91" s="6">
-        <v>2</v>
-      </c>
       <c r="W91" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>165</v>
+        <v>646</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>238</v>
+        <v>647</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>337</v>
+        <v>624</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+      <c r="O92" s="9"/>
+      <c r="Q92" s="2" t="s">
+        <v>622</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S92" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="V92" s="7">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="S92" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="R93" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="S93" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="V93" s="7">
         <v>3</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="R94" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S94" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="V94" s="7">
-        <v>3</v>
-      </c>
-      <c r="W94" s="2" t="s">
-        <v>69</v>
+      <c r="K94" s="4"/>
+      <c r="V94" s="6">
+        <v>2</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>117</v>
+        <v>367</v>
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>358</v>
+        <v>31</v>
       </c>
       <c r="V95" s="7">
         <v>3</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="R96" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="V96" s="7">
+        <v>3</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X96" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="R97" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="V97" s="7">
+        <v>3</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X97" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="R98" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S98" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="V98" s="5">
+        <v>1</v>
+      </c>
+      <c r="W98" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X98" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="V99" s="6">
+        <v>2</v>
+      </c>
+      <c r="W99" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X99" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="R100" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="S100" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="V100" s="7">
+        <v>3</v>
+      </c>
+      <c r="W100" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X100" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="R101" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S101" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="V101" s="7">
+        <v>3</v>
+      </c>
+      <c r="W101" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X101" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="R102" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="S102" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="V102" s="7">
+        <v>3</v>
+      </c>
+      <c r="W102" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X102" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="R103" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="V103" s="7">
+        <v>3</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X103" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B104" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="I96" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K96" s="4" t="s">
+      <c r="I104" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="R104" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="R96" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V96" s="6">
+      <c r="V104" s="6">
         <v>2</v>
       </c>
-      <c r="W96" s="2" t="s">
+      <c r="W104" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="X96" s="2" t="s">
+      <c r="X104" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6103,66 +6648,80 @@
     <hyperlink ref="K81" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
     <hyperlink ref="K82" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
     <hyperlink ref="K83" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="K84" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="K85" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="K87" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K88" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="K89" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="K90" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="K91" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K92" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K93" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K94" r:id="rId46" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K95" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K96" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="K3" r:id="rId49" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
-    <hyperlink ref="K4" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
-    <hyperlink ref="K5" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
-    <hyperlink ref="K6" r:id="rId52" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
-    <hyperlink ref="K7" r:id="rId53" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
-    <hyperlink ref="K8" r:id="rId54" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
-    <hyperlink ref="K9" r:id="rId55" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
-    <hyperlink ref="K10" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
-    <hyperlink ref="K18" r:id="rId57" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
-    <hyperlink ref="K19" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
-    <hyperlink ref="K21" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
-    <hyperlink ref="K20" r:id="rId60" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
-    <hyperlink ref="K22" r:id="rId61" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
-    <hyperlink ref="M18" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
-    <hyperlink ref="K23" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
-    <hyperlink ref="K27" r:id="rId64" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
-    <hyperlink ref="K28" r:id="rId65" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
-    <hyperlink ref="M28" r:id="rId66" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
-    <hyperlink ref="K29" r:id="rId67" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
-    <hyperlink ref="K30" r:id="rId68" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
-    <hyperlink ref="K31" r:id="rId69" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
-    <hyperlink ref="K32" r:id="rId70" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
-    <hyperlink ref="K11" r:id="rId71" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
-    <hyperlink ref="K12" r:id="rId72" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
-    <hyperlink ref="K13" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
-    <hyperlink ref="K14" r:id="rId74" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
-    <hyperlink ref="K15" r:id="rId75" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
-    <hyperlink ref="K16" r:id="rId76" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
-    <hyperlink ref="K34" r:id="rId77" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
-    <hyperlink ref="K35" r:id="rId78" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
-    <hyperlink ref="K36" r:id="rId79" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
-    <hyperlink ref="K37" r:id="rId80" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
-    <hyperlink ref="K38" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
-    <hyperlink ref="K39" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
-    <hyperlink ref="K40" r:id="rId83" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
-    <hyperlink ref="K41" r:id="rId84" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
-    <hyperlink ref="K54" r:id="rId85" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
-    <hyperlink ref="K55" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
-    <hyperlink ref="M55" r:id="rId87" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
-    <hyperlink ref="K56" r:id="rId88" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
-    <hyperlink ref="M56" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
-    <hyperlink ref="K57" r:id="rId90" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
-    <hyperlink ref="K46" r:id="rId91" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
-    <hyperlink ref="K47" r:id="rId92" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
-    <hyperlink ref="K50" r:id="rId93" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
-    <hyperlink ref="M49" r:id="rId94" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
-    <hyperlink ref="K48" r:id="rId95" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
-    <hyperlink ref="K51" r:id="rId96" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
+    <hyperlink ref="K93" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K95" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K96" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K97" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K98" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="K99" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K100" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K101" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K102" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K103" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K104" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K3" r:id="rId48" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
+    <hyperlink ref="K4" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
+    <hyperlink ref="K5" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
+    <hyperlink ref="K6" r:id="rId51" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
+    <hyperlink ref="K7" r:id="rId52" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
+    <hyperlink ref="K8" r:id="rId53" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
+    <hyperlink ref="K9" r:id="rId54" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
+    <hyperlink ref="K10" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
+    <hyperlink ref="K18" r:id="rId56" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
+    <hyperlink ref="K19" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
+    <hyperlink ref="K21" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
+    <hyperlink ref="K20" r:id="rId59" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
+    <hyperlink ref="K22" r:id="rId60" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
+    <hyperlink ref="M18" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
+    <hyperlink ref="K23" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
+    <hyperlink ref="K27" r:id="rId63" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
+    <hyperlink ref="K28" r:id="rId64" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
+    <hyperlink ref="M28" r:id="rId65" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
+    <hyperlink ref="K29" r:id="rId66" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
+    <hyperlink ref="K30" r:id="rId67" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
+    <hyperlink ref="K31" r:id="rId68" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
+    <hyperlink ref="K32" r:id="rId69" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
+    <hyperlink ref="K11" r:id="rId70" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
+    <hyperlink ref="K12" r:id="rId71" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
+    <hyperlink ref="K13" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
+    <hyperlink ref="K14" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
+    <hyperlink ref="K15" r:id="rId74" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
+    <hyperlink ref="K16" r:id="rId75" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
+    <hyperlink ref="K34" r:id="rId76" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
+    <hyperlink ref="K35" r:id="rId77" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
+    <hyperlink ref="K36" r:id="rId78" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
+    <hyperlink ref="K37" r:id="rId79" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
+    <hyperlink ref="K38" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
+    <hyperlink ref="K39" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
+    <hyperlink ref="K40" r:id="rId82" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
+    <hyperlink ref="K41" r:id="rId83" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
+    <hyperlink ref="K54" r:id="rId84" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
+    <hyperlink ref="K55" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
+    <hyperlink ref="M55" r:id="rId86" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
+    <hyperlink ref="K56" r:id="rId87" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
+    <hyperlink ref="M56" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
+    <hyperlink ref="K57" r:id="rId89" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
+    <hyperlink ref="K46" r:id="rId90" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
+    <hyperlink ref="K47" r:id="rId91" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
+    <hyperlink ref="K50" r:id="rId92" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
+    <hyperlink ref="K49" r:id="rId93" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
+    <hyperlink ref="K48" r:id="rId94" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
+    <hyperlink ref="K51" r:id="rId95" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
+    <hyperlink ref="K85" r:id="rId96" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
+    <hyperlink ref="M86" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
+    <hyperlink ref="K86" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
+    <hyperlink ref="K87" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
+    <hyperlink ref="K88" r:id="rId100" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
+    <hyperlink ref="K92" r:id="rId101" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
+    <hyperlink ref="M89" r:id="rId102" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
+    <hyperlink ref="K89" r:id="rId103" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
+    <hyperlink ref="M91" r:id="rId104" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
+    <hyperlink ref="K90" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
+    <hyperlink ref="K91" r:id="rId106" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
+    <hyperlink ref="M84" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
+    <hyperlink ref="K84" r:id="rId108" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
+    <hyperlink ref="O84" r:id="rId109" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
+    <hyperlink ref="M87" r:id="rId110" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BF1CF5-4519-4E35-A27E-CEF3F09D8058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39AFA0B-D7FE-4060-B351-CA6D06BB310F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="652">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -791,9 +791,6 @@
     <t>"Le Duel allégorique entre Albrecht Dürer et Apelle"</t>
   </si>
   <si>
-    <t>"L'Enlèvement d'Hélène par Pâris."</t>
-  </si>
-  <si>
     <t>"L'Escalier doré"</t>
   </si>
   <si>
@@ -809,9 +806,6 @@
     <t>"Rencontre des saints Joachim et Anne"</t>
   </si>
   <si>
-    <t>"La Résurrection (fragment du jubé)"</t>
-  </si>
-  <si>
     <t>"Tabernacle"</t>
   </si>
   <si>
@@ -821,9 +815,6 @@
     <t>"Retable majeur du Pilar"</t>
   </si>
   <si>
-    <t>"La Fontaine d'Auguste (Augustusbrunnen)"</t>
-  </si>
-  <si>
     <t>"La Fontaine des Innocents"</t>
   </si>
   <si>
@@ -836,18 +827,12 @@
     <t>"La Tireuse d'épine"</t>
   </si>
   <si>
-    <t>"Portail du cloître (Arc de Jamete)"</t>
-  </si>
-  <si>
     <t>"Le Surtout de table Merkel (Merkelsche Tafelaufsatz)"</t>
   </si>
   <si>
     <t>"Tombeau de Louis XII et d'Anne de Bretagne"</t>
   </si>
   <si>
-    <t>"La Fontaine des Tortues (avec Giacomo della Porta)"</t>
-  </si>
-  <si>
     <t>"Le Retable du maître-autel de Moosburg"</t>
   </si>
   <si>
@@ -866,9 +851,6 @@
     <t>"Retable du Saint-Sacrement (albâtre)"</t>
   </si>
   <si>
-    <t>"Fontaine du Géant (avec Pietro Bernini)"</t>
-  </si>
-  <si>
     <t>"Tombeau de Philippe le Beau et Jeanne la Folle"</t>
   </si>
   <si>
@@ -878,9 +860,6 @@
     <t>"Le Transi de René de Chalon"</t>
   </si>
   <si>
-    <t>"Autel du Saint-Sang (Heilig-Blut-Altar)"</t>
-  </si>
-  <si>
     <t>"Le Baptême du Christ"</t>
   </si>
   <si>
@@ -893,15 +872,6 @@
     <t>"La Nature"</t>
   </si>
   <si>
-    <t>"Mercure (bronze)"</t>
-  </si>
-  <si>
-    <t>"Hercule et Cacus (bronze)"</t>
-  </si>
-  <si>
-    <t>"La Châsse de Saint Sebald (Sebaldusgrab)"</t>
-  </si>
-  <si>
     <t>"Monument funéraire d'Alessandro Vittoria"</t>
   </si>
   <si>
@@ -1136,9 +1106,6 @@
     <t>146 cm environ</t>
   </si>
   <si>
-    <t>REICHLE</t>
-  </si>
-  <si>
     <t>La Fontaine de Neptune</t>
   </si>
   <si>
@@ -1481,9 +1448,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8f/Caceres_-_Iglesia_de_Santiago_04.jpg/960px-Caceres_-_Iglesia_de_Santiago_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Michel Ange</t>
-  </si>
-  <si>
     <t>Atlas soutenant le monde</t>
   </si>
   <si>
@@ -1817,9 +1781,6 @@
     <t>Cathédrale de Valladolid</t>
   </si>
   <si>
-    <t>Retable majeur (Retablo mayor)</t>
-  </si>
-  <si>
     <t>Retablo mayor de la Catedral de Valladolid</t>
   </si>
   <si>
@@ -1979,7 +1940,55 @@
     <t>Eglise Saint Paul</t>
   </si>
   <si>
-    <t>165</t>
+    <t>Terre cuite</t>
+  </si>
+  <si>
+    <t>"Mercure"</t>
+  </si>
+  <si>
+    <t>"Autel du Saint-Sang"</t>
+  </si>
+  <si>
+    <t>"La Châsse de Saint Sebald"</t>
+  </si>
+  <si>
+    <t>"La Fontaine des Tortues"</t>
+  </si>
+  <si>
+    <t>"La Fontaine d'Auguste"</t>
+  </si>
+  <si>
+    <t>"La Résurrection"</t>
+  </si>
+  <si>
+    <t>Retable majeur</t>
+  </si>
+  <si>
+    <t>"Portail du cloître "</t>
+  </si>
+  <si>
+    <t>"Fontaine du Géant)"</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ensemble du maître-autel</t>
+  </si>
+  <si>
+    <t>Hélène et Thésée</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/La_grotta_grande.jpg/1280px-La_grotta_grande.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/99/BUONTALENTI.JPG/1280px-BUONTALENTI.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Vincenzo_de%27_rossi%2C_teseo_e_arianna%2C_01.JPG/1920px-Vincenzo_de%27_rossi%2C_teseo_e_arianna%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2016,7 +2025,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2038,6 +2047,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2073,7 +2094,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2082,7 +2103,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2101,6 +2121,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2406,33 +2446,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y102"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="18" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="24.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="46.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="2"/>
-    <col min="13" max="13" width="5.140625" style="2" customWidth="1"/>
-    <col min="14" max="17" width="9.140625" style="2" hidden="1" customWidth="1"/>
-    <col min="18" max="19" width="9.140625" style="2"/>
+    <col min="1" max="1" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="5.140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="2"/>
+    <col min="19" max="19" width="9.140625" style="2" customWidth="1"/>
     <col min="20" max="20" width="5.140625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5.42578125" style="2" customWidth="1"/>
     <col min="22" max="22" width="5.28515625" style="3" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="2"/>
-    <col min="24" max="24" width="22.28515625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" style="2"/>
+    <col min="23" max="23" width="8" style="2" customWidth="1"/>
+    <col min="24" max="24" width="6" style="2" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2463,13 +2507,13 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
@@ -2506,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2537,13 +2581,13 @@
       <c r="J2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N2" s="1" t="s">
@@ -2574,7 +2618,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -2591,22 +2635,22 @@
         <v>197</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>290</v>
+        <v>358</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="S3" s="2">
         <v>560</v>
       </c>
-      <c r="V3" s="5" t="s">
-        <v>410</v>
+      <c r="V3" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
@@ -2615,7 +2659,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -2623,31 +2667,31 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>375</v>
+        <v>363</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>410</v>
+        <v>365</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
@@ -2656,7 +2700,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -2664,31 +2708,31 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>381</v>
+        <v>369</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S5" s="2">
         <v>262</v>
       </c>
-      <c r="V5" s="5" t="s">
-        <v>410</v>
+      <c r="V5" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
@@ -2697,7 +2741,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -2705,31 +2749,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>385</v>
+        <v>373</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>374</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S6" s="2">
         <v>139</v>
       </c>
-      <c r="V6" s="5" t="s">
-        <v>410</v>
+      <c r="V6" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
@@ -2738,7 +2782,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -2746,28 +2790,28 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>390</v>
+        <v>378</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>379</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="V7" s="5" t="s">
-        <v>410</v>
+        <v>380</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
@@ -2776,7 +2820,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -2784,28 +2828,28 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>396</v>
+        <v>384</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>385</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>410</v>
+        <v>386</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
@@ -2814,7 +2858,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -2822,28 +2866,28 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="V9" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V9" s="5" t="s">
-        <v>410</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
@@ -2852,7 +2896,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -2860,31 +2904,31 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>407</v>
+        <v>395</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>396</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>410</v>
+        <v>398</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
@@ -2893,7 +2937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -2910,22 +2954,22 @@
         <v>198</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>291</v>
+        <v>472</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>281</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V11" s="6" t="s">
-        <v>486</v>
+        <v>332</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>474</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
@@ -2934,7 +2978,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -2951,22 +2995,22 @@
         <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>489</v>
+        <v>476</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>477</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>486</v>
+        <v>332</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>474</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>23</v>
@@ -2975,7 +3019,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -2983,34 +3027,34 @@
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>495</v>
+        <v>482</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>483</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V13" s="6" t="s">
-        <v>486</v>
+        <v>332</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>474</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>23</v>
@@ -3019,7 +3063,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -3027,34 +3071,34 @@
         <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>499</v>
+        <v>486</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>487</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V14" s="6" t="s">
-        <v>486</v>
+        <v>332</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>474</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>23</v>
@@ -3063,7 +3107,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
@@ -3071,35 +3115,35 @@
         <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="M15" s="4"/>
+        <v>492</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="M15" s="7"/>
       <c r="Q15" s="2" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V15" s="6" t="s">
-        <v>486</v>
+        <v>332</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>474</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>23</v>
@@ -3108,7 +3152,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -3116,7 +3160,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>176</v>
@@ -3125,25 +3169,25 @@
         <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>510</v>
+        <v>497</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>498</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="V16" s="6" t="s">
-        <v>486</v>
+        <v>500</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>474</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>23</v>
@@ -3152,7 +3196,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -3168,13 +3212,13 @@
       <c r="I17" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>292</v>
+      <c r="K17" s="7" t="s">
+        <v>282</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V17" s="7">
+      <c r="V17" s="6">
         <v>3</v>
       </c>
       <c r="W17" s="2" t="s">
@@ -3184,7 +3228,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -3201,28 +3245,28 @@
         <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>413</v>
+        <v>401</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>402</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="V18" s="5" t="s">
-        <v>410</v>
+        <v>404</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
@@ -3231,7 +3275,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -3239,34 +3283,34 @@
         <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>419</v>
+        <v>407</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>408</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="V19" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
+      </c>
+      <c r="V19" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W19" s="2" t="s">
         <v>25</v>
@@ -3275,7 +3319,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
@@ -3283,7 +3327,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>170</v>
@@ -3292,28 +3336,28 @@
         <v>200</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>425</v>
+        <v>413</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>414</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="V20" s="5" t="s">
-        <v>410</v>
+        <v>415</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>25</v>
@@ -3322,7 +3366,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
@@ -3330,19 +3374,19 @@
         <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>429</v>
+        <v>417</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>418</v>
       </c>
       <c r="S21" s="2">
         <v>78</v>
@@ -3350,8 +3394,8 @@
       <c r="T21" s="2">
         <v>75</v>
       </c>
-      <c r="V21" s="5" t="s">
-        <v>410</v>
+      <c r="V21" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
@@ -3360,7 +3404,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
@@ -3368,37 +3412,37 @@
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>435</v>
+        <v>423</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>424</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="V22" s="5" t="s">
-        <v>410</v>
+        <v>425</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>25</v>
@@ -3407,7 +3451,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
@@ -3415,37 +3459,37 @@
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>442</v>
+        <v>430</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>431</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="V23" s="5" t="s">
-        <v>410</v>
+        <v>432</v>
+      </c>
+      <c r="V23" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>25</v>
@@ -3454,7 +3498,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -3473,16 +3517,16 @@
       <c r="I24" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>293</v>
+      <c r="K24" s="7" t="s">
+        <v>283</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="V24" s="5">
+        <v>348</v>
+      </c>
+      <c r="V24" s="4">
         <v>1</v>
       </c>
       <c r="W24" s="2" t="s">
@@ -3492,7 +3536,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -3511,16 +3555,16 @@
       <c r="I25" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>294</v>
+      <c r="K25" s="7" t="s">
+        <v>284</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="V25" s="7">
+        <v>349</v>
+      </c>
+      <c r="V25" s="6">
         <v>3</v>
       </c>
       <c r="W25" s="2" t="s">
@@ -3530,7 +3574,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -3546,13 +3590,13 @@
       <c r="I26" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>295</v>
+      <c r="K26" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V26" s="7">
+        <v>334</v>
+      </c>
+      <c r="V26" s="6">
         <v>3</v>
       </c>
       <c r="W26" s="2" t="s">
@@ -3562,7 +3606,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
@@ -3579,21 +3623,21 @@
         <v>202</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>446</v>
+        <v>434</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>435</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V27" s="6">
+        <v>334</v>
+      </c>
+      <c r="V27" s="5">
         <v>2</v>
       </c>
       <c r="W27" s="2" t="s">
@@ -3603,7 +3647,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
@@ -3620,30 +3664,30 @@
         <v>202</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>451</v>
+        <v>438</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>440</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="V28" s="6">
+        <v>442</v>
+      </c>
+      <c r="V28" s="5">
         <v>2</v>
       </c>
       <c r="W28" s="2" t="s">
@@ -3653,7 +3697,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -3661,33 +3705,33 @@
         <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>460</v>
+        <v>448</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>449</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="V29" s="6">
+        <v>451</v>
+      </c>
+      <c r="V29" s="5">
         <v>2</v>
       </c>
       <c r="W29" s="2" t="s">
@@ -3697,7 +3741,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
@@ -3705,33 +3749,33 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>468</v>
+        <v>456</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>457</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="V30" s="6">
+        <v>459</v>
+      </c>
+      <c r="V30" s="5">
         <v>2</v>
       </c>
       <c r="W30" s="2" t="s">
@@ -3741,7 +3785,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
@@ -3758,27 +3802,27 @@
         <v>202</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>473</v>
+        <v>461</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>462</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="V31" s="6">
+        <v>464</v>
+      </c>
+      <c r="V31" s="5">
         <v>2</v>
       </c>
       <c r="W31" s="2" t="s">
@@ -3788,7 +3832,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -3796,30 +3840,30 @@
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>481</v>
+        <v>469</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V32" s="6">
+        <v>334</v>
+      </c>
+      <c r="V32" s="5">
         <v>2</v>
       </c>
       <c r="W32" s="2" t="s">
@@ -3829,7 +3873,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -3845,13 +3889,13 @@
       <c r="I33" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="K33" s="4" t="s">
-        <v>296</v>
+      <c r="K33" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V33" s="7">
+        <v>334</v>
+      </c>
+      <c r="V33" s="6">
         <v>3</v>
       </c>
       <c r="W33" s="2" t="s">
@@ -3861,7 +3905,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
@@ -3878,25 +3922,25 @@
         <v>204</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>515</v>
+        <v>502</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>503</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="V34" s="5" t="s">
-        <v>410</v>
+        <v>504</v>
+      </c>
+      <c r="V34" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -3905,7 +3949,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
@@ -3913,34 +3957,34 @@
         <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>521</v>
+        <v>358</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>509</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="V35" s="5" t="s">
-        <v>410</v>
+        <v>511</v>
+      </c>
+      <c r="V35" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -3949,7 +3993,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>30</v>
       </c>
@@ -3957,34 +4001,34 @@
         <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>527</v>
+        <v>514</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>515</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="V36" s="5" t="s">
-        <v>410</v>
+        <v>516</v>
+      </c>
+      <c r="V36" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -3993,7 +4037,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
@@ -4004,31 +4048,31 @@
         <v>128</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>533</v>
+        <v>520</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>521</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="V37" s="5" t="s">
-        <v>410</v>
+        <v>524</v>
+      </c>
+      <c r="V37" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4037,7 +4081,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>30</v>
       </c>
@@ -4045,7 +4089,7 @@
         <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>170</v>
@@ -4054,25 +4098,25 @@
         <v>197</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>540</v>
+        <v>527</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>528</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="V38" s="5" t="s">
-        <v>410</v>
+        <v>530</v>
+      </c>
+      <c r="V38" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4081,7 +4125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
@@ -4089,34 +4133,34 @@
         <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>546</v>
+        <v>533</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>534</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="V39" s="5" t="s">
-        <v>410</v>
+        <v>536</v>
+      </c>
+      <c r="V39" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4125,7 +4169,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>30</v>
       </c>
@@ -4133,34 +4177,34 @@
         <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>550</v>
+        <v>407</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>538</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="V40" s="5" t="s">
-        <v>410</v>
+        <v>539</v>
+      </c>
+      <c r="V40" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4169,7 +4213,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>30</v>
       </c>
@@ -4177,7 +4221,7 @@
         <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>170</v>
@@ -4186,25 +4230,25 @@
         <v>204</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>555</v>
+        <v>542</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>543</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="V41" s="5" t="s">
-        <v>410</v>
+        <v>544</v>
+      </c>
+      <c r="V41" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4213,7 +4257,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
@@ -4229,16 +4273,16 @@
       <c r="I42" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="K42" s="4" t="s">
-        <v>297</v>
+      <c r="K42" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="V42" s="7">
+        <v>350</v>
+      </c>
+      <c r="V42" s="6">
         <v>3</v>
       </c>
       <c r="W42" s="2" t="s">
@@ -4248,7 +4292,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>35</v>
       </c>
@@ -4267,16 +4311,16 @@
       <c r="I43" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="K43" s="4" t="s">
-        <v>298</v>
+      <c r="K43" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="V43" s="7">
+        <v>351</v>
+      </c>
+      <c r="V43" s="6">
         <v>3</v>
       </c>
       <c r="W43" s="2" t="s">
@@ -4286,7 +4330,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
@@ -4305,16 +4349,16 @@
       <c r="I44" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="K44" s="4" t="s">
-        <v>299</v>
+      <c r="K44" s="7" t="s">
+        <v>289</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="V44" s="7">
+        <v>352</v>
+      </c>
+      <c r="V44" s="6">
         <v>3</v>
       </c>
       <c r="W44" s="2" t="s">
@@ -4324,7 +4368,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>32</v>
       </c>
@@ -4343,13 +4387,13 @@
       <c r="I45" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="K45" s="4" t="s">
-        <v>300</v>
+      <c r="K45" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V45" s="7">
+        <v>333</v>
+      </c>
+      <c r="V45" s="6">
         <v>3</v>
       </c>
       <c r="W45" s="2" t="s">
@@ -4359,7 +4403,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
@@ -4376,21 +4420,21 @@
         <v>202</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>301</v>
+        <v>566</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>291</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="V46" s="6">
+        <v>335</v>
+      </c>
+      <c r="V46" s="5">
         <v>2</v>
       </c>
       <c r="W46" s="2" t="s">
@@ -4400,7 +4444,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>37</v>
       </c>
@@ -4408,7 +4452,7 @@
         <v>83</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>172</v>
@@ -4417,24 +4461,24 @@
         <v>202</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>582</v>
+        <v>569</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>570</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="V47" s="6">
+        <v>571</v>
+      </c>
+      <c r="V47" s="5">
         <v>2</v>
       </c>
       <c r="W47" s="2" t="s">
@@ -4444,7 +4488,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>37</v>
       </c>
@@ -4452,33 +4496,33 @@
         <v>83</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>590</v>
+        <v>577</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>578</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="V48" s="6">
+        <v>579</v>
+      </c>
+      <c r="V48" s="5">
         <v>2</v>
       </c>
       <c r="W48" s="2" t="s">
@@ -4488,7 +4532,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>37</v>
       </c>
@@ -4496,36 +4540,36 @@
         <v>83</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>594</v>
+        <v>642</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>596</v>
+        <v>582</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>583</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="V49" s="6">
+        <v>398</v>
+      </c>
+      <c r="V49" s="5">
         <v>2</v>
       </c>
       <c r="W49" s="2" t="s">
@@ -4535,7 +4579,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>37</v>
       </c>
@@ -4543,33 +4587,33 @@
         <v>83</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>605</v>
+        <v>591</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>592</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="V50" s="6">
+        <v>335</v>
+      </c>
+      <c r="V50" s="5">
         <v>2</v>
       </c>
       <c r="W50" s="2" t="s">
@@ -4579,7 +4623,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>37</v>
       </c>
@@ -4587,33 +4631,33 @@
         <v>83</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>610</v>
+        <v>596</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>597</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="V51" s="6">
+        <v>598</v>
+      </c>
+      <c r="V51" s="5">
         <v>2</v>
       </c>
       <c r="W51" s="2" t="s">
@@ -4623,45 +4667,66 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:25" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="R52" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S52" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="V52" s="7">
+      <c r="F52" s="11"/>
+      <c r="G52" s="13" t="s">
+        <v>649</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>648</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="J52" s="11"/>
+      <c r="K52" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="L52" s="11"/>
+      <c r="M52" s="14" t="s">
+        <v>650</v>
+      </c>
+      <c r="N52" s="11"/>
+      <c r="O52" s="13" t="s">
+        <v>651</v>
+      </c>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+      <c r="R52" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="S52" s="11">
+        <v>182</v>
+      </c>
+      <c r="T52" s="11"/>
+      <c r="U52" s="11"/>
+      <c r="V52" s="12">
         <v>3</v>
       </c>
-      <c r="W52" s="2" t="s">
+      <c r="W52" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="X52" s="2" t="s">
+      <c r="X52" s="11" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y52" s="11"/>
+    </row>
+    <row r="53" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>38</v>
       </c>
@@ -4675,15 +4740,15 @@
         <v>211</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>303</v>
+        <v>252</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V53" s="7">
+      <c r="V53" s="6">
         <v>3</v>
       </c>
       <c r="W53" s="2" t="s">
@@ -4693,7 +4758,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>39</v>
       </c>
@@ -4710,25 +4775,25 @@
         <v>206</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>304</v>
+        <v>546</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="V54" s="5" t="s">
-        <v>410</v>
+        <v>547</v>
+      </c>
+      <c r="V54" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>39</v>
@@ -4737,7 +4802,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>39</v>
       </c>
@@ -4745,34 +4810,34 @@
         <v>86</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>565</v>
+        <v>551</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>553</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="V55" s="5" t="s">
-        <v>410</v>
+        <v>336</v>
+      </c>
+      <c r="V55" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>39</v>
@@ -4781,7 +4846,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>39</v>
       </c>
@@ -4789,34 +4854,34 @@
         <v>86</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="M56" s="4" t="s">
-        <v>570</v>
+        <v>556</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>558</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="V56" s="5" t="s">
-        <v>410</v>
+        <v>336</v>
+      </c>
+      <c r="V56" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W56" s="2" t="s">
         <v>39</v>
@@ -4825,7 +4890,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>39</v>
       </c>
@@ -4833,7 +4898,7 @@
         <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>186</v>
@@ -4842,25 +4907,25 @@
         <v>227</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>574</v>
+        <v>561</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>562</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="V57" s="5" t="s">
-        <v>410</v>
+        <v>564</v>
+      </c>
+      <c r="V57" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W57" s="2" t="s">
         <v>39</v>
@@ -4869,7 +4934,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>39</v>
       </c>
@@ -4886,18 +4951,18 @@
         <v>206</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>304</v>
+        <v>253</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="V58" s="5">
+        <v>353</v>
+      </c>
+      <c r="V58" s="4">
         <v>1</v>
       </c>
       <c r="W58" s="2" t="s">
@@ -4907,7 +4972,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>40</v>
       </c>
@@ -4921,15 +4986,15 @@
         <v>212</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>305</v>
+        <v>254</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>295</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="V59" s="7">
+        <v>331</v>
+      </c>
+      <c r="V59" s="6">
         <v>3</v>
       </c>
       <c r="W59" s="2" t="s">
@@ -4939,7 +5004,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>41</v>
       </c>
@@ -4956,15 +5021,15 @@
         <v>213</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>306</v>
+        <v>255</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="V60" s="6">
+        <v>336</v>
+      </c>
+      <c r="V60" s="5">
         <v>2</v>
       </c>
       <c r="W60" s="2" t="s">
@@ -4974,7 +5039,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>42</v>
       </c>
@@ -4991,15 +5056,15 @@
         <v>214</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>307</v>
+        <v>256</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>297</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="V61" s="7">
+        <v>335</v>
+      </c>
+      <c r="V61" s="6">
         <v>3</v>
       </c>
       <c r="W61" s="2" t="s">
@@ -5009,7 +5074,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>43</v>
       </c>
@@ -5026,15 +5091,15 @@
         <v>215</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>308</v>
+        <v>641</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V62" s="7">
+        <v>333</v>
+      </c>
+      <c r="V62" s="6">
         <v>3</v>
       </c>
       <c r="W62" s="2" t="s">
@@ -5044,7 +5109,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>44</v>
       </c>
@@ -5061,15 +5126,15 @@
         <v>216</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>309</v>
+        <v>257</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>299</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="V63" s="7">
+        <v>337</v>
+      </c>
+      <c r="V63" s="6">
         <v>3</v>
       </c>
       <c r="W63" s="2" t="s">
@@ -5079,7 +5144,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>45</v>
       </c>
@@ -5093,18 +5158,18 @@
         <v>217</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>310</v>
+        <v>258</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="V64" s="6">
+        <v>354</v>
+      </c>
+      <c r="V64" s="5">
         <v>2</v>
       </c>
       <c r="W64" s="2" t="s">
@@ -5114,7 +5179,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>46</v>
       </c>
@@ -5131,15 +5196,15 @@
         <v>218</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>311</v>
+        <v>259</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="V65" s="7">
+        <v>339</v>
+      </c>
+      <c r="V65" s="6">
         <v>3</v>
       </c>
       <c r="W65" s="2" t="s">
@@ -5149,7 +5214,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>47</v>
       </c>
@@ -5166,15 +5231,15 @@
         <v>219</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>312</v>
+        <v>640</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>302</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V66" s="6">
+        <v>332</v>
+      </c>
+      <c r="V66" s="5">
         <v>2</v>
       </c>
       <c r="W66" s="2" t="s">
@@ -5184,7 +5249,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>30</v>
       </c>
@@ -5201,15 +5266,15 @@
         <v>220</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>313</v>
+        <v>260</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V67" s="5">
+      <c r="V67" s="4">
         <v>1</v>
       </c>
       <c r="W67" s="2" t="s">
@@ -5219,7 +5284,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>48</v>
       </c>
@@ -5236,15 +5301,15 @@
         <v>221</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>314</v>
+        <v>261</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="V68" s="7">
+        <v>340</v>
+      </c>
+      <c r="V68" s="6">
         <v>3</v>
       </c>
       <c r="W68" s="2" t="s">
@@ -5254,7 +5319,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>49</v>
       </c>
@@ -5271,18 +5336,18 @@
         <v>222</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>315</v>
+        <v>262</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="V69" s="7">
+        <v>355</v>
+      </c>
+      <c r="V69" s="6">
         <v>3</v>
       </c>
       <c r="W69" s="2" t="s">
@@ -5292,7 +5357,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>50</v>
       </c>
@@ -5309,18 +5374,24 @@
         <v>206</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>316</v>
+        <v>263</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>306</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="V70" s="7">
+        <v>635</v>
+      </c>
+      <c r="S70" s="2">
+        <v>26</v>
+      </c>
+      <c r="T70" s="2">
+        <v>22</v>
+      </c>
+      <c r="U70" s="2">
+        <v>14</v>
+      </c>
+      <c r="V70" s="6">
         <v>3</v>
       </c>
       <c r="W70" s="2" t="s">
@@ -5330,7 +5401,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>51</v>
       </c>
@@ -5344,15 +5415,15 @@
         <v>223</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>317</v>
+        <v>643</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>307</v>
       </c>
       <c r="R71" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V71" s="7">
+      <c r="V71" s="6">
         <v>3</v>
       </c>
       <c r="W71" s="2" t="s">
@@ -5362,7 +5433,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>52</v>
       </c>
@@ -5379,18 +5450,18 @@
         <v>224</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>318</v>
+        <v>264</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="V72" s="7">
+        <v>349</v>
+      </c>
+      <c r="V72" s="6">
         <v>3</v>
       </c>
       <c r="W72" s="2" t="s">
@@ -5400,7 +5471,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>53</v>
       </c>
@@ -5417,15 +5488,15 @@
         <v>205</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>319</v>
+        <v>265</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>309</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V73" s="7">
+        <v>333</v>
+      </c>
+      <c r="V73" s="6">
         <v>3</v>
       </c>
       <c r="W73" s="2" t="s">
@@ -5435,7 +5506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>54</v>
       </c>
@@ -5452,15 +5523,15 @@
         <v>225</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>320</v>
+        <v>639</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="V74" s="7">
+        <v>336</v>
+      </c>
+      <c r="V74" s="6">
         <v>3</v>
       </c>
       <c r="W74" s="2" t="s">
@@ -5470,42 +5541,60 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
+    <row r="75" spans="1:25" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D75" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E75" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="K75" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="R75" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="V75" s="7">
+      <c r="F75" s="15"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="J75" s="15"/>
+      <c r="K75" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="L75" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="N75" s="15"/>
+      <c r="O75" s="15"/>
+      <c r="P75" s="15"/>
+      <c r="Q75" s="15"/>
+      <c r="R75" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="S75" s="15"/>
+      <c r="T75" s="15"/>
+      <c r="U75" s="15"/>
+      <c r="V75" s="17">
         <v>3</v>
       </c>
-      <c r="W75" s="2" t="s">
+      <c r="W75" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="X75" s="2" t="s">
+      <c r="X75" s="15" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y75" s="15"/>
+    </row>
+    <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>55</v>
       </c>
@@ -5522,15 +5611,15 @@
         <v>227</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>322</v>
+        <v>267</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V76" s="6">
+        <v>332</v>
+      </c>
+      <c r="V76" s="5">
         <v>2</v>
       </c>
       <c r="W76" s="2" t="s">
@@ -5540,7 +5629,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>56</v>
       </c>
@@ -5554,15 +5643,15 @@
         <v>228</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K77" s="4" t="s">
-        <v>323</v>
+        <v>268</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>313</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="V77" s="6">
+        <v>342</v>
+      </c>
+      <c r="V77" s="5">
         <v>2</v>
       </c>
       <c r="W77" s="2" t="s">
@@ -5572,7 +5661,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>57</v>
       </c>
@@ -5589,15 +5678,15 @@
         <v>229</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>324</v>
+        <v>269</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V78" s="7">
+        <v>332</v>
+      </c>
+      <c r="V78" s="6">
         <v>3</v>
       </c>
       <c r="W78" s="2" t="s">
@@ -5607,7 +5696,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>58</v>
       </c>
@@ -5624,15 +5713,15 @@
         <v>230</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>325</v>
+        <v>270</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="V79" s="7">
+        <v>343</v>
+      </c>
+      <c r="V79" s="6">
         <v>3</v>
       </c>
       <c r="W79" s="2" t="s">
@@ -5642,118 +5731,165 @@
         <v>105</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="K80" s="4"/>
-      <c r="V80" s="5">
-        <v>1</v>
+    <row r="80" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="V80" s="6">
+        <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K81" s="4" t="s">
-        <v>326</v>
+        <v>644</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>317</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="V81" s="7">
+        <v>333</v>
+      </c>
+      <c r="V81" s="6">
         <v>3</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>327</v>
+        <v>272</v>
+      </c>
+      <c r="K82" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V82" s="7">
+        <v>344</v>
+      </c>
+      <c r="V82" s="6">
         <v>3</v>
       </c>
       <c r="W82" s="2" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="K83" s="4" t="s">
-        <v>328</v>
+        <v>599</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="M83" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="O83" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>604</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="V83" s="7">
-        <v>3</v>
+        <v>331</v>
+      </c>
+      <c r="S83" s="3">
+        <v>450</v>
+      </c>
+      <c r="T83" s="3">
+        <v>350</v>
+      </c>
+      <c r="U83" s="3">
+        <v>250</v>
+      </c>
+      <c r="V83" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5763,8 +5899,8 @@
       <c r="B84" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>158</v>
+      <c r="C84" s="9">
+        <v>1583</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>173</v>
@@ -5773,37 +5909,31 @@
         <v>205</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="K84" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="L84" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="M84" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="O84" s="8" t="s">
-        <v>616</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="K84" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="L84" s="8"/>
+      <c r="M84" s="7"/>
+      <c r="O84" s="7"/>
       <c r="Q84" s="2" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="S84" s="3">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="T84" s="3">
-        <v>350</v>
+        <v>223</v>
       </c>
       <c r="U84" s="3">
-        <v>250</v>
-      </c>
-      <c r="V84" s="5" t="s">
-        <v>410</v>
+        <v>166</v>
+      </c>
+      <c r="V84" s="4">
+        <v>1</v>
       </c>
       <c r="W84" s="2" t="s">
         <v>60</v>
@@ -5819,35 +5949,43 @@
       <c r="B85" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C85" s="10">
-        <v>1583</v>
+      <c r="C85" s="2" t="s">
+        <v>419</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="K85" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="L85" s="9"/>
-      <c r="M85" s="8"/>
+        <v>606</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="L85" s="8"/>
+      <c r="M85" s="7" t="s">
+        <v>608</v>
+      </c>
       <c r="O85" s="8"/>
       <c r="Q85" s="2" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S85" s="3"/>
-      <c r="T85" s="3"/>
-      <c r="U85" s="3"/>
-      <c r="V85" s="5">
-        <v>1</v>
+        <v>333</v>
+      </c>
+      <c r="S85" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="T85" s="3">
+        <v>75</v>
+      </c>
+      <c r="U85" s="3">
+        <v>75</v>
+      </c>
+      <c r="V85" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W85" s="2" t="s">
         <v>60</v>
@@ -5863,8 +6001,8 @@
       <c r="B86" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>430</v>
+      <c r="C86" s="9">
+        <v>1586</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>173</v>
@@ -5873,29 +6011,35 @@
         <v>206</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="K86" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="L86" s="9"/>
-      <c r="M86" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="O86" s="9"/>
+        <v>611</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="L86" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="M86" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="O86" s="8"/>
       <c r="Q86" s="2" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>343</v>
+        <v>615</v>
       </c>
       <c r="S86" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="T86" s="3"/>
-      <c r="U86" s="3"/>
-      <c r="V86" s="5" t="s">
-        <v>410</v>
+        <v>616</v>
+      </c>
+      <c r="T86" s="3">
+        <v>120</v>
+      </c>
+      <c r="U86" s="3">
+        <v>81</v>
+      </c>
+      <c r="V86" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W86" s="2" t="s">
         <v>60</v>
@@ -5911,8 +6055,8 @@
       <c r="B87" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="10">
-        <v>1586</v>
+      <c r="C87" s="2" t="s">
+        <v>617</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>173</v>
@@ -5921,35 +6065,26 @@
         <v>206</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="K87" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="M87" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="O87" s="9"/>
+        <v>618</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="L87" s="8"/>
+      <c r="O87" s="8"/>
       <c r="Q87" s="2" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>628</v>
+        <v>333</v>
       </c>
       <c r="S87" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="T87" s="3">
-        <v>120</v>
-      </c>
-      <c r="U87" s="3">
-        <v>81</v>
-      </c>
-      <c r="V87" s="5" t="s">
-        <v>410</v>
+        <v>547</v>
+      </c>
+      <c r="T87" s="3"/>
+      <c r="U87" s="3"/>
+      <c r="V87" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W87" s="2" t="s">
         <v>60</v>
@@ -5966,7 +6101,7 @@
         <v>109</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>173</v>
@@ -5975,27 +6110,33 @@
         <v>206</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="K88" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="L88" s="9"/>
-      <c r="M88" s="9"/>
-      <c r="O88" s="9"/>
+        <v>621</v>
+      </c>
+      <c r="K88" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="L88" s="8"/>
+      <c r="M88" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="O88" s="8"/>
       <c r="Q88" s="2" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S88" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="T88" s="3"/>
-      <c r="U88" s="3"/>
-      <c r="V88" s="5" t="s">
-        <v>410</v>
+        <v>333</v>
+      </c>
+      <c r="S88" s="3">
+        <v>83</v>
+      </c>
+      <c r="T88" s="3">
+        <v>191</v>
+      </c>
+      <c r="U88" s="3">
+        <v>49</v>
+      </c>
+      <c r="V88" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W88" s="2" t="s">
         <v>60</v>
@@ -6012,7 +6153,7 @@
         <v>109</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>173</v>
@@ -6021,33 +6162,30 @@
         <v>206</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="K89" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="L89" s="9"/>
-      <c r="M89" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="O89" s="9"/>
+        <v>625</v>
+      </c>
+      <c r="K89" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="L89" s="8"/>
+      <c r="O89" s="8"/>
       <c r="Q89" s="2" t="s">
-        <v>622</v>
+        <v>458</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="S89" s="3">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="T89" s="3">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="U89" s="3">
-        <v>49</v>
-      </c>
-      <c r="V89" s="5" t="s">
-        <v>410</v>
+        <v>80</v>
+      </c>
+      <c r="V89" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W89" s="2" t="s">
         <v>60</v>
@@ -6063,41 +6201,45 @@
       <c r="B90" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>637</v>
+      <c r="C90" s="9">
+        <v>1570</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>173</v>
+        <v>627</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>206</v>
+        <v>628</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="K90" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="L90" s="9"/>
-      <c r="M90" s="9"/>
-      <c r="O90" s="9"/>
+        <v>629</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="M90" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="O90" s="8"/>
       <c r="Q90" s="2" t="s">
-        <v>469</v>
+        <v>609</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="S90" s="3">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="T90" s="3">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="U90" s="3">
-        <v>80</v>
-      </c>
-      <c r="V90" s="5" t="s">
-        <v>410</v>
+        <v>18</v>
+      </c>
+      <c r="V90" s="4">
+        <v>1</v>
       </c>
       <c r="W90" s="2" t="s">
         <v>60</v>
@@ -6113,45 +6255,40 @@
       <c r="B91" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C91" s="10">
-        <v>1570</v>
+      <c r="C91" s="2" t="s">
+        <v>633</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>640</v>
+        <v>173</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="K91" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="L91" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="M91" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="O91" s="9"/>
+        <v>611</v>
+      </c>
+      <c r="K91" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="L91" s="8"/>
+      <c r="O91" s="8"/>
       <c r="Q91" s="2" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="S91" s="3">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="T91" s="3">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="U91" s="3">
-        <v>18</v>
-      </c>
-      <c r="V91" s="5">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="V91" s="4" t="s">
+        <v>399</v>
       </c>
       <c r="W91" s="2" t="s">
         <v>60</v>
@@ -6162,450 +6299,404 @@
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>646</v>
+        <v>159</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>647</v>
+        <v>206</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="K92" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="L92" s="9"/>
-      <c r="M92" s="9"/>
-      <c r="O92" s="9"/>
-      <c r="Q92" s="2" t="s">
-        <v>622</v>
+        <v>273</v>
+      </c>
+      <c r="K92" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S92" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="T92" s="3"/>
-      <c r="U92" s="3"/>
-      <c r="V92" s="5" t="s">
-        <v>410</v>
+        <v>333</v>
+      </c>
+      <c r="S92" s="2">
+        <v>43</v>
+      </c>
+      <c r="T92" s="2">
+        <v>180</v>
+      </c>
+      <c r="U92" s="2">
+        <v>60</v>
+      </c>
+      <c r="V92" s="6">
+        <v>3</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="I93" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V93" s="6">
+        <v>3</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X93" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="R94" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="V94" s="6">
+        <v>3</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X94" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="V95" s="6">
+        <v>3</v>
+      </c>
+      <c r="W95" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="R96" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="S96" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="V96" s="4">
+        <v>1</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X96" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="R97" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="V97" s="5">
+        <v>2</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X97" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="R98" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="S98" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="V98" s="6">
+        <v>3</v>
+      </c>
+      <c r="W98" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X98" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="V99" s="6">
+        <v>3</v>
+      </c>
+      <c r="W99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X99" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="R100" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="S100" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="V100" s="6">
+        <v>3</v>
+      </c>
+      <c r="W100" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X100" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="R101" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="V101" s="6">
+        <v>3</v>
+      </c>
+      <c r="W101" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X101" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I102" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="K93" s="4" t="s">
+      <c r="K102" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="R93" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V93" s="7">
-        <v>3</v>
-      </c>
-      <c r="W93" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="X93" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="K94" s="4"/>
-      <c r="V94" s="6">
+      <c r="R102" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="V102" s="5">
         <v>2</v>
       </c>
-      <c r="X94" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="K95" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="R95" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V95" s="7">
-        <v>3</v>
-      </c>
-      <c r="W95" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="X95" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="R96" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="V96" s="7">
-        <v>3</v>
-      </c>
-      <c r="W96" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="X96" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="R97" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V97" s="7">
-        <v>3</v>
-      </c>
-      <c r="W97" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="X97" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="R98" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="V98" s="5">
-        <v>1</v>
-      </c>
-      <c r="W98" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="X98" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="V99" s="6">
-        <v>2</v>
-      </c>
-      <c r="W99" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X99" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="R100" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="V100" s="7">
-        <v>3</v>
-      </c>
-      <c r="W100" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="X100" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="K101" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="R101" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="S101" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="V101" s="7">
-        <v>3</v>
-      </c>
-      <c r="W101" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="X101" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K102" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="R102" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="S102" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="V102" s="7">
-        <v>3</v>
-      </c>
       <c r="W102" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="K103" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="R103" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="V103" s="7">
-        <v>3</v>
-      </c>
-      <c r="W103" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X103" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="K104" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="R104" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="V104" s="6">
-        <v>2</v>
-      </c>
-      <c r="W104" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X104" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6645,20 +6736,20 @@
     <hyperlink ref="K77" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
     <hyperlink ref="K78" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
     <hyperlink ref="K79" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="K81" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="K82" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="K83" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="K93" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="K95" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K96" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="K97" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="K98" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="K99" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K100" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K101" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K102" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K103" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K104" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K80" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K81" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K82" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K92" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K93" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K94" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K95" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K96" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="K97" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K98" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K99" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K100" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K101" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K102" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
     <hyperlink ref="K3" r:id="rId48" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
     <hyperlink ref="K4" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
     <hyperlink ref="K5" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
@@ -6707,21 +6798,26 @@
     <hyperlink ref="K49" r:id="rId93" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
     <hyperlink ref="K48" r:id="rId94" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
     <hyperlink ref="K51" r:id="rId95" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
-    <hyperlink ref="K85" r:id="rId96" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
-    <hyperlink ref="M86" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
-    <hyperlink ref="K86" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
-    <hyperlink ref="K87" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
-    <hyperlink ref="K88" r:id="rId100" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
-    <hyperlink ref="K92" r:id="rId101" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
-    <hyperlink ref="M89" r:id="rId102" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
-    <hyperlink ref="K89" r:id="rId103" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
-    <hyperlink ref="M91" r:id="rId104" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
-    <hyperlink ref="K90" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
-    <hyperlink ref="K91" r:id="rId106" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
-    <hyperlink ref="M84" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
-    <hyperlink ref="K84" r:id="rId108" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
-    <hyperlink ref="O84" r:id="rId109" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
-    <hyperlink ref="M87" r:id="rId110" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
+    <hyperlink ref="K84" r:id="rId96" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
+    <hyperlink ref="M85" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
+    <hyperlink ref="K85" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
+    <hyperlink ref="K86" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
+    <hyperlink ref="K87" r:id="rId100" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
+    <hyperlink ref="K91" r:id="rId101" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
+    <hyperlink ref="M88" r:id="rId102" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
+    <hyperlink ref="K88" r:id="rId103" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
+    <hyperlink ref="M90" r:id="rId104" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
+    <hyperlink ref="K89" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
+    <hyperlink ref="K90" r:id="rId106" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
+    <hyperlink ref="M83" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
+    <hyperlink ref="K83" r:id="rId108" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
+    <hyperlink ref="O83" r:id="rId109" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
+    <hyperlink ref="M86" r:id="rId110" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
+    <hyperlink ref="M75" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
+    <hyperlink ref="H52" r:id="rId112" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
+    <hyperlink ref="G52" r:id="rId113" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
+    <hyperlink ref="M52" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
+    <hyperlink ref="O52" r:id="rId115" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39AFA0B-D7FE-4060-B351-CA6D06BB310F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A43B18E-CAFD-4BBF-B754-61556F89DB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4683,8 +4683,7 @@
       <c r="E52" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="F52" s="11"/>
-      <c r="G52" s="13" t="s">
+      <c r="F52" s="13" t="s">
         <v>649</v>
       </c>
       <c r="H52" s="13" t="s">
@@ -6815,7 +6814,7 @@
     <hyperlink ref="M86" r:id="rId110" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
     <hyperlink ref="M75" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
     <hyperlink ref="H52" r:id="rId112" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
-    <hyperlink ref="G52" r:id="rId113" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
+    <hyperlink ref="F52" r:id="rId113" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
     <hyperlink ref="M52" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
     <hyperlink ref="O52" r:id="rId115" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
   </hyperlinks>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A43B18E-CAFD-4BBF-B754-61556F89DB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9202C9C0-ABB2-4C88-AB77-72056003D8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="677">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -695,9 +695,6 @@
     <t>Rathausplatz</t>
   </si>
   <si>
-    <t>Place Joachim-du-Bellay</t>
-  </si>
-  <si>
     <t>Taft Museum of Art</t>
   </si>
   <si>
@@ -815,9 +812,6 @@
     <t>"Retable majeur du Pilar"</t>
   </si>
   <si>
-    <t>"La Fontaine des Innocents"</t>
-  </si>
-  <si>
     <t>"Annonciation"</t>
   </si>
   <si>
@@ -1244,9 +1238,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Sculpture</t>
-  </si>
-  <si>
     <t>505</t>
   </si>
   <si>
@@ -1268,9 +1259,6 @@
     <t>1547-1572</t>
   </si>
   <si>
-    <t>Salone dei Cinquecento</t>
-  </si>
-  <si>
     <t>Monument à Cosme Ier de Médicis</t>
   </si>
   <si>
@@ -1298,9 +1286,6 @@
     <t>Basilique de la Santissima Annunziata</t>
   </si>
   <si>
-    <t>Cappella Bandinelli</t>
-  </si>
-  <si>
     <t>Pietà avec saint Jean, la Vierge et Nicodème</t>
   </si>
   <si>
@@ -1373,9 +1358,6 @@
     <t>Cathédrale Sainte-Marie</t>
   </si>
   <si>
-    <t>Chœur</t>
-  </si>
-  <si>
     <t>Stalles de la Transfiguration</t>
   </si>
   <si>
@@ -1409,9 +1391,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b5/Interior_del_Hospital_de_Tavera%2C_Toledo_31.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Tombeau</t>
-  </si>
-  <si>
     <t>Marbre de Carrare</t>
   </si>
   <si>
@@ -1454,9 +1433,6 @@
     <t>Atlante che sorregge il mondo</t>
   </si>
   <si>
-    <t>Statue</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -1475,9 +1451,6 @@
     <t>Église de San Francesco della Vigna</t>
   </si>
   <si>
-    <t>Façade (niches)</t>
-  </si>
-  <si>
     <t>Moïse</t>
   </si>
   <si>
@@ -1487,9 +1460,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statue monumentale</t>
-  </si>
-  <si>
     <t>Saint Paul</t>
   </si>
   <si>
@@ -1532,9 +1502,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bf/Mars_as_Contemporary_Warrior_MET_DP248150.jpg/960px-Mars_as_Contemporary_Warrior_MET_DP248150.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statuette</t>
-  </si>
-  <si>
     <t>55</t>
   </si>
   <si>
@@ -1565,9 +1532,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Fontaine monumentale</t>
-  </si>
-  <si>
     <t>320 cm (Neptune)</t>
   </si>
   <si>
@@ -1601,9 +1565,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/d/da/Appennino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Statue colossale</t>
-  </si>
-  <si>
     <t>Pierre et brique, stuc</t>
   </si>
   <si>
@@ -1622,9 +1583,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statue équestre</t>
-  </si>
-  <si>
     <t>450 cm</t>
   </si>
   <si>
@@ -1724,9 +1682,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Kaiser_Rudolf_II._%28de_Vries_1603%29.jpg/960px-Kaiser_Rudolf_II._%28de_Vries_1603%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Buste</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -1850,9 +1805,6 @@
     <t>Monument funéraire</t>
   </si>
   <si>
-    <t>Dalle funéraire</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monument du cœur d'Henri II </t>
   </si>
   <si>
@@ -1862,9 +1814,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Ronde-bosse</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
@@ -1989,6 +1938,132 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Vincenzo_de%27_rossi%2C_teseo_e_arianna%2C_01.JPG/1920px-Vincenzo_de%27_rossi%2C_teseo_e_arianna%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1547-1549</t>
+  </si>
+  <si>
+    <t>Nymphe et Triton entourés de deux petits génies</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Cariatides de la Tribune</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Tribune-louvre_%283%29.jpg/1280px-Tribune-louvre_%283%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statues-colonnes </t>
+  </si>
+  <si>
+    <t>Pierre de Tonnerre</t>
+  </si>
+  <si>
+    <t>1544-1545</t>
+  </si>
+  <si>
+    <t>Déploration du Christ</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ce bas-relief aisait partie du jubé de l'église Saint-Germain-l'Auxerrois à Paris construit par Pierre Lescot et Jean Goujon et démonté en 1745.</t>
+  </si>
+  <si>
+    <t>Bas-reliefs de jubé</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Saint Jean</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1540-1542</t>
+  </si>
+  <si>
+    <t>Rouen</t>
+  </si>
+  <si>
+    <t>Cathédrale Notre-Dame de Rouen</t>
+  </si>
+  <si>
+    <t>Tombeau de Louis de Brézé</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/Tombeau_de_Louis_de_Br%C3%A9z%C3%A9.jpg/960px-Tombeau_de_Louis_de_Br%C3%A9z%C3%A9.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1555-1560</t>
+  </si>
+  <si>
+    <t>Hôtel de Carnavalet</t>
+  </si>
+  <si>
+    <t>Façades de la cour</t>
+  </si>
+  <si>
+    <t>Les Quatre Saisons</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1548-1550</t>
+  </si>
+  <si>
+    <t>Palais du Louvre</t>
+  </si>
+  <si>
+    <t>Façade de l'aile Lescot, aile ouest de la Cour Carrée, avant corps sud</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7e/Aile_Lescot%2C_Palais_du_Louvre.jpg/1280px-Aile_Lescot%2C_Palais_du_Louvre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Cérès</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg/960px-Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ce relief architectural fait partie des décorations de l'Attique , endacrant une fenêtre avec Neptune en pendant</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Reliefs architecturaux</t>
+  </si>
+  <si>
+    <t>Château de Chantilly</t>
+  </si>
+  <si>
+    <t>Le Départ de Phaéton</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ce relief ornait l'autel de la Chapelle du château d'Ecouen, détruite en 1793</t>
+  </si>
+  <si>
+    <t>Bas-relief monumental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Façade </t>
+  </si>
+  <si>
+    <t>Salon des Cinq-Cents</t>
+  </si>
+  <si>
+    <t>Chapelle  Bandinelli</t>
   </si>
 </sst>
 </file>
@@ -2094,7 +2169,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2139,8 +2214,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2446,7 +2529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y102"/>
+  <dimension ref="A1:Y109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -2635,22 +2718,22 @@
         <v>197</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="S3" s="2">
         <v>560</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
@@ -2667,31 +2750,31 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="R4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="V4" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
@@ -2708,31 +2791,31 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>370</v>
-      </c>
       <c r="R5" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S5" s="2">
         <v>262</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
@@ -2749,31 +2832,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>374</v>
-      </c>
       <c r="R6" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S6" s="2">
         <v>139</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
@@ -2790,28 +2873,28 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="V7" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
@@ -2828,28 +2911,28 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="V8" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
@@ -2866,28 +2949,28 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="K9" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>391</v>
-      </c>
       <c r="R9" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
@@ -2904,31 +2987,31 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="K10" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="S10" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="V10" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
@@ -2954,22 +3037,19 @@
         <v>198</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>473</v>
+        <v>279</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
@@ -2995,22 +3075,19 @@
         <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>23</v>
@@ -3027,34 +3104,31 @@
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>480</v>
+        <v>674</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>23</v>
@@ -3071,34 +3145,31 @@
         <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>480</v>
+        <v>674</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>23</v>
@@ -3115,35 +3186,35 @@
         <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="M15" s="7"/>
       <c r="Q15" s="2" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>23</v>
@@ -3160,7 +3231,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>176</v>
@@ -3169,25 +3240,22 @@
         <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>23</v>
@@ -3210,10 +3278,10 @@
         <v>199</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>31</v>
@@ -3245,28 +3313,25 @@
         <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="M18" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="R18" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="V18" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
@@ -3283,34 +3348,31 @@
         <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>409</v>
-      </c>
       <c r="V19" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W19" s="2" t="s">
         <v>25</v>
@@ -3327,7 +3389,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>170</v>
@@ -3336,28 +3398,25 @@
         <v>200</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S20" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="V20" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>25</v>
@@ -3374,19 +3433,19 @@
         <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="S21" s="2">
         <v>78</v>
@@ -3395,7 +3454,7 @@
         <v>75</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
@@ -3412,37 +3471,34 @@
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S22" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="V22" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>25</v>
@@ -3459,37 +3515,34 @@
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S23" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>432</v>
-      </c>
       <c r="V23" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>25</v>
@@ -3515,16 +3568,16 @@
         <v>197</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="V24" s="4">
         <v>1</v>
@@ -3553,16 +3606,16 @@
         <v>200</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="V25" s="6">
         <v>3</v>
@@ -3588,13 +3641,13 @@
         <v>201</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="V26" s="6">
         <v>3</v>
@@ -3623,19 +3676,19 @@
         <v>202</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="V27" s="5">
         <v>2</v>
@@ -3664,28 +3717,25 @@
         <v>202</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="T28" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="V28" s="5">
         <v>2</v>
@@ -3705,31 +3755,28 @@
         <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="V29" s="5">
         <v>2</v>
@@ -3749,31 +3796,25 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="R30" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="V30" s="5">
         <v>2</v>
@@ -3802,25 +3843,22 @@
         <v>202</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>403</v>
+        <v>455</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="V31" s="5">
         <v>2</v>
@@ -3840,28 +3878,25 @@
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="V32" s="5">
         <v>2</v>
@@ -3887,13 +3922,13 @@
         <v>203</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="V33" s="6">
         <v>3</v>
@@ -3922,25 +3957,22 @@
         <v>204</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="V34" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -3957,34 +3989,31 @@
         <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="V35" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -4001,34 +4030,31 @@
         <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="V36" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4048,31 +4074,28 @@
         <v>128</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="V37" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4089,7 +4112,7 @@
         <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>170</v>
@@ -4098,25 +4121,22 @@
         <v>197</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="V38" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4133,34 +4153,34 @@
         <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>532</v>
+        <v>518</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="V39" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4177,34 +4197,31 @@
         <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4221,7 +4238,7 @@
         <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>170</v>
@@ -4230,25 +4247,25 @@
         <v>204</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="V41" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4271,16 +4288,16 @@
         <v>207</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="V42" s="6">
         <v>3</v>
@@ -4309,16 +4326,16 @@
         <v>200</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="V43" s="6">
         <v>3</v>
@@ -4347,16 +4364,16 @@
         <v>208</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="V44" s="6">
         <v>3</v>
@@ -4385,13 +4402,13 @@
         <v>209</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="V45" s="6">
         <v>3</v>
@@ -4420,19 +4437,19 @@
         <v>202</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="V46" s="5">
         <v>2</v>
@@ -4452,7 +4469,7 @@
         <v>83</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>172</v>
@@ -4461,22 +4478,19 @@
         <v>202</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>403</v>
+        <v>555</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="V47" s="5">
         <v>2</v>
@@ -4496,31 +4510,31 @@
         <v>83</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="V48" s="5">
         <v>2</v>
@@ -4540,34 +4554,34 @@
         <v>83</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="V49" s="5">
         <v>2</v>
@@ -4587,31 +4601,31 @@
         <v>83</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="V50" s="5">
         <v>2</v>
@@ -4631,31 +4645,28 @@
         <v>83</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>403</v>
+        <v>582</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="V51" s="5">
         <v>2</v>
@@ -4667,7 +4678,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:25" s="19" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>36</v>
       </c>
@@ -4684,30 +4695,30 @@
         <v>210</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="J52" s="11"/>
       <c r="K52" s="14" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L52" s="11"/>
       <c r="M52" s="14" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="N52" s="11"/>
       <c r="O52" s="13" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="P52" s="11"/>
       <c r="Q52" s="11"/>
       <c r="R52" s="11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S52" s="11">
         <v>182</v>
@@ -4739,10 +4750,10 @@
         <v>211</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>31</v>
@@ -4774,25 +4785,22 @@
         <v>206</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>403</v>
+        <v>292</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="V54" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>39</v>
@@ -4809,34 +4817,31 @@
         <v>86</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>510</v>
+        <v>539</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="V55" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W55" s="2" t="s">
         <v>39</v>
@@ -4853,34 +4858,31 @@
         <v>86</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="V56" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W56" s="2" t="s">
         <v>39</v>
@@ -4897,34 +4899,31 @@
         <v>86</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>186</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="Q57" s="2" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="V57" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="W57" s="2" t="s">
         <v>39</v>
@@ -4950,16 +4949,16 @@
         <v>206</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="V58" s="4">
         <v>1</v>
@@ -4985,13 +4984,13 @@
         <v>212</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="V59" s="6">
         <v>3</v>
@@ -5020,13 +5019,13 @@
         <v>213</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="V60" s="5">
         <v>2</v>
@@ -5055,13 +5054,13 @@
         <v>214</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="V61" s="6">
         <v>3</v>
@@ -5090,13 +5089,13 @@
         <v>215</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="V62" s="6">
         <v>3</v>
@@ -5125,13 +5124,13 @@
         <v>216</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="V63" s="6">
         <v>3</v>
@@ -5157,16 +5156,16 @@
         <v>217</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="V64" s="5">
         <v>2</v>
@@ -5178,7 +5177,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>46</v>
       </c>
@@ -5195,13 +5194,13 @@
         <v>218</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="V65" s="6">
         <v>3</v>
@@ -5213,7 +5212,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>47</v>
       </c>
@@ -5230,13 +5229,13 @@
         <v>219</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="V66" s="5">
         <v>2</v>
@@ -5248,7 +5247,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>30</v>
       </c>
@@ -5256,22 +5255,38 @@
         <v>94</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>144</v>
+        <v>635</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K67" s="7" t="s">
-        <v>303</v>
+        <v>636</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>637</v>
+      </c>
+      <c r="L67" s="8"/>
+      <c r="M67" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>484</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>31</v>
+        <v>331</v>
+      </c>
+      <c r="S67" s="3">
+        <v>73</v>
+      </c>
+      <c r="T67" s="3">
+        <v>195</v>
+      </c>
+      <c r="U67" s="3">
+        <v>12</v>
       </c>
       <c r="V67" s="4">
         <v>1</v>
@@ -5283,88 +5298,115 @@
         <v>94</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>145</v>
+        <v>635</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="K68" s="7" t="s">
-        <v>304</v>
+        <v>638</v>
+      </c>
+      <c r="K68" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="L68" s="8"/>
+      <c r="M68" s="20"/>
+      <c r="Q68" s="2" t="s">
+        <v>640</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="V68" s="6">
-        <v>3</v>
+        <v>641</v>
+      </c>
+      <c r="S68" s="3">
+        <v>210</v>
+      </c>
+      <c r="T68" s="3">
+        <v>60</v>
+      </c>
+      <c r="U68" s="3">
+        <v>65</v>
+      </c>
+      <c r="V68" s="4">
+        <v>1</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>146</v>
+        <v>642</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="K69" s="19" t="s">
+        <v>644</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="M69" s="20"/>
+      <c r="Q69" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="T69" s="3">
         <v>182</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="R69" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="S69" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="V69" s="6">
-        <v>3</v>
+      <c r="U69" s="3">
+        <v>7</v>
+      </c>
+      <c r="V69" s="4">
+        <v>1</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>147</v>
+        <v>642</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>173</v>
@@ -5373,824 +5415,802 @@
         <v>206</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K70" s="7" t="s">
-        <v>306</v>
+        <v>648</v>
+      </c>
+      <c r="K70" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="M70" s="20"/>
+      <c r="Q70" s="2" t="s">
+        <v>646</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="S70" s="2">
+        <v>331</v>
+      </c>
+      <c r="S70" s="3">
+        <v>79</v>
+      </c>
+      <c r="T70" s="3">
+        <v>56</v>
+      </c>
+      <c r="U70" s="3">
+        <v>11</v>
+      </c>
+      <c r="V70" s="4">
+        <v>1</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="K71" s="19" t="s">
+        <v>654</v>
+      </c>
+      <c r="L71" s="8"/>
+      <c r="M71" s="20"/>
+      <c r="Q71" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="S71" s="3">
+        <v>700</v>
+      </c>
+      <c r="T71" s="3">
+        <v>366</v>
+      </c>
+      <c r="U71" s="3">
+        <v>93</v>
+      </c>
+      <c r="V71" s="4">
+        <v>1</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X71" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="K72" s="19" t="s">
+        <v>659</v>
+      </c>
+      <c r="L72" s="8"/>
+      <c r="M72" s="20"/>
+      <c r="Q72" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S72" s="3">
+        <v>215</v>
+      </c>
+      <c r="T72" s="3">
+        <v>95</v>
+      </c>
+      <c r="U72" s="3">
+        <v>6</v>
+      </c>
+      <c r="V72" s="4">
+        <v>1</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="H73" s="19" t="s">
+        <v>663</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>665</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="M73" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S73" s="3">
+        <v>205</v>
+      </c>
+      <c r="T73" s="3">
+        <v>90</v>
+      </c>
+      <c r="U73" s="3">
+        <v>6</v>
+      </c>
+      <c r="V73" s="4">
+        <v>1</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X73" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D74"/>
+      <c r="E74" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="J74"/>
+      <c r="K74" s="19" t="s">
+        <v>671</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="M74" s="20"/>
+      <c r="Q74" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S74" s="3">
+        <v>80</v>
+      </c>
+      <c r="T74" s="3">
+        <v>202</v>
+      </c>
+      <c r="U74" s="3">
+        <v>8</v>
+      </c>
+      <c r="V74" s="4">
+        <v>1</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="V75" s="4">
+        <v>3</v>
+      </c>
+      <c r="W75" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X75" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="V76" s="6">
+        <v>3</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X76" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="S77" s="2">
         <v>26</v>
       </c>
-      <c r="T70" s="2">
+      <c r="T77" s="2">
         <v>22</v>
       </c>
-      <c r="U70" s="2">
+      <c r="U77" s="2">
         <v>14</v>
       </c>
-      <c r="V70" s="6">
+      <c r="V77" s="6">
         <v>3</v>
       </c>
-      <c r="W70" s="2" t="s">
+      <c r="W77" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="X70" s="2" t="s">
+      <c r="X77" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
+    <row r="78" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="K71" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="R71" s="2" t="s">
+      <c r="E78" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="R78" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="V71" s="6">
-        <v>3</v>
-      </c>
-      <c r="W71" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X71" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K72" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="R72" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="V72" s="6">
-        <v>3</v>
-      </c>
-      <c r="W72" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="X72" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="K73" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="R73" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="V73" s="6">
-        <v>3</v>
-      </c>
-      <c r="W73" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X73" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="K74" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="R74" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="V74" s="6">
-        <v>3</v>
-      </c>
-      <c r="W74" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="X74" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B75" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C75" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="E75" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="J75" s="15"/>
-      <c r="K75" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="L75" s="15" t="s">
-        <v>646</v>
-      </c>
-      <c r="M75" s="16" t="s">
-        <v>645</v>
-      </c>
-      <c r="N75" s="15"/>
-      <c r="O75" s="15"/>
-      <c r="P75" s="15"/>
-      <c r="Q75" s="15"/>
-      <c r="R75" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="S75" s="15"/>
-      <c r="T75" s="15"/>
-      <c r="U75" s="15"/>
-      <c r="V75" s="17">
-        <v>3</v>
-      </c>
-      <c r="W75" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="X75" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y75" s="15"/>
-    </row>
-    <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K76" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="R76" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="V76" s="5">
-        <v>2</v>
-      </c>
-      <c r="W76" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="X76" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K77" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="R77" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V77" s="5">
-        <v>2</v>
-      </c>
-      <c r="W77" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="X77" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K78" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="R78" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="V78" s="6">
         <v>3</v>
       </c>
       <c r="W78" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="V79" s="6">
         <v>3</v>
       </c>
       <c r="W79" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="V80" s="6">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>644</v>
+        <v>622</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="V81" s="6">
         <v>3</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="K82" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="R82" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V82" s="6">
+      <c r="A82" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E82" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F82" s="15"/>
+      <c r="G82" s="15"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="J82" s="15"/>
+      <c r="K82" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="L82" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>628</v>
+      </c>
+      <c r="N82" s="15"/>
+      <c r="O82" s="15"/>
+      <c r="P82" s="15"/>
+      <c r="Q82" s="15"/>
+      <c r="R82" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="S82" s="15"/>
+      <c r="T82" s="15"/>
+      <c r="U82" s="15"/>
+      <c r="V82" s="17">
         <v>3</v>
       </c>
-      <c r="W82" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="X82" s="2" t="s">
-        <v>108</v>
+      <c r="W82" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="X82" s="15" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>599</v>
+        <v>265</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="L83" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="M83" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="O83" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q83" s="2" t="s">
-        <v>604</v>
+        <v>310</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S83" s="3">
-        <v>450</v>
-      </c>
-      <c r="T83" s="3">
-        <v>350</v>
-      </c>
-      <c r="U83" s="3">
-        <v>250</v>
-      </c>
-      <c r="V83" s="4" t="s">
-        <v>399</v>
+        <v>330</v>
+      </c>
+      <c r="V83" s="5">
+        <v>2</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C84" s="9">
-        <v>1583</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>173</v>
+        <v>103</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>599</v>
+        <v>266</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="L84" s="8"/>
-      <c r="M84" s="7"/>
-      <c r="O84" s="7"/>
-      <c r="Q84" s="2" t="s">
-        <v>605</v>
+        <v>311</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S84" s="3">
-        <v>90</v>
-      </c>
-      <c r="T84" s="3">
-        <v>223</v>
-      </c>
-      <c r="U84" s="3">
-        <v>166</v>
-      </c>
-      <c r="V84" s="4">
-        <v>1</v>
+        <v>340</v>
+      </c>
+      <c r="V84" s="5">
+        <v>2</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>419</v>
+        <v>154</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>606</v>
+        <v>267</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>607</v>
-      </c>
-      <c r="L85" s="8"/>
-      <c r="M85" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="O85" s="8"/>
-      <c r="Q85" s="2" t="s">
-        <v>609</v>
+        <v>312</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S85" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="T85" s="3">
-        <v>75</v>
-      </c>
-      <c r="U85" s="3">
-        <v>75</v>
-      </c>
-      <c r="V85" s="4" t="s">
-        <v>399</v>
+        <v>330</v>
+      </c>
+      <c r="V85" s="6">
+        <v>3</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C86" s="9">
-        <v>1586</v>
+        <v>105</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>611</v>
+        <v>268</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>612</v>
-      </c>
-      <c r="L86" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="M86" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="O86" s="8"/>
-      <c r="Q86" s="2" t="s">
-        <v>609</v>
+        <v>313</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="S86" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="T86" s="3">
-        <v>120</v>
-      </c>
-      <c r="U86" s="3">
-        <v>81</v>
-      </c>
-      <c r="V86" s="4" t="s">
-        <v>399</v>
+        <v>341</v>
+      </c>
+      <c r="V86" s="6">
+        <v>3</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>617</v>
+        <v>155</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>618</v>
+        <v>269</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="L87" s="8"/>
-      <c r="O87" s="8"/>
-      <c r="Q87" s="2" t="s">
-        <v>609</v>
+        <v>314</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S87" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="T87" s="3"/>
-      <c r="U87" s="3"/>
-      <c r="V87" s="4" t="s">
-        <v>399</v>
+        <v>337</v>
+      </c>
+      <c r="V87" s="6">
+        <v>3</v>
       </c>
       <c r="W87" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>620</v>
+        <v>156</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>622</v>
-      </c>
-      <c r="L88" s="8"/>
-      <c r="M88" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="O88" s="8"/>
-      <c r="Q88" s="2" t="s">
-        <v>609</v>
+        <v>315</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S88" s="3">
-        <v>83</v>
-      </c>
-      <c r="T88" s="3">
-        <v>191</v>
-      </c>
-      <c r="U88" s="3">
-        <v>49</v>
-      </c>
-      <c r="V88" s="4" t="s">
-        <v>399</v>
+        <v>331</v>
+      </c>
+      <c r="V88" s="6">
+        <v>3</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>624</v>
+        <v>157</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>625</v>
+        <v>270</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="L89" s="8"/>
-      <c r="O89" s="8"/>
-      <c r="Q89" s="2" t="s">
-        <v>458</v>
+        <v>316</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="S89" s="3">
-        <v>140</v>
-      </c>
-      <c r="T89" s="3">
-        <v>210</v>
-      </c>
-      <c r="U89" s="3">
-        <v>80</v>
-      </c>
-      <c r="V89" s="4" t="s">
-        <v>399</v>
+        <v>342</v>
+      </c>
+      <c r="V89" s="6">
+        <v>3</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6200,45 +6220,44 @@
       <c r="B90" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C90" s="9">
-        <v>1570</v>
+      <c r="C90" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>627</v>
+        <v>173</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>628</v>
+        <v>205</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>629</v>
+        <v>584</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>630</v>
+        <v>585</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>631</v>
+        <v>586</v>
       </c>
       <c r="M90" s="7" t="s">
-        <v>632</v>
-      </c>
-      <c r="O90" s="8"/>
-      <c r="Q90" s="2" t="s">
-        <v>609</v>
+        <v>587</v>
+      </c>
+      <c r="O90" s="7" t="s">
+        <v>588</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="S90" s="3">
-        <v>96</v>
+        <v>450</v>
       </c>
       <c r="T90" s="3">
-        <v>25</v>
+        <v>350</v>
       </c>
       <c r="U90" s="3">
-        <v>18</v>
-      </c>
-      <c r="V90" s="4">
-        <v>1</v>
+        <v>250</v>
+      </c>
+      <c r="V90" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="W90" s="2" t="s">
         <v>60</v>
@@ -6254,40 +6273,38 @@
       <c r="B91" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>633</v>
+      <c r="C91" s="9">
+        <v>1583</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>634</v>
+        <v>205</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>614</v>
+        <v>317</v>
       </c>
       <c r="L91" s="8"/>
-      <c r="O91" s="8"/>
-      <c r="Q91" s="2" t="s">
-        <v>609</v>
-      </c>
+      <c r="M91" s="7"/>
+      <c r="O91" s="7"/>
       <c r="R91" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="S91" s="3">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="T91" s="3">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="U91" s="3">
-        <v>81</v>
-      </c>
-      <c r="V91" s="4" t="s">
-        <v>399</v>
+        <v>166</v>
+      </c>
+      <c r="V91" s="4">
+        <v>1</v>
       </c>
       <c r="W91" s="2" t="s">
         <v>60</v>
@@ -6298,13 +6315,13 @@
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>159</v>
+        <v>415</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>173</v>
@@ -6313,389 +6330,723 @@
         <v>206</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>273</v>
+        <v>590</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>320</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="L92" s="8"/>
+      <c r="M92" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="O92" s="8"/>
       <c r="R92" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S92" s="2">
-        <v>43</v>
-      </c>
-      <c r="T92" s="2">
-        <v>180</v>
-      </c>
-      <c r="U92" s="2">
+        <v>331</v>
+      </c>
+      <c r="S92" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="T92" s="3">
+        <v>75</v>
+      </c>
+      <c r="U92" s="3">
+        <v>75</v>
+      </c>
+      <c r="V92" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="W92" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V92" s="6">
-        <v>3</v>
-      </c>
-      <c r="W92" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="X92" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>160</v>
+        <v>109</v>
+      </c>
+      <c r="C93" s="9">
+        <v>1586</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>274</v>
+        <v>594</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>321</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="M93" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="O93" s="8"/>
       <c r="R93" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V93" s="6">
-        <v>3</v>
+        <v>598</v>
+      </c>
+      <c r="S93" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="T93" s="3">
+        <v>120</v>
+      </c>
+      <c r="U93" s="3">
+        <v>81</v>
+      </c>
+      <c r="V93" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>161</v>
+        <v>600</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>637</v>
+        <v>601</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>322</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="L94" s="8"/>
+      <c r="O94" s="8"/>
       <c r="R94" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="V94" s="6">
-        <v>3</v>
+        <v>331</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>162</v>
+        <v>603</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>275</v>
+        <v>604</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>323</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="L95" s="8"/>
+      <c r="M95" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="O95" s="8"/>
       <c r="R95" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="V95" s="6">
-        <v>3</v>
+        <v>331</v>
+      </c>
+      <c r="S95" s="3">
+        <v>83</v>
+      </c>
+      <c r="T95" s="3">
+        <v>191</v>
+      </c>
+      <c r="U95" s="3">
+        <v>49</v>
+      </c>
+      <c r="V95" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>163</v>
+        <v>607</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>276</v>
+        <v>608</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>324</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="L96" s="8"/>
+      <c r="O96" s="8"/>
       <c r="R96" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="V96" s="4">
-        <v>1</v>
+        <v>330</v>
+      </c>
+      <c r="S96" s="3">
+        <v>140</v>
+      </c>
+      <c r="T96" s="3">
+        <v>210</v>
+      </c>
+      <c r="U96" s="3">
+        <v>80</v>
+      </c>
+      <c r="V96" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>164</v>
+        <v>109</v>
+      </c>
+      <c r="C97" s="9">
+        <v>1570</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>193</v>
+        <v>610</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>237</v>
+        <v>611</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>277</v>
+        <v>612</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>325</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="M97" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="O97" s="8"/>
       <c r="R97" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="V97" s="5">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="S97" s="3">
+        <v>96</v>
+      </c>
+      <c r="T97" s="3">
+        <v>25</v>
+      </c>
+      <c r="U97" s="3">
+        <v>18</v>
+      </c>
+      <c r="V97" s="4">
+        <v>1</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>165</v>
+        <v>616</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>238</v>
+        <v>617</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>278</v>
+        <v>594</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>326</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="L98" s="8"/>
+      <c r="O98" s="8"/>
       <c r="R98" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="V98" s="6">
-        <v>3</v>
+        <v>331</v>
+      </c>
+      <c r="S98" s="3">
+        <v>159</v>
+      </c>
+      <c r="T98" s="3">
+        <v>120</v>
+      </c>
+      <c r="U98" s="3">
+        <v>81</v>
+      </c>
+      <c r="V98" s="4" t="s">
+        <v>397</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>636</v>
+        <v>271</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>354</v>
+        <v>331</v>
+      </c>
+      <c r="S99" s="2">
+        <v>43</v>
+      </c>
+      <c r="T99" s="2">
+        <v>180</v>
+      </c>
+      <c r="U99" s="2">
+        <v>60</v>
       </c>
       <c r="V99" s="6">
         <v>3</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>354</v>
+        <v>31</v>
       </c>
       <c r="V100" s="6">
         <v>3</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>638</v>
+        <v>620</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="R101" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="V101" s="6">
         <v>3</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="R102" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="V102" s="5">
+      <c r="V102" s="6">
+        <v>3</v>
+      </c>
+      <c r="W102" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X102" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="R103" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S103" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="V103" s="4">
+        <v>1</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X103" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K104" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="R104" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="V104" s="5">
         <v>2</v>
       </c>
-      <c r="W102" s="2" t="s">
+      <c r="W104" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X104" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="R105" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S105" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="V105" s="6">
+        <v>3</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X105" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="K106" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="R106" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="S106" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="V106" s="6">
+        <v>3</v>
+      </c>
+      <c r="W106" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X106" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="R107" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="S107" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="V107" s="6">
+        <v>3</v>
+      </c>
+      <c r="W107" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X107" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="K108" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="R108" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="V108" s="6">
+        <v>3</v>
+      </c>
+      <c r="W108" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X108" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="X102" s="2" t="s">
+      <c r="B109" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="V109" s="5">
+        <v>2</v>
+      </c>
+      <c r="W109" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X109" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -6722,101 +7073,111 @@
     <hyperlink ref="K64" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
     <hyperlink ref="K65" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
     <hyperlink ref="K66" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="K67" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="K68" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="K69" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="K70" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="K71" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="K72" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="K73" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="K74" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="K75" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="K76" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="K77" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="K78" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="K79" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="K80" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="K81" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="K82" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="K92" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="K93" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K94" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="K95" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="K96" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="K97" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K98" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K99" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K100" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K101" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K102" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="K3" r:id="rId48" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
-    <hyperlink ref="K4" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
-    <hyperlink ref="K5" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
-    <hyperlink ref="K6" r:id="rId51" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
-    <hyperlink ref="K7" r:id="rId52" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
-    <hyperlink ref="K8" r:id="rId53" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
-    <hyperlink ref="K9" r:id="rId54" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
-    <hyperlink ref="K10" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
-    <hyperlink ref="K18" r:id="rId56" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
-    <hyperlink ref="K19" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
-    <hyperlink ref="K21" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
-    <hyperlink ref="K20" r:id="rId59" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
-    <hyperlink ref="K22" r:id="rId60" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
-    <hyperlink ref="M18" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
-    <hyperlink ref="K23" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
-    <hyperlink ref="K27" r:id="rId63" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
-    <hyperlink ref="K28" r:id="rId64" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
-    <hyperlink ref="M28" r:id="rId65" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
-    <hyperlink ref="K29" r:id="rId66" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
-    <hyperlink ref="K30" r:id="rId67" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
-    <hyperlink ref="K31" r:id="rId68" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
-    <hyperlink ref="K32" r:id="rId69" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
-    <hyperlink ref="K11" r:id="rId70" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
-    <hyperlink ref="K12" r:id="rId71" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
-    <hyperlink ref="K13" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
-    <hyperlink ref="K14" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
-    <hyperlink ref="K15" r:id="rId74" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
-    <hyperlink ref="K16" r:id="rId75" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
-    <hyperlink ref="K34" r:id="rId76" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
-    <hyperlink ref="K35" r:id="rId77" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
-    <hyperlink ref="K36" r:id="rId78" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
-    <hyperlink ref="K37" r:id="rId79" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
-    <hyperlink ref="K38" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
-    <hyperlink ref="K39" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
-    <hyperlink ref="K40" r:id="rId82" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
-    <hyperlink ref="K41" r:id="rId83" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
-    <hyperlink ref="K54" r:id="rId84" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
-    <hyperlink ref="K55" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
-    <hyperlink ref="M55" r:id="rId86" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
-    <hyperlink ref="K56" r:id="rId87" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
-    <hyperlink ref="M56" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
-    <hyperlink ref="K57" r:id="rId89" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
-    <hyperlink ref="K46" r:id="rId90" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
-    <hyperlink ref="K47" r:id="rId91" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
-    <hyperlink ref="K50" r:id="rId92" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
-    <hyperlink ref="K49" r:id="rId93" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
-    <hyperlink ref="K48" r:id="rId94" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
-    <hyperlink ref="K51" r:id="rId95" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
-    <hyperlink ref="K84" r:id="rId96" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
-    <hyperlink ref="M85" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
-    <hyperlink ref="K85" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
-    <hyperlink ref="K86" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
-    <hyperlink ref="K87" r:id="rId100" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
-    <hyperlink ref="K91" r:id="rId101" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
-    <hyperlink ref="M88" r:id="rId102" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
-    <hyperlink ref="K88" r:id="rId103" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
-    <hyperlink ref="M90" r:id="rId104" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
-    <hyperlink ref="K89" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
-    <hyperlink ref="K90" r:id="rId106" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
-    <hyperlink ref="M83" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
-    <hyperlink ref="K83" r:id="rId108" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
-    <hyperlink ref="O83" r:id="rId109" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
-    <hyperlink ref="M86" r:id="rId110" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
-    <hyperlink ref="M75" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
-    <hyperlink ref="H52" r:id="rId112" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
-    <hyperlink ref="F52" r:id="rId113" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
-    <hyperlink ref="M52" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
-    <hyperlink ref="O52" r:id="rId115" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
+    <hyperlink ref="K75" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K76" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="K77" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K78" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K79" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K80" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="K81" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K82" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="K83" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K84" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="K85" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K86" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="K87" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K88" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K89" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K99" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K100" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K101" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K102" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K103" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="K104" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K105" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K106" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K107" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K108" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K109" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="K3" r:id="rId47" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
+    <hyperlink ref="K4" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
+    <hyperlink ref="K5" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
+    <hyperlink ref="K6" r:id="rId50" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
+    <hyperlink ref="K7" r:id="rId51" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
+    <hyperlink ref="K8" r:id="rId52" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
+    <hyperlink ref="K9" r:id="rId53" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
+    <hyperlink ref="K10" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
+    <hyperlink ref="K18" r:id="rId55" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
+    <hyperlink ref="K19" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
+    <hyperlink ref="K21" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
+    <hyperlink ref="K20" r:id="rId58" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
+    <hyperlink ref="K22" r:id="rId59" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
+    <hyperlink ref="M18" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
+    <hyperlink ref="K23" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
+    <hyperlink ref="K27" r:id="rId62" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
+    <hyperlink ref="K28" r:id="rId63" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
+    <hyperlink ref="M28" r:id="rId64" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
+    <hyperlink ref="K29" r:id="rId65" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
+    <hyperlink ref="K30" r:id="rId66" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
+    <hyperlink ref="K31" r:id="rId67" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
+    <hyperlink ref="K32" r:id="rId68" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
+    <hyperlink ref="K11" r:id="rId69" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
+    <hyperlink ref="K12" r:id="rId70" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
+    <hyperlink ref="K13" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
+    <hyperlink ref="K14" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
+    <hyperlink ref="K15" r:id="rId73" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
+    <hyperlink ref="K16" r:id="rId74" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
+    <hyperlink ref="K34" r:id="rId75" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
+    <hyperlink ref="K35" r:id="rId76" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
+    <hyperlink ref="K36" r:id="rId77" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
+    <hyperlink ref="K37" r:id="rId78" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
+    <hyperlink ref="K38" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
+    <hyperlink ref="K39" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
+    <hyperlink ref="K40" r:id="rId81" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
+    <hyperlink ref="K41" r:id="rId82" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
+    <hyperlink ref="K54" r:id="rId83" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
+    <hyperlink ref="K55" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
+    <hyperlink ref="M55" r:id="rId85" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
+    <hyperlink ref="K56" r:id="rId86" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
+    <hyperlink ref="M56" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
+    <hyperlink ref="K57" r:id="rId88" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
+    <hyperlink ref="K46" r:id="rId89" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
+    <hyperlink ref="K47" r:id="rId90" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
+    <hyperlink ref="K50" r:id="rId91" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
+    <hyperlink ref="K49" r:id="rId92" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
+    <hyperlink ref="K48" r:id="rId93" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
+    <hyperlink ref="K51" r:id="rId94" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
+    <hyperlink ref="K91" r:id="rId95" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
+    <hyperlink ref="M92" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
+    <hyperlink ref="K92" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
+    <hyperlink ref="K93" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
+    <hyperlink ref="K94" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
+    <hyperlink ref="K98" r:id="rId100" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
+    <hyperlink ref="M95" r:id="rId101" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
+    <hyperlink ref="K95" r:id="rId102" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
+    <hyperlink ref="M97" r:id="rId103" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
+    <hyperlink ref="K96" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
+    <hyperlink ref="K97" r:id="rId105" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
+    <hyperlink ref="M90" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
+    <hyperlink ref="K90" r:id="rId107" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
+    <hyperlink ref="O90" r:id="rId108" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
+    <hyperlink ref="M93" r:id="rId109" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
+    <hyperlink ref="M82" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
+    <hyperlink ref="H52" r:id="rId111" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
+    <hyperlink ref="F52" r:id="rId112" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
+    <hyperlink ref="M52" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
+    <hyperlink ref="O52" r:id="rId114" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
+    <hyperlink ref="M67" r:id="rId115" xr:uid="{D4E31208-1729-474B-8613-04CAF9B8C025}"/>
+    <hyperlink ref="K67" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F8517-F853-4BC2-B1A3-2FAE2DAB6C9A}"/>
+    <hyperlink ref="K68" r:id="rId117" xr:uid="{61D85FE2-8DE3-4825-8491-0FE8BB47E3E1}"/>
+    <hyperlink ref="K69" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F36EF-2268-403C-A6B7-E58ACFE0642D}"/>
+    <hyperlink ref="K70" r:id="rId119" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B578D29-DC36-40D0-9947-A27ECB77A9CF}"/>
+    <hyperlink ref="K71" r:id="rId120" xr:uid="{57B652B7-7292-4EAC-B631-5C96CD2691B8}"/>
+    <hyperlink ref="K72" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9E7BF8E-41C2-4812-BC18-7E39D390B4DB}"/>
+    <hyperlink ref="H73" r:id="rId122" xr:uid="{0D8B79CB-4807-4139-98AD-96CFF7161C32}"/>
+    <hyperlink ref="K73" r:id="rId123" xr:uid="{B472E107-96D8-49AE-8D43-42D5D303C124}"/>
+    <hyperlink ref="M73" r:id="rId124" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9F3C81B0-62F8-4827-8155-5167D81363EB}"/>
+    <hyperlink ref="K74" r:id="rId125" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{841BFC94-91FA-4580-9546-612A91A5451F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9202C9C0-ABB2-4C88-AB77-72056003D8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1405789F-8AAE-414E-9C84-B9B6AA361792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="782">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -857,18 +857,12 @@
     <t>"Le Baptême du Christ"</t>
   </si>
   <si>
-    <t>"Bacchus"</t>
-  </si>
-  <si>
     <t>"Tombeau d'Henri VII et Élisabeth d'York"</t>
   </si>
   <si>
     <t>"La Nature"</t>
   </si>
   <si>
-    <t>"Monument funéraire d'Alessandro Vittoria"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1019,9 +1013,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4b/N%C3%BCrnberg_St._Sebald_Sebaldusgrab_01.jpg/960px-N%C3%BCrnberg_St._Sebald_Sebaldusgrab_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Alessandro_Vittoria_Tombeau.jpg/960px-Alessandro_Vittoria_Tombeau.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>Marbre et bronze</t>
   </si>
   <si>
@@ -2064,6 +2055,330 @@
   </si>
   <si>
     <t>Chapelle  Bandinelli</t>
+  </si>
+  <si>
+    <t>BUONARROTI</t>
+  </si>
+  <si>
+    <t>1501-1504</t>
+  </si>
+  <si>
+    <t>Les galeries de l'Académie</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Sculpture</t>
+  </si>
+  <si>
+    <t>Bruges</t>
+  </si>
+  <si>
+    <t>Église Notre-Dame</t>
+  </si>
+  <si>
+    <t>Vierge de Bruges</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/3/37/Madonna_michelangelo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1503-1505</t>
+  </si>
+  <si>
+    <t>Tondo Pitti</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg/1280px-Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>1505-1545</t>
+  </si>
+  <si>
+    <t>Basilique Saint-Pierre-aux-Liens</t>
+  </si>
+  <si>
+    <t>Tombeau de Jules II</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/%27Moses%27_by_Michelangelo_JBU010.jpg/960px-%27Moses%27_by_Michelangelo_JBU010.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1513</t>
+  </si>
+  <si>
+    <t>L'Esclave mourant</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>L'Esclave rebelle</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/%27Rebellious_Slave%27_Michelangelo_JBU81.jpg/960px-%27Rebellious_Slave%27_Michelangelo_JBU81.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1519-1521</t>
+  </si>
+  <si>
+    <t>Basilique de la Minerve</t>
+  </si>
+  <si>
+    <t>Le Christ de la Minerve</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>1520-1534</t>
+  </si>
+  <si>
+    <t>Sagrestia Nuova (Chapelles Médiciennes)</t>
+  </si>
+  <si>
+    <t>Tombeau de Laurent de Médicis</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Ensemble sculptural</t>
+  </si>
+  <si>
+    <t>Tombeau de Julien de Médicis</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/3/39/Tomb_of_Lorenzo_the_Magnificent_and_Giuliano_de%27_Medici%2C_Sagrestia_Nuova%2C_Medici_Chapels%2C_San_Lorenzo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>1547-1555</t>
+  </si>
+  <si>
+    <t>Pietà Bandini</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1511-1518</t>
+  </si>
+  <si>
+    <t>Saint Jacques</t>
+  </si>
+  <si>
+    <t>San Jacopo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg/960px-Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue</t>
+  </si>
+  <si>
+    <t>230 cm environ</t>
+  </si>
+  <si>
+    <t>1537-1541</t>
+  </si>
+  <si>
+    <t>Loggetta de la Place Saint-Marc</t>
+  </si>
+  <si>
+    <t>Minerve</t>
+  </si>
+  <si>
+    <t>Minerva</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Loggetta_Sansovino_Minerva_Venezia.jpg/960px-Loggetta_Sansovino_Minerva_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>149 cm</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Apollo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Loggetta_Sansovino_Apollo_Venezia.jpg/960px-Loggetta_Sansovino_Apollo_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>147 cm</t>
+  </si>
+  <si>
+    <t>Mercure</t>
+  </si>
+  <si>
+    <t>Mercurio</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Loggetta_Sansovino_Mercurio_Venezia.jpg/960px-Loggetta_Sansovino_Mercurio_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>148 cm</t>
+  </si>
+  <si>
+    <t>La Paix</t>
+  </si>
+  <si>
+    <t>La Pace</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Loggetta_Sansovino_allegoria_Pace_Venezia.jpg/960px-Loggetta_Sansovino_allegoria_Pace_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>150 cm</t>
+  </si>
+  <si>
+    <t>1554-1566</t>
+  </si>
+  <si>
+    <t>Escalier des Géants, Palais des Doges</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue monumentale</t>
+  </si>
+  <si>
+    <t>300 cm environ</t>
+  </si>
+  <si>
+    <t>Neptune</t>
+  </si>
+  <si>
+    <t>Nettuno</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a0/Jacopo_sansovino%2C_nettuno%2C_1554%2C_04.jpg/330px-Jacopo_sansovino%2C_nettuno%2C_1554%2C_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument funéraire d'Alessandro Vittoria</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Alessandro_Vittoria_Tombeau.jpg/960px-Alessandro_Vittoria_Tombeau.jpg</t>
+  </si>
+  <si>
+    <t>1564-1565</t>
+  </si>
+  <si>
+    <t>Église San Francesco della Vigna</t>
+  </si>
+  <si>
+    <t>Chapelle Montefeltro</t>
+  </si>
+  <si>
+    <t>Saint Roch</t>
+  </si>
+  <si>
+    <t>San Rocco</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>San Sebastiano</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>1576</t>
+  </si>
+  <si>
+    <t>Trevise</t>
+  </si>
+  <si>
+    <t>Cathédrale  de Saint Pierre Apôtre</t>
+  </si>
+  <si>
+    <t>San Giovanni Battista</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/c8/Alessandro_vittoria%2C_san_giovanni_battista%2C_1565_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Statue d'autel</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>vers 1580</t>
+  </si>
+  <si>
+    <t>Basilique des Saints Jean et Paul</t>
+  </si>
+  <si>
+    <t>Saint Jérôme</t>
+  </si>
+  <si>
+    <t>San Girolamo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1583-1584</t>
+  </si>
+  <si>
+    <t>Saint Zacharie</t>
+  </si>
+  <si>
+    <t>San Zaccaria</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Alessandro_Vittoria%2C_San_Zaccaria_%281543%29.jpg/960px-Alessandro_Vittoria%2C_San_Zaccaria_%281543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2169,7 +2484,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2224,6 +2539,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2529,7 +2845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y109"/>
+  <dimension ref="A1:Y131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -2550,9 +2866,9 @@
     <col min="16" max="16" width="13.5703125" style="2" customWidth="1"/>
     <col min="17" max="17" width="11.5703125" style="2" customWidth="1"/>
     <col min="18" max="18" width="9.140625" style="2"/>
-    <col min="19" max="19" width="9.140625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="5.140625" style="2" customWidth="1"/>
-    <col min="21" max="21" width="5.42578125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="5.140625" style="3" customWidth="1"/>
+    <col min="21" max="21" width="5.42578125" style="3" customWidth="1"/>
     <col min="22" max="22" width="5.28515625" style="3" customWidth="1"/>
     <col min="23" max="23" width="8" style="2" customWidth="1"/>
     <col min="24" max="24" width="6" style="2" customWidth="1"/>
@@ -2614,13 +2930,13 @@
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="3" t="s">
@@ -2718,22 +3034,22 @@
         <v>197</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="S3" s="2">
+        <v>326</v>
+      </c>
+      <c r="S3" s="3">
         <v>560</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
@@ -2750,31 +3066,31 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="R4" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="V4" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
@@ -2791,31 +3107,31 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>368</v>
-      </c>
       <c r="R5" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S5" s="2">
+        <v>328</v>
+      </c>
+      <c r="S5" s="3">
         <v>262</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
@@ -2832,31 +3148,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S6" s="2">
+        <v>328</v>
+      </c>
+      <c r="S6" s="3">
         <v>139</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
@@ -2873,28 +3189,28 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="V7" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
@@ -2911,28 +3227,28 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="V8" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
@@ -2949,28 +3265,28 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>389</v>
-      </c>
       <c r="R9" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
@@ -2987,31 +3303,31 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="K10" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="S10" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="V10" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
@@ -3037,19 +3353,19 @@
         <v>198</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
@@ -3075,19 +3391,19 @@
         <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>23</v>
@@ -3104,31 +3420,31 @@
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>474</v>
-      </c>
       <c r="R13" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>23</v>
@@ -3145,31 +3461,31 @@
         <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>23</v>
@@ -3186,35 +3502,35 @@
         <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="K15" s="7" t="s">
         <v>480</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>483</v>
       </c>
       <c r="M15" s="7"/>
       <c r="Q15" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>23</v>
@@ -3231,7 +3547,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>176</v>
@@ -3240,22 +3556,22 @@
         <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="V16" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>23</v>
@@ -3281,7 +3597,7 @@
         <v>242</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>31</v>
@@ -3313,25 +3629,25 @@
         <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="V18" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
@@ -3348,31 +3664,31 @@
         <v>73</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="V19" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W19" s="2" t="s">
         <v>25</v>
@@ -3389,7 +3705,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>170</v>
@@ -3398,25 +3714,25 @@
         <v>200</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="I20" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="V20" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>25</v>
@@ -3433,28 +3749,28 @@
         <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="S21" s="2">
+        <v>411</v>
+      </c>
+      <c r="S21" s="3">
         <v>78</v>
       </c>
-      <c r="T21" s="2">
+      <c r="T21" s="3">
         <v>75</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
@@ -3471,34 +3787,34 @@
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="R22" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>420</v>
-      </c>
       <c r="V22" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>25</v>
@@ -3515,34 +3831,34 @@
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="K23" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="R23" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>427</v>
-      </c>
       <c r="V23" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>25</v>
@@ -3571,13 +3887,13 @@
         <v>243</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>346</v>
+        <v>328</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="V24" s="4">
         <v>1</v>
@@ -3609,13 +3925,13 @@
         <v>244</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>347</v>
+        <v>327</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="V25" s="6">
         <v>3</v>
@@ -3644,10 +3960,10 @@
         <v>245</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="V26" s="6">
         <v>3</v>
@@ -3676,19 +3992,19 @@
         <v>202</v>
       </c>
       <c r="I27" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q27" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="J27" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="R27" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="V27" s="5">
         <v>2</v>
@@ -3717,25 +4033,25 @@
         <v>202</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="M28" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="R28" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="K28" s="7" t="s">
+      <c r="T28" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="V28" s="5">
         <v>2</v>
@@ -3755,28 +4071,28 @@
         <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="K29" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="V29" s="5">
         <v>2</v>
@@ -3796,25 +4112,25 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="K30" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="R30" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="V30" s="5">
         <v>2</v>
@@ -3843,22 +4159,22 @@
         <v>202</v>
       </c>
       <c r="I31" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="T31" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="V31" s="5">
         <v>2</v>
@@ -3878,25 +4194,25 @@
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="K32" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>463</v>
-      </c>
       <c r="R32" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="V32" s="5">
         <v>2</v>
@@ -3925,10 +4241,10 @@
         <v>246</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="V33" s="6">
         <v>3</v>
@@ -3957,22 +4273,22 @@
         <v>204</v>
       </c>
       <c r="I34" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="J34" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S34" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="V34" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -3989,31 +4305,31 @@
         <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="J35" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="K35" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="R35" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="S35" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="V35" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -4030,31 +4346,31 @@
         <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I36" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="V36" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4074,28 +4390,28 @@
         <v>128</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="K37" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="R37" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="S37" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="V37" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4112,7 +4428,7 @@
         <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>170</v>
@@ -4121,22 +4437,22 @@
         <v>197</v>
       </c>
       <c r="I38" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="V38" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4153,34 +4469,34 @@
         <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I39" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q39" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="R39" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="K39" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>522</v>
-      </c>
       <c r="V39" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4197,31 +4513,31 @@
         <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>525</v>
+        <v>327</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4238,7 +4554,7 @@
         <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>170</v>
@@ -4247,25 +4563,25 @@
         <v>204</v>
       </c>
       <c r="I41" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="J41" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S41" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="V41" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4276,1037 +4592,1154 @@
     </row>
     <row r="42" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>79</v>
+        <v>674</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>129</v>
+        <v>675</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>207</v>
+        <v>676</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>285</v>
+        <v>677</v>
+      </c>
+      <c r="K42" s="22" t="s">
+        <v>678</v>
+      </c>
+      <c r="M42" s="2"/>
+      <c r="Q42" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="V42" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S42" s="3">
+        <v>517</v>
+      </c>
+      <c r="T42" s="3">
+        <v>199</v>
+      </c>
+      <c r="U42" s="3">
+        <v>140</v>
+      </c>
+      <c r="V42" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>79</v>
+        <v>674</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>80</v>
+        <v>674</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>130</v>
+        <v>675</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>170</v>
+        <v>680</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>200</v>
+        <v>681</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>286</v>
+        <v>682</v>
+      </c>
+      <c r="K43" s="22" t="s">
+        <v>683</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="Q43" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S43" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="V43" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S43" s="3">
+        <v>128</v>
+      </c>
+      <c r="T43" s="3">
+        <v>64</v>
+      </c>
+      <c r="U43" s="3">
+        <v>63</v>
+      </c>
+      <c r="V43" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>80</v>
+        <v>674</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>81</v>
+        <v>674</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>131</v>
+        <v>684</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>208</v>
+        <v>362</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>287</v>
+        <v>685</v>
+      </c>
+      <c r="K44" s="22" t="s">
+        <v>686</v>
+      </c>
+      <c r="M44" s="2"/>
+      <c r="Q44" s="2" t="s">
+        <v>481</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S44" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="V44" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="V44" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>81</v>
+        <v>674</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>132</v>
+        <v>689</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>209</v>
+        <v>690</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>288</v>
+        <v>691</v>
+      </c>
+      <c r="K45" s="22" t="s">
+        <v>692</v>
+      </c>
+      <c r="M45" s="2"/>
+      <c r="Q45" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="V45" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S45" s="3">
+        <v>780</v>
+      </c>
+      <c r="T45" s="3">
+        <v>640</v>
+      </c>
+      <c r="V45" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>82</v>
+        <v>674</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>133</v>
+        <v>693</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>289</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="K46" s="22" t="s">
+        <v>695</v>
+      </c>
+      <c r="M46" s="2"/>
       <c r="Q46" s="2" t="s">
-        <v>431</v>
+        <v>679</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="V46" s="5">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="S46" s="3">
+        <v>228</v>
+      </c>
+      <c r="T46" s="3">
+        <v>72</v>
+      </c>
+      <c r="U46" s="3">
+        <v>53</v>
+      </c>
+      <c r="V46" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>552</v>
+        <v>693</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>555</v>
+        <v>696</v>
+      </c>
+      <c r="K47" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="Q47" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="V47" s="5">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="T47" s="3">
+        <v>49</v>
+      </c>
+      <c r="U47" s="3">
+        <v>75</v>
+      </c>
+      <c r="V47" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>557</v>
+        <v>698</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>558</v>
+        <v>175</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>560</v>
+        <v>699</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>563</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="K48" s="22" t="s">
+        <v>701</v>
+      </c>
+      <c r="M48" s="2"/>
       <c r="Q48" s="2" t="s">
-        <v>431</v>
+        <v>679</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="V48" s="5">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="T48" s="3">
+        <v>75</v>
+      </c>
+      <c r="U48" s="3">
+        <v>60</v>
+      </c>
+      <c r="V48" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>565</v>
+        <v>703</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>566</v>
+        <v>704</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>568</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="K49" s="22" t="s">
+        <v>706</v>
+      </c>
+      <c r="M49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>431</v>
+        <v>707</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="V49" s="5">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="S49" s="3">
+        <v>650</v>
+      </c>
+      <c r="T49" s="3">
+        <v>470</v>
+      </c>
+      <c r="V49" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>571</v>
+        <v>703</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>572</v>
+        <v>170</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>574</v>
+        <v>704</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>577</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="K50" s="22" t="s">
+        <v>709</v>
+      </c>
+      <c r="M50" s="2"/>
       <c r="Q50" s="2" t="s">
-        <v>578</v>
+        <v>707</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="V50" s="5">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="V50" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>364</v>
+        <v>712</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>579</v>
+        <v>420</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>582</v>
+        <v>713</v>
+      </c>
+      <c r="K51" s="22" t="s">
+        <v>714</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="Q51" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="V51" s="5">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="S51" s="3">
+        <v>277</v>
+      </c>
+      <c r="T51" s="3">
+        <v>138</v>
+      </c>
+      <c r="U51" s="3">
+        <v>125</v>
+      </c>
+      <c r="V51" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>83</v>
+        <v>674</v>
       </c>
     </row>
     <row r="52" spans="1:25" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>632</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>631</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>630</v>
-      </c>
-      <c r="J52" s="11"/>
-      <c r="K52" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="L52" s="11"/>
-      <c r="M52" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="N52" s="11"/>
-      <c r="O52" s="13" t="s">
-        <v>634</v>
-      </c>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
-      <c r="R52" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="S52" s="11">
-        <v>182</v>
-      </c>
-      <c r="T52" s="11"/>
-      <c r="U52" s="11"/>
-      <c r="V52" s="12">
+      <c r="A52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="6">
         <v>3</v>
       </c>
-      <c r="W52" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="X52" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y52" s="11"/>
+      <c r="W52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y52" s="2"/>
     </row>
     <row r="53" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>31</v>
+        <v>328</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="V53" s="6">
         <v>3</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>532</v>
+        <v>249</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S54" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="V54" s="4" t="s">
-        <v>397</v>
+        <v>328</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="V54" s="6">
+        <v>3</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>534</v>
+        <v>132</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>535</v>
+        <v>209</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="M55" s="7" t="s">
-        <v>539</v>
+        <v>286</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="V55" s="4" t="s">
-        <v>397</v>
+        <v>328</v>
+      </c>
+      <c r="V55" s="6">
+        <v>3</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>540</v>
+        <v>133</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>535</v>
+        <v>202</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="M56" s="7" t="s">
-        <v>544</v>
+        <v>287</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="V56" s="4" t="s">
-        <v>397</v>
+        <v>330</v>
+      </c>
+      <c r="V56" s="5">
+        <v>2</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="S57" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="V57" s="4" t="s">
-        <v>397</v>
+      <c r="S57" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="V57" s="5">
+        <v>2</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>136</v>
+        <v>554</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>173</v>
+        <v>555</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>206</v>
+        <v>556</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>557</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>252</v>
+        <v>558</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>559</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>292</v>
+        <v>560</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S58" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="V58" s="4">
-        <v>1</v>
+        <v>561</v>
+      </c>
+      <c r="V58" s="5">
+        <v>2</v>
       </c>
       <c r="W58" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>137</v>
+        <v>562</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>212</v>
+        <v>563</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>253</v>
+        <v>622</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>564</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>293</v>
+        <v>565</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="V59" s="6">
-        <v>3</v>
+        <v>566</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="V59" s="5">
+        <v>2</v>
       </c>
       <c r="W59" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>138</v>
+        <v>568</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>175</v>
+        <v>569</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>213</v>
+        <v>570</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>571</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>254</v>
+        <v>572</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>573</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>294</v>
+        <v>574</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>575</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="V60" s="5">
         <v>2</v>
       </c>
       <c r="W60" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>139</v>
+        <v>361</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>214</v>
+        <v>576</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>255</v>
+        <v>577</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>578</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>295</v>
+        <v>579</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="V61" s="6">
+        <v>330</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="V61" s="5">
+        <v>2</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X61" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>629</v>
+      </c>
+      <c r="G62" s="18"/>
+      <c r="H62" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="J62" s="11"/>
+      <c r="K62" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="L62" s="11"/>
+      <c r="M62" s="14" t="s">
+        <v>630</v>
+      </c>
+      <c r="N62" s="11"/>
+      <c r="O62" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="P62" s="11"/>
+      <c r="Q62" s="11"/>
+      <c r="R62" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="S62" s="12">
+        <v>182</v>
+      </c>
+      <c r="T62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12">
         <v>3</v>
       </c>
-      <c r="W61" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X61" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="K62" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="R62" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="V62" s="6">
-        <v>3</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X62" s="2" t="s">
-        <v>89</v>
-      </c>
+      <c r="W62" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="X62" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y62" s="11"/>
     </row>
     <row r="63" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>335</v>
+        <v>31</v>
       </c>
       <c r="V63" s="6">
         <v>3</v>
       </c>
       <c r="W63" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>257</v>
+        <v>528</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="V64" s="5">
-        <v>2</v>
+        <v>327</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="V64" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W64" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>142</v>
+        <v>531</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>218</v>
+        <v>532</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>258</v>
+        <v>533</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>534</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>299</v>
+        <v>535</v>
+      </c>
+      <c r="M65" s="7" t="s">
+        <v>536</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="V65" s="6">
-        <v>3</v>
+        <v>331</v>
+      </c>
+      <c r="V65" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>143</v>
+        <v>537</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>219</v>
+        <v>532</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>623</v>
+        <v>538</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>539</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>300</v>
+        <v>540</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>541</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="V66" s="5">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="V66" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W66" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>635</v>
+        <v>542</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="K67" s="19" t="s">
-        <v>637</v>
-      </c>
-      <c r="L67" s="8"/>
-      <c r="M67" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q67" s="2" t="s">
-        <v>484</v>
+        <v>543</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>545</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S67" s="3">
-        <v>73</v>
-      </c>
-      <c r="T67" s="3">
-        <v>195</v>
-      </c>
-      <c r="U67" s="3">
-        <v>12</v>
-      </c>
-      <c r="V67" s="4">
-        <v>1</v>
+        <v>327</v>
+      </c>
+      <c r="S67" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="V67" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>635</v>
+        <v>136</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>173</v>
@@ -5315,435 +5748,313 @@
         <v>206</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="K68" s="19" t="s">
-        <v>639</v>
-      </c>
-      <c r="L68" s="8"/>
-      <c r="M68" s="20"/>
-      <c r="Q68" s="2" t="s">
-        <v>640</v>
+        <v>252</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="S68" s="3">
-        <v>210</v>
-      </c>
-      <c r="T68" s="3">
-        <v>60</v>
-      </c>
-      <c r="U68" s="3">
-        <v>65</v>
+        <v>327</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>348</v>
       </c>
       <c r="V68" s="4">
         <v>1</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="K69" s="19" t="s">
-        <v>644</v>
-      </c>
-      <c r="L69" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="M69" s="20"/>
-      <c r="Q69" s="2" t="s">
-        <v>646</v>
+        <v>253</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>291</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="T69" s="3">
-        <v>182</v>
-      </c>
-      <c r="U69" s="3">
-        <v>7</v>
-      </c>
-      <c r="V69" s="4">
-        <v>1</v>
+        <v>326</v>
+      </c>
+      <c r="V69" s="6">
+        <v>3</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>642</v>
+        <v>138</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="K70" s="19" t="s">
-        <v>649</v>
-      </c>
-      <c r="L70" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="M70" s="20"/>
-      <c r="Q70" s="2" t="s">
-        <v>646</v>
+        <v>254</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>292</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="S70" s="3">
-        <v>79</v>
-      </c>
-      <c r="T70" s="3">
-        <v>56</v>
-      </c>
-      <c r="U70" s="3">
-        <v>11</v>
-      </c>
-      <c r="V70" s="4">
-        <v>1</v>
+      <c r="V70" s="5">
+        <v>2</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>650</v>
+        <v>139</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>651</v>
+        <v>176</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>652</v>
+        <v>214</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="K71" s="19" t="s">
-        <v>654</v>
-      </c>
-      <c r="L71" s="8"/>
-      <c r="M71" s="20"/>
-      <c r="Q71" s="2" t="s">
-        <v>589</v>
+        <v>255</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="S71" s="3">
-        <v>700</v>
-      </c>
-      <c r="T71" s="3">
-        <v>366</v>
-      </c>
-      <c r="U71" s="3">
-        <v>93</v>
-      </c>
-      <c r="V71" s="4">
-        <v>1</v>
+        <v>330</v>
+      </c>
+      <c r="V71" s="6">
+        <v>3</v>
       </c>
       <c r="W71" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>655</v>
+        <v>140</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>657</v>
+        <v>215</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="K72" s="19" t="s">
-        <v>659</v>
-      </c>
-      <c r="L72" s="8"/>
-      <c r="M72" s="20"/>
-      <c r="Q72" s="2" t="s">
-        <v>646</v>
+        <v>621</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S72" s="3">
-        <v>215</v>
-      </c>
-      <c r="T72" s="3">
-        <v>95</v>
-      </c>
-      <c r="U72" s="3">
-        <v>6</v>
-      </c>
-      <c r="V72" s="4">
-        <v>1</v>
+        <v>328</v>
+      </c>
+      <c r="V72" s="6">
+        <v>3</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>660</v>
+        <v>141</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="H73" s="19" t="s">
-        <v>663</v>
+        <v>216</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="K73" s="19" t="s">
-        <v>665</v>
-      </c>
-      <c r="L73" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="M73" s="21" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q73" s="2" t="s">
-        <v>668</v>
+        <v>256</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>295</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S73" s="3">
-        <v>205</v>
-      </c>
-      <c r="T73" s="3">
+        <v>332</v>
+      </c>
+      <c r="V73" s="6">
+        <v>3</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X73" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="U73" s="3">
-        <v>6</v>
-      </c>
-      <c r="V73" s="4">
-        <v>1</v>
-      </c>
-      <c r="W73" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X73" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D74"/>
+        <v>139</v>
+      </c>
       <c r="E74" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>448</v>
+        <v>217</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="J74"/>
-      <c r="K74" s="19" t="s">
-        <v>671</v>
-      </c>
-      <c r="L74" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="M74" s="20"/>
-      <c r="Q74" s="2" t="s">
-        <v>673</v>
+        <v>257</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S74" s="3">
-        <v>80</v>
-      </c>
-      <c r="T74" s="3">
-        <v>202</v>
-      </c>
-      <c r="U74" s="3">
-        <v>8</v>
-      </c>
-      <c r="V74" s="4">
-        <v>1</v>
+        <v>333</v>
+      </c>
+      <c r="S74" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="V74" s="5">
+        <v>2</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="V75" s="4">
+        <v>334</v>
+      </c>
+      <c r="V75" s="6">
         <v>3</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>260</v>
+        <v>620</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S76" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="V76" s="6">
-        <v>3</v>
+        <v>327</v>
+      </c>
+      <c r="V76" s="5">
+        <v>2</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>147</v>
+        <v>632</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>173</v>
@@ -5752,1301 +6063,2369 @@
         <v>206</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="K77" s="7" t="s">
-        <v>304</v>
+        <v>633</v>
+      </c>
+      <c r="K77" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="L77" s="8"/>
+      <c r="M77" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>481</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="S77" s="2">
-        <v>26</v>
-      </c>
-      <c r="T77" s="2">
-        <v>22</v>
-      </c>
-      <c r="U77" s="2">
-        <v>14</v>
-      </c>
-      <c r="V77" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S77" s="3">
+        <v>73</v>
+      </c>
+      <c r="T77" s="3">
+        <v>195</v>
+      </c>
+      <c r="U77" s="3">
+        <v>12</v>
+      </c>
+      <c r="V77" s="4">
+        <v>1</v>
       </c>
       <c r="W77" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>148</v>
+        <v>632</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="K78" s="7" t="s">
-        <v>305</v>
+        <v>635</v>
+      </c>
+      <c r="K78" s="19" t="s">
+        <v>636</v>
+      </c>
+      <c r="L78" s="8"/>
+      <c r="M78" s="20"/>
+      <c r="Q78" s="2" t="s">
+        <v>637</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V78" s="6">
-        <v>3</v>
+        <v>638</v>
+      </c>
+      <c r="S78" s="3">
+        <v>210</v>
+      </c>
+      <c r="T78" s="3">
+        <v>60</v>
+      </c>
+      <c r="U78" s="3">
+        <v>65</v>
+      </c>
+      <c r="V78" s="4">
+        <v>1</v>
       </c>
       <c r="W78" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>130</v>
+        <v>639</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>306</v>
+        <v>640</v>
+      </c>
+      <c r="K79" s="19" t="s">
+        <v>641</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="M79" s="20"/>
+      <c r="Q79" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="V79" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S79" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="T79" s="3">
+        <v>182</v>
+      </c>
+      <c r="U79" s="3">
+        <v>7</v>
+      </c>
+      <c r="V79" s="4">
+        <v>1</v>
       </c>
       <c r="W79" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="X79" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>149</v>
+        <v>639</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>307</v>
+        <v>645</v>
+      </c>
+      <c r="K80" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="M80" s="20"/>
+      <c r="Q80" s="2" t="s">
+        <v>643</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="V80" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S80" s="3">
+        <v>79</v>
+      </c>
+      <c r="T80" s="3">
+        <v>56</v>
+      </c>
+      <c r="U80" s="3">
+        <v>11</v>
+      </c>
+      <c r="V80" s="4">
+        <v>1</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>150</v>
+        <v>647</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>175</v>
+        <v>648</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>224</v>
+        <v>649</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="K81" s="7" t="s">
-        <v>308</v>
+        <v>650</v>
+      </c>
+      <c r="K81" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="L81" s="8"/>
+      <c r="M81" s="20"/>
+      <c r="Q81" s="2" t="s">
+        <v>586</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="V81" s="6">
-        <v>3</v>
+        <v>338</v>
+      </c>
+      <c r="S81" s="3">
+        <v>700</v>
+      </c>
+      <c r="T81" s="3">
+        <v>366</v>
+      </c>
+      <c r="U81" s="3">
+        <v>93</v>
+      </c>
+      <c r="V81" s="4">
+        <v>1</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B82" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C82" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="E82" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="J82" s="15"/>
-      <c r="K82" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="L82" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="M82" s="16" t="s">
-        <v>628</v>
-      </c>
-      <c r="N82" s="15"/>
-      <c r="O82" s="15"/>
-      <c r="P82" s="15"/>
-      <c r="Q82" s="15"/>
-      <c r="R82" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="S82" s="15"/>
-      <c r="T82" s="15"/>
-      <c r="U82" s="15"/>
-      <c r="V82" s="17">
-        <v>3</v>
-      </c>
-      <c r="W82" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="X82" s="15" t="s">
-        <v>102</v>
+      <c r="A82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="K82" s="19" t="s">
+        <v>656</v>
+      </c>
+      <c r="L82" s="8"/>
+      <c r="M82" s="20"/>
+      <c r="Q82" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="R82" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S82" s="3">
+        <v>215</v>
+      </c>
+      <c r="T82" s="3">
+        <v>95</v>
+      </c>
+      <c r="U82" s="3">
+        <v>6</v>
+      </c>
+      <c r="V82" s="4">
+        <v>1</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>152</v>
+        <v>657</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>226</v>
+        <v>658</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="H83" s="19" t="s">
+        <v>660</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="K83" s="7" t="s">
-        <v>310</v>
+        <v>661</v>
+      </c>
+      <c r="K83" s="19" t="s">
+        <v>662</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="M83" s="21" t="s">
+        <v>664</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>665</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="V83" s="5">
-        <v>2</v>
+        <v>31</v>
+      </c>
+      <c r="S83" s="3">
+        <v>205</v>
+      </c>
+      <c r="T83" s="3">
+        <v>90</v>
+      </c>
+      <c r="U83" s="3">
+        <v>6</v>
+      </c>
+      <c r="V83" s="4">
+        <v>1</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>153</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="D84"/>
       <c r="E84" s="2" t="s">
-        <v>227</v>
+        <v>666</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K84" s="7" t="s">
-        <v>311</v>
+        <v>667</v>
+      </c>
+      <c r="J84"/>
+      <c r="K84" s="19" t="s">
+        <v>668</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="M84" s="20"/>
+      <c r="Q84" s="2" t="s">
+        <v>670</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="V84" s="5">
-        <v>2</v>
+        <v>31</v>
+      </c>
+      <c r="S84" s="3">
+        <v>80</v>
+      </c>
+      <c r="T84" s="3">
+        <v>202</v>
+      </c>
+      <c r="U84" s="3">
+        <v>8</v>
+      </c>
+      <c r="V84" s="4">
+        <v>1</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="V85" s="6">
+        <v>335</v>
+      </c>
+      <c r="V85" s="4">
         <v>3</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>341</v>
+        <v>330</v>
+      </c>
+      <c r="S86" s="3" t="s">
+        <v>350</v>
       </c>
       <c r="V86" s="6">
         <v>3</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>337</v>
+        <v>615</v>
+      </c>
+      <c r="S87" s="3">
+        <v>26</v>
+      </c>
+      <c r="T87" s="3">
+        <v>22</v>
+      </c>
+      <c r="U87" s="3">
+        <v>14</v>
       </c>
       <c r="V87" s="6">
         <v>3</v>
       </c>
       <c r="W87" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>331</v>
+        <v>31</v>
       </c>
       <c r="V88" s="6">
         <v>3</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="V89" s="6">
         <v>3</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>205</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>584</v>
+        <v>263</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="L90" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="M90" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="O90" s="7" t="s">
-        <v>588</v>
+        <v>305</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="S90" s="3">
-        <v>450</v>
-      </c>
-      <c r="T90" s="3">
-        <v>350</v>
-      </c>
-      <c r="U90" s="3">
-        <v>250</v>
-      </c>
-      <c r="V90" s="4" t="s">
-        <v>397</v>
+        <v>328</v>
+      </c>
+      <c r="V90" s="6">
+        <v>3</v>
       </c>
       <c r="W90" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C91" s="9">
-        <v>1583</v>
+        <v>101</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>584</v>
+        <v>619</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="L91" s="8"/>
-      <c r="M91" s="7"/>
-      <c r="O91" s="7"/>
+        <v>306</v>
+      </c>
       <c r="R91" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="S91" s="3">
-        <v>90</v>
-      </c>
-      <c r="T91" s="3">
-        <v>223</v>
-      </c>
-      <c r="U91" s="3">
-        <v>166</v>
-      </c>
-      <c r="V91" s="4">
-        <v>1</v>
+      <c r="V91" s="6">
+        <v>3</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="K92" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="L92" s="8"/>
-      <c r="M92" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="O92" s="8"/>
-      <c r="R92" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S92" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="T92" s="3">
-        <v>75</v>
-      </c>
-      <c r="U92" s="3">
-        <v>75</v>
-      </c>
-      <c r="V92" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="W92" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X92" s="2" t="s">
-        <v>109</v>
+      <c r="A92" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F92" s="15"/>
+      <c r="G92" s="15"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="J92" s="15"/>
+      <c r="K92" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="L92" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="M92" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="N92" s="15"/>
+      <c r="O92" s="15"/>
+      <c r="P92" s="15"/>
+      <c r="Q92" s="15"/>
+      <c r="R92" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="S92" s="17"/>
+      <c r="T92" s="17"/>
+      <c r="U92" s="17"/>
+      <c r="V92" s="17">
+        <v>3</v>
+      </c>
+      <c r="W92" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="X92" s="15" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C93" s="9">
-        <v>1586</v>
+        <v>103</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>594</v>
+        <v>265</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="L93" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="M93" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="O93" s="8"/>
+        <v>308</v>
+      </c>
       <c r="R93" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="S93" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="T93" s="3">
-        <v>120</v>
-      </c>
-      <c r="U93" s="3">
-        <v>81</v>
-      </c>
-      <c r="V93" s="4" t="s">
-        <v>397</v>
+        <v>327</v>
+      </c>
+      <c r="V93" s="5">
+        <v>2</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>601</v>
+        <v>266</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="L94" s="8"/>
-      <c r="O94" s="8"/>
+        <v>309</v>
+      </c>
       <c r="R94" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
-      <c r="V94" s="4" t="s">
-        <v>397</v>
+        <v>337</v>
+      </c>
+      <c r="V94" s="5">
+        <v>2</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>603</v>
+        <v>154</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>604</v>
+        <v>267</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="L95" s="8"/>
-      <c r="M95" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="O95" s="8"/>
+        <v>310</v>
+      </c>
       <c r="R95" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S95" s="3">
-        <v>83</v>
-      </c>
-      <c r="T95" s="3">
-        <v>191</v>
-      </c>
-      <c r="U95" s="3">
-        <v>49</v>
-      </c>
-      <c r="V95" s="4" t="s">
-        <v>397</v>
+        <v>327</v>
+      </c>
+      <c r="V95" s="6">
+        <v>3</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>607</v>
+        <v>126</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>608</v>
+        <v>268</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="L96" s="8"/>
-      <c r="O96" s="8"/>
+        <v>311</v>
+      </c>
       <c r="R96" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S96" s="3">
-        <v>140</v>
-      </c>
-      <c r="T96" s="3">
-        <v>210</v>
-      </c>
-      <c r="U96" s="3">
-        <v>80</v>
-      </c>
-      <c r="V96" s="4" t="s">
-        <v>397</v>
+        <v>338</v>
+      </c>
+      <c r="V96" s="6">
+        <v>3</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C97" s="9">
-        <v>1570</v>
+        <v>106</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>610</v>
+        <v>188</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>611</v>
+        <v>230</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>612</v>
+        <v>269</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="L97" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="M97" s="7" t="s">
-        <v>615</v>
-      </c>
-      <c r="O97" s="8"/>
+        <v>312</v>
+      </c>
       <c r="R97" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S97" s="3">
-        <v>96</v>
-      </c>
-      <c r="T97" s="3">
-        <v>25</v>
-      </c>
-      <c r="U97" s="3">
-        <v>18</v>
-      </c>
-      <c r="V97" s="4">
-        <v>1</v>
+        <v>334</v>
+      </c>
+      <c r="V97" s="6">
+        <v>3</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>616</v>
+        <v>156</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>617</v>
+        <v>231</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="L98" s="8"/>
-      <c r="O98" s="8"/>
+        <v>313</v>
+      </c>
       <c r="R98" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S98" s="3">
-        <v>159</v>
-      </c>
-      <c r="T98" s="3">
-        <v>120</v>
-      </c>
-      <c r="U98" s="3">
-        <v>81</v>
-      </c>
-      <c r="V98" s="4" t="s">
-        <v>397</v>
+        <v>328</v>
+      </c>
+      <c r="V98" s="6">
+        <v>3</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S99" s="2">
-        <v>43</v>
-      </c>
-      <c r="T99" s="2">
-        <v>180</v>
-      </c>
-      <c r="U99" s="2">
-        <v>60</v>
+        <v>339</v>
       </c>
       <c r="V99" s="6">
         <v>3</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>272</v>
+        <v>581</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>319</v>
+        <v>582</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="M100" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="O100" s="7" t="s">
+        <v>585</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V100" s="6">
-        <v>3</v>
+        <v>326</v>
+      </c>
+      <c r="S100" s="3">
+        <v>450</v>
+      </c>
+      <c r="T100" s="3">
+        <v>350</v>
+      </c>
+      <c r="U100" s="3">
+        <v>250</v>
+      </c>
+      <c r="V100" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>161</v>
+        <v>109</v>
+      </c>
+      <c r="C101" s="9">
+        <v>1583</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>620</v>
+        <v>581</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>320</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="L101" s="8"/>
+      <c r="M101" s="7"/>
+      <c r="O101" s="7"/>
       <c r="R101" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="V101" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S101" s="3">
+        <v>90</v>
+      </c>
+      <c r="T101" s="3">
+        <v>223</v>
+      </c>
+      <c r="U101" s="3">
+        <v>166</v>
+      </c>
+      <c r="V101" s="4">
+        <v>1</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>273</v>
+        <v>587</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>321</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="L102" s="8"/>
+      <c r="M102" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="O102" s="8"/>
       <c r="R102" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="V102" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="T102" s="3">
+        <v>75</v>
+      </c>
+      <c r="U102" s="3">
+        <v>75</v>
+      </c>
+      <c r="V102" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>163</v>
+        <v>109</v>
+      </c>
+      <c r="C103" s="9">
+        <v>1586</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>274</v>
+        <v>591</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>322</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="L103" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="M103" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="O103" s="8"/>
       <c r="R103" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S103" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="V103" s="4">
-        <v>1</v>
+        <v>595</v>
+      </c>
+      <c r="S103" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="T103" s="3">
+        <v>120</v>
+      </c>
+      <c r="U103" s="3">
+        <v>81</v>
+      </c>
+      <c r="V103" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W103" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>164</v>
+        <v>597</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>275</v>
+        <v>598</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>323</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="L104" s="8"/>
+      <c r="O104" s="8"/>
       <c r="R104" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="V104" s="5">
-        <v>2</v>
+        <v>328</v>
+      </c>
+      <c r="S104" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="V104" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>165</v>
+        <v>600</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>276</v>
+        <v>601</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>324</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="L105" s="8"/>
+      <c r="M105" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="O105" s="8"/>
       <c r="R105" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="S105" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="V105" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S105" s="3">
+        <v>83</v>
+      </c>
+      <c r="T105" s="3">
+        <v>191</v>
+      </c>
+      <c r="U105" s="3">
+        <v>49</v>
+      </c>
+      <c r="V105" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="X105" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>166</v>
+        <v>604</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>325</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="L106" s="8"/>
+      <c r="O106" s="8"/>
       <c r="R106" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S106" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="V106" s="6">
-        <v>3</v>
+        <v>327</v>
+      </c>
+      <c r="S106" s="3">
+        <v>140</v>
+      </c>
+      <c r="T106" s="3">
+        <v>210</v>
+      </c>
+      <c r="U106" s="3">
+        <v>80</v>
+      </c>
+      <c r="V106" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W106" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="X106" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>167</v>
+        <v>109</v>
+      </c>
+      <c r="C107" s="9">
+        <v>1570</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>195</v>
+        <v>607</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>239</v>
+        <v>608</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>243</v>
+        <v>609</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>326</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="M107" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="O107" s="8"/>
       <c r="R107" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S107" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="V107" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S107" s="3">
+        <v>96</v>
+      </c>
+      <c r="T107" s="3">
+        <v>25</v>
+      </c>
+      <c r="U107" s="3">
+        <v>18</v>
+      </c>
+      <c r="V107" s="4">
+        <v>1</v>
       </c>
       <c r="W107" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="X107" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>168</v>
+        <v>613</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>240</v>
+        <v>614</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>621</v>
+        <v>591</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>327</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="L108" s="8"/>
+      <c r="O108" s="8"/>
       <c r="R108" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="V108" s="6">
-        <v>3</v>
+        <v>328</v>
+      </c>
+      <c r="S108" s="3">
+        <v>159</v>
+      </c>
+      <c r="T108" s="3">
+        <v>120</v>
+      </c>
+      <c r="U108" s="3">
+        <v>81</v>
+      </c>
+      <c r="V108" s="4" t="s">
+        <v>394</v>
       </c>
       <c r="W108" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S109" s="3">
+        <v>43</v>
+      </c>
+      <c r="T109" s="3">
+        <v>180</v>
+      </c>
+      <c r="U109" s="3">
+        <v>60</v>
+      </c>
+      <c r="V109" s="6">
+        <v>3</v>
+      </c>
+      <c r="W109" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X109" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="K110" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="R110" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V110" s="6">
+        <v>3</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X110" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="K111" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="R111" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="V111" s="6">
+        <v>3</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X111" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="K112" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="R112" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="V112" s="6">
+        <v>3</v>
+      </c>
+      <c r="W112" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X112" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="K113" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="M113" s="2"/>
+      <c r="Q113" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S113" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="T113" s="2"/>
+      <c r="U113" s="2"/>
+      <c r="V113" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="W113" t="s">
+        <v>65</v>
+      </c>
+      <c r="X113" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y113"/>
+    </row>
+    <row r="114" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="K114" s="22" t="s">
+        <v>724</v>
+      </c>
+      <c r="M114" s="2"/>
+      <c r="Q114" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R114" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S114" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="T114" s="2"/>
+      <c r="U114" s="2"/>
+      <c r="V114" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="W114" t="s">
+        <v>65</v>
+      </c>
+      <c r="X114" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y114"/>
+    </row>
+    <row r="115" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="K115" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="M115" s="2"/>
+      <c r="Q115" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R115" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S115" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="T115" s="2"/>
+      <c r="U115" s="2"/>
+      <c r="V115" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="W115" t="s">
+        <v>65</v>
+      </c>
+      <c r="X115" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y115"/>
+    </row>
+    <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="K116" s="22" t="s">
+        <v>735</v>
+      </c>
+      <c r="M116" s="2"/>
+      <c r="Q116" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R116" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S116" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="T116" s="2"/>
+      <c r="U116" s="2"/>
+      <c r="V116" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="W116" t="s">
+        <v>65</v>
+      </c>
+      <c r="X116" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y116"/>
+    </row>
+    <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="K117" s="22" t="s">
+        <v>739</v>
+      </c>
+      <c r="M117" s="2"/>
+      <c r="Q117" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R117" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S117" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="T117" s="2"/>
+      <c r="U117" s="2"/>
+      <c r="V117" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="W117" t="s">
+        <v>65</v>
+      </c>
+      <c r="X117" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y117"/>
+    </row>
+    <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="K118" s="22" t="s">
+        <v>743</v>
+      </c>
+      <c r="M118" s="2"/>
+      <c r="Q118" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R118" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S118" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="T118" s="2"/>
+      <c r="U118" s="2"/>
+      <c r="V118" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="W118" t="s">
+        <v>65</v>
+      </c>
+      <c r="X118" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y118"/>
+    </row>
+    <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="K119" s="22" t="s">
+        <v>747</v>
+      </c>
+      <c r="M119" s="2"/>
+      <c r="Q119" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="R119" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S119" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="T119" s="2"/>
+      <c r="U119" s="2"/>
+      <c r="V119" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="W119" t="s">
+        <v>65</v>
+      </c>
+      <c r="X119" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y119"/>
+    </row>
+    <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="K120" s="22" t="s">
+        <v>752</v>
+      </c>
+      <c r="M120" s="2"/>
+      <c r="Q120" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="R120" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S120" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="T120" s="2"/>
+      <c r="U120" s="2"/>
+      <c r="V120" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="W120" t="s">
+        <v>65</v>
+      </c>
+      <c r="X120" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y120"/>
+    </row>
+    <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="R121" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="V121" s="5">
+        <v>2</v>
+      </c>
+      <c r="W121" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X121" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K122" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="R122" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S122" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="V122" s="6">
+        <v>3</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="K123" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="R123" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S123" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="V123" s="6">
+        <v>3</v>
+      </c>
+      <c r="W123" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X123" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K124" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="R124" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S124" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="V124" s="6">
+        <v>3</v>
+      </c>
+      <c r="W124" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="K125" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="R125" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="V125" s="6">
+        <v>3</v>
+      </c>
+      <c r="W125" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X125" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B126" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D126" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E109" s="2" t="s">
+      <c r="E126" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="I109" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="K109" s="7" t="s">
+      <c r="I126" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="K126" s="22" t="s">
+        <v>754</v>
+      </c>
+      <c r="M126" s="2"/>
+      <c r="Q126" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="R126" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="V126" s="5">
+        <v>2</v>
+      </c>
+      <c r="W126" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X126" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="K127" s="22" t="s">
+        <v>760</v>
+      </c>
+      <c r="M127" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q127" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R127" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="R109" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="V109" s="5">
+      <c r="S127" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="V127" s="5">
         <v>2</v>
       </c>
-      <c r="W109" s="2" t="s">
+      <c r="W127" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="X109" s="2" t="s">
+      <c r="X127" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="K128" s="22" t="s">
+        <v>764</v>
+      </c>
+      <c r="M128" s="22" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q128" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R128" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S128" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="V128" s="5">
+        <v>2</v>
+      </c>
+      <c r="W128" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X128" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="K129" s="22" t="s">
+        <v>770</v>
+      </c>
+      <c r="M129" s="2"/>
+      <c r="Q129" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="R129" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="S129" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="V129" s="5">
+        <v>2</v>
+      </c>
+      <c r="W129" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X129" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="K130" s="22" t="s">
+        <v>777</v>
+      </c>
+      <c r="M130" s="2"/>
+      <c r="Q130" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R130" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="S130" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="V130" s="5">
+        <v>2</v>
+      </c>
+      <c r="W130" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X130" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="K131" s="22" t="s">
+        <v>781</v>
+      </c>
+      <c r="M131" s="2"/>
+      <c r="Q131" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="R131" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="V131" s="5">
+        <v>2</v>
+      </c>
+      <c r="W131" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X131" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -7058,126 +8437,150 @@
     <hyperlink ref="K25" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="K26" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="K33" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="K42" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K43" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="K44" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K45" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K52" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K53" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K58" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K59" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K60" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K61" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K62" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K63" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K64" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="K65" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="K66" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="K75" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="K76" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="K77" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="K78" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="K79" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="K80" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="K81" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="K82" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="K83" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="K84" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="K85" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="K86" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="K87" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="K88" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="K89" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="K99" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="K100" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K101" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="K102" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="K103" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="K104" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K105" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K106" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K107" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K108" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K109" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="K3" r:id="rId47" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
-    <hyperlink ref="K4" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
-    <hyperlink ref="K5" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
-    <hyperlink ref="K6" r:id="rId50" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
-    <hyperlink ref="K7" r:id="rId51" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
-    <hyperlink ref="K8" r:id="rId52" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
-    <hyperlink ref="K9" r:id="rId53" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
-    <hyperlink ref="K10" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
-    <hyperlink ref="K18" r:id="rId55" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
-    <hyperlink ref="K19" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
-    <hyperlink ref="K21" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
-    <hyperlink ref="K20" r:id="rId58" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
-    <hyperlink ref="K22" r:id="rId59" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
-    <hyperlink ref="M18" r:id="rId60" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
-    <hyperlink ref="K23" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
-    <hyperlink ref="K27" r:id="rId62" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
-    <hyperlink ref="K28" r:id="rId63" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
-    <hyperlink ref="M28" r:id="rId64" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
-    <hyperlink ref="K29" r:id="rId65" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
-    <hyperlink ref="K30" r:id="rId66" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
-    <hyperlink ref="K31" r:id="rId67" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
-    <hyperlink ref="K32" r:id="rId68" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
-    <hyperlink ref="K11" r:id="rId69" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
-    <hyperlink ref="K12" r:id="rId70" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
-    <hyperlink ref="K13" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
-    <hyperlink ref="K14" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
-    <hyperlink ref="K15" r:id="rId73" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
-    <hyperlink ref="K16" r:id="rId74" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
-    <hyperlink ref="K34" r:id="rId75" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
-    <hyperlink ref="K35" r:id="rId76" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
-    <hyperlink ref="K36" r:id="rId77" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
-    <hyperlink ref="K37" r:id="rId78" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
-    <hyperlink ref="K38" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
-    <hyperlink ref="K39" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
-    <hyperlink ref="K40" r:id="rId81" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
-    <hyperlink ref="K41" r:id="rId82" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
-    <hyperlink ref="K54" r:id="rId83" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
-    <hyperlink ref="K55" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
-    <hyperlink ref="M55" r:id="rId85" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
-    <hyperlink ref="K56" r:id="rId86" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
-    <hyperlink ref="M56" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
-    <hyperlink ref="K57" r:id="rId88" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
-    <hyperlink ref="K46" r:id="rId89" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
-    <hyperlink ref="K47" r:id="rId90" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
-    <hyperlink ref="K50" r:id="rId91" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
-    <hyperlink ref="K49" r:id="rId92" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
-    <hyperlink ref="K48" r:id="rId93" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
-    <hyperlink ref="K51" r:id="rId94" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
-    <hyperlink ref="K91" r:id="rId95" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
-    <hyperlink ref="M92" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
-    <hyperlink ref="K92" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
-    <hyperlink ref="K93" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
-    <hyperlink ref="K94" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
-    <hyperlink ref="K98" r:id="rId100" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
-    <hyperlink ref="M95" r:id="rId101" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
-    <hyperlink ref="K95" r:id="rId102" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
-    <hyperlink ref="M97" r:id="rId103" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
-    <hyperlink ref="K96" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
-    <hyperlink ref="K97" r:id="rId105" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
-    <hyperlink ref="M90" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
-    <hyperlink ref="K90" r:id="rId107" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
-    <hyperlink ref="O90" r:id="rId108" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
-    <hyperlink ref="M93" r:id="rId109" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
-    <hyperlink ref="M82" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
-    <hyperlink ref="H52" r:id="rId111" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
-    <hyperlink ref="F52" r:id="rId112" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
-    <hyperlink ref="M52" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
-    <hyperlink ref="O52" r:id="rId114" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
-    <hyperlink ref="M67" r:id="rId115" xr:uid="{D4E31208-1729-474B-8613-04CAF9B8C025}"/>
-    <hyperlink ref="K67" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F8517-F853-4BC2-B1A3-2FAE2DAB6C9A}"/>
-    <hyperlink ref="K68" r:id="rId117" xr:uid="{61D85FE2-8DE3-4825-8491-0FE8BB47E3E1}"/>
-    <hyperlink ref="K69" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F36EF-2268-403C-A6B7-E58ACFE0642D}"/>
-    <hyperlink ref="K70" r:id="rId119" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B578D29-DC36-40D0-9947-A27ECB77A9CF}"/>
-    <hyperlink ref="K71" r:id="rId120" xr:uid="{57B652B7-7292-4EAC-B631-5C96CD2691B8}"/>
-    <hyperlink ref="K72" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9E7BF8E-41C2-4812-BC18-7E39D390B4DB}"/>
-    <hyperlink ref="H73" r:id="rId122" xr:uid="{0D8B79CB-4807-4139-98AD-96CFF7161C32}"/>
-    <hyperlink ref="K73" r:id="rId123" xr:uid="{B472E107-96D8-49AE-8D43-42D5D303C124}"/>
-    <hyperlink ref="M73" r:id="rId124" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9F3C81B0-62F8-4827-8155-5167D81363EB}"/>
-    <hyperlink ref="K74" r:id="rId125" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{841BFC94-91FA-4580-9546-612A91A5451F}"/>
+    <hyperlink ref="K52" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K53" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="K54" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K55" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K62" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K63" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K68" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K69" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K70" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K71" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K72" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K73" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K74" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="K75" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K76" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="K85" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K86" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="K87" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K88" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K89" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K90" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="K91" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K92" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="K93" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K94" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="K95" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K96" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="K97" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K98" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K99" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K109" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K110" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K111" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K112" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K3" r:id="rId40" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
+    <hyperlink ref="K4" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
+    <hyperlink ref="K5" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
+    <hyperlink ref="K6" r:id="rId43" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
+    <hyperlink ref="K7" r:id="rId44" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
+    <hyperlink ref="K8" r:id="rId45" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
+    <hyperlink ref="K9" r:id="rId46" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
+    <hyperlink ref="K10" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
+    <hyperlink ref="K18" r:id="rId48" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
+    <hyperlink ref="K19" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
+    <hyperlink ref="K21" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
+    <hyperlink ref="K20" r:id="rId51" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
+    <hyperlink ref="K22" r:id="rId52" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
+    <hyperlink ref="M18" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
+    <hyperlink ref="K23" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
+    <hyperlink ref="K27" r:id="rId55" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
+    <hyperlink ref="K28" r:id="rId56" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
+    <hyperlink ref="M28" r:id="rId57" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
+    <hyperlink ref="K29" r:id="rId58" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
+    <hyperlink ref="K30" r:id="rId59" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
+    <hyperlink ref="K31" r:id="rId60" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
+    <hyperlink ref="K32" r:id="rId61" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
+    <hyperlink ref="K11" r:id="rId62" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
+    <hyperlink ref="K12" r:id="rId63" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
+    <hyperlink ref="K13" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
+    <hyperlink ref="K14" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
+    <hyperlink ref="K15" r:id="rId66" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
+    <hyperlink ref="K16" r:id="rId67" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
+    <hyperlink ref="K34" r:id="rId68" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
+    <hyperlink ref="K35" r:id="rId69" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
+    <hyperlink ref="K36" r:id="rId70" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
+    <hyperlink ref="K37" r:id="rId71" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
+    <hyperlink ref="K38" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
+    <hyperlink ref="K39" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
+    <hyperlink ref="K40" r:id="rId74" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
+    <hyperlink ref="K41" r:id="rId75" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
+    <hyperlink ref="K64" r:id="rId76" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
+    <hyperlink ref="K65" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
+    <hyperlink ref="M65" r:id="rId78" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
+    <hyperlink ref="K66" r:id="rId79" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
+    <hyperlink ref="M66" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
+    <hyperlink ref="K67" r:id="rId81" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
+    <hyperlink ref="K56" r:id="rId82" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
+    <hyperlink ref="K57" r:id="rId83" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
+    <hyperlink ref="K60" r:id="rId84" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
+    <hyperlink ref="K59" r:id="rId85" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
+    <hyperlink ref="K58" r:id="rId86" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
+    <hyperlink ref="K61" r:id="rId87" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
+    <hyperlink ref="K101" r:id="rId88" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
+    <hyperlink ref="M102" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
+    <hyperlink ref="K102" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
+    <hyperlink ref="K103" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
+    <hyperlink ref="K104" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
+    <hyperlink ref="K108" r:id="rId93" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
+    <hyperlink ref="M105" r:id="rId94" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
+    <hyperlink ref="K105" r:id="rId95" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
+    <hyperlink ref="M107" r:id="rId96" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
+    <hyperlink ref="K106" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
+    <hyperlink ref="K107" r:id="rId98" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
+    <hyperlink ref="M100" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
+    <hyperlink ref="K100" r:id="rId100" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
+    <hyperlink ref="O100" r:id="rId101" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
+    <hyperlink ref="M103" r:id="rId102" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
+    <hyperlink ref="M92" r:id="rId103" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
+    <hyperlink ref="H62" r:id="rId104" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
+    <hyperlink ref="F62" r:id="rId105" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
+    <hyperlink ref="M62" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
+    <hyperlink ref="O62" r:id="rId107" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
+    <hyperlink ref="M77" r:id="rId108" xr:uid="{D4E31208-1729-474B-8613-04CAF9B8C025}"/>
+    <hyperlink ref="K77" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F8517-F853-4BC2-B1A3-2FAE2DAB6C9A}"/>
+    <hyperlink ref="K78" r:id="rId110" xr:uid="{61D85FE2-8DE3-4825-8491-0FE8BB47E3E1}"/>
+    <hyperlink ref="K79" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F36EF-2268-403C-A6B7-E58ACFE0642D}"/>
+    <hyperlink ref="K80" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B578D29-DC36-40D0-9947-A27ECB77A9CF}"/>
+    <hyperlink ref="K81" r:id="rId113" xr:uid="{57B652B7-7292-4EAC-B631-5C96CD2691B8}"/>
+    <hyperlink ref="K82" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9E7BF8E-41C2-4812-BC18-7E39D390B4DB}"/>
+    <hyperlink ref="H83" r:id="rId115" xr:uid="{0D8B79CB-4807-4139-98AD-96CFF7161C32}"/>
+    <hyperlink ref="K83" r:id="rId116" xr:uid="{B472E107-96D8-49AE-8D43-42D5D303C124}"/>
+    <hyperlink ref="M83" r:id="rId117" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9F3C81B0-62F8-4827-8155-5167D81363EB}"/>
+    <hyperlink ref="K84" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{841BFC94-91FA-4580-9546-612A91A5451F}"/>
+    <hyperlink ref="K42" r:id="rId119" xr:uid="{A95E99D8-AE5F-42F6-8170-14A073FA717E}"/>
+    <hyperlink ref="K43" r:id="rId120" xr:uid="{3ED1C2EF-8252-44A5-B551-1A43DD3F443F}"/>
+    <hyperlink ref="K44" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg/1280px-Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{751B356D-FC9A-4AD0-95E0-A8F1621E6F4F}"/>
+    <hyperlink ref="K45" r:id="rId122" xr:uid="{4DEEB737-1329-4597-919B-47ACF73325F8}"/>
+    <hyperlink ref="K46" r:id="rId123" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A5A253DF-D8FC-4464-832F-136C51B54ADE}"/>
+    <hyperlink ref="K47" r:id="rId124" xr:uid="{C26C012E-8A85-48D2-9B13-ADD3AEDEB4B0}"/>
+    <hyperlink ref="K48" r:id="rId125" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1D38CDDF-A325-49B8-BE2E-935C8E9D142B}"/>
+    <hyperlink ref="K51" r:id="rId126" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{471BE4AF-D2F1-433A-B3AC-795231C2AF30}"/>
+    <hyperlink ref="K49" r:id="rId127" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F1CACA00-310B-4B86-B079-D54654CC5BDD}"/>
+    <hyperlink ref="K50" r:id="rId128" display="https://upload.wikimedia.org/wikipedia/commons/3/39/Tomb_of_Lorenzo_the_Magnificent_and_Giuliano_de%27_Medici%2C_Sagrestia_Nuova%2C_Medici_Chapels%2C_San_Lorenzo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr" xr:uid="{0C4E85C8-1452-46E5-BAA1-9F134272222A}"/>
+    <hyperlink ref="K125" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K124" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K123" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K122" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K121" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K113" r:id="rId134" xr:uid="{B6FD0D1A-F931-482F-BA2B-9716DE045C80}"/>
+    <hyperlink ref="K114" r:id="rId135" xr:uid="{A861573B-3839-4318-BBAC-62B6CBA15FBD}"/>
+    <hyperlink ref="K115" r:id="rId136" xr:uid="{20DF76DA-E992-4E1D-A16E-22BE28C58483}"/>
+    <hyperlink ref="K116" r:id="rId137" xr:uid="{B1F4C251-A9D6-47B9-9136-6591399F5FD8}"/>
+    <hyperlink ref="K117" r:id="rId138" xr:uid="{D7FB2C86-EF32-4C98-B1CE-C0195DB8C4C6}"/>
+    <hyperlink ref="K118" r:id="rId139" xr:uid="{FE50DE30-8439-4013-8AF6-8076D7113E1F}"/>
+    <hyperlink ref="K119" r:id="rId140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDA4581C-5B96-4BDE-A351-45793B6F0EE8}"/>
+    <hyperlink ref="K120" r:id="rId141" xr:uid="{51ED3C40-5509-488A-841B-4E657C71C1FA}"/>
+    <hyperlink ref="K126" r:id="rId142" xr:uid="{F66E5A2C-A530-4199-AD87-0563CA44FE62}"/>
+    <hyperlink ref="K127" r:id="rId143" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D2E9D5D-E79A-4ADE-8B6A-4BF55D9DEAA1}"/>
+    <hyperlink ref="M127" r:id="rId144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{34AE602C-A94D-4947-A1E5-B9CB698DBCE9}"/>
+    <hyperlink ref="M128" r:id="rId145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7F17DDD6-358D-4949-BA30-757C7347BD64}"/>
+    <hyperlink ref="K128" r:id="rId146" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D595607E-E74C-423D-9949-0D9455718911}"/>
+    <hyperlink ref="K130" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46C65D64-593C-435B-985E-1487C0A3B6FF}"/>
+    <hyperlink ref="K131" r:id="rId148" xr:uid="{ABE79D9A-A8E7-4085-8D94-395C34C6D224}"/>
+    <hyperlink ref="K129" r:id="rId149" xr:uid="{29FC3D7D-FB63-4F1F-9086-C70F1D6EA865}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1405789F-8AAE-414E-9C84-B9B6AA361792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2ED469C-58E9-4EE9-800A-F68E79966528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16200" yWindow="0" windowWidth="12660" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="770">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -398,9 +398,6 @@
     <t>1563-1565</t>
   </si>
   <si>
-    <t>fin 16e s.</t>
-  </si>
-  <si>
     <t>1546 environ</t>
   </si>
   <si>
@@ -536,9 +533,6 @@
     <t>1570-1581 environ</t>
   </si>
   <si>
-    <t>16e siècle</t>
-  </si>
-  <si>
     <t>1507-1519</t>
   </si>
   <si>
@@ -641,9 +635,6 @@
     <t>Cathédrale d'Astorga</t>
   </si>
   <si>
-    <t>Museo Nacional de Escultura</t>
-  </si>
-  <si>
     <t>Cathédrale de Tolède</t>
   </si>
   <si>
@@ -659,9 +650,6 @@
     <t>Eglise Orsanmichele de Florence</t>
   </si>
   <si>
-    <t>Museo Nazionale del Bargello</t>
-  </si>
-  <si>
     <t>Bode-Museum</t>
   </si>
   <si>
@@ -767,33 +755,21 @@
     <t>"Hercule et Cacus"</t>
   </si>
   <si>
-    <t>"Junon (bronze, studiolo de François Ier de Médicis)"</t>
-  </si>
-  <si>
     <t>"Retable majeur de la cathédrale d'Astorga"</t>
   </si>
   <si>
     <t>"Reliefs du chœur (avec Alonso Berruguete)"</t>
   </si>
   <si>
-    <t>"La Metterza (Sainte Anne, la Vierge et l'Enfant)"</t>
-  </si>
-  <si>
     <t>"Samson et le Philistin"</t>
   </si>
   <si>
-    <t>"L'Onore che vince l'Inganno"</t>
-  </si>
-  <si>
     <t>"Le Duel allégorique entre Albrecht Dürer et Apelle"</t>
   </si>
   <si>
     <t>"L'Escalier doré"</t>
   </si>
   <si>
-    <t>"Mercure enlevant Psyché"</t>
-  </si>
-  <si>
     <t>"Monument funéraire de Vespasien Gonzague"</t>
   </si>
   <si>
@@ -821,9 +797,6 @@
     <t>"La Tireuse d'épine"</t>
   </si>
   <si>
-    <t>"Le Surtout de table Merkel (Merkelsche Tafelaufsatz)"</t>
-  </si>
-  <si>
     <t>"Tombeau de Louis XII et d'Anne de Bretagne"</t>
   </si>
   <si>
@@ -833,18 +806,12 @@
     <t>"Buste de Charles Quint"</t>
   </si>
   <si>
-    <t>"Cénotaphes de Charles Quint et de Philippe II et leurs familles"</t>
-  </si>
-  <si>
     <t>"Bases en bronze des mâts de la Piazza San Marco"</t>
   </si>
   <si>
     <t>"Tombeau de Marguerite d'Autriche"</t>
   </si>
   <si>
-    <t>"Retable du Saint-Sacrement (albâtre)"</t>
-  </si>
-  <si>
     <t>"Tombeau de Philippe le Beau et Jeanne la Folle"</t>
   </si>
   <si>
@@ -938,9 +905,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5a/Loy_Hering_Annunciation.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c1/San_Jer%C3%B3nimo_penitente%2C_Jer%C3%B3nimo_Hern%C3%A1ndez.jpg/1280px-San_Jer%C3%B3nimo_penitente%2C_Jer%C3%B3nimo_Hern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/49/La_Tireuse_d%27%C3%A9pine_-_Ponce_Jacquiot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3455.jpg/1280px-La_Tireuse_d%27%C3%A9pine_-_Ponce_Jacquiot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3455.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1085,9 +1049,6 @@
     <t>40 cm environ</t>
   </si>
   <si>
-    <t>175 cm environ</t>
-  </si>
-  <si>
     <t>146 cm environ</t>
   </si>
   <si>
@@ -1151,9 +1112,6 @@
     <t>Pont Santa Trinita</t>
   </si>
   <si>
-    <t>Reconstruction du Pont Santa Trinita</t>
-  </si>
-  <si>
     <t>Ponte Santa Trinita (Architettura)</t>
   </si>
   <si>
@@ -1178,18 +1136,12 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Palazzo_Pitti_Courtyard.jpg/1280px-Palazzo_Pitti_Courtyard.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Architecture (Bossage)</t>
-  </si>
-  <si>
     <t>1550-1553</t>
   </si>
   <si>
     <t>Église San Pietro in Montorio</t>
   </si>
   <si>
-    <t>Monumento funéraire d'Antonio del Monte</t>
-  </si>
-  <si>
     <t>Monumento funebre di Antonio del Monte</t>
   </si>
   <si>
@@ -1232,9 +1184,6 @@
     <t>505</t>
   </si>
   <si>
-    <t>1519-1525</t>
-  </si>
-  <si>
     <t>Bacchus</t>
   </si>
   <si>
@@ -1310,9 +1259,6 @@
     <t>220</t>
   </si>
   <si>
-    <t>Retable de San Benito (saint Benoît de Nursie)</t>
-  </si>
-  <si>
     <t>Retablo de San Benito de Sahagún</t>
   </si>
   <si>
@@ -1391,9 +1337,6 @@
     <t>San Sebastián</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Alonso_Berruguete%2C_San_St%C3%A9bastien.jpg/960px-Alonso_Berruguete%2C_San_St%C3%A9bastien.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>101</t>
   </si>
   <si>
@@ -1589,9 +1532,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Groupe sculpté</t>
-  </si>
-  <si>
     <t>260 cm</t>
   </si>
   <si>
@@ -1661,21 +1601,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>1603</t>
-  </si>
-  <si>
-    <t>Buste de l'empereur Rodolphe II</t>
-  </si>
-  <si>
-    <t>Büste Kaiser Rudolfs II.</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Kaiser_Rudolf_II._%28de_Vries_1603%29.jpg/960px-Kaiser_Rudolf_II._%28de_Vries_1603%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>L'Enterrement du Christ</t>
   </si>
   <si>
@@ -1718,9 +1643,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/Medina_de_Rioseco_-_Santa_Maria_de_Mediavilla1.jpg/960px-Medina_de_Rioseco_-_Santa_Maria_de_Mediavilla1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Terre cuite polychrome</t>
-  </si>
-  <si>
     <t>1571</t>
   </si>
   <si>
@@ -1751,24 +1673,12 @@
     <t>Chapelle de la Piedad</t>
   </si>
   <si>
-    <t>La Déploration du Christ (El Entierro de Cristo)</t>
-  </si>
-  <si>
     <t>El Santo Entierro / La Piedad</t>
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Retablo_del_Santo_Entierro%2C_Juan_de_Juni.jpg/960px-Retablo_del_Santo_Entierro%2C_Juan_de_Juni.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Groupe sculptural</t>
-  </si>
-  <si>
-    <t>Musée Diocésain et Cathédralice</t>
-  </si>
-  <si>
-    <t>La Vierge des Douleurs (Virgen de las Angustias)</t>
-  </si>
-  <si>
     <t>Virgen de las Angustias</t>
   </si>
   <si>
@@ -1793,9 +1703,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/a/a8/Tombeau_et_Monument_de_Henri_II_et_Catherine_de_M%C3%A9dicis%2C_Saint-Denis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Monument funéraire</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monument du cœur d'Henri II </t>
   </si>
   <si>
@@ -1814,9 +1721,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Modèle pour la Vierge de douleur actuellement à l'Eglise Saint Paul</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/00/Germain_pilon%2C_madonna_dolente%2C_1586%2C_01.JPG/960px-Germain_pilon%2C_madonna_dolente%2C_1586%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1907,9 +1811,6 @@
     <t>"Portail du cloître "</t>
   </si>
   <si>
-    <t>"Fontaine du Géant)"</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1946,9 +1847,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Tribune-louvre_%283%29.jpg/1280px-Tribune-louvre_%283%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t xml:space="preserve">Statues-colonnes </t>
-  </si>
-  <si>
     <t>Pierre de Tonnerre</t>
   </si>
   <si>
@@ -1961,12 +1859,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Ce bas-relief aisait partie du jubé de l'église Saint-Germain-l'Auxerrois à Paris construit par Pierre Lescot et Jean Goujon et démonté en 1745.</t>
-  </si>
-  <si>
-    <t>Bas-reliefs de jubé</t>
-  </si>
-  <si>
     <t>67</t>
   </si>
   <si>
@@ -1994,9 +1886,6 @@
     <t>1555-1560</t>
   </si>
   <si>
-    <t>Hôtel de Carnavalet</t>
-  </si>
-  <si>
     <t>Façades de la cour</t>
   </si>
   <si>
@@ -2024,15 +1913,9 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg/960px-Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Ce relief architectural fait partie des décorations de l'Attique , endacrant une fenêtre avec Neptune en pendant</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Reliefs architecturaux</t>
-  </si>
-  <si>
     <t>Château de Chantilly</t>
   </si>
   <si>
@@ -2045,9 +1928,6 @@
     <t>Ce relief ornait l'autel de la Chapelle du château d'Ecouen, détruite en 1793</t>
   </si>
   <si>
-    <t>Bas-relief monumental</t>
-  </si>
-  <si>
     <t xml:space="preserve">Façade </t>
   </si>
   <si>
@@ -2063,18 +1943,12 @@
     <t>1501-1504</t>
   </si>
   <si>
-    <t>Les galeries de l'Académie</t>
-  </si>
-  <si>
     <t>David</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Sculpture</t>
-  </si>
-  <si>
     <t>Bruges</t>
   </si>
   <si>
@@ -2147,18 +2021,12 @@
     <t>1520-1534</t>
   </si>
   <si>
-    <t>Sagrestia Nuova (Chapelles Médiciennes)</t>
-  </si>
-  <si>
     <t>Tombeau de Laurent de Médicis</t>
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
-    <t>Ensemble sculptural</t>
-  </si>
-  <si>
     <t>Tombeau de Julien de Médicis</t>
   </si>
   <si>
@@ -2210,9 +2078,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg/960px-Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statue</t>
-  </si>
-  <si>
     <t>230 cm environ</t>
   </si>
   <si>
@@ -2279,9 +2144,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Statue monumentale</t>
-  </si>
-  <si>
     <t>300 cm environ</t>
   </si>
   <si>
@@ -2348,9 +2210,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c8/Alessandro_vittoria%2C_san_giovanni_battista%2C_1565_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Statue d'autel</t>
-  </si>
-  <si>
     <t>115</t>
   </si>
   <si>
@@ -2379,6 +2238,111 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Alessandro_Vittoria%2C_San_Zaccaria_%281543%29.jpg/960px-Alessandro_Vittoria%2C_San_Zaccaria_%281543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>"Fontaine du Géant"</t>
+  </si>
+  <si>
+    <t>"Retable du Saint-Sacrement "</t>
+  </si>
+  <si>
+    <t>Pierre en bossage</t>
+  </si>
+  <si>
+    <t>"Cénotaphes de Charles Quint et de Philippe II et leur famille"</t>
+  </si>
+  <si>
+    <t>Chapelles des Médicis</t>
+  </si>
+  <si>
+    <t>Monument funéraire d'Antonio del Monte</t>
+  </si>
+  <si>
+    <t>Hôtel Carnavalet</t>
+  </si>
+  <si>
+    <t>Bois sculpté polychrome</t>
+  </si>
+  <si>
+    <t>1588-1590</t>
+  </si>
+  <si>
+    <t>1588-1591</t>
+  </si>
+  <si>
+    <t>200 environ</t>
+  </si>
+  <si>
+    <t>201 environ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Déploration du Christ </t>
+  </si>
+  <si>
+    <t>Modèle pour la "Vierge de douleur" actuellement à l'Eglise Saint Paul</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Loggetta_Sansovino_a_Venezia.jpg/1280px-Loggetta_Sansovino_a_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Galerie de l'Académie</t>
+  </si>
+  <si>
+    <t>Musée National de Sculpture</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg/1280px-San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ce bas-relief faisait partie du jubé de l'église Saint-Germain-l'Auxerrois à Paris, construit par Pierre Lescot et Jean Goujon et démonté en 1745.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Saint-Germain_l%27Auxerrois_edit.jpg/1280px-Saint-Germain_l%27Auxerrois_edit.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1560-1575</t>
+  </si>
+  <si>
+    <t>Statue que Michel Ange destinait à son propre tombeau. Il s'est représenté sous les traits de Nicodème.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Pieta_Bandini_Opera_Duomo_Florence_n04.jpg/960px-Pieta_Bandini_Opera_Duomo_Florence_n04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Ce relief architectural fait partie des décorations de l'Attique</t>
+  </si>
+  <si>
+    <t>Partie de Retable</t>
+  </si>
+  <si>
+    <t>Saint Benoît de Nursie</t>
+  </si>
+  <si>
+    <t>La statue était au centre d'un très grand retable disposé sur plusieurs étages du musée</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Alonso_Berruguete%2C_San_Sebasti%C3%A1n.jpg/960px-Alonso_Berruguete%2C_San_Sebasti%C3%A1n.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Sainte Anne, la Vierge et l'Enfant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Surtout de table Merkel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musée Diocésain </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Vierge des Douleurs </t>
+  </si>
+  <si>
+    <t>L'Honneur vainqueur de la Tromperie</t>
+  </si>
+  <si>
+    <t>Junon</t>
   </si>
 </sst>
 </file>
@@ -2484,7 +2448,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2514,14 +2478,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -2540,6 +2496,11 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2845,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y131"/>
+  <dimension ref="A1:Y129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -2859,7 +2820,7 @@
     <col min="9" max="9" width="28.85546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" style="2" customWidth="1"/>
     <col min="11" max="11" width="8.140625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="8" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" style="8" customWidth="1"/>
     <col min="14" max="14" width="5.140625" style="2" customWidth="1"/>
     <col min="15" max="15" width="10.28515625" style="2" customWidth="1"/>
@@ -2909,7 +2870,7 @@
       <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="8" t="s">
@@ -2983,7 +2944,7 @@
       <c r="K2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="10" t="s">
         <v>11</v>
       </c>
       <c r="M2" s="10" t="s">
@@ -3028,28 +2989,28 @@
         <v>120</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="S3" s="3">
         <v>560</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
@@ -3066,31 +3027,31 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
@@ -3107,31 +3068,31 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S5" s="3">
         <v>262</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
@@ -3148,31 +3109,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S6" s="3">
         <v>139</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
@@ -3189,28 +3150,25 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>371</v>
+        <v>168</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
@@ -3227,28 +3185,28 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="V8" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>394</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
@@ -3265,28 +3223,28 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>384</v>
+        <v>740</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
@@ -3303,31 +3261,31 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
@@ -3344,28 +3302,31 @@
         <v>71</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>121</v>
+        <v>743</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>745</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
@@ -3382,28 +3343,31 @@
         <v>71</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>121</v>
+        <v>744</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>746</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>23</v>
@@ -3420,31 +3384,31 @@
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>671</v>
+        <v>631</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>23</v>
@@ -3461,31 +3425,31 @@
         <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>671</v>
+        <v>631</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>23</v>
@@ -3502,35 +3466,35 @@
         <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="M15" s="7"/>
       <c r="Q15" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>23</v>
@@ -3547,31 +3511,31 @@
         <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>23</v>
@@ -3580,7 +3544,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -3588,16 +3552,16 @@
         <v>72</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>31</v>
@@ -3612,7 +3576,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
@@ -3620,34 +3584,34 @@
         <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
@@ -3656,48 +3620,60 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:25" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="W19" s="2" t="s">
+      <c r="C19" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="S19" s="13">
+        <v>224</v>
+      </c>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="W19" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="X19" s="2" t="s">
+      <c r="X19" s="11" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y19" s="11"/>
+    </row>
+    <row r="20" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
@@ -3705,34 +3681,34 @@
         <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>672</v>
+        <v>632</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>25</v>
@@ -3741,7 +3717,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
@@ -3749,19 +3725,22 @@
         <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>411</v>
+        <v>394</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="S21" s="3">
         <v>78</v>
@@ -3770,7 +3749,7 @@
         <v>75</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
@@ -3779,7 +3758,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>25</v>
       </c>
@@ -3787,34 +3766,34 @@
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>673</v>
+        <v>633</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>25</v>
@@ -3823,7 +3802,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
@@ -3831,34 +3810,34 @@
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="V23" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>25</v>
@@ -3867,7 +3846,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -3875,25 +3854,25 @@
         <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="V24" s="4">
         <v>1</v>
@@ -3905,7 +3884,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -3913,25 +3892,25 @@
         <v>74</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>244</v>
+        <v>769</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="V25" s="6">
         <v>3</v>
@@ -3943,7 +3922,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -3951,19 +3930,19 @@
         <v>75</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="V26" s="6">
         <v>3</v>
@@ -3975,48 +3954,66 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:25" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="R27" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="V27" s="5">
+      <c r="C27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>751</v>
+      </c>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>761</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>762</v>
+      </c>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="R27" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="S27" s="13">
+        <v>150</v>
+      </c>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13">
         <v>2</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="W27" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="X27" s="2" t="s">
+      <c r="X27" s="11" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y27" s="11"/>
+    </row>
+    <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
@@ -4024,34 +4021,37 @@
         <v>76</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>202</v>
+        <v>751</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>434</v>
+        <v>416</v>
+      </c>
+      <c r="U28" s="3">
+        <v>32</v>
       </c>
       <c r="V28" s="5">
         <v>2</v>
@@ -4063,7 +4063,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -4071,28 +4071,28 @@
         <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="V29" s="5">
         <v>2</v>
@@ -4104,7 +4104,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
@@ -4112,25 +4112,25 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="V30" s="5">
         <v>2</v>
@@ -4142,7 +4142,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
@@ -4150,31 +4150,31 @@
         <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>202</v>
+        <v>751</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>452</v>
+        <v>763</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="V31" s="5">
         <v>2</v>
@@ -4186,7 +4186,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -4194,25 +4194,25 @@
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="V32" s="5">
         <v>2</v>
@@ -4232,19 +4232,19 @@
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="V33" s="6">
         <v>3</v>
@@ -4264,31 +4264,31 @@
         <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="V34" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -4305,31 +4305,31 @@
         <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="V35" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -4346,31 +4346,31 @@
         <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="V36" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4387,31 +4387,31 @@
         <v>78</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="V37" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4428,31 +4428,31 @@
         <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="V38" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4469,34 +4469,31 @@
         <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="V39" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4513,31 +4510,31 @@
         <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4554,34 +4551,31 @@
         <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="V41" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4595,29 +4589,25 @@
         <v>33</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>675</v>
+        <v>635</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>676</v>
+        <v>750</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="K42" s="22" t="s">
-        <v>678</v>
-      </c>
-      <c r="M42" s="2"/>
-      <c r="Q42" s="2" t="s">
-        <v>679</v>
+        <v>636</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>637</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S42" s="3">
         <v>517</v>
@@ -4629,13 +4619,13 @@
         <v>140</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W42" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4643,29 +4633,25 @@
         <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>675</v>
+        <v>635</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>680</v>
+        <v>638</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>681</v>
+        <v>639</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="K43" s="22" t="s">
-        <v>683</v>
-      </c>
-      <c r="M43" s="2"/>
-      <c r="Q43" s="2" t="s">
-        <v>679</v>
+        <v>640</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>641</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S43" s="3">
         <v>128</v>
@@ -4677,13 +4663,13 @@
         <v>63</v>
       </c>
       <c r="V43" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W43" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4691,44 +4677,43 @@
         <v>33</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>684</v>
+        <v>642</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="K44" s="22" t="s">
-        <v>686</v>
-      </c>
-      <c r="M44" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>644</v>
+      </c>
       <c r="Q44" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>687</v>
+        <v>645</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>688</v>
+        <v>646</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W44" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4736,29 +4721,25 @@
         <v>33</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>689</v>
+        <v>647</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>690</v>
+        <v>648</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="K45" s="22" t="s">
-        <v>692</v>
-      </c>
-      <c r="M45" s="2"/>
-      <c r="Q45" s="2" t="s">
-        <v>679</v>
+        <v>649</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>650</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S45" s="3">
         <v>780</v>
@@ -4767,13 +4748,13 @@
         <v>640</v>
       </c>
       <c r="V45" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W45" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4781,29 +4762,25 @@
         <v>33</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>693</v>
+        <v>651</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="K46" s="22" t="s">
-        <v>695</v>
-      </c>
-      <c r="M46" s="2"/>
-      <c r="Q46" s="2" t="s">
-        <v>679</v>
+        <v>652</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>653</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S46" s="3">
         <v>228</v>
@@ -4815,13 +4792,13 @@
         <v>53</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4829,32 +4806,28 @@
         <v>33</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>693</v>
+        <v>651</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="K47" s="22" t="s">
-        <v>697</v>
-      </c>
-      <c r="M47" s="2"/>
-      <c r="Q47" s="2" t="s">
-        <v>679</v>
+        <v>654</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>655</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="T47" s="3">
         <v>49</v>
@@ -4863,13 +4836,13 @@
         <v>75</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4877,32 +4850,28 @@
         <v>33</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>698</v>
+        <v>656</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>699</v>
+        <v>657</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="K48" s="22" t="s">
-        <v>701</v>
-      </c>
-      <c r="M48" s="2"/>
-      <c r="Q48" s="2" t="s">
-        <v>679</v>
+        <v>658</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>659</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>702</v>
+        <v>660</v>
       </c>
       <c r="T48" s="3">
         <v>75</v>
@@ -4911,13 +4880,13 @@
         <v>60</v>
       </c>
       <c r="V48" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4925,29 +4894,25 @@
         <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="K49" s="22" t="s">
-        <v>706</v>
-      </c>
-      <c r="M49" s="2"/>
-      <c r="Q49" s="2" t="s">
-        <v>707</v>
+        <v>662</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>663</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S49" s="3">
         <v>650</v>
@@ -4956,13 +4921,13 @@
         <v>470</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4970,44 +4935,40 @@
         <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="K50" s="22" t="s">
-        <v>709</v>
-      </c>
-      <c r="M50" s="2"/>
-      <c r="Q50" s="2" t="s">
-        <v>707</v>
+        <v>664</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>665</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>710</v>
+        <v>666</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>711</v>
+        <v>667</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5015,29 +4976,31 @@
         <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>674</v>
+        <v>634</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>712</v>
+        <v>668</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="K51" s="22" t="s">
-        <v>714</v>
-      </c>
-      <c r="M51" s="2"/>
-      <c r="Q51" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>757</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S51" s="3">
         <v>277</v>
@@ -5049,16 +5012,16 @@
         <v>125</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>34</v>
       </c>
@@ -5066,33 +5029,33 @@
         <v>79</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>247</v>
+        <v>764</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="L52" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="L52" s="8"/>
       <c r="M52" s="8"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
@@ -5115,25 +5078,25 @@
         <v>80</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="V53" s="6">
         <v>3</v>
@@ -5153,25 +5116,25 @@
         <v>81</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>208</v>
+        <v>349</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>249</v>
+        <v>768</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="V54" s="6">
         <v>3</v>
@@ -5191,22 +5154,22 @@
         <v>82</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="V55" s="6">
         <v>3</v>
@@ -5226,28 +5189,37 @@
         <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>202</v>
+        <v>751</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>428</v>
+        <v>759</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
+      </c>
+      <c r="S56" s="3">
+        <v>190</v>
+      </c>
+      <c r="T56" s="3">
+        <v>325</v>
+      </c>
+      <c r="U56" s="3">
+        <v>160</v>
       </c>
       <c r="V56" s="5">
         <v>2</v>
@@ -5267,28 +5239,28 @@
         <v>83</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>202</v>
+        <v>751</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>551</v>
+        <v>526</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="V57" s="5">
         <v>2</v>
@@ -5308,31 +5280,31 @@
         <v>83</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>554</v>
+        <v>529</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>555</v>
+        <v>530</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>556</v>
+        <v>531</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>557</v>
+        <v>532</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>558</v>
+        <v>533</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>559</v>
+        <v>534</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>561</v>
+        <v>742</v>
       </c>
       <c r="V58" s="5">
         <v>2</v>
@@ -5352,34 +5324,34 @@
         <v>83</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>622</v>
+        <v>590</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>565</v>
+        <v>539</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="V59" s="5">
         <v>2</v>
@@ -5399,31 +5371,28 @@
         <v>83</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>572</v>
+        <v>747</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>573</v>
+        <v>546</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="V60" s="5">
         <v>2</v>
@@ -5443,28 +5412,28 @@
         <v>83</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>576</v>
+        <v>766</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>577</v>
+        <v>767</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>578</v>
+        <v>548</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="V61" s="5">
         <v>2</v>
@@ -5476,7 +5445,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>36</v>
       </c>
@@ -5484,47 +5453,46 @@
         <v>84</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>629</v>
-      </c>
-      <c r="G62" s="18"/>
-      <c r="H62" s="13" t="s">
-        <v>628</v>
+        <v>206</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>595</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>627</v>
+        <v>594</v>
       </c>
       <c r="J62" s="11"/>
-      <c r="K62" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="L62" s="11"/>
-      <c r="M62" s="14" t="s">
-        <v>630</v>
+      <c r="K62" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="L62" s="21"/>
+      <c r="M62" s="12" t="s">
+        <v>597</v>
       </c>
       <c r="N62" s="11"/>
-      <c r="O62" s="13" t="s">
-        <v>631</v>
+      <c r="O62" s="19" t="s">
+        <v>598</v>
       </c>
       <c r="P62" s="11"/>
       <c r="Q62" s="11"/>
       <c r="R62" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="S62" s="12">
+        <v>316</v>
+      </c>
+      <c r="S62" s="13">
         <v>182</v>
       </c>
-      <c r="T62" s="12"/>
-      <c r="U62" s="12"/>
-      <c r="V62" s="12">
+      <c r="T62" s="13"/>
+      <c r="U62" s="13"/>
+      <c r="V62" s="13">
         <v>3</v>
       </c>
       <c r="W62" s="11" t="s">
@@ -5543,16 +5511,16 @@
         <v>85</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="R63" s="2" t="s">
         <v>31</v>
@@ -5575,31 +5543,31 @@
         <v>86</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="V64" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W64" s="2" t="s">
         <v>39</v>
@@ -5616,31 +5584,31 @@
         <v>86</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="V65" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>39</v>
@@ -5657,31 +5625,31 @@
         <v>86</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="V66" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W66" s="2" t="s">
         <v>39</v>
@@ -5692,358 +5660,371 @@
     </row>
     <row r="67" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>186</v>
+        <v>136</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>544</v>
+        <v>245</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>545</v>
+        <v>280</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="S67" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="V67" s="4" t="s">
-        <v>394</v>
+        <v>314</v>
+      </c>
+      <c r="V67" s="6">
+        <v>3</v>
       </c>
       <c r="W67" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="V68" s="4">
-        <v>1</v>
+        <v>319</v>
+      </c>
+      <c r="V68" s="5">
+        <v>2</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="V69" s="6">
         <v>3</v>
       </c>
       <c r="W69" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>175</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>254</v>
+        <v>589</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="V70" s="5">
-        <v>2</v>
+        <v>316</v>
+      </c>
+      <c r="V70" s="6">
+        <v>3</v>
       </c>
       <c r="W70" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>176</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="V71" s="6">
         <v>3</v>
       </c>
       <c r="W71" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>621</v>
+        <v>249</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V72" s="6">
-        <v>3</v>
+        <v>321</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="V72" s="5">
+        <v>2</v>
       </c>
       <c r="W72" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="V73" s="6">
         <v>3</v>
       </c>
       <c r="W73" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>257</v>
+        <v>588</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="V74" s="5">
         <v>2</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>142</v>
+        <v>599</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K75" s="7" t="s">
-        <v>297</v>
+        <v>600</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="M75" s="15" t="s">
+        <v>288</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="V75" s="6">
-        <v>3</v>
+        <v>316</v>
+      </c>
+      <c r="S75" s="3">
+        <v>73</v>
+      </c>
+      <c r="T75" s="3">
+        <v>195</v>
+      </c>
+      <c r="U75" s="3">
+        <v>12</v>
+      </c>
+      <c r="V75" s="4">
+        <v>1</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>143</v>
+        <v>599</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="K76" s="7" t="s">
-        <v>298</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="M76" s="16"/>
       <c r="R76" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="V76" s="5">
-        <v>2</v>
+        <v>604</v>
+      </c>
+      <c r="S76" s="3">
+        <v>210</v>
+      </c>
+      <c r="T76" s="3">
+        <v>60</v>
+      </c>
+      <c r="U76" s="3">
+        <v>65</v>
+      </c>
+      <c r="V76" s="4">
+        <v>1</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6054,38 +6035,38 @@
         <v>94</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>754</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="K77" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="L77" s="8"/>
-      <c r="M77" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q77" s="2" t="s">
-        <v>481</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="M77" s="16"/>
       <c r="R77" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S77" s="3">
-        <v>73</v>
+        <v>316</v>
+      </c>
+      <c r="S77" s="3" t="s">
+        <v>608</v>
       </c>
       <c r="T77" s="3">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="U77" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="V77" s="4">
         <v>1</v>
@@ -6105,36 +6086,35 @@
         <v>94</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="K78" s="19" t="s">
-        <v>636</v>
-      </c>
-      <c r="L78" s="8"/>
-      <c r="M78" s="20"/>
-      <c r="Q78" s="2" t="s">
-        <v>637</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="K78" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="M78" s="16"/>
       <c r="R78" s="2" t="s">
-        <v>638</v>
+        <v>316</v>
       </c>
       <c r="S78" s="3">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="T78" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="U78" s="3">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="V78" s="4">
         <v>1</v>
@@ -6154,38 +6134,32 @@
         <v>94</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>639</v>
+        <v>611</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>173</v>
+        <v>612</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>206</v>
+        <v>613</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="K79" s="19" t="s">
-        <v>641</v>
-      </c>
-      <c r="L79" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="M79" s="20"/>
-      <c r="Q79" s="2" t="s">
-        <v>643</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="K79" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="M79" s="16"/>
       <c r="R79" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S79" s="3" t="s">
-        <v>644</v>
+        <v>326</v>
+      </c>
+      <c r="S79" s="3">
+        <v>700</v>
       </c>
       <c r="T79" s="3">
-        <v>182</v>
+        <v>366</v>
       </c>
       <c r="U79" s="3">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="V79" s="4">
         <v>1</v>
@@ -6205,38 +6179,35 @@
         <v>94</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>639</v>
+        <v>616</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>206</v>
+        <v>741</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>617</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="K80" s="19" t="s">
-        <v>646</v>
-      </c>
-      <c r="L80" s="8" t="s">
-        <v>642</v>
-      </c>
-      <c r="M80" s="20"/>
-      <c r="Q80" s="2" t="s">
-        <v>643</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="M80" s="16"/>
       <c r="R80" s="2" t="s">
-        <v>328</v>
+        <v>31</v>
       </c>
       <c r="S80" s="3">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="T80" s="3">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="U80" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="V80" s="4">
         <v>1</v>
@@ -6256,36 +6227,43 @@
         <v>94</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>647</v>
+        <v>620</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>648</v>
+        <v>171</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>649</v>
+        <v>621</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>623</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="K81" s="19" t="s">
-        <v>651</v>
-      </c>
-      <c r="L81" s="8"/>
-      <c r="M81" s="20"/>
-      <c r="Q81" s="2" t="s">
-        <v>586</v>
+        <v>624</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>625</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="M81" s="17" t="s">
+        <v>626</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>338</v>
+        <v>31</v>
       </c>
       <c r="S81" s="3">
-        <v>700</v>
+        <v>205</v>
       </c>
       <c r="T81" s="3">
-        <v>366</v>
+        <v>90</v>
       </c>
       <c r="U81" s="3">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="V81" s="4">
         <v>1</v>
@@ -6305,39 +6283,37 @@
         <v>94</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D82"/>
       <c r="E82" s="2" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>654</v>
+        <v>427</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="K82" s="19" t="s">
-        <v>656</v>
-      </c>
-      <c r="L82" s="8"/>
-      <c r="M82" s="20"/>
-      <c r="Q82" s="2" t="s">
-        <v>643</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="J82"/>
+      <c r="K82" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="M82" s="16"/>
       <c r="R82" s="2" t="s">
         <v>31</v>
       </c>
       <c r="S82" s="3">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="T82" s="3">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="U82" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V82" s="4">
         <v>1</v>
@@ -6351,668 +6327,670 @@
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>657</v>
+        <v>144</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="H83" s="19" t="s">
-        <v>660</v>
+        <v>216</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="K83" s="19" t="s">
-        <v>662</v>
-      </c>
-      <c r="L83" s="8" t="s">
-        <v>663</v>
-      </c>
-      <c r="M83" s="21" t="s">
-        <v>664</v>
-      </c>
-      <c r="Q83" s="2" t="s">
-        <v>665</v>
+        <v>251</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>289</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S83" s="3">
-        <v>205</v>
-      </c>
-      <c r="T83" s="3">
-        <v>90</v>
-      </c>
-      <c r="U83" s="3">
-        <v>6</v>
+        <v>323</v>
       </c>
       <c r="V83" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D84"/>
+        <v>145</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="E84" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>445</v>
+        <v>217</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="J84"/>
-      <c r="K84" s="19" t="s">
-        <v>668</v>
-      </c>
-      <c r="L84" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="M84" s="20"/>
-      <c r="Q84" s="2" t="s">
-        <v>670</v>
+        <v>252</v>
+      </c>
+      <c r="K84" s="7" t="s">
+        <v>752</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>31</v>
+        <v>318</v>
       </c>
       <c r="S84" s="3">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="T84" s="3">
-        <v>202</v>
+        <v>126</v>
       </c>
       <c r="U84" s="3">
-        <v>8</v>
-      </c>
-      <c r="V84" s="4">
-        <v>1</v>
+        <v>160</v>
+      </c>
+      <c r="V84" s="6">
+        <v>3</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="V85" s="4">
+        <v>583</v>
+      </c>
+      <c r="S85" s="3">
+        <v>26</v>
+      </c>
+      <c r="T85" s="3">
+        <v>22</v>
+      </c>
+      <c r="U85" s="3">
+        <v>14</v>
+      </c>
+      <c r="V85" s="6">
         <v>3</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>260</v>
+        <v>591</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="S86" s="3" t="s">
-        <v>350</v>
+        <v>31</v>
       </c>
       <c r="V86" s="6">
         <v>3</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>261</v>
+        <v>765</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="S87" s="3">
-        <v>26</v>
-      </c>
-      <c r="T87" s="3">
-        <v>22</v>
-      </c>
-      <c r="U87" s="3">
-        <v>14</v>
+        <v>324</v>
+      </c>
+      <c r="S87" s="3" t="s">
+        <v>332</v>
       </c>
       <c r="V87" s="6">
         <v>3</v>
       </c>
       <c r="W87" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="D88" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="E88" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>623</v>
+        <v>254</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>31</v>
+        <v>316</v>
       </c>
       <c r="V88" s="6">
         <v>3</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>262</v>
+        <v>587</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="V89" s="6">
         <v>3</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K90" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V90" s="6">
+      <c r="A90" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="J90" s="11"/>
+      <c r="K90" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="L90" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="M90" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="N90" s="11"/>
+      <c r="O90" s="11"/>
+      <c r="P90" s="11"/>
+      <c r="Q90" s="11"/>
+      <c r="R90" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="S90" s="13"/>
+      <c r="T90" s="13"/>
+      <c r="U90" s="13"/>
+      <c r="V90" s="13">
         <v>3</v>
       </c>
-      <c r="W90" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X90" s="2" t="s">
-        <v>100</v>
+      <c r="W90" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="X90" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>619</v>
+        <v>256</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="V91" s="6">
-        <v>3</v>
+        <v>315</v>
+      </c>
+      <c r="S91" s="3">
+        <v>113</v>
+      </c>
+      <c r="T91" s="3">
+        <v>59</v>
+      </c>
+      <c r="U91" s="3">
+        <v>40</v>
+      </c>
+      <c r="V91" s="5">
+        <v>2</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B92" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="E92" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="J92" s="15"/>
-      <c r="K92" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="L92" s="15" t="s">
-        <v>626</v>
-      </c>
-      <c r="M92" s="16" t="s">
-        <v>625</v>
-      </c>
-      <c r="N92" s="15"/>
-      <c r="O92" s="15"/>
-      <c r="P92" s="15"/>
-      <c r="Q92" s="15"/>
-      <c r="R92" s="15" t="s">
-        <v>330</v>
-      </c>
-      <c r="S92" s="17"/>
-      <c r="T92" s="17"/>
-      <c r="U92" s="17"/>
-      <c r="V92" s="17">
-        <v>3</v>
-      </c>
-      <c r="W92" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="X92" s="15" t="s">
-        <v>102</v>
+      <c r="A92" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="K92" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="V92" s="5">
+        <v>2</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="V93" s="5">
-        <v>2</v>
+        <v>315</v>
+      </c>
+      <c r="V93" s="6">
+        <v>3</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>153</v>
+        <v>125</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="V94" s="5">
-        <v>2</v>
+        <v>326</v>
+      </c>
+      <c r="V94" s="6">
+        <v>3</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>267</v>
+        <v>736</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="V95" s="6">
         <v>3</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>187</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>268</v>
+        <v>735</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="V96" s="6">
         <v>3</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>188</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="V97" s="6">
         <v>3</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>624</v>
+        <v>551</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>313</v>
+        <v>552</v>
+      </c>
+      <c r="L98" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="M98" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="O98" s="7" t="s">
+        <v>555</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V98" s="6">
-        <v>3</v>
+        <v>314</v>
+      </c>
+      <c r="S98" s="3">
+        <v>450</v>
+      </c>
+      <c r="T98" s="3">
+        <v>350</v>
+      </c>
+      <c r="U98" s="3">
+        <v>250</v>
+      </c>
+      <c r="V98" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>157</v>
+        <v>109</v>
+      </c>
+      <c r="C99" s="9">
+        <v>1583</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>270</v>
+        <v>551</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>314</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="M99" s="7"/>
+      <c r="O99" s="7"/>
       <c r="R99" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="V99" s="6">
-        <v>3</v>
+        <v>316</v>
+      </c>
+      <c r="S99" s="3">
+        <v>90</v>
+      </c>
+      <c r="T99" s="3">
+        <v>223</v>
+      </c>
+      <c r="U99" s="3">
+        <v>166</v>
+      </c>
+      <c r="V99" s="4">
+        <v>1</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>60</v>
       </c>
@@ -7020,43 +6998,38 @@
         <v>109</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>158</v>
+        <v>395</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="L100" s="8" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="M100" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="O100" s="7" t="s">
-        <v>585</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="O100" s="8"/>
       <c r="R100" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="S100" s="3">
-        <v>450</v>
+        <v>316</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>559</v>
       </c>
       <c r="T100" s="3">
-        <v>350</v>
+        <v>75</v>
       </c>
       <c r="U100" s="3">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="V100" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W100" s="2" t="s">
         <v>60</v>
@@ -7065,7 +7038,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>60</v>
       </c>
@@ -7073,37 +7046,41 @@
         <v>109</v>
       </c>
       <c r="C101" s="9">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="L101" s="8"/>
-      <c r="M101" s="7"/>
-      <c r="O101" s="7"/>
+        <v>561</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="M101" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="O101" s="8"/>
       <c r="R101" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S101" s="3">
-        <v>90</v>
+        <v>563</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>564</v>
       </c>
       <c r="T101" s="3">
-        <v>223</v>
+        <v>120</v>
       </c>
       <c r="U101" s="3">
-        <v>166</v>
-      </c>
-      <c r="V101" s="4">
-        <v>1</v>
+        <v>81</v>
+      </c>
+      <c r="V101" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>60</v>
@@ -7112,7 +7089,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>60</v>
       </c>
@@ -7120,39 +7097,29 @@
         <v>109</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>412</v>
+        <v>565</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="L102" s="8"/>
-      <c r="M102" s="7" t="s">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="O102" s="8"/>
       <c r="R102" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="T102" s="3">
-        <v>75</v>
-      </c>
-      <c r="U102" s="3">
-        <v>75</v>
+        <v>510</v>
       </c>
       <c r="V102" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W102" s="2" t="s">
         <v>60</v>
@@ -7161,49 +7128,46 @@
         <v>109</v>
       </c>
     </row>
-    <row r="103" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C103" s="9">
-        <v>1586</v>
+      <c r="C103" s="2" t="s">
+        <v>568</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="L103" s="8" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="M103" s="7" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="O103" s="8"/>
       <c r="R103" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="S103" s="3" t="s">
-        <v>596</v>
+        <v>316</v>
+      </c>
+      <c r="S103" s="3">
+        <v>83</v>
       </c>
       <c r="T103" s="3">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="U103" s="3">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="V103" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>60</v>
@@ -7212,7 +7176,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="104" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>60</v>
       </c>
@@ -7220,30 +7184,35 @@
         <v>109</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="L104" s="8"/>
+        <v>574</v>
+      </c>
       <c r="O104" s="8"/>
       <c r="R104" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S104" s="3" t="s">
-        <v>530</v>
+        <v>315</v>
+      </c>
+      <c r="S104" s="3">
+        <v>140</v>
+      </c>
+      <c r="T104" s="3">
+        <v>210</v>
+      </c>
+      <c r="U104" s="3">
+        <v>80</v>
       </c>
       <c r="V104" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W104" s="2" t="s">
         <v>60</v>
@@ -7252,47 +7221,49 @@
         <v>109</v>
       </c>
     </row>
-    <row r="105" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>600</v>
+      <c r="C105" s="9">
+        <v>1570</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>173</v>
+        <v>575</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>206</v>
+        <v>576</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="L105" s="8"/>
+        <v>578</v>
+      </c>
+      <c r="L105" s="8" t="s">
+        <v>579</v>
+      </c>
       <c r="M105" s="7" t="s">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="O105" s="8"/>
       <c r="R105" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S105" s="3">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="T105" s="3">
-        <v>191</v>
+        <v>25</v>
       </c>
       <c r="U105" s="3">
-        <v>49</v>
-      </c>
-      <c r="V105" s="4" t="s">
-        <v>394</v>
+        <v>18</v>
+      </c>
+      <c r="V105" s="4">
+        <v>1</v>
       </c>
       <c r="W105" s="2" t="s">
         <v>60</v>
@@ -7301,7 +7272,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="106" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>60</v>
       </c>
@@ -7309,36 +7280,35 @@
         <v>109</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>604</v>
+        <v>581</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>206</v>
+        <v>582</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>605</v>
+        <v>560</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>606</v>
-      </c>
-      <c r="L106" s="8"/>
+        <v>562</v>
+      </c>
       <c r="O106" s="8"/>
       <c r="R106" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="S106" s="3">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="T106" s="3">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="U106" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V106" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>60</v>
@@ -7347,253 +7317,244 @@
         <v>109</v>
       </c>
     </row>
-    <row r="107" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="R107" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="S107" s="3">
+        <v>43</v>
+      </c>
+      <c r="T107" s="3">
+        <v>180</v>
+      </c>
+      <c r="U107" s="3">
         <v>60</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C107" s="9">
-        <v>1570</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="K107" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="L107" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="M107" s="7" t="s">
-        <v>612</v>
-      </c>
-      <c r="O107" s="8"/>
-      <c r="R107" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S107" s="3">
-        <v>96</v>
-      </c>
-      <c r="T107" s="3">
-        <v>25</v>
-      </c>
-      <c r="U107" s="3">
-        <v>18</v>
-      </c>
-      <c r="V107" s="4">
-        <v>1</v>
+      <c r="V107" s="6">
+        <v>3</v>
       </c>
       <c r="W107" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="X107" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="108" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>613</v>
+        <v>159</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>614</v>
+        <v>229</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>591</v>
+        <v>261</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="L108" s="8"/>
-      <c r="O108" s="8"/>
+        <v>305</v>
+      </c>
       <c r="R108" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S108" s="3">
-        <v>159</v>
-      </c>
-      <c r="T108" s="3">
-        <v>120</v>
-      </c>
-      <c r="U108" s="3">
-        <v>81</v>
-      </c>
-      <c r="V108" s="4" t="s">
-        <v>394</v>
+        <v>31</v>
+      </c>
+      <c r="V108" s="6">
+        <v>3</v>
       </c>
       <c r="W108" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="109" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>271</v>
+        <v>585</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R109" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="S109" s="3">
-        <v>43</v>
-      </c>
-      <c r="T109" s="3">
-        <v>180</v>
-      </c>
-      <c r="U109" s="3">
-        <v>60</v>
-      </c>
       <c r="V109" s="6">
         <v>3</v>
       </c>
       <c r="W109" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="X109" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="110" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="R110" s="2" t="s">
-        <v>31</v>
+        <v>316</v>
       </c>
       <c r="V110" s="6">
         <v>3</v>
       </c>
       <c r="W110" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="X110" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="111" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>234</v>
+        <v>349</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>617</v>
+        <v>383</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>384</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="R111" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="V111" s="6">
-        <v>3</v>
-      </c>
-      <c r="W111" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="X111" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="112" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="S111" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="T111" s="2"/>
+      <c r="U111" s="2"/>
+      <c r="V111" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="W111" t="s">
+        <v>65</v>
+      </c>
+      <c r="X111" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y111"/>
+    </row>
+    <row r="112" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>162</v>
+        <v>677</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>235</v>
+        <v>402</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>273</v>
+        <v>678</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>319</v>
+        <v>680</v>
       </c>
       <c r="R112" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V112" s="6">
-        <v>3</v>
-      </c>
-      <c r="W112" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="X112" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="S112" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="T112" s="2"/>
+      <c r="U112" s="2"/>
+      <c r="V112" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="W112" t="s">
+        <v>65</v>
+      </c>
+      <c r="X112" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="113" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y112"/>
+    </row>
+    <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>65</v>
       </c>
@@ -7601,37 +7562,36 @@
         <v>113</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>163</v>
+        <v>682</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>208</v>
+        <v>683</v>
+      </c>
+      <c r="F113" s="18" t="s">
+        <v>749</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>400</v>
+        <v>684</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="K113" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="M113" s="2"/>
-      <c r="Q113" s="2" t="s">
-        <v>679</v>
+        <v>685</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>686</v>
       </c>
       <c r="R113" s="2" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>351</v>
+        <v>687</v>
       </c>
       <c r="T113" s="2"/>
       <c r="U113" s="2"/>
       <c r="V113" s="4" t="s">
-        <v>394</v>
+        <v>671</v>
       </c>
       <c r="W113" t="s">
         <v>65</v>
@@ -7649,37 +7609,36 @@
         <v>113</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>721</v>
+        <v>682</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>419</v>
+        <v>683</v>
+      </c>
+      <c r="F114" s="18" t="s">
+        <v>749</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>722</v>
+        <v>688</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="K114" s="22" t="s">
-        <v>724</v>
-      </c>
-      <c r="M114" s="2"/>
-      <c r="Q114" s="2" t="s">
-        <v>725</v>
+        <v>689</v>
+      </c>
+      <c r="K114" s="7" t="s">
+        <v>690</v>
       </c>
       <c r="R114" s="2" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>726</v>
+        <v>691</v>
       </c>
       <c r="T114" s="2"/>
       <c r="U114" s="2"/>
       <c r="V114" s="4" t="s">
-        <v>463</v>
+        <v>672</v>
       </c>
       <c r="W114" t="s">
         <v>65</v>
@@ -7697,37 +7656,36 @@
         <v>113</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>727</v>
+        <v>682</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>728</v>
+        <v>683</v>
+      </c>
+      <c r="F115" s="18" t="s">
+        <v>749</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>729</v>
+        <v>692</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="K115" s="22" t="s">
-        <v>731</v>
-      </c>
-      <c r="M115" s="2"/>
-      <c r="Q115" s="2" t="s">
-        <v>725</v>
+        <v>693</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>694</v>
       </c>
       <c r="R115" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>732</v>
+        <v>695</v>
       </c>
       <c r="T115" s="2"/>
       <c r="U115" s="2"/>
       <c r="V115" s="4" t="s">
-        <v>715</v>
+        <v>673</v>
       </c>
       <c r="W115" t="s">
         <v>65</v>
@@ -7745,37 +7703,36 @@
         <v>113</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>727</v>
+        <v>682</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>728</v>
+        <v>683</v>
+      </c>
+      <c r="F116" s="18" t="s">
+        <v>749</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>733</v>
+        <v>696</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="K116" s="22" t="s">
-        <v>735</v>
-      </c>
-      <c r="M116" s="2"/>
-      <c r="Q116" s="2" t="s">
-        <v>725</v>
+        <v>697</v>
+      </c>
+      <c r="K116" s="7" t="s">
+        <v>698</v>
       </c>
       <c r="R116" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>736</v>
+        <v>699</v>
       </c>
       <c r="T116" s="2"/>
       <c r="U116" s="2"/>
       <c r="V116" s="4" t="s">
-        <v>716</v>
+        <v>674</v>
       </c>
       <c r="W116" t="s">
         <v>65</v>
@@ -7793,37 +7750,33 @@
         <v>113</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>737</v>
+        <v>464</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="K117" s="22" t="s">
-        <v>739</v>
-      </c>
-      <c r="M117" s="2"/>
-      <c r="Q117" s="2" t="s">
-        <v>725</v>
+        <v>465</v>
+      </c>
+      <c r="K117" s="7" t="s">
+        <v>702</v>
       </c>
       <c r="R117" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>740</v>
+        <v>703</v>
       </c>
       <c r="T117" s="2"/>
       <c r="U117" s="2"/>
       <c r="V117" s="4" t="s">
-        <v>717</v>
+        <v>675</v>
       </c>
       <c r="W117" t="s">
         <v>65</v>
@@ -7841,37 +7794,33 @@
         <v>113</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>741</v>
+        <v>704</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="K118" s="22" t="s">
-        <v>743</v>
-      </c>
-      <c r="M118" s="2"/>
-      <c r="Q118" s="2" t="s">
-        <v>725</v>
+        <v>705</v>
+      </c>
+      <c r="K118" s="7" t="s">
+        <v>706</v>
       </c>
       <c r="R118" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>744</v>
+        <v>703</v>
       </c>
       <c r="T118" s="2"/>
       <c r="U118" s="2"/>
       <c r="V118" s="4" t="s">
-        <v>718</v>
+        <v>676</v>
       </c>
       <c r="W118" t="s">
         <v>65</v>
@@ -7883,176 +7832,162 @@
     </row>
     <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>745</v>
+        <v>163</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>746</v>
+        <v>232</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="K119" s="22" t="s">
-        <v>747</v>
-      </c>
-      <c r="M119" s="2"/>
-      <c r="Q119" s="2" t="s">
-        <v>748</v>
+        <v>263</v>
+      </c>
+      <c r="K119" s="7" t="s">
+        <v>309</v>
       </c>
       <c r="R119" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S119" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="T119" s="2"/>
-      <c r="U119" s="2"/>
-      <c r="V119" s="4" t="s">
-        <v>719</v>
-      </c>
-      <c r="W119" t="s">
-        <v>65</v>
-      </c>
-      <c r="X119" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y119"/>
+        <v>329</v>
+      </c>
+      <c r="V119" s="5">
+        <v>2</v>
+      </c>
+      <c r="W119" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X119" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>746</v>
+        <v>233</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="J120" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="K120" s="22" t="s">
-        <v>752</v>
-      </c>
-      <c r="M120" s="2"/>
-      <c r="Q120" s="2" t="s">
-        <v>748</v>
+        <v>264</v>
+      </c>
+      <c r="K120" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S120" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="T120" s="2"/>
-      <c r="U120" s="2"/>
-      <c r="V120" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="W120" t="s">
-        <v>65</v>
-      </c>
-      <c r="X120" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y120"/>
+        <v>316</v>
+      </c>
+      <c r="S120" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="V120" s="6">
+        <v>3</v>
+      </c>
+      <c r="W120" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X120" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="R121" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="S121" s="3">
         <v>114</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="K121" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="R121" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="V121" s="5">
-        <v>2</v>
+      <c r="T121" s="3">
+        <v>53</v>
+      </c>
+      <c r="U121" s="3">
+        <v>48</v>
+      </c>
+      <c r="V121" s="6">
+        <v>3</v>
       </c>
       <c r="W121" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X121" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>165</v>
+        <v>755</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="R122" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S122" s="3" t="s">
-        <v>348</v>
+        <v>315</v>
+      </c>
+      <c r="S122" s="3">
+        <v>34</v>
       </c>
       <c r="V122" s="6">
         <v>3</v>
       </c>
       <c r="W122" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X122" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>166</v>
@@ -8061,101 +7996,107 @@
         <v>194</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>616</v>
+        <v>586</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="R123" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="S123" s="3" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="V123" s="6">
         <v>3</v>
       </c>
       <c r="W123" s="2" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="X123" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>167</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>243</v>
+        <v>707</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>324</v>
+        <v>708</v>
       </c>
       <c r="R124" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="S124" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="V124" s="6">
-        <v>3</v>
+        <v>316</v>
+      </c>
+      <c r="V124" s="5">
+        <v>2</v>
       </c>
       <c r="W124" s="2" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="X124" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="125" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>168</v>
+        <v>709</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>240</v>
+        <v>710</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>711</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>618</v>
+        <v>712</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>713</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>325</v>
+        <v>714</v>
+      </c>
+      <c r="M125" s="7" t="s">
+        <v>715</v>
       </c>
       <c r="R125" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="V125" s="6">
-        <v>3</v>
+        <v>316</v>
+      </c>
+      <c r="S125" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="V125" s="5">
+        <v>2</v>
       </c>
       <c r="W125" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="X125" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8166,26 +8107,34 @@
         <v>119</v>
       </c>
       <c r="C126" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="E126" s="2" t="s">
-        <v>241</v>
+        <v>710</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>711</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="K126" s="22" t="s">
-        <v>754</v>
-      </c>
-      <c r="M126" s="2"/>
-      <c r="Q126" s="2" t="s">
-        <v>586</v>
+        <v>432</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="M126" s="7" t="s">
+        <v>715</v>
       </c>
       <c r="R126" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
+      </c>
+      <c r="S126" s="3" t="s">
+        <v>719</v>
       </c>
       <c r="V126" s="5">
         <v>2</v>
@@ -8205,37 +8154,28 @@
         <v>119</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>755</v>
+        <v>720</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>171</v>
+        <v>721</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>757</v>
+        <v>722</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>758</v>
+        <v>525</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="K127" s="22" t="s">
-        <v>760</v>
-      </c>
-      <c r="M127" s="22" t="s">
-        <v>761</v>
-      </c>
-      <c r="Q127" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="K127" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="R127" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="S127" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="R127" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S127" s="3" t="s">
-        <v>762</v>
       </c>
       <c r="V127" s="5">
         <v>2</v>
@@ -8255,37 +8195,28 @@
         <v>119</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>755</v>
+        <v>726</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>757</v>
+        <v>727</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>450</v>
+        <v>728</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="K128" s="22" t="s">
-        <v>764</v>
-      </c>
-      <c r="M128" s="22" t="s">
-        <v>761</v>
-      </c>
-      <c r="Q128" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
+      </c>
+      <c r="K128" s="7" t="s">
+        <v>730</v>
       </c>
       <c r="R128" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="S128" s="3" t="s">
-        <v>765</v>
+        <v>386</v>
       </c>
       <c r="V128" s="5">
         <v>2</v>
@@ -8305,32 +8236,25 @@
         <v>119</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>767</v>
+        <v>169</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>768</v>
+        <v>237</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>550</v>
+        <v>732</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="K129" s="22" t="s">
-        <v>770</v>
-      </c>
-      <c r="M129" s="2"/>
-      <c r="Q129" s="2" t="s">
-        <v>771</v>
+        <v>733</v>
+      </c>
+      <c r="K129" s="7" t="s">
+        <v>734</v>
       </c>
       <c r="R129" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="S129" s="3" t="s">
-        <v>772</v>
+        <v>316</v>
       </c>
       <c r="V129" s="5">
         <v>2</v>
@@ -8339,93 +8263,6 @@
         <v>57</v>
       </c>
       <c r="X129" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="J130" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="K130" s="22" t="s">
-        <v>777</v>
-      </c>
-      <c r="M130" s="2"/>
-      <c r="Q130" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="R130" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="S130" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="V130" s="5">
-        <v>2</v>
-      </c>
-      <c r="W130" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X130" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="I131" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="J131" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="K131" s="22" t="s">
-        <v>781</v>
-      </c>
-      <c r="M131" s="2"/>
-      <c r="Q131" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="R131" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V131" s="5">
-        <v>2</v>
-      </c>
-      <c r="W131" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X131" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -8443,144 +8280,146 @@
     <hyperlink ref="K55" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
     <hyperlink ref="K62" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
     <hyperlink ref="K63" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K68" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K69" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K70" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K71" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K72" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K73" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K74" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="K75" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="K76" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="K85" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="K86" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="K87" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="K88" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="K89" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="K90" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="K91" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="K92" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="K93" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="K94" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="K95" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="K96" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="K97" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="K98" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="K99" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="K109" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="K110" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K111" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="K112" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="K3" r:id="rId40" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
-    <hyperlink ref="K4" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
-    <hyperlink ref="K5" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
-    <hyperlink ref="K6" r:id="rId43" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
-    <hyperlink ref="K7" r:id="rId44" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
-    <hyperlink ref="K8" r:id="rId45" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
-    <hyperlink ref="K9" r:id="rId46" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
-    <hyperlink ref="K10" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
-    <hyperlink ref="K18" r:id="rId48" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
-    <hyperlink ref="K19" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
-    <hyperlink ref="K21" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
-    <hyperlink ref="K20" r:id="rId51" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
-    <hyperlink ref="K22" r:id="rId52" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
-    <hyperlink ref="M18" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
-    <hyperlink ref="K23" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
-    <hyperlink ref="K27" r:id="rId55" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
-    <hyperlink ref="K28" r:id="rId56" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
-    <hyperlink ref="M28" r:id="rId57" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
-    <hyperlink ref="K29" r:id="rId58" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
-    <hyperlink ref="K30" r:id="rId59" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
-    <hyperlink ref="K31" r:id="rId60" xr:uid="{7DA58717-212C-4C51-8E3B-A68A2F68CDF1}"/>
-    <hyperlink ref="K32" r:id="rId61" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
-    <hyperlink ref="K11" r:id="rId62" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
-    <hyperlink ref="K12" r:id="rId63" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
-    <hyperlink ref="K13" r:id="rId64" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
-    <hyperlink ref="K14" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
-    <hyperlink ref="K15" r:id="rId66" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
-    <hyperlink ref="K16" r:id="rId67" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
-    <hyperlink ref="K34" r:id="rId68" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
-    <hyperlink ref="K35" r:id="rId69" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
-    <hyperlink ref="K36" r:id="rId70" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
-    <hyperlink ref="K37" r:id="rId71" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
-    <hyperlink ref="K38" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
-    <hyperlink ref="K39" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
-    <hyperlink ref="K40" r:id="rId74" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
-    <hyperlink ref="K41" r:id="rId75" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
-    <hyperlink ref="K64" r:id="rId76" xr:uid="{4CD59BF1-312D-43DE-B499-693D63137AF4}"/>
-    <hyperlink ref="K65" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
-    <hyperlink ref="M65" r:id="rId78" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
-    <hyperlink ref="K66" r:id="rId79" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
-    <hyperlink ref="M66" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
-    <hyperlink ref="K67" r:id="rId81" xr:uid="{B437B26E-0D51-47C7-95F1-575E844ABAC9}"/>
-    <hyperlink ref="K56" r:id="rId82" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
-    <hyperlink ref="K57" r:id="rId83" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
-    <hyperlink ref="K60" r:id="rId84" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
-    <hyperlink ref="K59" r:id="rId85" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
-    <hyperlink ref="K58" r:id="rId86" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
-    <hyperlink ref="K61" r:id="rId87" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
-    <hyperlink ref="K101" r:id="rId88" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
-    <hyperlink ref="M102" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
-    <hyperlink ref="K102" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
-    <hyperlink ref="K103" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
-    <hyperlink ref="K104" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
-    <hyperlink ref="K108" r:id="rId93" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
-    <hyperlink ref="M105" r:id="rId94" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
-    <hyperlink ref="K105" r:id="rId95" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
-    <hyperlink ref="M107" r:id="rId96" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
-    <hyperlink ref="K106" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
-    <hyperlink ref="K107" r:id="rId98" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
-    <hyperlink ref="M100" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
-    <hyperlink ref="K100" r:id="rId100" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
-    <hyperlink ref="O100" r:id="rId101" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
-    <hyperlink ref="M103" r:id="rId102" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
-    <hyperlink ref="M92" r:id="rId103" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
-    <hyperlink ref="H62" r:id="rId104" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
-    <hyperlink ref="F62" r:id="rId105" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
-    <hyperlink ref="M62" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
-    <hyperlink ref="O62" r:id="rId107" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
-    <hyperlink ref="M77" r:id="rId108" xr:uid="{D4E31208-1729-474B-8613-04CAF9B8C025}"/>
-    <hyperlink ref="K77" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F8517-F853-4BC2-B1A3-2FAE2DAB6C9A}"/>
-    <hyperlink ref="K78" r:id="rId110" xr:uid="{61D85FE2-8DE3-4825-8491-0FE8BB47E3E1}"/>
-    <hyperlink ref="K79" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F36EF-2268-403C-A6B7-E58ACFE0642D}"/>
-    <hyperlink ref="K80" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B578D29-DC36-40D0-9947-A27ECB77A9CF}"/>
-    <hyperlink ref="K81" r:id="rId113" xr:uid="{57B652B7-7292-4EAC-B631-5C96CD2691B8}"/>
-    <hyperlink ref="K82" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9E7BF8E-41C2-4812-BC18-7E39D390B4DB}"/>
-    <hyperlink ref="H83" r:id="rId115" xr:uid="{0D8B79CB-4807-4139-98AD-96CFF7161C32}"/>
-    <hyperlink ref="K83" r:id="rId116" xr:uid="{B472E107-96D8-49AE-8D43-42D5D303C124}"/>
-    <hyperlink ref="M83" r:id="rId117" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9F3C81B0-62F8-4827-8155-5167D81363EB}"/>
-    <hyperlink ref="K84" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{841BFC94-91FA-4580-9546-612A91A5451F}"/>
-    <hyperlink ref="K42" r:id="rId119" xr:uid="{A95E99D8-AE5F-42F6-8170-14A073FA717E}"/>
-    <hyperlink ref="K43" r:id="rId120" xr:uid="{3ED1C2EF-8252-44A5-B551-1A43DD3F443F}"/>
-    <hyperlink ref="K44" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg/1280px-Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{751B356D-FC9A-4AD0-95E0-A8F1621E6F4F}"/>
-    <hyperlink ref="K45" r:id="rId122" xr:uid="{4DEEB737-1329-4597-919B-47ACF73325F8}"/>
-    <hyperlink ref="K46" r:id="rId123" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A5A253DF-D8FC-4464-832F-136C51B54ADE}"/>
-    <hyperlink ref="K47" r:id="rId124" xr:uid="{C26C012E-8A85-48D2-9B13-ADD3AEDEB4B0}"/>
-    <hyperlink ref="K48" r:id="rId125" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1D38CDDF-A325-49B8-BE2E-935C8E9D142B}"/>
-    <hyperlink ref="K51" r:id="rId126" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{471BE4AF-D2F1-433A-B3AC-795231C2AF30}"/>
-    <hyperlink ref="K49" r:id="rId127" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F1CACA00-310B-4B86-B079-D54654CC5BDD}"/>
-    <hyperlink ref="K50" r:id="rId128" display="https://upload.wikimedia.org/wikipedia/commons/3/39/Tomb_of_Lorenzo_the_Magnificent_and_Giuliano_de%27_Medici%2C_Sagrestia_Nuova%2C_Medici_Chapels%2C_San_Lorenzo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr" xr:uid="{0C4E85C8-1452-46E5-BAA1-9F134272222A}"/>
-    <hyperlink ref="K125" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K124" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K123" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K122" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K121" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K113" r:id="rId134" xr:uid="{B6FD0D1A-F931-482F-BA2B-9716DE045C80}"/>
-    <hyperlink ref="K114" r:id="rId135" xr:uid="{A861573B-3839-4318-BBAC-62B6CBA15FBD}"/>
-    <hyperlink ref="K115" r:id="rId136" xr:uid="{20DF76DA-E992-4E1D-A16E-22BE28C58483}"/>
-    <hyperlink ref="K116" r:id="rId137" xr:uid="{B1F4C251-A9D6-47B9-9136-6591399F5FD8}"/>
-    <hyperlink ref="K117" r:id="rId138" xr:uid="{D7FB2C86-EF32-4C98-B1CE-C0195DB8C4C6}"/>
-    <hyperlink ref="K118" r:id="rId139" xr:uid="{FE50DE30-8439-4013-8AF6-8076D7113E1F}"/>
-    <hyperlink ref="K119" r:id="rId140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDA4581C-5B96-4BDE-A351-45793B6F0EE8}"/>
-    <hyperlink ref="K120" r:id="rId141" xr:uid="{51ED3C40-5509-488A-841B-4E657C71C1FA}"/>
-    <hyperlink ref="K126" r:id="rId142" xr:uid="{F66E5A2C-A530-4199-AD87-0563CA44FE62}"/>
-    <hyperlink ref="K127" r:id="rId143" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D2E9D5D-E79A-4ADE-8B6A-4BF55D9DEAA1}"/>
-    <hyperlink ref="M127" r:id="rId144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{34AE602C-A94D-4947-A1E5-B9CB698DBCE9}"/>
-    <hyperlink ref="M128" r:id="rId145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7F17DDD6-358D-4949-BA30-757C7347BD64}"/>
-    <hyperlink ref="K128" r:id="rId146" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D595607E-E74C-423D-9949-0D9455718911}"/>
-    <hyperlink ref="K130" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46C65D64-593C-435B-985E-1487C0A3B6FF}"/>
-    <hyperlink ref="K131" r:id="rId148" xr:uid="{ABE79D9A-A8E7-4085-8D94-395C34C6D224}"/>
-    <hyperlink ref="K129" r:id="rId149" xr:uid="{29FC3D7D-FB63-4F1F-9086-C70F1D6EA865}"/>
+    <hyperlink ref="K67" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K68" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K69" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K70" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K71" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K72" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="K73" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K74" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="K83" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K85" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K86" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K87" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K88" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="K89" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K90" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="K91" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K92" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="K93" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K94" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="K95" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K96" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K97" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K107" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K108" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K109" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K110" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K3" r:id="rId38" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
+    <hyperlink ref="K4" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
+    <hyperlink ref="K5" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
+    <hyperlink ref="K6" r:id="rId41" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
+    <hyperlink ref="K7" r:id="rId42" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
+    <hyperlink ref="K8" r:id="rId43" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
+    <hyperlink ref="K9" r:id="rId44" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
+    <hyperlink ref="K10" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
+    <hyperlink ref="K18" r:id="rId46" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
+    <hyperlink ref="K19" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
+    <hyperlink ref="K21" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
+    <hyperlink ref="K20" r:id="rId49" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
+    <hyperlink ref="K22" r:id="rId50" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
+    <hyperlink ref="M18" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
+    <hyperlink ref="K23" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
+    <hyperlink ref="K27" r:id="rId53" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
+    <hyperlink ref="K28" r:id="rId54" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
+    <hyperlink ref="M28" r:id="rId55" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
+    <hyperlink ref="K29" r:id="rId56" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
+    <hyperlink ref="K30" r:id="rId57" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
+    <hyperlink ref="K32" r:id="rId58" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
+    <hyperlink ref="K11" r:id="rId59" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
+    <hyperlink ref="K12" r:id="rId60" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
+    <hyperlink ref="K13" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
+    <hyperlink ref="K14" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
+    <hyperlink ref="K15" r:id="rId63" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
+    <hyperlink ref="K16" r:id="rId64" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
+    <hyperlink ref="K34" r:id="rId65" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
+    <hyperlink ref="K35" r:id="rId66" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
+    <hyperlink ref="K36" r:id="rId67" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
+    <hyperlink ref="K37" r:id="rId68" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
+    <hyperlink ref="K38" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
+    <hyperlink ref="K39" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
+    <hyperlink ref="K40" r:id="rId71" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
+    <hyperlink ref="K41" r:id="rId72" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
+    <hyperlink ref="K65" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
+    <hyperlink ref="M65" r:id="rId74" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
+    <hyperlink ref="K66" r:id="rId75" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
+    <hyperlink ref="M66" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
+    <hyperlink ref="K56" r:id="rId77" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
+    <hyperlink ref="K57" r:id="rId78" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
+    <hyperlink ref="K60" r:id="rId79" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
+    <hyperlink ref="K59" r:id="rId80" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
+    <hyperlink ref="K58" r:id="rId81" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
+    <hyperlink ref="K61" r:id="rId82" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
+    <hyperlink ref="K99" r:id="rId83" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
+    <hyperlink ref="M100" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
+    <hyperlink ref="K100" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
+    <hyperlink ref="K101" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
+    <hyperlink ref="K102" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
+    <hyperlink ref="K106" r:id="rId88" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
+    <hyperlink ref="M103" r:id="rId89" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
+    <hyperlink ref="K103" r:id="rId90" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
+    <hyperlink ref="M105" r:id="rId91" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
+    <hyperlink ref="K104" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
+    <hyperlink ref="K105" r:id="rId93" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
+    <hyperlink ref="M98" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
+    <hyperlink ref="K98" r:id="rId95" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
+    <hyperlink ref="O98" r:id="rId96" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
+    <hyperlink ref="M101" r:id="rId97" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
+    <hyperlink ref="M90" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
+    <hyperlink ref="H62" r:id="rId99" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
+    <hyperlink ref="F62" r:id="rId100" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
+    <hyperlink ref="M62" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
+    <hyperlink ref="O62" r:id="rId102" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
+    <hyperlink ref="M75" r:id="rId103" xr:uid="{D4E31208-1729-474B-8613-04CAF9B8C025}"/>
+    <hyperlink ref="K75" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F8517-F853-4BC2-B1A3-2FAE2DAB6C9A}"/>
+    <hyperlink ref="K76" r:id="rId105" xr:uid="{61D85FE2-8DE3-4825-8491-0FE8BB47E3E1}"/>
+    <hyperlink ref="K77" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F36EF-2268-403C-A6B7-E58ACFE0642D}"/>
+    <hyperlink ref="K78" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B578D29-DC36-40D0-9947-A27ECB77A9CF}"/>
+    <hyperlink ref="K79" r:id="rId108" xr:uid="{57B652B7-7292-4EAC-B631-5C96CD2691B8}"/>
+    <hyperlink ref="K80" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9E7BF8E-41C2-4812-BC18-7E39D390B4DB}"/>
+    <hyperlink ref="H81" r:id="rId110" xr:uid="{0D8B79CB-4807-4139-98AD-96CFF7161C32}"/>
+    <hyperlink ref="K81" r:id="rId111" xr:uid="{B472E107-96D8-49AE-8D43-42D5D303C124}"/>
+    <hyperlink ref="M81" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9F3C81B0-62F8-4827-8155-5167D81363EB}"/>
+    <hyperlink ref="K82" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{841BFC94-91FA-4580-9546-612A91A5451F}"/>
+    <hyperlink ref="K42" r:id="rId114" xr:uid="{A95E99D8-AE5F-42F6-8170-14A073FA717E}"/>
+    <hyperlink ref="K43" r:id="rId115" xr:uid="{3ED1C2EF-8252-44A5-B551-1A43DD3F443F}"/>
+    <hyperlink ref="K44" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg/1280px-Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{751B356D-FC9A-4AD0-95E0-A8F1621E6F4F}"/>
+    <hyperlink ref="K45" r:id="rId117" xr:uid="{4DEEB737-1329-4597-919B-47ACF73325F8}"/>
+    <hyperlink ref="K46" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A5A253DF-D8FC-4464-832F-136C51B54ADE}"/>
+    <hyperlink ref="K47" r:id="rId119" xr:uid="{C26C012E-8A85-48D2-9B13-ADD3AEDEB4B0}"/>
+    <hyperlink ref="K48" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1D38CDDF-A325-49B8-BE2E-935C8E9D142B}"/>
+    <hyperlink ref="K51" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{471BE4AF-D2F1-433A-B3AC-795231C2AF30}"/>
+    <hyperlink ref="K49" r:id="rId122" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F1CACA00-310B-4B86-B079-D54654CC5BDD}"/>
+    <hyperlink ref="K50" r:id="rId123" display="https://upload.wikimedia.org/wikipedia/commons/3/39/Tomb_of_Lorenzo_the_Magnificent_and_Giuliano_de%27_Medici%2C_Sagrestia_Nuova%2C_Medici_Chapels%2C_San_Lorenzo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr" xr:uid="{0C4E85C8-1452-46E5-BAA1-9F134272222A}"/>
+    <hyperlink ref="K123" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K122" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K121" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K120" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K119" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K111" r:id="rId129" xr:uid="{B6FD0D1A-F931-482F-BA2B-9716DE045C80}"/>
+    <hyperlink ref="K112" r:id="rId130" xr:uid="{A861573B-3839-4318-BBAC-62B6CBA15FBD}"/>
+    <hyperlink ref="K113" r:id="rId131" xr:uid="{20DF76DA-E992-4E1D-A16E-22BE28C58483}"/>
+    <hyperlink ref="K114" r:id="rId132" xr:uid="{B1F4C251-A9D6-47B9-9136-6591399F5FD8}"/>
+    <hyperlink ref="K115" r:id="rId133" xr:uid="{D7FB2C86-EF32-4C98-B1CE-C0195DB8C4C6}"/>
+    <hyperlink ref="K116" r:id="rId134" xr:uid="{FE50DE30-8439-4013-8AF6-8076D7113E1F}"/>
+    <hyperlink ref="K117" r:id="rId135" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDA4581C-5B96-4BDE-A351-45793B6F0EE8}"/>
+    <hyperlink ref="K118" r:id="rId136" xr:uid="{51ED3C40-5509-488A-841B-4E657C71C1FA}"/>
+    <hyperlink ref="K124" r:id="rId137" xr:uid="{F66E5A2C-A530-4199-AD87-0563CA44FE62}"/>
+    <hyperlink ref="K125" r:id="rId138" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D2E9D5D-E79A-4ADE-8B6A-4BF55D9DEAA1}"/>
+    <hyperlink ref="M125" r:id="rId139" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{34AE602C-A94D-4947-A1E5-B9CB698DBCE9}"/>
+    <hyperlink ref="M126" r:id="rId140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7F17DDD6-358D-4949-BA30-757C7347BD64}"/>
+    <hyperlink ref="K126" r:id="rId141" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D595607E-E74C-423D-9949-0D9455718911}"/>
+    <hyperlink ref="K128" r:id="rId142" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46C65D64-593C-435B-985E-1487C0A3B6FF}"/>
+    <hyperlink ref="K129" r:id="rId143" xr:uid="{ABE79D9A-A8E7-4085-8D94-395C34C6D224}"/>
+    <hyperlink ref="K127" r:id="rId144" xr:uid="{29FC3D7D-FB63-4F1F-9086-C70F1D6EA865}"/>
+    <hyperlink ref="F113" r:id="rId145" xr:uid="{2D04002B-8C33-4E33-A9BC-035BE367ACFB}"/>
+    <hyperlink ref="F114:F116" r:id="rId146" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Loggetta_Sansovino_a_Venezia.jpg/1280px-Loggetta_Sansovino_a_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{83BABDFD-B232-49ED-9178-8A0C58DB9E5B}"/>
+    <hyperlink ref="K84" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg/1280px-San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B16DCA1D-61FA-47E3-AEC7-CAF732E10DD2}"/>
+    <hyperlink ref="F77" r:id="rId148" xr:uid="{F860FC30-4D00-4CD5-A8BB-B4414CC5D08F}"/>
+    <hyperlink ref="M51" r:id="rId149" xr:uid="{15D2D5F0-5EFB-40A5-BBAA-91DD811E84CC}"/>
+    <hyperlink ref="M27" r:id="rId150" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56BAEEFF-2EBF-4B02-97DC-C24781018097}"/>
+    <hyperlink ref="K31" r:id="rId151" xr:uid="{2CFFED1D-5528-4009-9B87-0FD8518C9CC4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2ED469C-58E9-4EE9-800A-F68E79966528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C572739D-C806-4C49-ADDC-DCF4DEEEA371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16200" yWindow="0" windowWidth="12660" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="818">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -674,15 +674,9 @@
     <t>Eglise Saint-Léonard</t>
   </si>
   <si>
-    <t>Musée du diocèse de Rottenburg</t>
-  </si>
-  <si>
     <t>Basilique-cathédrale Nuestra Señora del Pilar</t>
   </si>
   <si>
-    <t>Rathausplatz</t>
-  </si>
-  <si>
     <t>Taft Museum of Art</t>
   </si>
   <si>
@@ -782,9 +776,6 @@
     <t>"Tabernacle"</t>
   </si>
   <si>
-    <t>"Saint Sébastien"</t>
-  </si>
-  <si>
     <t>"Retable majeur du Pilar"</t>
   </si>
   <si>
@@ -896,9 +887,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/Retablo_Mayor_Pilar_Zaragoza_Damian_Forment.jpg/1280px-Retablo_Mayor_Pilar_Zaragoza_Damian_Forment.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/Augsburg_Augustusbrunnen_4.JPG/1280px-Augsburg_Augustusbrunnen_4.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/30/Fontaine_des_Innocents%2C_Paris_1st_001.JPG/1280px-Fontaine_des_Innocents%2C_Paris_1st_001.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -998,9 +986,6 @@
     <t>Marbre et albâtre</t>
   </si>
   <si>
-    <t>Bois</t>
-  </si>
-  <si>
     <t>Albâtre</t>
   </si>
   <si>
@@ -1799,9 +1784,6 @@
     <t>"La Fontaine des Tortues"</t>
   </si>
   <si>
-    <t>"La Fontaine d'Auguste"</t>
-  </si>
-  <si>
     <t>"La Résurrection"</t>
   </si>
   <si>
@@ -2343,6 +2325,168 @@
   </si>
   <si>
     <t>Junon</t>
+  </si>
+  <si>
+    <t>Place de la Mairie</t>
+  </si>
+  <si>
+    <t>La Fontaine d'Auguste</t>
+  </si>
+  <si>
+    <t>Augustusbrunnen</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/71/Augsburg_Augustusbrunnen_4.JPG/1280px-Augsburg_Augustusbrunnen_4.JPG</t>
+  </si>
+  <si>
+    <t>450 cm environ</t>
+  </si>
+  <si>
+    <t>1593-1595</t>
+  </si>
+  <si>
+    <t>Munich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Église Saint-Michel </t>
+  </si>
+  <si>
+    <t>Façade extérieure</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/89/20060416-Michaelskirche_Muenchen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>L'Archange Saint Michel terrassant le Démon</t>
+  </si>
+  <si>
+    <t>St. Michael im Kampf mit dem Drachen</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg/960px-M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>380 cm</t>
+  </si>
+  <si>
+    <t>1589-1593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residence </t>
+  </si>
+  <si>
+    <t>Wittelsbacherbrunnen</t>
+  </si>
+  <si>
+    <t>Fontaine des Wittelsbach</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ad/Wittelsbacherbrunnen_Residenz_Muenchen-2.jpg/960px-Wittelsbacherbrunnen_Residenz_Muenchen-2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1593-1596</t>
+  </si>
+  <si>
+    <t>Ange à la vasque d'eau bénite</t>
+  </si>
+  <si>
+    <t>Kreuzigungsgruppe</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/St._Michael_-_Munich_-_Weihwasser-Engel.jpg/960px-St._Michael_-_Munich_-_Weihwasser-Engel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Rottenburg am Neckar</t>
+  </si>
+  <si>
+    <t>Musée du diocèse de Rottenburg (Diözesanmuseum)</t>
+  </si>
+  <si>
+    <t>Heiliger Sebastian</t>
+  </si>
+  <si>
+    <t>Bois (buis)</t>
+  </si>
+  <si>
+    <t>vers 1540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musée national germanique </t>
+  </si>
+  <si>
+    <t>Allégorie de la Vanité (Femme nue au miroir)</t>
+  </si>
+  <si>
+    <t>Vanitas (Nackte Frau mit Spiegel)</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
+  </si>
+  <si>
+    <t>Cette plaque de bronze fait partie de la série des" Sept pêchés capitaux"</t>
+  </si>
+  <si>
+    <t>Allégorie de l'Envie</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de</t>
+  </si>
+  <si>
+    <t>1534-1535</t>
+  </si>
+  <si>
+    <t>Fembohaus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statue d'Apollon </t>
+  </si>
+  <si>
+    <t>Statue des Apollo (Apollobrunnen)</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg/960px-Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bronze fondu</t>
+  </si>
+  <si>
+    <t>105 cm</t>
+  </si>
+  <si>
+    <t>1526-1533</t>
+  </si>
+  <si>
+    <t>Château Tucher</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/2/27/Tucherschloss--.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Salle Hirsvogel</t>
+  </si>
+  <si>
+    <t>Portail d'accès au jardin conçu comme une fausse chaminée.</t>
+  </si>
+  <si>
+    <t>Prunkkamin im Hirschvogelsaal</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg/1280px-N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Salle contruite en 1534 pour la maison du marchand Hirschvogel, détruite en 1945 et reconstruite au château Tucher à l'identique</t>
+  </si>
+  <si>
+    <t>Pierre calcaire sculptée (style Renaissance)</t>
+  </si>
+  <si>
+    <t>380 cm environ</t>
+  </si>
+  <si>
+    <t>Boiseries de la salle</t>
+  </si>
+  <si>
+    <t>Bois sculpté et peint</t>
   </si>
 </sst>
 </file>
@@ -2806,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y129"/>
+  <dimension ref="A1:Z137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -2995,22 +3139,22 @@
         <v>195</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="S3" s="3">
         <v>560</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
@@ -3027,31 +3171,31 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="R4" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>347</v>
-      </c>
       <c r="V4" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
@@ -3068,31 +3212,31 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S5" s="3">
         <v>262</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
@@ -3109,31 +3253,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S6" s="3">
         <v>139</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
@@ -3150,25 +3294,25 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>168</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
@@ -3185,28 +3329,28 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
@@ -3223,28 +3367,28 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
@@ -3261,31 +3405,31 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="R10" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="S10" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="V10" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>378</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
@@ -3302,7 +3446,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>169</v>
@@ -3311,22 +3455,22 @@
         <v>196</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
@@ -3343,7 +3487,7 @@
         <v>71</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>169</v>
@@ -3352,22 +3496,22 @@
         <v>196</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>23</v>
@@ -3384,31 +3528,31 @@
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>23</v>
@@ -3425,31 +3569,31 @@
         <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>454</v>
-      </c>
       <c r="K14" s="7" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>23</v>
@@ -3466,35 +3610,35 @@
         <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="K15" s="7" t="s">
         <v>456</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>461</v>
       </c>
       <c r="M15" s="7"/>
       <c r="Q15" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>23</v>
@@ -3511,7 +3655,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>174</v>
@@ -3520,22 +3664,22 @@
         <v>210</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>23</v>
@@ -3558,10 +3702,10 @@
         <v>197</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>31</v>
@@ -3593,25 +3737,25 @@
         <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="V18" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
@@ -3628,25 +3772,25 @@
         <v>73</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>168</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="L19" s="21"/>
       <c r="M19" s="21"/>
@@ -3655,15 +3799,15 @@
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
       <c r="R19" s="11" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S19" s="13">
         <v>224</v>
       </c>
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
-      <c r="V19" s="13" t="s">
-        <v>378</v>
+      <c r="V19" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="W19" s="11" t="s">
         <v>25</v>
@@ -3681,7 +3825,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>168</v>
@@ -3690,25 +3834,25 @@
         <v>198</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>25</v>
@@ -3725,22 +3869,22 @@
         <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S21" s="3">
         <v>78</v>
@@ -3749,7 +3893,7 @@
         <v>75</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
@@ -3766,34 +3910,34 @@
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>25</v>
@@ -3810,34 +3954,34 @@
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>407</v>
-      </c>
       <c r="V23" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>25</v>
@@ -3863,16 +4007,16 @@
         <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="V24" s="4">
         <v>1</v>
@@ -3901,16 +4045,16 @@
         <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="V25" s="6">
         <v>3</v>
@@ -3936,13 +4080,13 @@
         <v>199</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="V26" s="6">
         <v>3</v>
@@ -3968,41 +4112,41 @@
         <v>170</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="N27" s="11"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="S27" s="13">
         <v>150</v>
       </c>
       <c r="T27" s="13"/>
       <c r="U27" s="13"/>
-      <c r="V27" s="13">
+      <c r="V27" s="5">
         <v>2</v>
       </c>
       <c r="W27" s="11" t="s">
@@ -4027,28 +4171,28 @@
         <v>170</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="T28" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="U28" s="3">
         <v>32</v>
@@ -4071,28 +4215,28 @@
         <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="V29" s="5">
         <v>2</v>
@@ -4112,25 +4256,25 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K30" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="V30" s="5">
         <v>2</v>
@@ -4156,25 +4300,25 @@
         <v>170</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="V31" s="5">
         <v>2</v>
@@ -4194,25 +4338,25 @@
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="K32" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>441</v>
-      </c>
       <c r="R32" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="V32" s="5">
         <v>2</v>
@@ -4238,13 +4382,13 @@
         <v>200</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="V33" s="6">
         <v>3</v>
@@ -4273,22 +4417,22 @@
         <v>201</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="V34" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -4305,31 +4449,31 @@
         <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="S35" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="V35" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -4346,31 +4490,31 @@
         <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="V36" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4390,28 +4534,28 @@
         <v>127</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="R37" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="S37" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="V37" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4428,7 +4572,7 @@
         <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>168</v>
@@ -4437,22 +4581,22 @@
         <v>195</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="V38" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4469,31 +4613,31 @@
         <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="V39" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4510,31 +4654,31 @@
         <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4551,7 +4695,7 @@
         <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>168</v>
@@ -4560,22 +4704,22 @@
         <v>201</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="V41" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4589,25 +4733,25 @@
         <v>33</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S42" s="3">
         <v>517</v>
@@ -4619,13 +4763,13 @@
         <v>140</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W42" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4633,25 +4777,25 @@
         <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="I43" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="K43" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>641</v>
-      </c>
       <c r="R43" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S43" s="3">
         <v>128</v>
@@ -4663,13 +4807,13 @@
         <v>63</v>
       </c>
       <c r="V43" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W43" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4677,43 +4821,43 @@
         <v>33</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W44" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4721,25 +4865,25 @@
         <v>33</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S45" s="3">
         <v>780</v>
@@ -4748,13 +4892,13 @@
         <v>640</v>
       </c>
       <c r="V45" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W45" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4762,10 +4906,10 @@
         <v>33</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>171</v>
@@ -4774,13 +4918,13 @@
         <v>203</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S46" s="3">
         <v>228</v>
@@ -4792,13 +4936,13 @@
         <v>53</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4806,10 +4950,10 @@
         <v>33</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>171</v>
@@ -4818,16 +4962,16 @@
         <v>203</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="T47" s="3">
         <v>49</v>
@@ -4836,13 +4980,13 @@
         <v>75</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4850,28 +4994,28 @@
         <v>33</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="T48" s="3">
         <v>75</v>
@@ -4880,39 +5024,39 @@
         <v>60</v>
       </c>
       <c r="V48" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S49" s="3">
         <v>650</v>
@@ -4921,86 +5065,86 @@
         <v>470</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S51" s="3">
         <v>277</v>
@@ -5012,16 +5156,16 @@
         <v>125</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>34</v>
       </c>
@@ -5039,11 +5183,11 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
@@ -5052,10 +5196,10 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
@@ -5069,8 +5213,9 @@
         <v>79</v>
       </c>
       <c r="Y52" s="2"/>
-    </row>
-    <row r="53" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z52" s="20"/>
+    </row>
+    <row r="53" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>35</v>
       </c>
@@ -5087,16 +5232,16 @@
         <v>198</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="V53" s="6">
         <v>3</v>
@@ -5108,7 +5253,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>36</v>
       </c>
@@ -5122,19 +5267,19 @@
         <v>168</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="V54" s="6">
         <v>3</v>
@@ -5146,7 +5291,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>32</v>
       </c>
@@ -5163,13 +5308,13 @@
         <v>205</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="V55" s="6">
         <v>3</v>
@@ -5181,7 +5326,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>37</v>
       </c>
@@ -5195,22 +5340,22 @@
         <v>170</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="S56" s="3">
         <v>190</v>
@@ -5231,7 +5376,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>37</v>
       </c>
@@ -5239,28 +5384,28 @@
         <v>83</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="V57" s="5">
         <v>2</v>
@@ -5272,7 +5417,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>37</v>
       </c>
@@ -5280,31 +5425,31 @@
         <v>83</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="K58" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>535</v>
-      </c>
       <c r="Q58" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="V58" s="5">
         <v>2</v>
@@ -5316,7 +5461,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>37</v>
       </c>
@@ -5324,34 +5469,34 @@
         <v>83</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="V59" s="5">
         <v>2</v>
@@ -5363,7 +5508,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>37</v>
       </c>
@@ -5371,28 +5516,28 @@
         <v>83</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="K60" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>547</v>
-      </c>
       <c r="R60" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="V60" s="5">
         <v>2</v>
@@ -5404,7 +5549,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>37</v>
       </c>
@@ -5412,28 +5557,28 @@
         <v>83</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="V61" s="5">
         <v>2</v>
@@ -5445,7 +5590,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:25" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>36</v>
       </c>
@@ -5462,37 +5607,37 @@
         <v>206</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="J62" s="11"/>
       <c r="K62" s="12" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L62" s="21"/>
       <c r="M62" s="12" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="N62" s="11"/>
       <c r="O62" s="19" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="P62" s="11"/>
       <c r="Q62" s="11"/>
       <c r="R62" s="11" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S62" s="13">
         <v>182</v>
       </c>
       <c r="T62" s="13"/>
       <c r="U62" s="13"/>
-      <c r="V62" s="13">
+      <c r="V62" s="6">
         <v>3</v>
       </c>
       <c r="W62" s="11" t="s">
@@ -5503,7 +5648,7 @@
       </c>
       <c r="Y62" s="11"/>
     </row>
-    <row r="63" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>38</v>
       </c>
@@ -5517,10 +5662,10 @@
         <v>207</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="R63" s="2" t="s">
         <v>31</v>
@@ -5535,7 +5680,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>39</v>
       </c>
@@ -5552,22 +5697,22 @@
         <v>203</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="V64" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W64" s="2" t="s">
         <v>39</v>
@@ -5584,31 +5729,31 @@
         <v>86</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>178</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="V65" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>39</v>
@@ -5625,31 +5770,31 @@
         <v>86</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>178</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="V66" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W66" s="2" t="s">
         <v>39</v>
@@ -5672,13 +5817,13 @@
         <v>208</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="V67" s="6">
         <v>3</v>
@@ -5707,13 +5852,13 @@
         <v>209</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="V68" s="5">
         <v>2</v>
@@ -5742,13 +5887,13 @@
         <v>210</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="V69" s="6">
         <v>3</v>
@@ -5777,13 +5922,13 @@
         <v>211</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="V70" s="6">
         <v>3</v>
@@ -5812,13 +5957,13 @@
         <v>212</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="V71" s="6">
         <v>3</v>
@@ -5840,21 +5985,30 @@
       <c r="C72" s="2" t="s">
         <v>138</v>
       </c>
+      <c r="D72" s="2" t="s">
+        <v>787</v>
+      </c>
       <c r="E72" s="2" t="s">
-        <v>213</v>
+        <v>788</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>249</v>
+        <v>427</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>789</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>285</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="M72" s="2"/>
       <c r="R72" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>337</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2"/>
       <c r="V72" s="5">
         <v>2</v>
       </c>
@@ -5867,552 +6021,570 @@
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>141</v>
+        <v>791</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>214</v>
+        <v>792</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>250</v>
+        <v>793</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>794</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>286</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="M73" s="2"/>
       <c r="R73" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="V73" s="6">
-        <v>3</v>
+        <v>311</v>
+      </c>
+      <c r="S73" s="2">
+        <v>8</v>
+      </c>
+      <c r="T73" s="2">
+        <v>5</v>
+      </c>
+      <c r="U73" s="2"/>
+      <c r="V73" s="5">
+        <v>2</v>
       </c>
       <c r="W73" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>142</v>
+        <v>791</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>215</v>
+        <v>792</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>588</v>
+        <v>797</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>287</v>
-      </c>
+        <v>798</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="M74" s="2"/>
       <c r="R74" s="2" t="s">
-        <v>315</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="S74" s="2">
+        <v>8</v>
+      </c>
+      <c r="T74" s="2">
+        <v>5</v>
+      </c>
+      <c r="U74" s="2"/>
       <c r="V74" s="5">
         <v>2</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>599</v>
+        <v>799</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>203</v>
+        <v>800</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="K75" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="M75" s="15" t="s">
-        <v>288</v>
-      </c>
+        <v>801</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="M75" s="2"/>
       <c r="R75" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S75" s="3">
-        <v>73</v>
-      </c>
-      <c r="T75" s="3">
-        <v>195</v>
-      </c>
-      <c r="U75" s="3">
-        <v>12</v>
-      </c>
-      <c r="V75" s="4">
-        <v>1</v>
+        <v>804</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="T75" s="2"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="5">
+        <v>2</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>599</v>
+        <v>806</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>203</v>
+        <v>807</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>808</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="K76" s="15" t="s">
-        <v>603</v>
-      </c>
-      <c r="M76" s="16"/>
+        <v>810</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="M76" s="2"/>
       <c r="R76" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="S76" s="3">
-        <v>210</v>
-      </c>
-      <c r="T76" s="3">
-        <v>60</v>
-      </c>
-      <c r="U76" s="3">
-        <v>65</v>
-      </c>
-      <c r="V76" s="4">
-        <v>1</v>
+        <v>814</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="T76" s="2"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="5">
+        <v>2</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>605</v>
+        <v>806</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>203</v>
+        <v>807</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>754</v>
+        <v>808</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="K77" s="15" t="s">
-        <v>607</v>
+        <v>816</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>812</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="M77" s="16"/>
+        <v>813</v>
+      </c>
+      <c r="M77" s="2"/>
       <c r="R77" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S77" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="T77" s="3">
-        <v>182</v>
-      </c>
-      <c r="U77" s="3">
-        <v>7</v>
-      </c>
-      <c r="V77" s="4">
-        <v>1</v>
+        <v>817</v>
+      </c>
+      <c r="S77" s="2"/>
+      <c r="T77" s="2"/>
+      <c r="U77" s="2"/>
+      <c r="V77" s="5">
+        <v>2</v>
       </c>
       <c r="W77" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="X77" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>605</v>
+        <v>141</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="K78" s="15" t="s">
-        <v>610</v>
-      </c>
-      <c r="L78" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="M78" s="16"/>
+        <v>247</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>283</v>
+      </c>
       <c r="R78" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S78" s="3">
-        <v>79</v>
-      </c>
-      <c r="T78" s="3">
-        <v>56</v>
-      </c>
-      <c r="U78" s="3">
-        <v>11</v>
-      </c>
-      <c r="V78" s="4">
-        <v>1</v>
+        <v>317</v>
+      </c>
+      <c r="V78" s="6">
+        <v>3</v>
       </c>
       <c r="W78" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="X78" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>611</v>
+        <v>142</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>612</v>
+        <v>178</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>613</v>
+        <v>764</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="K79" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="M79" s="16"/>
+        <v>765</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="K79" s="18" t="s">
+        <v>767</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
       <c r="R79" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="S79" s="3">
-        <v>700</v>
-      </c>
-      <c r="T79" s="3">
-        <v>366</v>
-      </c>
-      <c r="U79" s="3">
+        <v>311</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="T79" s="2"/>
+      <c r="U79" s="2"/>
+      <c r="V79" s="5">
+        <v>2</v>
+      </c>
+      <c r="W79" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X79" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="V79" s="4">
-        <v>1</v>
-      </c>
-      <c r="W79" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X79" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>616</v>
+        <v>769</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>171</v>
+        <v>770</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>741</v>
+        <v>771</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>617</v>
+        <v>772</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>773</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="K80" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="M80" s="16"/>
+        <v>774</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="K80" s="18" t="s">
+        <v>776</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
       <c r="R80" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S80" s="3">
-        <v>215</v>
-      </c>
-      <c r="T80" s="3">
-        <v>95</v>
-      </c>
-      <c r="U80" s="3">
-        <v>6</v>
-      </c>
-      <c r="V80" s="4">
-        <v>1</v>
+        <v>311</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="T80" s="2"/>
+      <c r="U80" s="2"/>
+      <c r="V80" s="5">
+        <v>2</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="X80" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>620</v>
+        <v>778</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>171</v>
+        <v>770</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>621</v>
+        <v>779</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="H81" s="15" t="s">
-        <v>623</v>
+        <v>780</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="K81" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="L81" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="M81" s="17" t="s">
-        <v>626</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="K81" s="18" t="s">
+        <v>782</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
       <c r="R81" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S81" s="3">
-        <v>205</v>
-      </c>
-      <c r="T81" s="3">
-        <v>90</v>
-      </c>
-      <c r="U81" s="3">
-        <v>6</v>
-      </c>
-      <c r="V81" s="4">
-        <v>1</v>
+        <v>311</v>
+      </c>
+      <c r="S81" s="2"/>
+      <c r="T81" s="2"/>
+      <c r="U81" s="2"/>
+      <c r="V81" s="5">
+        <v>2</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D82"/>
+        <v>783</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>770</v>
+      </c>
       <c r="E82" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>427</v>
+        <v>771</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="J82"/>
-      <c r="K82" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="L82" s="8" t="s">
-        <v>630</v>
-      </c>
-      <c r="M82" s="16"/>
+        <v>784</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="K82" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
       <c r="R82" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S82" s="3">
-        <v>80</v>
-      </c>
-      <c r="T82" s="3">
-        <v>202</v>
-      </c>
-      <c r="U82" s="3">
-        <v>8</v>
-      </c>
-      <c r="V82" s="4">
-        <v>1</v>
+        <v>311</v>
+      </c>
+      <c r="S82" s="2">
+        <v>180</v>
+      </c>
+      <c r="T82" s="2"/>
+      <c r="U82" s="2"/>
+      <c r="V82" s="5">
+        <v>2</v>
       </c>
       <c r="W82" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>144</v>
+        <v>593</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="K83" s="7" t="s">
-        <v>289</v>
+        <v>594</v>
+      </c>
+      <c r="K83" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="M83" s="15" t="s">
+        <v>284</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>323</v>
+        <v>312</v>
+      </c>
+      <c r="S83" s="3">
+        <v>73</v>
+      </c>
+      <c r="T83" s="3">
+        <v>195</v>
+      </c>
+      <c r="U83" s="3">
+        <v>12</v>
       </c>
       <c r="V83" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>145</v>
+        <v>593</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K84" s="7" t="s">
-        <v>752</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="K84" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="M84" s="16"/>
       <c r="R84" s="2" t="s">
-        <v>318</v>
+        <v>598</v>
       </c>
       <c r="S84" s="3">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="T84" s="3">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="U84" s="3">
-        <v>160</v>
-      </c>
-      <c r="V84" s="6">
-        <v>3</v>
+        <v>65</v>
+      </c>
+      <c r="V84" s="4">
+        <v>1</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>146</v>
+        <v>599</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>171</v>
@@ -6420,856 +6592,852 @@
       <c r="E85" s="2" t="s">
         <v>203</v>
       </c>
+      <c r="F85" s="18" t="s">
+        <v>748</v>
+      </c>
       <c r="I85" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="K85" s="7" t="s">
-        <v>290</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="M85" s="16"/>
       <c r="R85" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="S85" s="3">
-        <v>26</v>
+        <v>312</v>
+      </c>
+      <c r="S85" s="3" t="s">
+        <v>602</v>
       </c>
       <c r="T85" s="3">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="U85" s="3">
-        <v>14</v>
-      </c>
-      <c r="V85" s="6">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="V85" s="4">
+        <v>1</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>147</v>
+        <v>599</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="K86" s="7" t="s">
-        <v>291</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="K86" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="L86" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="M86" s="16"/>
       <c r="R86" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V86" s="6">
-        <v>3</v>
+        <v>312</v>
+      </c>
+      <c r="S86" s="3">
+        <v>79</v>
+      </c>
+      <c r="T86" s="3">
+        <v>56</v>
+      </c>
+      <c r="U86" s="3">
+        <v>11</v>
+      </c>
+      <c r="V86" s="4">
+        <v>1</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>129</v>
+        <v>605</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>181</v>
+        <v>606</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>219</v>
+        <v>607</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="K87" s="7" t="s">
-        <v>292</v>
-      </c>
+        <v>608</v>
+      </c>
+      <c r="K87" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="M87" s="16"/>
       <c r="R87" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="S87" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="V87" s="6">
-        <v>3</v>
+        <v>321</v>
+      </c>
+      <c r="S87" s="3">
+        <v>700</v>
+      </c>
+      <c r="T87" s="3">
+        <v>366</v>
+      </c>
+      <c r="U87" s="3">
+        <v>93</v>
+      </c>
+      <c r="V87" s="4">
+        <v>1</v>
       </c>
       <c r="W87" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>148</v>
+        <v>610</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>202</v>
+        <v>735</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>611</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K88" s="7" t="s">
-        <v>293</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="M88" s="16"/>
       <c r="R88" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="V88" s="6">
-        <v>3</v>
+        <v>31</v>
+      </c>
+      <c r="S88" s="3">
+        <v>215</v>
+      </c>
+      <c r="T88" s="3">
+        <v>95</v>
+      </c>
+      <c r="U88" s="3">
+        <v>6</v>
+      </c>
+      <c r="V88" s="4">
+        <v>1</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>149</v>
+        <v>614</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>220</v>
+        <v>615</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>617</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="K89" s="7" t="s">
-        <v>294</v>
+        <v>618</v>
+      </c>
+      <c r="K89" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="M89" s="17" t="s">
+        <v>620</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="V89" s="6">
-        <v>3</v>
+        <v>31</v>
+      </c>
+      <c r="S89" s="3">
+        <v>205</v>
+      </c>
+      <c r="T89" s="3">
+        <v>90</v>
+      </c>
+      <c r="U89" s="3">
+        <v>6</v>
+      </c>
+      <c r="V89" s="4">
+        <v>1</v>
       </c>
       <c r="W89" s="2" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-      <c r="H90" s="11"/>
-      <c r="I90" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="J90" s="11"/>
-      <c r="K90" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="L90" s="21" t="s">
-        <v>593</v>
-      </c>
-      <c r="M90" s="12" t="s">
-        <v>592</v>
-      </c>
-      <c r="N90" s="11"/>
-      <c r="O90" s="11"/>
-      <c r="P90" s="11"/>
-      <c r="Q90" s="11"/>
-      <c r="R90" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="S90" s="13"/>
-      <c r="T90" s="13"/>
-      <c r="U90" s="13"/>
-      <c r="V90" s="13">
-        <v>3</v>
-      </c>
-      <c r="W90" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="X90" s="11" t="s">
-        <v>102</v>
+      <c r="A90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D90"/>
+      <c r="E90" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="J90"/>
+      <c r="K90" s="15" t="s">
+        <v>623</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="M90" s="16"/>
+      <c r="R90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S90" s="3">
+        <v>80</v>
+      </c>
+      <c r="T90" s="3">
+        <v>202</v>
+      </c>
+      <c r="U90" s="3">
+        <v>8</v>
+      </c>
+      <c r="V90" s="4">
+        <v>1</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S91" s="3">
-        <v>113</v>
-      </c>
-      <c r="T91" s="3">
-        <v>59</v>
-      </c>
-      <c r="U91" s="3">
-        <v>40</v>
-      </c>
-      <c r="V91" s="5">
-        <v>2</v>
+        <v>318</v>
+      </c>
+      <c r="V91" s="4">
+        <v>3</v>
       </c>
       <c r="W91" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>738</v>
+        <v>249</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>297</v>
+        <v>746</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="V92" s="5">
-        <v>2</v>
+        <v>314</v>
+      </c>
+      <c r="S92" s="3">
+        <v>224</v>
+      </c>
+      <c r="T92" s="3">
+        <v>126</v>
+      </c>
+      <c r="U92" s="3">
+        <v>160</v>
+      </c>
+      <c r="V92" s="6">
+        <v>3</v>
       </c>
       <c r="W92" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>315</v>
+        <v>578</v>
+      </c>
+      <c r="S93" s="3">
+        <v>26</v>
+      </c>
+      <c r="T93" s="3">
+        <v>22</v>
+      </c>
+      <c r="U93" s="3">
+        <v>14</v>
       </c>
       <c r="V93" s="6">
         <v>3</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>258</v>
+        <v>585</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>326</v>
+        <v>31</v>
       </c>
       <c r="V94" s="6">
         <v>3</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
+      </c>
+      <c r="S95" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="V95" s="6">
         <v>3</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>735</v>
+        <v>251</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="V96" s="6">
         <v>3</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>259</v>
+        <v>582</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="V97" s="6">
         <v>3</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="L98" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="M98" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="O98" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="R98" s="2" t="s">
+      <c r="A98" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="J98" s="11"/>
+      <c r="K98" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="L98" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="M98" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="N98" s="11"/>
+      <c r="O98" s="11"/>
+      <c r="P98" s="11"/>
+      <c r="Q98" s="11"/>
+      <c r="R98" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="S98" s="3">
-        <v>450</v>
-      </c>
-      <c r="T98" s="3">
-        <v>350</v>
-      </c>
-      <c r="U98" s="3">
-        <v>250</v>
-      </c>
-      <c r="V98" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="W98" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X98" s="2" t="s">
-        <v>109</v>
+      <c r="S98" s="13"/>
+      <c r="T98" s="13"/>
+      <c r="U98" s="13"/>
+      <c r="V98" s="6">
+        <v>3</v>
+      </c>
+      <c r="W98" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="X98" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C99" s="9">
-        <v>1583</v>
+        <v>103</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>551</v>
+        <v>253</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="M99" s="7"/>
-      <c r="O99" s="7"/>
+        <v>292</v>
+      </c>
       <c r="R99" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="S99" s="3">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="T99" s="3">
-        <v>223</v>
+        <v>59</v>
       </c>
       <c r="U99" s="3">
-        <v>166</v>
-      </c>
-      <c r="V99" s="4">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="V99" s="5">
+        <v>2</v>
       </c>
       <c r="W99" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>556</v>
+        <v>732</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="M100" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="O100" s="8"/>
+        <v>293</v>
+      </c>
       <c r="R100" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="T100" s="3">
-        <v>75</v>
-      </c>
-      <c r="U100" s="3">
-        <v>75</v>
-      </c>
-      <c r="V100" s="4" t="s">
-        <v>378</v>
+        <v>320</v>
+      </c>
+      <c r="V100" s="5">
+        <v>2</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C101" s="9">
-        <v>1586</v>
+        <v>104</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>560</v>
+        <v>254</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="L101" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="M101" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="O101" s="8"/>
+        <v>294</v>
+      </c>
       <c r="R101" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="T101" s="3">
-        <v>120</v>
-      </c>
-      <c r="U101" s="3">
-        <v>81</v>
-      </c>
-      <c r="V101" s="4" t="s">
-        <v>378</v>
+        <v>311</v>
+      </c>
+      <c r="V101" s="6">
+        <v>3</v>
       </c>
       <c r="W101" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>565</v>
+        <v>125</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>566</v>
+        <v>255</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="O102" s="8"/>
+        <v>295</v>
+      </c>
       <c r="R102" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="V102" s="4" t="s">
-        <v>378</v>
+        <v>321</v>
+      </c>
+      <c r="V102" s="6">
+        <v>3</v>
       </c>
       <c r="W102" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>568</v>
+        <v>154</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>569</v>
+        <v>730</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="M103" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="O103" s="8"/>
+        <v>296</v>
+      </c>
       <c r="R103" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S103" s="3">
-        <v>83</v>
-      </c>
-      <c r="T103" s="3">
-        <v>191</v>
-      </c>
-      <c r="U103" s="3">
-        <v>49</v>
-      </c>
-      <c r="V103" s="4" t="s">
-        <v>378</v>
+        <v>317</v>
+      </c>
+      <c r="V103" s="6">
+        <v>3</v>
       </c>
       <c r="W103" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>572</v>
+        <v>155</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>573</v>
+        <v>729</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="O104" s="8"/>
+        <v>297</v>
+      </c>
       <c r="R104" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S104" s="3">
-        <v>140</v>
-      </c>
-      <c r="T104" s="3">
-        <v>210</v>
-      </c>
-      <c r="U104" s="3">
-        <v>80</v>
-      </c>
-      <c r="V104" s="4" t="s">
-        <v>378</v>
+        <v>312</v>
+      </c>
+      <c r="V104" s="6">
+        <v>3</v>
       </c>
       <c r="W104" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C105" s="9">
-        <v>1570</v>
+        <v>108</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>575</v>
+        <v>188</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>576</v>
+        <v>226</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>577</v>
+        <v>256</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="L105" s="8" t="s">
-        <v>579</v>
-      </c>
-      <c r="M105" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="O105" s="8"/>
+        <v>298</v>
+      </c>
       <c r="R105" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S105" s="3">
-        <v>96</v>
-      </c>
-      <c r="T105" s="3">
-        <v>25</v>
-      </c>
-      <c r="U105" s="3">
-        <v>18</v>
-      </c>
-      <c r="V105" s="4">
-        <v>1</v>
+        <v>322</v>
+      </c>
+      <c r="V105" s="6">
+        <v>3</v>
       </c>
       <c r="W105" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X105" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7280,35 +7448,43 @@
         <v>109</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>581</v>
+        <v>157</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>582</v>
+        <v>202</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="O106" s="8"/>
+        <v>547</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="M106" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="O106" s="7" t="s">
+        <v>550</v>
+      </c>
       <c r="R106" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="S106" s="3">
-        <v>159</v>
+        <v>450</v>
       </c>
       <c r="T106" s="3">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="U106" s="3">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="V106" s="4" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>60</v>
@@ -7319,950 +7495,1323 @@
     </row>
     <row r="107" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>158</v>
+        <v>109</v>
+      </c>
+      <c r="C107" s="9">
+        <v>1583</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>260</v>
+        <v>546</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>304</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="M107" s="7"/>
+      <c r="O107" s="7"/>
       <c r="R107" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S107" s="3">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="T107" s="3">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="U107" s="3">
+        <v>166</v>
+      </c>
+      <c r="V107" s="4">
+        <v>1</v>
+      </c>
+      <c r="W107" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V107" s="6">
-        <v>3</v>
-      </c>
-      <c r="W107" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="X107" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>159</v>
+        <v>390</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>261</v>
+        <v>551</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>305</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="M108" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="O108" s="8"/>
       <c r="R108" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V108" s="6">
-        <v>3</v>
+        <v>312</v>
+      </c>
+      <c r="S108" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="T108" s="3">
+        <v>75</v>
+      </c>
+      <c r="U108" s="3">
+        <v>75</v>
+      </c>
+      <c r="V108" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="W108" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="109" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>160</v>
+        <v>109</v>
+      </c>
+      <c r="C109" s="9">
+        <v>1586</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>306</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="M109" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="O109" s="8"/>
       <c r="R109" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="V109" s="6">
-        <v>3</v>
+        <v>558</v>
+      </c>
+      <c r="S109" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="T109" s="3">
+        <v>120</v>
+      </c>
+      <c r="U109" s="3">
+        <v>81</v>
+      </c>
+      <c r="V109" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="W109" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="X109" s="2" t="s">
-        <v>112</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Y109"/>
     </row>
     <row r="110" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>161</v>
+        <v>560</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>262</v>
+        <v>561</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>307</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="O110" s="8"/>
       <c r="R110" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="V110" s="6">
-        <v>3</v>
+        <v>312</v>
+      </c>
+      <c r="S110" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="V110" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="W110" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="X110" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="111" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="Y110"/>
+    </row>
+    <row r="111" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>162</v>
+        <v>563</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>349</v>
+        <v>203</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>384</v>
+        <v>564</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>308</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="M111" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="O111" s="8"/>
       <c r="R111" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S111" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="T111" s="2"/>
-      <c r="U111" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="S111" s="3">
+        <v>83</v>
+      </c>
+      <c r="T111" s="3">
+        <v>191</v>
+      </c>
+      <c r="U111" s="3">
+        <v>49</v>
+      </c>
       <c r="V111" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="W111" t="s">
-        <v>65</v>
-      </c>
-      <c r="X111" t="s">
-        <v>113</v>
+        <v>373</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X111" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="Y111"/>
     </row>
     <row r="112" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>677</v>
+        <v>567</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>402</v>
+        <v>203</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>679</v>
+        <v>568</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>680</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="O112" s="8"/>
       <c r="R112" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S112" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="T112" s="2"/>
-      <c r="U112" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="S112" s="3">
+        <v>140</v>
+      </c>
+      <c r="T112" s="3">
+        <v>210</v>
+      </c>
+      <c r="U112" s="3">
+        <v>80</v>
+      </c>
       <c r="V112" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="W112" t="s">
-        <v>65</v>
-      </c>
-      <c r="X112" t="s">
-        <v>113</v>
+        <v>373</v>
+      </c>
+      <c r="W112" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X112" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="Y112"/>
     </row>
     <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>682</v>
+        <v>109</v>
+      </c>
+      <c r="C113" s="9">
+        <v>1570</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>169</v>
+        <v>570</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F113" s="18" t="s">
-        <v>749</v>
+        <v>571</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>685</v>
+        <v>572</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>686</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="M113" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="O113" s="8"/>
       <c r="R113" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S113" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="T113" s="2"/>
-      <c r="U113" s="2"/>
-      <c r="V113" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="W113" t="s">
-        <v>65</v>
-      </c>
-      <c r="X113" t="s">
-        <v>113</v>
+        <v>312</v>
+      </c>
+      <c r="S113" s="3">
+        <v>96</v>
+      </c>
+      <c r="T113" s="3">
+        <v>25</v>
+      </c>
+      <c r="U113" s="3">
+        <v>18</v>
+      </c>
+      <c r="V113" s="4">
+        <v>1</v>
+      </c>
+      <c r="W113" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X113" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="Y113"/>
     </row>
     <row r="114" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>682</v>
+        <v>576</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F114" s="18" t="s">
-        <v>749</v>
+        <v>577</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>689</v>
+        <v>555</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>690</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="O114" s="8"/>
       <c r="R114" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S114" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="T114" s="2"/>
-      <c r="U114" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="S114" s="3">
+        <v>159</v>
+      </c>
+      <c r="T114" s="3">
+        <v>120</v>
+      </c>
+      <c r="U114" s="3">
+        <v>81</v>
+      </c>
       <c r="V114" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="W114" t="s">
-        <v>65</v>
-      </c>
-      <c r="X114" t="s">
-        <v>113</v>
+        <v>373</v>
+      </c>
+      <c r="W114" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X114" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="Y114"/>
     </row>
     <row r="115" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>682</v>
+        <v>158</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F115" s="18" t="s">
-        <v>749</v>
+        <v>203</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>693</v>
+        <v>257</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>694</v>
+        <v>300</v>
       </c>
       <c r="R115" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S115" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="T115" s="2"/>
-      <c r="U115" s="2"/>
-      <c r="V115" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="W115" t="s">
-        <v>65</v>
-      </c>
-      <c r="X115" t="s">
-        <v>113</v>
+        <v>312</v>
+      </c>
+      <c r="S115" s="3">
+        <v>43</v>
+      </c>
+      <c r="T115" s="3">
+        <v>180</v>
+      </c>
+      <c r="U115" s="3">
+        <v>60</v>
+      </c>
+      <c r="V115" s="6">
+        <v>3</v>
+      </c>
+      <c r="W115" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X115" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="Y115"/>
     </row>
     <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>682</v>
+        <v>159</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="F116" s="18" t="s">
-        <v>749</v>
+        <v>227</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>697</v>
+        <v>258</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>698</v>
+        <v>301</v>
       </c>
       <c r="R116" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S116" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="T116" s="2"/>
-      <c r="U116" s="2"/>
-      <c r="V116" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="W116" t="s">
-        <v>65</v>
-      </c>
-      <c r="X116" t="s">
-        <v>113</v>
+        <v>31</v>
+      </c>
+      <c r="V116" s="6">
+        <v>3</v>
+      </c>
+      <c r="W116" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X116" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="Y116"/>
     </row>
     <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>701</v>
+        <v>228</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="J117" s="2" t="s">
-        <v>465</v>
+        <v>580</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>702</v>
+        <v>302</v>
       </c>
       <c r="R117" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S117" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="T117" s="2"/>
-      <c r="U117" s="2"/>
-      <c r="V117" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="W117" t="s">
-        <v>65</v>
-      </c>
-      <c r="X117" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y117"/>
+        <v>323</v>
+      </c>
+      <c r="V117" s="6">
+        <v>3</v>
+      </c>
+      <c r="W117" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="X117" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>700</v>
+        <v>161</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>701</v>
+        <v>229</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="J118" s="2" t="s">
-        <v>705</v>
+        <v>259</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>706</v>
+        <v>303</v>
       </c>
       <c r="R118" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S118" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="T118" s="2"/>
-      <c r="U118" s="2"/>
-      <c r="V118" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="W118" t="s">
-        <v>65</v>
-      </c>
-      <c r="X118" t="s">
+        <v>312</v>
+      </c>
+      <c r="V118" s="6">
+        <v>3</v>
+      </c>
+      <c r="W118" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X118" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="Y118"/>
     </row>
     <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>232</v>
+        <v>344</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>263</v>
+        <v>378</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="R119" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="V119" s="5">
-        <v>2</v>
-      </c>
-      <c r="W119" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="X119" s="2" t="s">
-        <v>114</v>
+        <v>312</v>
+      </c>
+      <c r="S119" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="T119" s="2"/>
+      <c r="U119" s="2"/>
+      <c r="V119" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="W119" t="s">
+        <v>65</v>
+      </c>
+      <c r="X119" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>164</v>
+        <v>671</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>233</v>
+        <v>397</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>264</v>
+        <v>672</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>673</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>310</v>
+        <v>674</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S120" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="V120" s="6">
-        <v>3</v>
-      </c>
-      <c r="W120" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="X120" s="2" t="s">
-        <v>115</v>
+        <v>312</v>
+      </c>
+      <c r="S120" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="T120" s="2"/>
+      <c r="U120" s="2"/>
+      <c r="V120" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="W120" t="s">
+        <v>65</v>
+      </c>
+      <c r="X120" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>165</v>
+        <v>676</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>234</v>
+        <v>677</v>
+      </c>
+      <c r="F121" s="18" t="s">
+        <v>743</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>584</v>
+        <v>678</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="K121" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="R121" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="R121" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S121" s="3">
-        <v>114</v>
-      </c>
-      <c r="T121" s="3">
-        <v>53</v>
-      </c>
-      <c r="U121" s="3">
-        <v>48</v>
-      </c>
-      <c r="V121" s="6">
-        <v>3</v>
-      </c>
-      <c r="W121" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="X121" s="2" t="s">
-        <v>116</v>
+      <c r="S121" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="T121" s="2"/>
+      <c r="U121" s="2"/>
+      <c r="V121" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="W121" t="s">
+        <v>65</v>
+      </c>
+      <c r="X121" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>755</v>
+        <v>676</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>235</v>
+        <v>677</v>
+      </c>
+      <c r="F122" s="18" t="s">
+        <v>743</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>239</v>
+        <v>682</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>683</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>312</v>
+        <v>684</v>
       </c>
       <c r="R122" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S122" s="3">
-        <v>34</v>
-      </c>
-      <c r="V122" s="6">
-        <v>3</v>
-      </c>
-      <c r="W122" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="X122" s="2" t="s">
-        <v>117</v>
+        <v>311</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="T122" s="2"/>
+      <c r="U122" s="2"/>
+      <c r="V122" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="W122" t="s">
+        <v>65</v>
+      </c>
+      <c r="X122" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>166</v>
+        <v>676</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>236</v>
+        <v>677</v>
+      </c>
+      <c r="F123" s="18" t="s">
+        <v>743</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>586</v>
+        <v>686</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>687</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>313</v>
+        <v>688</v>
       </c>
       <c r="R123" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="V123" s="6">
-        <v>3</v>
-      </c>
-      <c r="W123" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X123" s="2" t="s">
-        <v>118</v>
+        <v>311</v>
+      </c>
+      <c r="S123" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="T123" s="2"/>
+      <c r="U123" s="2"/>
+      <c r="V123" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="W123" t="s">
+        <v>65</v>
+      </c>
+      <c r="X123" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>167</v>
+        <v>676</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>237</v>
+        <v>677</v>
+      </c>
+      <c r="F124" s="18" t="s">
+        <v>743</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>707</v>
+        <v>690</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>691</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="R124" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="V124" s="5">
-        <v>2</v>
-      </c>
-      <c r="W124" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X124" s="2" t="s">
-        <v>119</v>
+        <v>311</v>
+      </c>
+      <c r="S124" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="T124" s="2"/>
+      <c r="U124" s="2"/>
+      <c r="V124" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="W124" t="s">
+        <v>65</v>
+      </c>
+      <c r="X124" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>712</v>
+        <v>459</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>713</v>
+        <v>460</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>714</v>
-      </c>
-      <c r="M125" s="7" t="s">
-        <v>715</v>
+        <v>696</v>
       </c>
       <c r="R125" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S125" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="V125" s="5">
-        <v>2</v>
-      </c>
-      <c r="W125" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X125" s="2" t="s">
-        <v>119</v>
+        <v>312</v>
+      </c>
+      <c r="S125" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="T125" s="2"/>
+      <c r="U125" s="2"/>
+      <c r="V125" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="W125" t="s">
+        <v>65</v>
+      </c>
+      <c r="X125" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="126" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>432</v>
+        <v>698</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>718</v>
-      </c>
-      <c r="M126" s="7" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="R126" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S126" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="V126" s="5">
-        <v>2</v>
-      </c>
-      <c r="W126" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X126" s="2" t="s">
-        <v>119</v>
+        <v>312</v>
+      </c>
+      <c r="S126" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="T126" s="2"/>
+      <c r="U126" s="2"/>
+      <c r="V126" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="W126" t="s">
+        <v>65</v>
+      </c>
+      <c r="X126" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="127" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>720</v>
+        <v>163</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>721</v>
+        <v>191</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>722</v>
+        <v>230</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="J127" s="2" t="s">
-        <v>723</v>
+        <v>260</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>724</v>
+        <v>305</v>
       </c>
       <c r="R127" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="S127" s="3" t="s">
-        <v>725</v>
+        <v>324</v>
       </c>
       <c r="V127" s="5">
         <v>2</v>
       </c>
       <c r="W127" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="X127" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="128" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>727</v>
+        <v>231</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>729</v>
+        <v>261</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>730</v>
+        <v>306</v>
       </c>
       <c r="R128" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="S128" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="V128" s="5">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="V128" s="6">
+        <v>3</v>
       </c>
       <c r="W128" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="X128" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="129" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="K129" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="R129" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S129" s="3">
+        <v>114</v>
+      </c>
+      <c r="T129" s="3">
+        <v>53</v>
+      </c>
+      <c r="U129" s="3">
+        <v>48</v>
+      </c>
+      <c r="V129" s="6">
+        <v>3</v>
+      </c>
+      <c r="W129" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X129" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="K130" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="R130" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S130" s="3">
+        <v>34</v>
+      </c>
+      <c r="V130" s="6">
+        <v>3</v>
+      </c>
+      <c r="W130" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X130" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="K131" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="R131" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="V131" s="6">
+        <v>3</v>
+      </c>
+      <c r="W131" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X131" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B132" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="D129" s="2" t="s">
+      <c r="C132" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D132" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E129" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="J129" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="K129" s="7" t="s">
-        <v>734</v>
-      </c>
-      <c r="R129" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="V129" s="5">
+      <c r="E132" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="K132" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="R132" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="V132" s="5">
         <v>2</v>
       </c>
-      <c r="W129" s="2" t="s">
+      <c r="W132" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="X129" s="2" t="s">
+      <c r="X132" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="K133" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="M133" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="R133" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="S133" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="V133" s="5">
+        <v>2</v>
+      </c>
+      <c r="W133" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X133" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="K134" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="M134" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="R134" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="S134" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="V134" s="5">
+        <v>2</v>
+      </c>
+      <c r="W134" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X134" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="K135" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="R135" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="S135" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="V135" s="5">
+        <v>2</v>
+      </c>
+      <c r="W135" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X135" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="K136" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="R136" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="S136" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="V136" s="5">
+        <v>2</v>
+      </c>
+      <c r="W136" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X136" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="K137" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="R137" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="V137" s="5">
+        <v>2</v>
+      </c>
+      <c r="W137" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X137" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -8285,141 +8834,152 @@
     <hyperlink ref="K69" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
     <hyperlink ref="K70" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
     <hyperlink ref="K71" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K72" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="K73" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="K74" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="K83" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="K85" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="K86" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="K87" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="K88" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="K89" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="K90" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="K91" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="K92" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="K93" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="K94" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="K95" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="K96" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="K97" r:id="rId33" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="K107" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="K108" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="K109" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="K110" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="K3" r:id="rId38" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
-    <hyperlink ref="K4" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
-    <hyperlink ref="K5" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
-    <hyperlink ref="K6" r:id="rId41" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
-    <hyperlink ref="K7" r:id="rId42" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
-    <hyperlink ref="K8" r:id="rId43" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
-    <hyperlink ref="K9" r:id="rId44" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
-    <hyperlink ref="K10" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
-    <hyperlink ref="K18" r:id="rId46" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
-    <hyperlink ref="K19" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
-    <hyperlink ref="K21" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
-    <hyperlink ref="K20" r:id="rId49" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
-    <hyperlink ref="K22" r:id="rId50" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
-    <hyperlink ref="M18" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
-    <hyperlink ref="K23" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
-    <hyperlink ref="K27" r:id="rId53" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
-    <hyperlink ref="K28" r:id="rId54" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
-    <hyperlink ref="M28" r:id="rId55" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
-    <hyperlink ref="K29" r:id="rId56" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
-    <hyperlink ref="K30" r:id="rId57" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
-    <hyperlink ref="K32" r:id="rId58" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
-    <hyperlink ref="K11" r:id="rId59" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
-    <hyperlink ref="K12" r:id="rId60" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
-    <hyperlink ref="K13" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
-    <hyperlink ref="K14" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
-    <hyperlink ref="K15" r:id="rId63" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
-    <hyperlink ref="K16" r:id="rId64" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
-    <hyperlink ref="K34" r:id="rId65" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
-    <hyperlink ref="K35" r:id="rId66" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
-    <hyperlink ref="K36" r:id="rId67" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
-    <hyperlink ref="K37" r:id="rId68" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
-    <hyperlink ref="K38" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
-    <hyperlink ref="K39" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
-    <hyperlink ref="K40" r:id="rId71" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
-    <hyperlink ref="K41" r:id="rId72" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
-    <hyperlink ref="K65" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
-    <hyperlink ref="M65" r:id="rId74" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
-    <hyperlink ref="K66" r:id="rId75" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
-    <hyperlink ref="M66" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
-    <hyperlink ref="K56" r:id="rId77" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
-    <hyperlink ref="K57" r:id="rId78" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
-    <hyperlink ref="K60" r:id="rId79" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
-    <hyperlink ref="K59" r:id="rId80" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
-    <hyperlink ref="K58" r:id="rId81" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
-    <hyperlink ref="K61" r:id="rId82" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
-    <hyperlink ref="K99" r:id="rId83" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
-    <hyperlink ref="M100" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
-    <hyperlink ref="K100" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
-    <hyperlink ref="K101" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
-    <hyperlink ref="K102" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
-    <hyperlink ref="K106" r:id="rId88" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
-    <hyperlink ref="M103" r:id="rId89" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
-    <hyperlink ref="K103" r:id="rId90" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
-    <hyperlink ref="M105" r:id="rId91" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
-    <hyperlink ref="K104" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
-    <hyperlink ref="K105" r:id="rId93" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
-    <hyperlink ref="M98" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
-    <hyperlink ref="K98" r:id="rId95" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
-    <hyperlink ref="O98" r:id="rId96" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
-    <hyperlink ref="M101" r:id="rId97" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
-    <hyperlink ref="M90" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
-    <hyperlink ref="H62" r:id="rId99" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
-    <hyperlink ref="F62" r:id="rId100" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
-    <hyperlink ref="M62" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
-    <hyperlink ref="O62" r:id="rId102" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
-    <hyperlink ref="M75" r:id="rId103" xr:uid="{D4E31208-1729-474B-8613-04CAF9B8C025}"/>
-    <hyperlink ref="K75" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F8517-F853-4BC2-B1A3-2FAE2DAB6C9A}"/>
-    <hyperlink ref="K76" r:id="rId105" xr:uid="{61D85FE2-8DE3-4825-8491-0FE8BB47E3E1}"/>
-    <hyperlink ref="K77" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F36EF-2268-403C-A6B7-E58ACFE0642D}"/>
-    <hyperlink ref="K78" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B578D29-DC36-40D0-9947-A27ECB77A9CF}"/>
-    <hyperlink ref="K79" r:id="rId108" xr:uid="{57B652B7-7292-4EAC-B631-5C96CD2691B8}"/>
-    <hyperlink ref="K80" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9E7BF8E-41C2-4812-BC18-7E39D390B4DB}"/>
-    <hyperlink ref="H81" r:id="rId110" xr:uid="{0D8B79CB-4807-4139-98AD-96CFF7161C32}"/>
-    <hyperlink ref="K81" r:id="rId111" xr:uid="{B472E107-96D8-49AE-8D43-42D5D303C124}"/>
-    <hyperlink ref="M81" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9F3C81B0-62F8-4827-8155-5167D81363EB}"/>
-    <hyperlink ref="K82" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{841BFC94-91FA-4580-9546-612A91A5451F}"/>
-    <hyperlink ref="K42" r:id="rId114" xr:uid="{A95E99D8-AE5F-42F6-8170-14A073FA717E}"/>
-    <hyperlink ref="K43" r:id="rId115" xr:uid="{3ED1C2EF-8252-44A5-B551-1A43DD3F443F}"/>
-    <hyperlink ref="K44" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg/1280px-Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{751B356D-FC9A-4AD0-95E0-A8F1621E6F4F}"/>
-    <hyperlink ref="K45" r:id="rId117" xr:uid="{4DEEB737-1329-4597-919B-47ACF73325F8}"/>
-    <hyperlink ref="K46" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A5A253DF-D8FC-4464-832F-136C51B54ADE}"/>
-    <hyperlink ref="K47" r:id="rId119" xr:uid="{C26C012E-8A85-48D2-9B13-ADD3AEDEB4B0}"/>
-    <hyperlink ref="K48" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1D38CDDF-A325-49B8-BE2E-935C8E9D142B}"/>
-    <hyperlink ref="K51" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{471BE4AF-D2F1-433A-B3AC-795231C2AF30}"/>
-    <hyperlink ref="K49" r:id="rId122" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F1CACA00-310B-4B86-B079-D54654CC5BDD}"/>
-    <hyperlink ref="K50" r:id="rId123" display="https://upload.wikimedia.org/wikipedia/commons/3/39/Tomb_of_Lorenzo_the_Magnificent_and_Giuliano_de%27_Medici%2C_Sagrestia_Nuova%2C_Medici_Chapels%2C_San_Lorenzo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr" xr:uid="{0C4E85C8-1452-46E5-BAA1-9F134272222A}"/>
-    <hyperlink ref="K123" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K122" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K121" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K120" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K119" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K111" r:id="rId129" xr:uid="{B6FD0D1A-F931-482F-BA2B-9716DE045C80}"/>
-    <hyperlink ref="K112" r:id="rId130" xr:uid="{A861573B-3839-4318-BBAC-62B6CBA15FBD}"/>
-    <hyperlink ref="K113" r:id="rId131" xr:uid="{20DF76DA-E992-4E1D-A16E-22BE28C58483}"/>
-    <hyperlink ref="K114" r:id="rId132" xr:uid="{B1F4C251-A9D6-47B9-9136-6591399F5FD8}"/>
-    <hyperlink ref="K115" r:id="rId133" xr:uid="{D7FB2C86-EF32-4C98-B1CE-C0195DB8C4C6}"/>
-    <hyperlink ref="K116" r:id="rId134" xr:uid="{FE50DE30-8439-4013-8AF6-8076D7113E1F}"/>
-    <hyperlink ref="K117" r:id="rId135" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDA4581C-5B96-4BDE-A351-45793B6F0EE8}"/>
-    <hyperlink ref="K118" r:id="rId136" xr:uid="{51ED3C40-5509-488A-841B-4E657C71C1FA}"/>
-    <hyperlink ref="K124" r:id="rId137" xr:uid="{F66E5A2C-A530-4199-AD87-0563CA44FE62}"/>
-    <hyperlink ref="K125" r:id="rId138" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D2E9D5D-E79A-4ADE-8B6A-4BF55D9DEAA1}"/>
-    <hyperlink ref="M125" r:id="rId139" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{34AE602C-A94D-4947-A1E5-B9CB698DBCE9}"/>
-    <hyperlink ref="M126" r:id="rId140" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7F17DDD6-358D-4949-BA30-757C7347BD64}"/>
-    <hyperlink ref="K126" r:id="rId141" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D595607E-E74C-423D-9949-0D9455718911}"/>
-    <hyperlink ref="K128" r:id="rId142" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46C65D64-593C-435B-985E-1487C0A3B6FF}"/>
-    <hyperlink ref="K129" r:id="rId143" xr:uid="{ABE79D9A-A8E7-4085-8D94-395C34C6D224}"/>
-    <hyperlink ref="K127" r:id="rId144" xr:uid="{29FC3D7D-FB63-4F1F-9086-C70F1D6EA865}"/>
-    <hyperlink ref="F113" r:id="rId145" xr:uid="{2D04002B-8C33-4E33-A9BC-035BE367ACFB}"/>
-    <hyperlink ref="F114:F116" r:id="rId146" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Loggetta_Sansovino_a_Venezia.jpg/1280px-Loggetta_Sansovino_a_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{83BABDFD-B232-49ED-9178-8A0C58DB9E5B}"/>
-    <hyperlink ref="K84" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg/1280px-San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B16DCA1D-61FA-47E3-AEC7-CAF732E10DD2}"/>
-    <hyperlink ref="F77" r:id="rId148" xr:uid="{F860FC30-4D00-4CD5-A8BB-B4414CC5D08F}"/>
-    <hyperlink ref="M51" r:id="rId149" xr:uid="{15D2D5F0-5EFB-40A5-BBAA-91DD811E84CC}"/>
-    <hyperlink ref="M27" r:id="rId150" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56BAEEFF-2EBF-4B02-97DC-C24781018097}"/>
-    <hyperlink ref="K31" r:id="rId151" xr:uid="{2CFFED1D-5528-4009-9B87-0FD8518C9CC4}"/>
+    <hyperlink ref="K91" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="K93" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="K94" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="K95" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="K96" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="K97" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="K98" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="K99" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="K100" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="K101" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="K102" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="K103" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="K104" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="K105" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="K115" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="K116" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="K117" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="K118" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="K3" r:id="rId35" xr:uid="{536B5DC8-AB2C-4F9F-95E7-527FEE173E87}"/>
+    <hyperlink ref="K4" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{08CA7CE3-7060-4AEB-B667-B94A5DE8C5A5}"/>
+    <hyperlink ref="K5" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg/960px-Bartolomeo_ammannati%2C_monumento_funebre_a_mario_nari%2C_1540-42%2C_dalla_ss._annunziata_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40C160BE-BE63-4993-81D2-93EFE7C967CD}"/>
+    <hyperlink ref="K6" r:id="rId38" xr:uid="{BB31404B-260F-456F-A48F-34841F5627A4}"/>
+    <hyperlink ref="K7" r:id="rId39" xr:uid="{52FA8F6E-6CC6-413A-B788-E63F724B2FE1}"/>
+    <hyperlink ref="K8" r:id="rId40" xr:uid="{ED010421-15AE-4DD8-8FCC-A7445FE744DE}"/>
+    <hyperlink ref="K9" r:id="rId41" xr:uid="{1A0532B7-3CFB-4243-AE72-DBA87D00AD94}"/>
+    <hyperlink ref="K10" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Speculum_Romanae_Magnificentiae-_Hercules_Colossus_at_Padua_%28L%27Ercole_di_casa_Benavides_a_Padova%29_%28IA_mma_speculum_romanae_magnificentiae_hercules_colossus_at_padua_lercole_di_cas_365368%29.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F36A7CA5-6658-4390-9AD9-7A8D3B6E1F69}"/>
+    <hyperlink ref="K18" r:id="rId43" xr:uid="{350D3BE0-6499-4F05-8F49-D051E769DAA0}"/>
+    <hyperlink ref="K19" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1E3F0C9D-0E05-4F4A-991D-3813712D59A2}"/>
+    <hyperlink ref="K21" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5EC6D800-EC04-46DB-912F-C7048449B4ED}"/>
+    <hyperlink ref="K20" r:id="rId46" xr:uid="{A8A79C84-53BF-41F5-B6CD-8D0109B42C7F}"/>
+    <hyperlink ref="K22" r:id="rId47" xr:uid="{7D3EB90E-7582-4920-BC7B-8E0D56E91F93}"/>
+    <hyperlink ref="M18" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg/960px-Baccio_Bandinelli%2C_Hercules_and_Cacus%2C_c1525%2C_wax%2C_Bode_Museum%2C_Berlin_%28Inv._2612%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8DA3DD73-6715-43AC-AB0D-460A012D67B3}"/>
+    <hyperlink ref="K23" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5345A3F9-BA70-4993-8046-6366FCD164E6}"/>
+    <hyperlink ref="K27" r:id="rId50" xr:uid="{2A7509F8-4912-45E9-A5C0-86711BAB366E}"/>
+    <hyperlink ref="K28" r:id="rId51" xr:uid="{608A63FA-9E19-47E1-9F7F-6F0FAD11B401}"/>
+    <hyperlink ref="M28" r:id="rId52" xr:uid="{25A23FBD-79A3-4259-B1E6-1E23B044194E}"/>
+    <hyperlink ref="K29" r:id="rId53" xr:uid="{0939FD81-D321-4C11-AB0A-59E4FB22545D}"/>
+    <hyperlink ref="K30" r:id="rId54" xr:uid="{464D0452-8AB3-4307-A15B-A37AF2D0F598}"/>
+    <hyperlink ref="K32" r:id="rId55" xr:uid="{911384D0-0B23-4C3C-8F9B-D3C7E41D4FE7}"/>
+    <hyperlink ref="K11" r:id="rId56" xr:uid="{A8B15AA6-6D67-4359-845B-4261F146863A}"/>
+    <hyperlink ref="K12" r:id="rId57" xr:uid="{7F264098-95CA-4799-A3FB-8F66C1B552A7}"/>
+    <hyperlink ref="K13" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Moses_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D8E172A-9EF7-4545-8A30-C950BC990ACE}"/>
+    <hyperlink ref="K14" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b2/Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg/960px-Facade_of_San_Francesco_della_Vigna_%28Venice%29_Saint_Paul_by_Tiziano_Aspetti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46CDE25D-F348-478F-AACB-3DAF83D5FAFC}"/>
+    <hyperlink ref="K15" r:id="rId60" xr:uid="{B0E5923B-2E43-404C-91B5-06FACA417F27}"/>
+    <hyperlink ref="K16" r:id="rId61" xr:uid="{E77BD6BF-1426-4867-B27A-9E40BC3E60DC}"/>
+    <hyperlink ref="K34" r:id="rId62" xr:uid="{72C90FBB-4501-489C-8A5D-91A5379C8287}"/>
+    <hyperlink ref="K35" r:id="rId63" xr:uid="{FDF4330D-52F7-4C44-A941-9A76408BFC1C}"/>
+    <hyperlink ref="K36" r:id="rId64" xr:uid="{43CC0C24-6FD6-42D1-B6B9-F3D4CD7C1455}"/>
+    <hyperlink ref="K37" r:id="rId65" xr:uid="{C5EDCA25-7AFD-4D17-96F3-2381A07353BE}"/>
+    <hyperlink ref="K38" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B87A0D6B-49D7-4294-AA52-2EBC8AF3ED95}"/>
+    <hyperlink ref="K39" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{88F15031-BF59-46C6-B79E-1EE1AC8E6198}"/>
+    <hyperlink ref="K40" r:id="rId68" xr:uid="{2FC40162-6234-4737-8022-64E508935EEE}"/>
+    <hyperlink ref="K41" r:id="rId69" xr:uid="{9AD0C633-D1D6-40E1-BEFF-17B74AB92E6B}"/>
+    <hyperlink ref="K65" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg/960px-Augsburg_Maximilianmuseum_Merkur_u_Amor_Brunnenfigur_220325.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{68DBB97F-D410-4AE5-9A25-0582E0B9EC09}"/>
+    <hyperlink ref="M65" r:id="rId71" xr:uid="{57FB9CD0-5DCD-41D3-A020-A033F941FB1E}"/>
+    <hyperlink ref="K66" r:id="rId72" xr:uid="{1980AFE3-573E-4793-983F-D48C3C55923C}"/>
+    <hyperlink ref="M66" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg/1280px-Augsburg%2C_Maximilanstra%C3%9Fe%2C_Herkulesbrunnen%2C_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46094B3F-ADF4-4CB2-84D4-0B038329AE39}"/>
+    <hyperlink ref="K56" r:id="rId74" xr:uid="{D8CB2F16-FDEE-47FD-B078-905640E54585}"/>
+    <hyperlink ref="K57" r:id="rId75" xr:uid="{4F6B1F49-19B3-4758-A2D7-7A01BFF2FE69}"/>
+    <hyperlink ref="K60" r:id="rId76" xr:uid="{8FDF141B-E5A5-4001-A509-7677442969AD}"/>
+    <hyperlink ref="K59" r:id="rId77" xr:uid="{D6A89A53-6F08-431B-96CE-73456527BA1E}"/>
+    <hyperlink ref="K58" r:id="rId78" xr:uid="{46F9B73D-D389-4181-B2B1-1C476F442A21}"/>
+    <hyperlink ref="K61" r:id="rId79" xr:uid="{AEE75F6A-B699-4761-96A7-9D90F98CA00D}"/>
+    <hyperlink ref="K107" r:id="rId80" xr:uid="{215F3667-C7E4-4233-9999-73E691A85BCB}"/>
+    <hyperlink ref="M108" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg/1280px-Soubassement_du_monument_du_coeur_du_roi_Henri_II_%281519-1559%29_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_B_%3B_N_15166.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A2E493BC-AB3C-46FB-9D60-90B9B2937552}"/>
+    <hyperlink ref="K108" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4BAF966F-961F-47B1-97E4-33AB0DDF9CA3}"/>
+    <hyperlink ref="K109" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1312AD99-DBE6-4B26-8A3E-7013D5AD7839}"/>
+    <hyperlink ref="K110" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4A56E458-E9EC-4FD8-A835-7DEA716AD3AE}"/>
+    <hyperlink ref="K114" r:id="rId85" xr:uid="{409F37CA-1732-4493-B195-1FC8D4FBA9FB}"/>
+    <hyperlink ref="M111" r:id="rId86" xr:uid="{0956A91B-5EF3-48F9-8C16-A07E15721FCC}"/>
+    <hyperlink ref="K111" r:id="rId87" xr:uid="{FCCD2EF7-C1DB-4F7B-8FCB-A135702F2279}"/>
+    <hyperlink ref="M113" r:id="rId88" xr:uid="{2E1FA89D-404F-4E3D-B202-FCECA18C2961}"/>
+    <hyperlink ref="K112" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CC6B363D-4607-4E5C-ADF8-FDF706FC7BD6}"/>
+    <hyperlink ref="K113" r:id="rId90" xr:uid="{478A536C-2D34-483A-B39F-5775F99F87FB}"/>
+    <hyperlink ref="M106" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg/1280px-Tombeau_Henri_II_Catherine_M%C3%A9dicis_Basilique_St_Denis_St_Denis_Seine_St_Denis_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C156EBC6-0CD9-4AB7-A99F-EE9D0F9C628C}"/>
+    <hyperlink ref="K106" r:id="rId92" xr:uid="{B54113D7-6CCF-4C86-94F9-17A108A08ECE}"/>
+    <hyperlink ref="O106" r:id="rId93" xr:uid="{37CB529E-7680-4091-AF5F-2D0EA0C25DAC}"/>
+    <hyperlink ref="M109" r:id="rId94" xr:uid="{12106A2D-C09C-4730-87CF-736AA8448BE6}"/>
+    <hyperlink ref="M98" r:id="rId95" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg/500px-Moosburg_-_Kastulusm%C3%BCnster_-_Leinberger_Altar_-_Gesamtansicht.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6BD665CB-D4AC-47F0-A305-FD3121F52829}"/>
+    <hyperlink ref="H62" r:id="rId96" xr:uid="{8EBC7694-AF2B-4E24-A6FB-669D3AF6F914}"/>
+    <hyperlink ref="F62" r:id="rId97" xr:uid="{4B9BBB8B-E963-436E-80B3-093DF24BA3F9}"/>
+    <hyperlink ref="M62" r:id="rId98" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG/960px-Grotta_del_buontalenti%2C_Vincenzo_de%27_Rossi%2C_Paride_che_rapisce_Elena_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C7AD36A6-5DE2-4116-A7CC-94A5865A312A}"/>
+    <hyperlink ref="O62" r:id="rId99" xr:uid="{EC1E3AD8-83D8-4FA0-B952-16AF174DEE27}"/>
+    <hyperlink ref="M83" r:id="rId100" xr:uid="{D4E31208-1729-474B-8613-04CAF9B8C025}"/>
+    <hyperlink ref="K83" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F8517-F853-4BC2-B1A3-2FAE2DAB6C9A}"/>
+    <hyperlink ref="K84" r:id="rId102" xr:uid="{61D85FE2-8DE3-4825-8491-0FE8BB47E3E1}"/>
+    <hyperlink ref="K85" r:id="rId103" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{603F36EF-2268-403C-A6B7-E58ACFE0642D}"/>
+    <hyperlink ref="K86" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B578D29-DC36-40D0-9947-A27ECB77A9CF}"/>
+    <hyperlink ref="K87" r:id="rId105" xr:uid="{57B652B7-7292-4EAC-B631-5C96CD2691B8}"/>
+    <hyperlink ref="K88" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9E7BF8E-41C2-4812-BC18-7E39D390B4DB}"/>
+    <hyperlink ref="H89" r:id="rId107" xr:uid="{0D8B79CB-4807-4139-98AD-96CFF7161C32}"/>
+    <hyperlink ref="K89" r:id="rId108" xr:uid="{B472E107-96D8-49AE-8D43-42D5D303C124}"/>
+    <hyperlink ref="M89" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg/1280px-A_Window_in_the_Oldest_Part_of_the_Louvre_Still_Visible_%28From_late_1500%27s%29_%2812412618155%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9F3C81B0-62F8-4827-8155-5167D81363EB}"/>
+    <hyperlink ref="K90" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{841BFC94-91FA-4580-9546-612A91A5451F}"/>
+    <hyperlink ref="K42" r:id="rId111" xr:uid="{A95E99D8-AE5F-42F6-8170-14A073FA717E}"/>
+    <hyperlink ref="K43" r:id="rId112" xr:uid="{3ED1C2EF-8252-44A5-B551-1A43DD3F443F}"/>
+    <hyperlink ref="K44" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6e/Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg/1280px-Michelangelo%2C_Madonna_and_Child_with_the_Young_St._John_%28Pitti_Tondo%29%2C_ca_1505%3B_Bargello%2C_Florence_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{751B356D-FC9A-4AD0-95E0-A8F1621E6F4F}"/>
+    <hyperlink ref="K45" r:id="rId114" xr:uid="{4DEEB737-1329-4597-919B-47ACF73325F8}"/>
+    <hyperlink ref="K46" r:id="rId115" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A5A253DF-D8FC-4464-832F-136C51B54ADE}"/>
+    <hyperlink ref="K47" r:id="rId116" xr:uid="{C26C012E-8A85-48D2-9B13-ADD3AEDEB4B0}"/>
+    <hyperlink ref="K48" r:id="rId117" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{1D38CDDF-A325-49B8-BE2E-935C8E9D142B}"/>
+    <hyperlink ref="K51" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{471BE4AF-D2F1-433A-B3AC-795231C2AF30}"/>
+    <hyperlink ref="K49" r:id="rId119" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F1CACA00-310B-4B86-B079-D54654CC5BDD}"/>
+    <hyperlink ref="K50" r:id="rId120" display="https://upload.wikimedia.org/wikipedia/commons/3/39/Tomb_of_Lorenzo_the_Magnificent_and_Giuliano_de%27_Medici%2C_Sagrestia_Nuova%2C_Medici_Chapels%2C_San_Lorenzo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr" xr:uid="{0C4E85C8-1452-46E5-BAA1-9F134272222A}"/>
+    <hyperlink ref="K131" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K130" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K129" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K128" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K127" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="K119" r:id="rId126" xr:uid="{B6FD0D1A-F931-482F-BA2B-9716DE045C80}"/>
+    <hyperlink ref="K120" r:id="rId127" xr:uid="{A861573B-3839-4318-BBAC-62B6CBA15FBD}"/>
+    <hyperlink ref="K121" r:id="rId128" xr:uid="{20DF76DA-E992-4E1D-A16E-22BE28C58483}"/>
+    <hyperlink ref="K122" r:id="rId129" xr:uid="{B1F4C251-A9D6-47B9-9136-6591399F5FD8}"/>
+    <hyperlink ref="K123" r:id="rId130" xr:uid="{D7FB2C86-EF32-4C98-B1CE-C0195DB8C4C6}"/>
+    <hyperlink ref="K124" r:id="rId131" xr:uid="{FE50DE30-8439-4013-8AF6-8076D7113E1F}"/>
+    <hyperlink ref="K125" r:id="rId132" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDA4581C-5B96-4BDE-A351-45793B6F0EE8}"/>
+    <hyperlink ref="K126" r:id="rId133" xr:uid="{51ED3C40-5509-488A-841B-4E657C71C1FA}"/>
+    <hyperlink ref="K132" r:id="rId134" xr:uid="{F66E5A2C-A530-4199-AD87-0563CA44FE62}"/>
+    <hyperlink ref="K133" r:id="rId135" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D2E9D5D-E79A-4ADE-8B6A-4BF55D9DEAA1}"/>
+    <hyperlink ref="M133" r:id="rId136" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{34AE602C-A94D-4947-A1E5-B9CB698DBCE9}"/>
+    <hyperlink ref="M134" r:id="rId137" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7F17DDD6-358D-4949-BA30-757C7347BD64}"/>
+    <hyperlink ref="K134" r:id="rId138" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D595607E-E74C-423D-9949-0D9455718911}"/>
+    <hyperlink ref="K136" r:id="rId139" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46C65D64-593C-435B-985E-1487C0A3B6FF}"/>
+    <hyperlink ref="K137" r:id="rId140" xr:uid="{ABE79D9A-A8E7-4085-8D94-395C34C6D224}"/>
+    <hyperlink ref="K135" r:id="rId141" xr:uid="{29FC3D7D-FB63-4F1F-9086-C70F1D6EA865}"/>
+    <hyperlink ref="F121" r:id="rId142" xr:uid="{2D04002B-8C33-4E33-A9BC-035BE367ACFB}"/>
+    <hyperlink ref="F122:F124" r:id="rId143" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Loggetta_Sansovino_a_Venezia.jpg/1280px-Loggetta_Sansovino_a_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{83BABDFD-B232-49ED-9178-8A0C58DB9E5B}"/>
+    <hyperlink ref="K92" r:id="rId144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg/1280px-San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B16DCA1D-61FA-47E3-AEC7-CAF732E10DD2}"/>
+    <hyperlink ref="F85" r:id="rId145" xr:uid="{F860FC30-4D00-4CD5-A8BB-B4414CC5D08F}"/>
+    <hyperlink ref="M51" r:id="rId146" xr:uid="{15D2D5F0-5EFB-40A5-BBAA-91DD811E84CC}"/>
+    <hyperlink ref="M27" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56BAEEFF-2EBF-4B02-97DC-C24781018097}"/>
+    <hyperlink ref="K31" r:id="rId148" xr:uid="{2CFFED1D-5528-4009-9B87-0FD8518C9CC4}"/>
+    <hyperlink ref="K82" r:id="rId149" xr:uid="{F7CE1142-E22B-4EC9-BFC7-4D2802C57705}"/>
+    <hyperlink ref="K81" r:id="rId150" xr:uid="{25746EEE-5BA1-48E1-BB21-0A52A9841D1C}"/>
+    <hyperlink ref="K80" r:id="rId151" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg/960px-M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EE70FD57-D070-4E8D-B5CD-AC117B37AF31}"/>
+    <hyperlink ref="H80" r:id="rId152" xr:uid="{A0C5872B-5FF8-49A5-9978-E73764344B28}"/>
+    <hyperlink ref="K79" r:id="rId153" xr:uid="{35E4135B-8BF0-442D-B156-290FBACB38C6}"/>
+    <hyperlink ref="K78" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K72" r:id="rId155" xr:uid="{9D0C953D-C1FF-4622-B7D4-DC05686BE242}"/>
+    <hyperlink ref="K75" r:id="rId156" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg/960px-Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BFFAA60E-0E9F-4396-BBB5-5E669CEF926F}"/>
+    <hyperlink ref="K76" r:id="rId157" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg/1280px-N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{162AD1A5-1953-49BA-B027-879183D534CB}"/>
+    <hyperlink ref="K77" r:id="rId158" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg/1280px-N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4ED9E081-E1F6-468D-9522-5C82DB135714}"/>
+    <hyperlink ref="F76" r:id="rId159" xr:uid="{94951BEB-AA44-4E7C-BDE5-A40411294AB4}"/>
+    <hyperlink ref="F77" r:id="rId160" xr:uid="{160ACA90-23AD-4430-B2DE-410F26BADA28}"/>
+    <hyperlink ref="K73" r:id="rId161" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{483C2C74-4B1F-45DD-8E56-CAF03C380447}"/>
+    <hyperlink ref="K74" r:id="rId162" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{97405316-B643-499E-8CE1-D0518D573E81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C572739D-C806-4C49-ADDC-DCF4DEEEA371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76D84CD-EC3F-41E9-8CDB-1C75AFBB9169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="840">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -815,9 +815,6 @@
     <t>"Le Baptême du Christ"</t>
   </si>
   <si>
-    <t>"Tombeau d'Henri VII et Élisabeth d'York"</t>
-  </si>
-  <si>
     <t>"La Nature"</t>
   </si>
   <si>
@@ -1025,18 +1022,12 @@
     <t>129 cm environ</t>
   </si>
   <si>
-    <t>200 cm environ</t>
-  </si>
-  <si>
     <t>210 cm environ</t>
   </si>
   <si>
     <t>40 cm environ</t>
   </si>
   <si>
-    <t>146 cm environ</t>
-  </si>
-  <si>
     <t>La Fontaine de Neptune</t>
   </si>
   <si>
@@ -1559,9 +1550,6 @@
     <t>Maximilianstraße</t>
   </si>
   <si>
-    <t>Fontaine de Mercure</t>
-  </si>
-  <si>
     <t>Merkurbrunnen</t>
   </si>
   <si>
@@ -1574,9 +1562,6 @@
     <t>1597-1600</t>
   </si>
   <si>
-    <t>Fontaine d'Hercule</t>
-  </si>
-  <si>
     <t>Herkulesbrunnen</t>
   </si>
   <si>
@@ -2060,9 +2045,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg/960px-Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>230 cm environ</t>
-  </si>
-  <si>
     <t>1537-1541</t>
   </si>
   <si>
@@ -2078,9 +2060,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Loggetta_Sansovino_Minerva_Venezia.jpg/960px-Loggetta_Sansovino_Minerva_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>149 cm</t>
-  </si>
-  <si>
     <t>Apollon</t>
   </si>
   <si>
@@ -2090,9 +2069,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Loggetta_Sansovino_Apollo_Venezia.jpg/960px-Loggetta_Sansovino_Apollo_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>147 cm</t>
-  </si>
-  <si>
     <t>Mercure</t>
   </si>
   <si>
@@ -2102,9 +2078,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Loggetta_Sansovino_Mercurio_Venezia.jpg/960px-Loggetta_Sansovino_Mercurio_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>148 cm</t>
-  </si>
-  <si>
     <t>La Paix</t>
   </si>
   <si>
@@ -2114,9 +2087,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Loggetta_Sansovino_allegoria_Pace_Venezia.jpg/960px-Loggetta_Sansovino_allegoria_Pace_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>150 cm</t>
-  </si>
-  <si>
     <t>1554-1566</t>
   </si>
   <si>
@@ -2273,9 +2243,6 @@
     <t>Musée National de Sculpture</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg/1280px-San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>Ce bas-relief faisait partie du jubé de l'église Saint-Germain-l'Auxerrois à Paris, construit par Pierre Lescot et Jean Goujon et démonté en 1745.</t>
   </si>
   <si>
@@ -2487,6 +2454,105 @@
   </si>
   <si>
     <t>Bois sculpté et peint</t>
+  </si>
+  <si>
+    <t>Groupe de trois sculptures</t>
+  </si>
+  <si>
+    <t>Tombeau d'Henri VII et Élisabeth d'York</t>
+  </si>
+  <si>
+    <t>1511-1513</t>
+  </si>
+  <si>
+    <t>Tombeau de Marguerite de Beaufort</t>
+  </si>
+  <si>
+    <t>Tomb of Margaret Beaufort</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/31/Margaret_Beaufort_2.jpg/1280px-Margaret_Beaufort_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bronze doré et marbre</t>
+  </si>
+  <si>
+    <t>c. 1509-1511</t>
+  </si>
+  <si>
+    <t>Victoria and Albert Museum</t>
+  </si>
+  <si>
+    <t>Buste du roi Henri VII</t>
+  </si>
+  <si>
+    <t>Bust of King Henry VII</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Henry_VII.JPG/960px-Henry_VII.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Terre cuite peinte et dorée</t>
+  </si>
+  <si>
+    <t>1510-1515</t>
+  </si>
+  <si>
+    <t>Buste de John Fisher, évêque de Rochester</t>
+  </si>
+  <si>
+    <t>Portrait Bust of John Fisher</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4b/Bishop_John_Fisher_MET_DP242659.jpg/960px-Bishop_John_Fisher_MET_DP242659.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Terre cuite polychrome</t>
+  </si>
+  <si>
+    <t>Saint Jérôme pénitent</t>
+  </si>
+  <si>
+    <t>San Jerónimo penitente</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/65/San_Jer%C3%B3nimo_penitente_001.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Virgen con el Niño</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7f/Virgen_de_Bel%C3%A9n_%28Pietro_Torrigiano%29.jpg/960px-Virgen_de_Bel%C3%A9n_%28Pietro_Torrigiano%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/San_Jer%C3%B3nimo_penitente%2C_Jer%C3%B3nimo_Hern%C3%A1ndez.jpg/1280px-San_Jer%C3%B3nimo_penitente%2C_Jer%C3%B3nimo_Hern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1525 environ</t>
+  </si>
+  <si>
+    <t>Terre cuite polychromée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronze </t>
+  </si>
+  <si>
+    <t>Mercure et Cupidon</t>
+  </si>
+  <si>
+    <t>Le groupe statuaire est au sommet de la fontaine de Mercure, entièrement conçue par Adrian de Vries</t>
+  </si>
+  <si>
+    <t>Le groupe statuaire est au sommet de la fontaine d'Hercule, entièrement conçue par Adrian de Vries</t>
+  </si>
+  <si>
+    <t>Hercule et l'Hydre</t>
+  </si>
+  <si>
+    <t>Pierre de Solnhofen</t>
+  </si>
+  <si>
+    <t>250 environ</t>
   </si>
 </sst>
 </file>
@@ -2561,7 +2627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2584,6 +2650,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2592,7 +2671,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2645,6 +2724,24 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2950,7 +3047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z137"/>
+  <dimension ref="A1:Z142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -3139,22 +3236,22 @@
         <v>195</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S3" s="3">
         <v>560</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W3" s="2" t="s">
         <v>22</v>
@@ -3171,31 +3268,31 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="R4" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="V4" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>22</v>
@@ -3212,31 +3309,31 @@
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>347</v>
-      </c>
       <c r="R5" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S5" s="3">
         <v>262</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W5" s="2" t="s">
         <v>22</v>
@@ -3253,31 +3350,31 @@
         <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S6" s="3">
         <v>139</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W6" s="2" t="s">
         <v>22</v>
@@ -3294,25 +3391,25 @@
         <v>70</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>168</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="V7" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>22</v>
@@ -3329,28 +3426,28 @@
         <v>70</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>361</v>
-      </c>
       <c r="R8" s="2" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W8" s="2" t="s">
         <v>22</v>
@@ -3367,28 +3464,28 @@
         <v>70</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>22</v>
@@ -3405,31 +3502,31 @@
         <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="K10" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="S10" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="V10" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="V10" s="4" t="s">
-        <v>373</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>22</v>
@@ -3446,7 +3543,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>169</v>
@@ -3455,22 +3552,22 @@
         <v>196</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>23</v>
@@ -3487,7 +3584,7 @@
         <v>71</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>169</v>
@@ -3496,22 +3593,22 @@
         <v>196</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>23</v>
@@ -3528,31 +3625,34 @@
         <v>71</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>447</v>
-      </c>
       <c r="R13" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>839</v>
       </c>
       <c r="V13" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>23</v>
@@ -3569,31 +3669,31 @@
         <v>71</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="V14" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>23</v>
@@ -3610,35 +3710,35 @@
         <v>71</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="K15" s="7" t="s">
         <v>453</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>456</v>
       </c>
       <c r="M15" s="7"/>
       <c r="Q15" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>23</v>
@@ -3655,7 +3755,7 @@
         <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>174</v>
@@ -3664,22 +3764,22 @@
         <v>210</v>
       </c>
       <c r="I16" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>462</v>
-      </c>
       <c r="V16" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>23</v>
@@ -3705,7 +3805,7 @@
         <v>236</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>31</v>
@@ -3737,25 +3837,25 @@
         <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>377</v>
-      </c>
       <c r="V18" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W18" s="2" t="s">
         <v>25</v>
@@ -3772,25 +3872,25 @@
         <v>73</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>168</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="11" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L19" s="21"/>
       <c r="M19" s="21"/>
@@ -3799,7 +3899,7 @@
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
       <c r="R19" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S19" s="13">
         <v>224</v>
@@ -3807,7 +3907,7 @@
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
       <c r="V19" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W19" s="11" t="s">
         <v>25</v>
@@ -3825,7 +3925,7 @@
         <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>168</v>
@@ -3834,25 +3934,25 @@
         <v>198</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="I20" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="V20" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W20" s="2" t="s">
         <v>25</v>
@@ -3869,22 +3969,22 @@
         <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S21" s="3">
         <v>78</v>
@@ -3893,7 +3993,7 @@
         <v>75</v>
       </c>
       <c r="V21" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W21" s="2" t="s">
         <v>25</v>
@@ -3910,34 +4010,34 @@
         <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="R22" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>395</v>
-      </c>
       <c r="V22" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W22" s="2" t="s">
         <v>25</v>
@@ -3954,34 +4054,34 @@
         <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="K23" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="R23" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>402</v>
-      </c>
       <c r="V23" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>25</v>
@@ -4010,13 +4110,13 @@
         <v>237</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="V24" s="4">
         <v>1</v>
@@ -4045,16 +4145,16 @@
         <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="V25" s="6">
         <v>3</v>
@@ -4083,10 +4183,10 @@
         <v>238</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="V26" s="6">
         <v>3</v>
@@ -4112,34 +4212,34 @@
         <v>170</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="11" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="N27" s="11"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="R27" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="S27" s="13">
         <v>150</v>
@@ -4171,28 +4271,28 @@
         <v>170</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="M28" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="R28" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="K28" s="7" t="s">
+      <c r="T28" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="U28" s="3">
         <v>32</v>
@@ -4215,28 +4315,28 @@
         <v>76</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="K29" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="V29" s="5">
         <v>2</v>
@@ -4256,25 +4356,25 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="K30" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="R30" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="V30" s="5">
         <v>2</v>
@@ -4300,25 +4400,25 @@
         <v>170</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="I31" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="T31" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>430</v>
       </c>
       <c r="V31" s="5">
         <v>2</v>
@@ -4338,25 +4438,25 @@
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="K32" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>436</v>
-      </c>
       <c r="R32" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="V32" s="5">
         <v>2</v>
@@ -4385,10 +4485,10 @@
         <v>239</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="V33" s="6">
         <v>3</v>
@@ -4417,22 +4517,22 @@
         <v>201</v>
       </c>
       <c r="I34" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="J34" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>466</v>
-      </c>
       <c r="V34" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -4449,31 +4549,31 @@
         <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="J35" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="K35" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="R35" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="S35" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>472</v>
-      </c>
       <c r="V35" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -4490,31 +4590,31 @@
         <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I36" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="V36" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4534,28 +4634,28 @@
         <v>127</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="K37" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="R37" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="S37" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="V37" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4572,7 +4672,7 @@
         <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>168</v>
@@ -4581,22 +4681,22 @@
         <v>195</v>
       </c>
       <c r="I38" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="V38" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4613,31 +4713,31 @@
         <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I39" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="J39" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="V39" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4654,31 +4754,31 @@
         <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="V40" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4695,7 +4795,7 @@
         <v>78</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>168</v>
@@ -4704,22 +4804,22 @@
         <v>201</v>
       </c>
       <c r="I41" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="J41" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>502</v>
-      </c>
       <c r="V41" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4733,25 +4833,25 @@
         <v>33</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S42" s="3">
         <v>517</v>
@@ -4763,13 +4863,13 @@
         <v>140</v>
       </c>
       <c r="V42" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W42" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4777,25 +4877,25 @@
         <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="I43" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>634</v>
-      </c>
       <c r="K43" s="7" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S43" s="3">
         <v>128</v>
@@ -4807,13 +4907,13 @@
         <v>63</v>
       </c>
       <c r="V43" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W43" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4821,43 +4921,43 @@
         <v>33</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W44" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4865,25 +4965,25 @@
         <v>33</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S45" s="3">
         <v>780</v>
@@ -4892,13 +4992,13 @@
         <v>640</v>
       </c>
       <c r="V45" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W45" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4906,10 +5006,10 @@
         <v>33</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>171</v>
@@ -4918,13 +5018,13 @@
         <v>203</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S46" s="3">
         <v>228</v>
@@ -4936,13 +5036,13 @@
         <v>53</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4950,10 +5050,10 @@
         <v>33</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>171</v>
@@ -4962,16 +5062,16 @@
         <v>203</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="T47" s="3">
         <v>49</v>
@@ -4980,13 +5080,13 @@
         <v>75</v>
       </c>
       <c r="V47" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4994,28 +5094,28 @@
         <v>33</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>173</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="T48" s="3">
         <v>75</v>
@@ -5024,13 +5124,13 @@
         <v>60</v>
       </c>
       <c r="V48" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="49" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5038,25 +5138,25 @@
         <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S49" s="3">
         <v>650</v>
@@ -5065,13 +5165,13 @@
         <v>470</v>
       </c>
       <c r="V49" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="50" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5079,40 +5179,40 @@
         <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="V50" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="51" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5120,31 +5220,31 @@
         <v>33</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S51" s="3">
         <v>277</v>
@@ -5156,13 +5256,13 @@
         <v>125</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>33</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="52" spans="1:26" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5183,11 +5283,11 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
@@ -5196,10 +5296,10 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
@@ -5235,13 +5335,13 @@
         <v>240</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="V53" s="6">
         <v>3</v>
@@ -5267,19 +5367,19 @@
         <v>168</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>330</v>
+        <v>311</v>
+      </c>
+      <c r="S54" s="3">
+        <v>190</v>
       </c>
       <c r="V54" s="6">
         <v>3</v>
@@ -5311,10 +5411,22 @@
         <v>241</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>454</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>312</v>
+        <v>838</v>
+      </c>
+      <c r="S55" s="3">
+        <v>23</v>
+      </c>
+      <c r="T55" s="3">
+        <v>17</v>
+      </c>
+      <c r="U55" s="3">
+        <v>2</v>
       </c>
       <c r="V55" s="6">
         <v>3</v>
@@ -5340,22 +5452,22 @@
         <v>170</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S56" s="3">
         <v>190</v>
@@ -5384,28 +5496,28 @@
         <v>83</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="V57" s="5">
         <v>2</v>
@@ -5425,31 +5537,31 @@
         <v>83</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J58" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="K58" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>530</v>
-      </c>
       <c r="Q58" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="V58" s="5">
         <v>2</v>
@@ -5469,34 +5581,34 @@
         <v>83</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="V59" s="5">
         <v>2</v>
@@ -5516,28 +5628,31 @@
         <v>83</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="K60" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>542</v>
+      <c r="Q60" s="2" t="s">
+        <v>402</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="V60" s="5">
         <v>2</v>
@@ -5557,28 +5672,28 @@
         <v>83</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>170</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="V61" s="5">
         <v>2</v>
@@ -5607,30 +5722,30 @@
         <v>206</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="J62" s="11"/>
       <c r="K62" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L62" s="21"/>
       <c r="M62" s="12" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="N62" s="11"/>
       <c r="O62" s="19" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="P62" s="11"/>
       <c r="Q62" s="11"/>
       <c r="R62" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S62" s="13">
         <v>182</v>
@@ -5665,7 +5780,7 @@
         <v>242</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R63" s="2" t="s">
         <v>31</v>
@@ -5697,22 +5812,28 @@
         <v>203</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
+      </c>
+      <c r="T64" s="3">
+        <v>92</v>
+      </c>
+      <c r="U64" s="3">
+        <v>72</v>
       </c>
       <c r="V64" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W64" s="2" t="s">
         <v>39</v>
@@ -5729,31 +5850,37 @@
         <v>86</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>178</v>
       </c>
       <c r="E65" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="M65" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="K65" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="M65" s="7" t="s">
-        <v>511</v>
-      </c>
       <c r="R65" s="2" t="s">
-        <v>315</v>
+        <v>833</v>
+      </c>
+      <c r="S65" s="3">
+        <v>269</v>
       </c>
       <c r="V65" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>39</v>
@@ -5770,31 +5897,37 @@
         <v>86</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>178</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>513</v>
+        <v>837</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>515</v>
+        <v>510</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>835</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
+      </c>
+      <c r="S66" s="3">
+        <v>347</v>
       </c>
       <c r="V66" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W66" s="2" t="s">
         <v>39</v>
@@ -5820,10 +5953,10 @@
         <v>243</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="V67" s="6">
         <v>3</v>
@@ -5855,10 +5988,10 @@
         <v>244</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V68" s="5">
         <v>2</v>
@@ -5890,10 +6023,10 @@
         <v>245</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="V69" s="6">
         <v>3</v>
@@ -5922,13 +6055,13 @@
         <v>211</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V70" s="6">
         <v>3</v>
@@ -5960,10 +6093,10 @@
         <v>246</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="V71" s="6">
         <v>3</v>
@@ -5986,26 +6119,26 @@
         <v>138</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M72" s="2"/>
       <c r="R72" s="2" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
@@ -6027,29 +6160,29 @@
         <v>91</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>194</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="M73" s="2"/>
       <c r="R73" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S73" s="2">
         <v>8</v>
@@ -6076,26 +6209,26 @@
         <v>91</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>194</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="M74" s="2"/>
       <c r="R74" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S74" s="2">
         <v>8</v>
@@ -6122,29 +6255,29 @@
         <v>91</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>194</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="M75" s="2"/>
       <c r="R75" s="2" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="T75" s="2"/>
       <c r="U75" s="2"/>
@@ -6166,38 +6299,38 @@
         <v>91</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>194</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="F76" s="18" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="M76" s="2"/>
       <c r="R76" s="2" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="T76" s="2"/>
       <c r="U76" s="2"/>
@@ -6219,35 +6352,35 @@
         <v>91</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>194</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="M77" s="2"/>
       <c r="R77" s="2" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="S77" s="2"/>
       <c r="T77" s="2"/>
@@ -6282,10 +6415,10 @@
         <v>247</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="V78" s="6">
         <v>3</v>
@@ -6311,24 +6444,24 @@
         <v>178</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="K79" s="18" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="R79" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="T79" s="2"/>
       <c r="U79" s="2"/>
@@ -6350,36 +6483,36 @@
         <v>93</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="K80" s="18" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="R80" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="T80" s="2"/>
       <c r="U80" s="2"/>
@@ -6393,7 +6526,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>47</v>
       </c>
@@ -6401,30 +6534,30 @@
         <v>93</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="I81" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="J81" s="8" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="K81" s="18" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="R81" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S81" s="2"/>
       <c r="T81" s="2"/>
@@ -6439,7 +6572,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="82" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>47</v>
       </c>
@@ -6447,27 +6580,27 @@
         <v>93</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="K82" s="18" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="R82" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S82" s="2">
         <v>180</v>
@@ -6484,7 +6617,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>30</v>
       </c>
@@ -6492,7 +6625,7 @@
         <v>94</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>171</v>
@@ -6501,16 +6634,16 @@
         <v>203</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="M83" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S83" s="3">
         <v>73</v>
@@ -6531,7 +6664,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>30</v>
       </c>
@@ -6539,7 +6672,7 @@
         <v>94</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>171</v>
@@ -6548,14 +6681,14 @@
         <v>203</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="M84" s="16"/>
       <c r="R84" s="2" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="S84" s="3">
         <v>210</v>
@@ -6576,7 +6709,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>30</v>
       </c>
@@ -6584,7 +6717,7 @@
         <v>94</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>171</v>
@@ -6593,23 +6726,23 @@
         <v>203</v>
       </c>
       <c r="F85" s="18" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="M85" s="16"/>
       <c r="R85" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S85" s="3" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="T85" s="3">
         <v>182</v>
@@ -6627,7 +6760,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>30</v>
       </c>
@@ -6635,7 +6768,7 @@
         <v>94</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>171</v>
@@ -6644,17 +6777,17 @@
         <v>203</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="M86" s="16"/>
       <c r="R86" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S86" s="3">
         <v>79</v>
@@ -6675,7 +6808,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>30</v>
       </c>
@@ -6683,23 +6816,23 @@
         <v>94</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="M87" s="16"/>
       <c r="R87" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S87" s="3">
         <v>700</v>
@@ -6720,7 +6853,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>30</v>
       </c>
@@ -6728,22 +6861,22 @@
         <v>94</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="M88" s="16"/>
       <c r="R88" s="2" t="s">
@@ -6768,7 +6901,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>30</v>
       </c>
@@ -6776,31 +6909,31 @@
         <v>94</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E89" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="K89" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="M89" s="17" t="s">
         <v>615</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="H89" s="15" t="s">
-        <v>617</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="K89" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="L89" s="8" t="s">
-        <v>752</v>
-      </c>
-      <c r="M89" s="17" t="s">
-        <v>620</v>
       </c>
       <c r="R89" s="2" t="s">
         <v>31</v>
@@ -6824,7 +6957,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>30</v>
       </c>
@@ -6836,20 +6969,20 @@
       </c>
       <c r="D90"/>
       <c r="E90" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="J90"/>
       <c r="K90" s="15" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="M90" s="16"/>
       <c r="R90" s="2" t="s">
@@ -6874,7 +7007,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>48</v>
       </c>
@@ -6894,10 +7027,10 @@
         <v>248</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="V91" s="4">
         <v>3</v>
@@ -6909,51 +7042,53 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
+    <row r="92" spans="1:25" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D92" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="E92" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="I92" s="2" t="s">
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="K92" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="R92" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="S92" s="3">
-        <v>224</v>
-      </c>
-      <c r="T92" s="3">
-        <v>126</v>
-      </c>
-      <c r="U92" s="3">
-        <v>160</v>
-      </c>
-      <c r="V92" s="6">
+      <c r="J92" s="22"/>
+      <c r="K92" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="L92" s="28"/>
+      <c r="M92" s="28"/>
+      <c r="N92" s="22"/>
+      <c r="O92" s="22"/>
+      <c r="P92" s="22"/>
+      <c r="Q92" s="22"/>
+      <c r="R92" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="V92" s="5">
         <v>3</v>
       </c>
-      <c r="W92" s="2" t="s">
+      <c r="W92" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="X92" s="2" t="s">
+      <c r="X92" s="22" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y92" s="22"/>
+    </row>
+    <row r="93" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>50</v>
       </c>
@@ -6973,10 +7108,10 @@
         <v>250</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="S93" s="3">
         <v>26</v>
@@ -6997,7 +7132,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>51</v>
       </c>
@@ -7011,10 +7146,10 @@
         <v>216</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R94" s="2" t="s">
         <v>31</v>
@@ -7029,7 +7164,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>52</v>
       </c>
@@ -7046,16 +7181,16 @@
         <v>217</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="V95" s="6">
         <v>3</v>
@@ -7067,7 +7202,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>53</v>
       </c>
@@ -7087,10 +7222,10 @@
         <v>251</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V96" s="6">
         <v>3</v>
@@ -7119,13 +7254,13 @@
         <v>218</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="V97" s="6">
         <v>3</v>
@@ -7161,20 +7296,20 @@
       </c>
       <c r="J98" s="11"/>
       <c r="K98" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L98" s="21" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="M98" s="12" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="N98" s="11"/>
       <c r="O98" s="11"/>
       <c r="P98" s="11"/>
       <c r="Q98" s="11"/>
       <c r="R98" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S98" s="13"/>
       <c r="T98" s="13"/>
@@ -7209,10 +7344,10 @@
         <v>253</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S99" s="3">
         <v>113</v>
@@ -7247,13 +7382,13 @@
         <v>221</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="V100" s="5">
         <v>2</v>
@@ -7285,10 +7420,10 @@
         <v>254</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R101" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="V101" s="6">
         <v>3</v>
@@ -7320,10 +7455,10 @@
         <v>255</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="R102" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="V102" s="6">
         <v>3</v>
@@ -7352,13 +7487,13 @@
         <v>224</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R103" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="V103" s="6">
         <v>3</v>
@@ -7387,13 +7522,13 @@
         <v>225</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="R104" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V104" s="6">
         <v>3</v>
@@ -7425,10 +7560,10 @@
         <v>256</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R105" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="V105" s="6">
         <v>3</v>
@@ -7457,22 +7592,22 @@
         <v>202</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="M106" s="7" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="O106" s="7" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="R106" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S106" s="3">
         <v>450</v>
@@ -7484,7 +7619,7 @@
         <v>250</v>
       </c>
       <c r="V106" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>60</v>
@@ -7510,15 +7645,15 @@
         <v>202</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M107" s="7"/>
       <c r="O107" s="7"/>
       <c r="R107" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S107" s="3">
         <v>90</v>
@@ -7547,7 +7682,7 @@
         <v>109</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>171</v>
@@ -7556,20 +7691,20 @@
         <v>203</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="M108" s="7" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="O108" s="8"/>
       <c r="R108" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S108" s="3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="T108" s="3">
         <v>75</v>
@@ -7578,7 +7713,7 @@
         <v>75</v>
       </c>
       <c r="V108" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W108" s="2" t="s">
         <v>60</v>
@@ -7604,23 +7739,23 @@
         <v>203</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="M109" s="7" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="O109" s="8"/>
       <c r="R109" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="S109" s="3" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="T109" s="3">
         <v>120</v>
@@ -7629,7 +7764,7 @@
         <v>81</v>
       </c>
       <c r="V109" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W109" s="2" t="s">
         <v>60</v>
@@ -7647,7 +7782,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>171</v>
@@ -7656,20 +7791,23 @@
         <v>203</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="O110" s="8"/>
+      <c r="Q110" s="2" t="s">
+        <v>807</v>
+      </c>
       <c r="R110" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S110" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="V110" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W110" s="2" t="s">
         <v>60</v>
@@ -7687,7 +7825,7 @@
         <v>109</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>171</v>
@@ -7696,17 +7834,17 @@
         <v>203</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="M111" s="7" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="O111" s="8"/>
       <c r="R111" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S111" s="3">
         <v>83</v>
@@ -7718,7 +7856,7 @@
         <v>49</v>
       </c>
       <c r="V111" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W111" s="2" t="s">
         <v>60</v>
@@ -7736,7 +7874,7 @@
         <v>109</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>171</v>
@@ -7745,14 +7883,14 @@
         <v>203</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="O112" s="8"/>
       <c r="R112" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S112" s="3">
         <v>140</v>
@@ -7764,7 +7902,7 @@
         <v>80</v>
       </c>
       <c r="V112" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W112" s="2" t="s">
         <v>60</v>
@@ -7785,26 +7923,26 @@
         <v>1570</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="M113" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="K113" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="L113" s="8" t="s">
-        <v>574</v>
-      </c>
-      <c r="M113" s="7" t="s">
-        <v>575</v>
       </c>
       <c r="O113" s="8"/>
       <c r="R113" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S113" s="3">
         <v>96</v>
@@ -7834,23 +7972,23 @@
         <v>109</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>171</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="O114" s="8"/>
       <c r="R114" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S114" s="3">
         <v>159</v>
@@ -7862,7 +8000,7 @@
         <v>81</v>
       </c>
       <c r="V114" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W114" s="2" t="s">
         <v>60</v>
@@ -7892,10 +8030,10 @@
         <v>257</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R115" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S115" s="3">
         <v>43</v>
@@ -7937,10 +8075,19 @@
         <v>258</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R116" s="2" t="s">
         <v>31</v>
+      </c>
+      <c r="S116" s="3">
+        <v>177</v>
+      </c>
+      <c r="T116" s="3">
+        <v>70</v>
+      </c>
+      <c r="U116" s="3">
+        <v>60</v>
       </c>
       <c r="V116" s="6">
         <v>3</v>
@@ -7970,13 +8117,19 @@
         <v>228</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R117" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
+      </c>
+      <c r="S117" s="3">
+        <v>970</v>
+      </c>
+      <c r="T117" s="3">
+        <v>370</v>
       </c>
       <c r="V117" s="6">
         <v>3</v>
@@ -8008,10 +8161,19 @@
         <v>259</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R118" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
+      </c>
+      <c r="S118" s="3">
+        <v>240</v>
+      </c>
+      <c r="T118" s="3">
+        <v>250</v>
+      </c>
+      <c r="U118" s="3">
+        <v>245</v>
       </c>
       <c r="V118" s="6">
         <v>3</v>
@@ -8037,27 +8199,31 @@
         <v>168</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R119" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S119" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="T119" s="2"/>
-      <c r="U119" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="S119" s="2">
+        <v>146</v>
+      </c>
+      <c r="T119" s="2">
+        <v>60</v>
+      </c>
+      <c r="U119" s="2">
+        <v>65</v>
+      </c>
       <c r="V119" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W119" t="s">
         <v>65</v>
@@ -8074,33 +8240,35 @@
         <v>113</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>168</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S120" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="T120" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="S120" s="2">
+        <v>320</v>
+      </c>
+      <c r="T120" s="2">
+        <v>145</v>
+      </c>
       <c r="U120" s="2"/>
       <c r="V120" s="4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="W120" t="s">
         <v>65</v>
@@ -8117,36 +8285,36 @@
         <v>113</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F121" s="18" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="R121" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S121" s="2" t="s">
-        <v>681</v>
+        <v>310</v>
+      </c>
+      <c r="S121" s="2">
+        <v>147</v>
       </c>
       <c r="T121" s="2"/>
       <c r="U121" s="2"/>
       <c r="V121" s="4" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="W121" t="s">
         <v>65</v>
@@ -8163,36 +8331,36 @@
         <v>113</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E122" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F122" s="18" t="s">
+        <v>733</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="K122" s="7" t="s">
         <v>677</v>
       </c>
-      <c r="F122" s="18" t="s">
-        <v>743</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="K122" s="7" t="s">
-        <v>684</v>
-      </c>
       <c r="R122" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S122" s="2" t="s">
-        <v>685</v>
+        <v>310</v>
+      </c>
+      <c r="S122" s="2">
+        <v>147</v>
       </c>
       <c r="T122" s="2"/>
       <c r="U122" s="2"/>
       <c r="V122" s="4" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="W122" t="s">
         <v>65</v>
@@ -8209,36 +8377,36 @@
         <v>113</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F123" s="18" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="R123" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S123" s="2" t="s">
-        <v>689</v>
+        <v>310</v>
+      </c>
+      <c r="S123" s="2">
+        <v>147</v>
       </c>
       <c r="T123" s="2"/>
       <c r="U123" s="2"/>
       <c r="V123" s="4" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="W123" t="s">
         <v>65</v>
@@ -8255,36 +8423,36 @@
         <v>113</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F124" s="18" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="R124" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S124" s="2" t="s">
-        <v>693</v>
+        <v>310</v>
+      </c>
+      <c r="S124" s="2">
+        <v>147</v>
       </c>
       <c r="T124" s="2"/>
       <c r="U124" s="2"/>
       <c r="V124" s="4" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="W124" t="s">
         <v>65</v>
@@ -8301,33 +8469,33 @@
         <v>113</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>169</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="R125" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S125" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="T125" s="2"/>
       <c r="U125" s="2"/>
       <c r="V125" s="4" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="W125" t="s">
         <v>65</v>
@@ -8337,40 +8505,49 @@
       </c>
     </row>
     <row r="126" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="D126" s="2" t="s">
+      <c r="C126" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D126" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="E126" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="J126" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="K126" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="R126" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S126" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="T126" s="2"/>
-      <c r="U126" s="2"/>
-      <c r="V126" s="4" t="s">
-        <v>670</v>
+      <c r="E126" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="F126" s="23"/>
+      <c r="G126" s="23"/>
+      <c r="H126" s="23"/>
+      <c r="I126" s="23" t="s">
+        <v>688</v>
+      </c>
+      <c r="J126" s="23" t="s">
+        <v>689</v>
+      </c>
+      <c r="K126" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="L126" s="25"/>
+      <c r="M126" s="25"/>
+      <c r="N126" s="23"/>
+      <c r="O126" s="23"/>
+      <c r="P126" s="23"/>
+      <c r="Q126" s="23"/>
+      <c r="R126" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="S126" s="23" t="s">
+        <v>687</v>
+      </c>
+      <c r="T126" s="23"/>
+      <c r="U126" s="23"/>
+      <c r="V126" s="26" t="s">
+        <v>665</v>
       </c>
       <c r="W126" t="s">
         <v>65</v>
@@ -8396,13 +8573,24 @@
         <v>230</v>
       </c>
       <c r="I127" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="K127" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="L127" s="2"/>
+      <c r="M127" s="2"/>
+      <c r="R127" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="S127" s="2">
+        <v>170</v>
+      </c>
+      <c r="T127" s="2">
         <v>260</v>
       </c>
-      <c r="K127" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="R127" s="2" t="s">
-        <v>324</v>
+      <c r="U127" s="2">
+        <v>180</v>
       </c>
       <c r="V127" s="5">
         <v>2</v>
@@ -8416,365 +8604,404 @@
     </row>
     <row r="128" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>164</v>
+        <v>809</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="K128" s="7" t="s">
-        <v>306</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="K128" s="18" t="s">
+        <v>812</v>
+      </c>
+      <c r="L128" s="2"/>
+      <c r="M128" s="2"/>
       <c r="R128" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S128" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="V128" s="6">
-        <v>3</v>
+        <v>813</v>
+      </c>
+      <c r="S128" s="2">
+        <v>155</v>
+      </c>
+      <c r="T128" s="2">
+        <v>230</v>
+      </c>
+      <c r="U128" s="2">
+        <v>120</v>
+      </c>
+      <c r="V128" s="5">
+        <v>2</v>
       </c>
       <c r="W128" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X128" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>165</v>
+        <v>814</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>232</v>
+        <v>815</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="K129" s="7" t="s">
-        <v>307</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="K129" s="18" t="s">
+        <v>818</v>
+      </c>
+      <c r="L129" s="2"/>
+      <c r="M129" s="2"/>
       <c r="R129" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S129" s="3">
+        <v>819</v>
+      </c>
+      <c r="S129" s="2">
+        <v>61</v>
+      </c>
+      <c r="T129" s="2">
+        <v>69</v>
+      </c>
+      <c r="U129" s="2">
+        <v>36</v>
+      </c>
+      <c r="V129" s="5">
+        <v>2</v>
+      </c>
+      <c r="W129" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X129" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="T129" s="3">
-        <v>53</v>
-      </c>
-      <c r="U129" s="3">
-        <v>48</v>
-      </c>
-      <c r="V129" s="6">
-        <v>3</v>
-      </c>
-      <c r="W129" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="X129" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="130" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>749</v>
+        <v>820</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="K130" s="7" t="s">
-        <v>308</v>
-      </c>
+        <v>821</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="K130" s="18" t="s">
+        <v>823</v>
+      </c>
+      <c r="L130" s="2"/>
+      <c r="M130" s="2"/>
       <c r="R130" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S130" s="3">
+        <v>824</v>
+      </c>
+      <c r="S130" s="2">
+        <v>62</v>
+      </c>
+      <c r="T130" s="2">
+        <v>66</v>
+      </c>
+      <c r="U130" s="2">
         <v>34</v>
       </c>
-      <c r="V130" s="6">
-        <v>3</v>
+      <c r="V130" s="5">
+        <v>2</v>
       </c>
       <c r="W130" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="X130" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="131" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>166</v>
+        <v>831</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="K131" s="7" t="s">
-        <v>309</v>
-      </c>
+        <v>825</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="K131" s="18" t="s">
+        <v>827</v>
+      </c>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
       <c r="R131" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="V131" s="6">
-        <v>3</v>
+        <v>824</v>
+      </c>
+      <c r="S131" s="13">
+        <v>224</v>
+      </c>
+      <c r="T131" s="13">
+        <v>126</v>
+      </c>
+      <c r="U131" s="13">
+        <v>160</v>
+      </c>
+      <c r="V131" s="5">
+        <v>2</v>
       </c>
       <c r="W131" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="X131" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="132" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>167</v>
+        <v>831</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="K132" s="7" t="s">
-        <v>702</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="K132" s="18" t="s">
+        <v>829</v>
+      </c>
+      <c r="L132" s="2"/>
+      <c r="M132" s="2"/>
       <c r="R132" s="2" t="s">
-        <v>312</v>
-      </c>
+        <v>832</v>
+      </c>
+      <c r="S132" s="3">
+        <v>140</v>
+      </c>
+      <c r="T132" s="2"/>
+      <c r="U132" s="2"/>
       <c r="V132" s="5">
         <v>2</v>
       </c>
       <c r="W132" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="X132" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="133" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>705</v>
+        <v>231</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>707</v>
+        <v>260</v>
       </c>
       <c r="K133" s="7" t="s">
-        <v>708</v>
-      </c>
-      <c r="M133" s="7" t="s">
-        <v>709</v>
+        <v>305</v>
       </c>
       <c r="R133" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S133" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="V133" s="5">
-        <v>2</v>
+        <v>329</v>
+      </c>
+      <c r="V133" s="6">
+        <v>3</v>
       </c>
       <c r="W133" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="X133" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>703</v>
+        <v>165</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>705</v>
+        <v>232</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>711</v>
+        <v>574</v>
       </c>
       <c r="K134" s="7" t="s">
-        <v>712</v>
-      </c>
-      <c r="M134" s="7" t="s">
-        <v>709</v>
+        <v>306</v>
       </c>
       <c r="R134" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S134" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="V134" s="5">
-        <v>2</v>
+        <v>310</v>
+      </c>
+      <c r="S134" s="3">
+        <v>114</v>
+      </c>
+      <c r="T134" s="3">
+        <v>53</v>
+      </c>
+      <c r="U134" s="3">
+        <v>48</v>
+      </c>
+      <c r="V134" s="6">
+        <v>3</v>
       </c>
       <c r="W134" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="X134" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>714</v>
+        <v>738</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>715</v>
+        <v>193</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>716</v>
+        <v>233</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>717</v>
+        <v>237</v>
       </c>
       <c r="K135" s="7" t="s">
-        <v>718</v>
+        <v>307</v>
       </c>
       <c r="R135" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S135" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="V135" s="5">
-        <v>2</v>
+        <v>310</v>
+      </c>
+      <c r="S135" s="3">
+        <v>34</v>
+      </c>
+      <c r="V135" s="6">
+        <v>3</v>
       </c>
       <c r="W135" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="X135" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="136" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>720</v>
+        <v>166</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>721</v>
+        <v>234</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="J136" s="2" t="s">
-        <v>723</v>
+        <v>576</v>
       </c>
       <c r="K136" s="7" t="s">
-        <v>724</v>
+        <v>308</v>
       </c>
       <c r="R136" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="S136" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="V136" s="5">
-        <v>2</v>
+        <v>324</v>
+      </c>
+      <c r="S136" s="3">
+        <v>442</v>
+      </c>
+      <c r="T136" s="3">
+        <v>266</v>
+      </c>
+      <c r="U136" s="3">
+        <v>148</v>
+      </c>
+      <c r="V136" s="6">
+        <v>3</v>
       </c>
       <c r="W136" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="X136" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="137" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8785,7 +9012,7 @@
         <v>119</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>725</v>
+        <v>167</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>169</v>
@@ -8794,16 +9021,13 @@
         <v>235</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="J137" s="2" t="s">
-        <v>727</v>
+        <v>691</v>
       </c>
       <c r="K137" s="7" t="s">
-        <v>728</v>
+        <v>692</v>
       </c>
       <c r="R137" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="V137" s="5">
         <v>2</v>
@@ -8812,6 +9036,220 @@
         <v>57</v>
       </c>
       <c r="X137" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="K138" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="M138" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="R138" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S138" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="V138" s="5">
+        <v>2</v>
+      </c>
+      <c r="W138" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X138" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="K139" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="M139" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="R139" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S139" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="V139" s="5">
+        <v>2</v>
+      </c>
+      <c r="W139" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X139" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="K140" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="R140" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S140" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="V140" s="5">
+        <v>2</v>
+      </c>
+      <c r="W140" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X140" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="K141" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="R141" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="S141" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="V141" s="5">
+        <v>2</v>
+      </c>
+      <c r="W141" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X141" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="K142" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="R142" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="V142" s="5">
+        <v>2</v>
+      </c>
+      <c r="W142" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X142" s="2" t="s">
         <v>119</v>
       </c>
     </row>
@@ -8938,48 +9376,53 @@
     <hyperlink ref="K51" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{471BE4AF-D2F1-433A-B3AC-795231C2AF30}"/>
     <hyperlink ref="K49" r:id="rId119" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{F1CACA00-310B-4B86-B079-D54654CC5BDD}"/>
     <hyperlink ref="K50" r:id="rId120" display="https://upload.wikimedia.org/wikipedia/commons/3/39/Tomb_of_Lorenzo_the_Magnificent_and_Giuliano_de%27_Medici%2C_Sagrestia_Nuova%2C_Medici_Chapels%2C_San_Lorenzo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr" xr:uid="{0C4E85C8-1452-46E5-BAA1-9F134272222A}"/>
-    <hyperlink ref="K131" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="K130" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="K129" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="K128" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="K127" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="K119" r:id="rId126" xr:uid="{B6FD0D1A-F931-482F-BA2B-9716DE045C80}"/>
-    <hyperlink ref="K120" r:id="rId127" xr:uid="{A861573B-3839-4318-BBAC-62B6CBA15FBD}"/>
-    <hyperlink ref="K121" r:id="rId128" xr:uid="{20DF76DA-E992-4E1D-A16E-22BE28C58483}"/>
-    <hyperlink ref="K122" r:id="rId129" xr:uid="{B1F4C251-A9D6-47B9-9136-6591399F5FD8}"/>
-    <hyperlink ref="K123" r:id="rId130" xr:uid="{D7FB2C86-EF32-4C98-B1CE-C0195DB8C4C6}"/>
-    <hyperlink ref="K124" r:id="rId131" xr:uid="{FE50DE30-8439-4013-8AF6-8076D7113E1F}"/>
-    <hyperlink ref="K125" r:id="rId132" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDA4581C-5B96-4BDE-A351-45793B6F0EE8}"/>
-    <hyperlink ref="K126" r:id="rId133" xr:uid="{51ED3C40-5509-488A-841B-4E657C71C1FA}"/>
-    <hyperlink ref="K132" r:id="rId134" xr:uid="{F66E5A2C-A530-4199-AD87-0563CA44FE62}"/>
-    <hyperlink ref="K133" r:id="rId135" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D2E9D5D-E79A-4ADE-8B6A-4BF55D9DEAA1}"/>
-    <hyperlink ref="M133" r:id="rId136" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{34AE602C-A94D-4947-A1E5-B9CB698DBCE9}"/>
-    <hyperlink ref="M134" r:id="rId137" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7F17DDD6-358D-4949-BA30-757C7347BD64}"/>
-    <hyperlink ref="K134" r:id="rId138" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D595607E-E74C-423D-9949-0D9455718911}"/>
-    <hyperlink ref="K136" r:id="rId139" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46C65D64-593C-435B-985E-1487C0A3B6FF}"/>
-    <hyperlink ref="K137" r:id="rId140" xr:uid="{ABE79D9A-A8E7-4085-8D94-395C34C6D224}"/>
-    <hyperlink ref="K135" r:id="rId141" xr:uid="{29FC3D7D-FB63-4F1F-9086-C70F1D6EA865}"/>
-    <hyperlink ref="F121" r:id="rId142" xr:uid="{2D04002B-8C33-4E33-A9BC-035BE367ACFB}"/>
-    <hyperlink ref="F122:F124" r:id="rId143" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Loggetta_Sansovino_a_Venezia.jpg/1280px-Loggetta_Sansovino_a_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{83BABDFD-B232-49ED-9178-8A0C58DB9E5B}"/>
-    <hyperlink ref="K92" r:id="rId144" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg/1280px-San_Jer%C3%B3nimo_penitente_at_Seville_Museum_of_Fine_Arts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B16DCA1D-61FA-47E3-AEC7-CAF732E10DD2}"/>
-    <hyperlink ref="F85" r:id="rId145" xr:uid="{F860FC30-4D00-4CD5-A8BB-B4414CC5D08F}"/>
-    <hyperlink ref="M51" r:id="rId146" xr:uid="{15D2D5F0-5EFB-40A5-BBAA-91DD811E84CC}"/>
-    <hyperlink ref="M27" r:id="rId147" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56BAEEFF-2EBF-4B02-97DC-C24781018097}"/>
-    <hyperlink ref="K31" r:id="rId148" xr:uid="{2CFFED1D-5528-4009-9B87-0FD8518C9CC4}"/>
-    <hyperlink ref="K82" r:id="rId149" xr:uid="{F7CE1142-E22B-4EC9-BFC7-4D2802C57705}"/>
-    <hyperlink ref="K81" r:id="rId150" xr:uid="{25746EEE-5BA1-48E1-BB21-0A52A9841D1C}"/>
-    <hyperlink ref="K80" r:id="rId151" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg/960px-M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EE70FD57-D070-4E8D-B5CD-AC117B37AF31}"/>
-    <hyperlink ref="H80" r:id="rId152" xr:uid="{A0C5872B-5FF8-49A5-9978-E73764344B28}"/>
-    <hyperlink ref="K79" r:id="rId153" xr:uid="{35E4135B-8BF0-442D-B156-290FBACB38C6}"/>
-    <hyperlink ref="K78" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="K72" r:id="rId155" xr:uid="{9D0C953D-C1FF-4622-B7D4-DC05686BE242}"/>
-    <hyperlink ref="K75" r:id="rId156" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg/960px-Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BFFAA60E-0E9F-4396-BBB5-5E669CEF926F}"/>
-    <hyperlink ref="K76" r:id="rId157" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg/1280px-N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{162AD1A5-1953-49BA-B027-879183D534CB}"/>
-    <hyperlink ref="K77" r:id="rId158" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg/1280px-N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4ED9E081-E1F6-468D-9522-5C82DB135714}"/>
-    <hyperlink ref="F76" r:id="rId159" xr:uid="{94951BEB-AA44-4E7C-BDE5-A40411294AB4}"/>
-    <hyperlink ref="F77" r:id="rId160" xr:uid="{160ACA90-23AD-4430-B2DE-410F26BADA28}"/>
-    <hyperlink ref="K73" r:id="rId161" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{483C2C74-4B1F-45DD-8E56-CAF03C380447}"/>
-    <hyperlink ref="K74" r:id="rId162" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{97405316-B643-499E-8CE1-D0518D573E81}"/>
+    <hyperlink ref="K136" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="K135" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="K134" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="K133" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="K119" r:id="rId125" xr:uid="{B6FD0D1A-F931-482F-BA2B-9716DE045C80}"/>
+    <hyperlink ref="K120" r:id="rId126" xr:uid="{A861573B-3839-4318-BBAC-62B6CBA15FBD}"/>
+    <hyperlink ref="K121" r:id="rId127" xr:uid="{20DF76DA-E992-4E1D-A16E-22BE28C58483}"/>
+    <hyperlink ref="K122" r:id="rId128" xr:uid="{B1F4C251-A9D6-47B9-9136-6591399F5FD8}"/>
+    <hyperlink ref="K123" r:id="rId129" xr:uid="{D7FB2C86-EF32-4C98-B1CE-C0195DB8C4C6}"/>
+    <hyperlink ref="K124" r:id="rId130" xr:uid="{FE50DE30-8439-4013-8AF6-8076D7113E1F}"/>
+    <hyperlink ref="K125" r:id="rId131" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDA4581C-5B96-4BDE-A351-45793B6F0EE8}"/>
+    <hyperlink ref="K126" r:id="rId132" xr:uid="{51ED3C40-5509-488A-841B-4E657C71C1FA}"/>
+    <hyperlink ref="K137" r:id="rId133" xr:uid="{F66E5A2C-A530-4199-AD87-0563CA44FE62}"/>
+    <hyperlink ref="K138" r:id="rId134" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/68/Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Rocco_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5D2E9D5D-E79A-4ADE-8B6A-4BF55D9DEAA1}"/>
+    <hyperlink ref="M138" r:id="rId135" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{34AE602C-A94D-4947-A1E5-B9CB698DBCE9}"/>
+    <hyperlink ref="M139" r:id="rId136" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5a/Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg/960px-Altare_della_cappella_Montefeltro_di_Francesco_Smeraldi%2C_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7F17DDD6-358D-4949-BA30-757C7347BD64}"/>
+    <hyperlink ref="K139" r:id="rId137" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5b/Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg/960px-Cappella_Montefeltro_San_Sebastiano_Statue_d%27Alessandro_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D595607E-E74C-423D-9949-0D9455718911}"/>
+    <hyperlink ref="K141" r:id="rId138" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_altare_of_Verde_Scaligera%2C_with_Jerome_%2C_by_Vittoria.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{46C65D64-593C-435B-985E-1487C0A3B6FF}"/>
+    <hyperlink ref="K142" r:id="rId139" xr:uid="{ABE79D9A-A8E7-4085-8D94-395C34C6D224}"/>
+    <hyperlink ref="K140" r:id="rId140" xr:uid="{29FC3D7D-FB63-4F1F-9086-C70F1D6EA865}"/>
+    <hyperlink ref="F121" r:id="rId141" xr:uid="{2D04002B-8C33-4E33-A9BC-035BE367ACFB}"/>
+    <hyperlink ref="F122:F124" r:id="rId142" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Loggetta_Sansovino_a_Venezia.jpg/1280px-Loggetta_Sansovino_a_Venezia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{83BABDFD-B232-49ED-9178-8A0C58DB9E5B}"/>
+    <hyperlink ref="F85" r:id="rId143" xr:uid="{F860FC30-4D00-4CD5-A8BB-B4414CC5D08F}"/>
+    <hyperlink ref="M51" r:id="rId144" xr:uid="{15D2D5F0-5EFB-40A5-BBAA-91DD811E84CC}"/>
+    <hyperlink ref="M27" r:id="rId145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg/1280px-Retablo_Mayor_de_San_Benito_el_Real%2C_Valladolid._Primer_cuerpo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56BAEEFF-2EBF-4B02-97DC-C24781018097}"/>
+    <hyperlink ref="K31" r:id="rId146" xr:uid="{2CFFED1D-5528-4009-9B87-0FD8518C9CC4}"/>
+    <hyperlink ref="K82" r:id="rId147" xr:uid="{F7CE1142-E22B-4EC9-BFC7-4D2802C57705}"/>
+    <hyperlink ref="K81" r:id="rId148" xr:uid="{25746EEE-5BA1-48E1-BB21-0A52A9841D1C}"/>
+    <hyperlink ref="K80" r:id="rId149" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg/960px-M%C3%BCnchen_Neuhauser_Stra%C3%9Fe_6_Jesuitenkirche_St._Michael_BW_2017-03-13_17-17-25.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EE70FD57-D070-4E8D-B5CD-AC117B37AF31}"/>
+    <hyperlink ref="H80" r:id="rId150" xr:uid="{A0C5872B-5FF8-49A5-9978-E73764344B28}"/>
+    <hyperlink ref="K79" r:id="rId151" xr:uid="{35E4135B-8BF0-442D-B156-290FBACB38C6}"/>
+    <hyperlink ref="K78" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="K72" r:id="rId153" xr:uid="{9D0C953D-C1FF-4622-B7D4-DC05686BE242}"/>
+    <hyperlink ref="K75" r:id="rId154" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg/960px-Apollo_Fountain_by_Peter_Vischer_the_younger_and_Peter_Floetner%2C_1532_AD%2C_cast_bronze%2C_view_1_-_Stadtmuseum_Fembohaus_-_Nuremberg%2C_Germany_-_DSC02206.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BFFAA60E-0E9F-4396-BBB5-5E669CEF926F}"/>
+    <hyperlink ref="K76" r:id="rId155" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg/1280px-N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{162AD1A5-1953-49BA-B027-879183D534CB}"/>
+    <hyperlink ref="K77" r:id="rId156" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg/1280px-N%C3%BCrnberg-Sebald-Tuchergarten-Hirsvogelsaal_DSC1876.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4ED9E081-E1F6-468D-9522-5C82DB135714}"/>
+    <hyperlink ref="F76" r:id="rId157" xr:uid="{94951BEB-AA44-4E7C-BDE5-A40411294AB4}"/>
+    <hyperlink ref="F77" r:id="rId158" xr:uid="{160ACA90-23AD-4430-B2DE-410F26BADA28}"/>
+    <hyperlink ref="K73" r:id="rId159" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_superbia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{483C2C74-4B1F-45DD-8E56-CAF03C380447}"/>
+    <hyperlink ref="K74" r:id="rId160" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG/960px-Peter_fl%C3%B6tner%2C_i_sette_peccati_capitali%2C_invidia%2C_1540_ca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=de" xr:uid="{97405316-B643-499E-8CE1-D0518D573E81}"/>
+    <hyperlink ref="K127" r:id="rId161" xr:uid="{4C89A484-8605-460F-BB4C-EC8A5FBD3A57}"/>
+    <hyperlink ref="K128" r:id="rId162" xr:uid="{EFAB8B48-719C-4538-8B49-4EE24EBCEF54}"/>
+    <hyperlink ref="K129" r:id="rId163" xr:uid="{DFE44842-AD5E-450A-9325-8F100A3ABA8C}"/>
+    <hyperlink ref="K130" r:id="rId164" xr:uid="{785DD1A2-EB78-43FB-92F4-F2E9F4BB2524}"/>
+    <hyperlink ref="K131" r:id="rId165" xr:uid="{8BC0E08D-C5EE-4814-A887-8CDA19564F7A}"/>
+    <hyperlink ref="K132" r:id="rId166" xr:uid="{0CFF0BA3-D7D9-4508-A3E5-440082F7F641}"/>
+    <hyperlink ref="K92" r:id="rId167" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/San_Jer%C3%B3nimo_penitente%2C_Jer%C3%B3nimo_Hern%C3%A1ndez.jpg/1280px-San_Jer%C3%B3nimo_penitente%2C_Jer%C3%B3nimo_Hern%C3%A1ndez.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F856A346-6BC5-42EE-9297-953DBD0949BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405667C5-0895-4236-BE0E-CE6053F0485D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EA2449-7AA5-4155-86B9-D29D9E2A30CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="420" windowWidth="28800" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2778,72 +2778,7 @@
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB6D7A8"/>
-          <bgColor rgb="FFB6D7A8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9FC5E8"/>
-          <bgColor rgb="FF9FC5E8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB4A7D6"/>
-          <bgColor rgb="FFB4A7D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF6B6B"/>
-          <bgColor rgb="FFFF6B6B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4B183"/>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -9506,32 +9441,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2:Z146">
-    <cfRule type="expression" dxfId="7" priority="1">
-      <formula>IFERROR(--$V2,0)=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
-      <formula>IFERROR(--$V2,0)=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>IFERROR(--$V2,0)=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>IFERROR(--$V2,0)=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="5">
-      <formula>IFERROR(--$V2,0)=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
-      <formula>IFERROR(--$V2,0)=6</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="7">
-      <formula>IFERROR(--$V2,0)=7</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>IFERROR(--$V2,0)=8</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K3" r:id="rId2" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg/960px-Church_of_the_Eremitani_%28Padua%29_-_Interior_-_Mausoleo_di_Marco_Mantova_Benavides_by_Bartolomeo_Ammannati.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4908D6CB-287E-42A7-9638-0E94E65FF28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CD7D35-933B-48FA-8900-CEE0D66DF726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="962">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2897,6 +2910,15 @@
   </si>
   <si>
     <t>Bas-reliefs du tombeau de François Ier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre </t>
+  </si>
+  <si>
+    <t>de FRANCQUEVILLE</t>
+  </si>
+  <si>
+    <t>Elément d'architecture</t>
   </si>
 </sst>
 </file>
@@ -4545,7 +4567,7 @@
         <v>165</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>166</v>
@@ -5129,7 +5151,7 @@
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="R36" s="1" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>41</v>
@@ -6033,16 +6055,17 @@
       </c>
     </row>
     <row r="55" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D55" t="s">
+      <c r="C55" s="1"/>
+      <c r="D55" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>329</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -6082,16 +6105,17 @@
       </c>
     </row>
     <row r="56" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D56" t="s">
+      <c r="C56" s="1"/>
+      <c r="D56" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -6134,16 +6158,17 @@
       </c>
     </row>
     <row r="57" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D57" t="s">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -6489,6 +6514,12 @@
       </c>
     </row>
     <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>960</v>
+      </c>
       <c r="C64" s="1" t="s">
         <v>375</v>
       </c>
@@ -6532,6 +6563,12 @@
       </c>
     </row>
     <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>960</v>
+      </c>
       <c r="C65" s="1" t="s">
         <v>375</v>
       </c>
@@ -6581,6 +6618,12 @@
       </c>
     </row>
     <row r="66" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>960</v>
+      </c>
       <c r="C66" s="1" t="s">
         <v>375</v>
       </c>
@@ -6624,6 +6667,12 @@
       </c>
     </row>
     <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>960</v>
+      </c>
       <c r="C67" s="1" t="s">
         <v>375</v>
       </c>
@@ -8359,7 +8408,7 @@
       </c>
       <c r="N102" s="13"/>
       <c r="R102" s="1" t="s">
-        <v>109</v>
+        <v>961</v>
       </c>
       <c r="S102" s="1" t="s">
         <v>607</v>
@@ -8466,7 +8515,7 @@
       </c>
       <c r="N104" s="13"/>
       <c r="R104" s="1" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="S104" s="1" t="s">
         <v>41</v>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4908D6CB-287E-42A7-9638-0E94E65FF28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A06CE7-D62C-46F8-AE60-0FD0C619639F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="961">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -439,9 +452,6 @@
     <t>1559</t>
   </si>
   <si>
-    <t>Basilique de la Santissima Annunziata</t>
-  </si>
-  <si>
     <t>Pietà avec saint Jean, la Vierge et Nicodème</t>
   </si>
   <si>
@@ -1081,9 +1091,6 @@
     <t>Pérouse</t>
   </si>
   <si>
-    <t>Cathédrale Saint-Laurent</t>
-  </si>
-  <si>
     <t>Statue du Pape Jules III</t>
   </si>
   <si>
@@ -2897,6 +2904,18 @@
   </si>
   <si>
     <t>Bas-reliefs du tombeau de François Ier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre </t>
+  </si>
+  <si>
+    <t>de FRANCQUEVILLE</t>
+  </si>
+  <si>
+    <t>Elément d'architecture</t>
+  </si>
+  <si>
+    <t>Basilique della Santissima Annunziata</t>
   </si>
 </sst>
 </file>
@@ -3544,7 +3563,7 @@
         <v>30</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>32</v>
@@ -3592,7 +3611,7 @@
         <v>39</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>41</v>
@@ -4381,16 +4400,16 @@
         <v>26</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>48</v>
@@ -4399,7 +4418,7 @@
         <v>41</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>33</v>
@@ -4420,22 +4439,22 @@
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>48</v>
@@ -4444,7 +4463,7 @@
         <v>41</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>33</v>
@@ -4458,47 +4477,47 @@
     </row>
     <row r="22" spans="1:25" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>151</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="L22" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="L22" s="10" t="s">
+      <c r="M22" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="M22" s="17" t="s">
+      <c r="N22" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S22" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="S22" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="T22" s="11">
         <v>150</v>
@@ -4509,52 +4528,52 @@
         <v>2</v>
       </c>
       <c r="X22" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y22" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="Y22" s="9" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="J23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="N23" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="N23" s="6" t="s">
+      <c r="R23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S23" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="R23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="S23" s="1" t="s">
+      <c r="T23" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="U23" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="U23" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="V23" s="2">
         <v>32</v>
@@ -4563,211 +4582,211 @@
         <v>2</v>
       </c>
       <c r="X23" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y23" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="R24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="W24" s="4">
         <v>2</v>
       </c>
       <c r="X24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y24" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="R25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="W25" s="4">
         <v>2</v>
       </c>
       <c r="X25" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y25" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="J26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T26" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="U26" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="W26" s="4">
         <v>2</v>
       </c>
       <c r="X26" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y26" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>192</v>
-      </c>
       <c r="R27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S27" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="W27" s="4">
         <v>2</v>
       </c>
       <c r="X27" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y27" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="Y27" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>48</v>
@@ -4776,73 +4795,73 @@
         <v>41</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W28" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y28" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="S29" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="T29" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X29" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y29" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y29" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>26</v>
@@ -4851,13 +4870,13 @@
         <v>44</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>48</v>
@@ -4866,73 +4885,73 @@
         <v>99</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="W30" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X30" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y30" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y30" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>57</v>
       </c>
       <c r="S31" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T31" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="W31" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X31" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y31" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>26</v>
@@ -4941,13 +4960,13 @@
         <v>27</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>31</v>
@@ -4956,28 +4975,28 @@
         <v>99</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y32" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>26</v>
@@ -4986,13 +5005,13 @@
         <v>44</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>48</v>
@@ -5001,28 +5020,28 @@
         <v>41</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X33" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y33" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>26</v>
@@ -5037,7 +5056,7 @@
         <v>126</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>48</v>
@@ -5046,43 +5065,43 @@
         <v>41</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W34" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X34" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y34" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y34" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>48</v>
@@ -5091,45 +5110,45 @@
         <v>41</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y35" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="J36" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="L36" s="15" t="s">
         <v>242</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>958</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>243</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="R36" s="1" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>41</v>
@@ -5144,34 +5163,34 @@
         <v>3</v>
       </c>
       <c r="X36" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y36" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="Y36" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="J37" s="1" t="s">
+      <c r="L37" s="15" t="s">
         <v>245</v>
-      </c>
-      <c r="L37" s="15" t="s">
-        <v>246</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -5188,34 +5207,34 @@
         <v>3</v>
       </c>
       <c r="X37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y37" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="L38" s="15" t="s">
         <v>250</v>
-      </c>
-      <c r="L38" s="15" t="s">
-        <v>251</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -5223,7 +5242,7 @@
         <v>40</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T38" s="2">
         <v>145</v>
@@ -5238,34 +5257,34 @@
         <v>3</v>
       </c>
       <c r="X38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y38" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="Y38" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J39" s="1" t="s">
+      <c r="L39" s="15" t="s">
         <v>254</v>
-      </c>
-      <c r="L39" s="15" t="s">
-        <v>255</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
@@ -5288,34 +5307,34 @@
         <v>3</v>
       </c>
       <c r="X39" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y39" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="L40" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>48</v>
@@ -5336,34 +5355,34 @@
         <v>33</v>
       </c>
       <c r="X40" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y40" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="L41" s="6" t="s">
         <v>264</v>
-      </c>
-      <c r="L41" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>48</v>
@@ -5384,22 +5403,22 @@
         <v>33</v>
       </c>
       <c r="X41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y41" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y41" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>26</v>
@@ -5408,10 +5427,10 @@
         <v>44</v>
       </c>
       <c r="J42" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>109</v>
@@ -5420,43 +5439,43 @@
         <v>41</v>
       </c>
       <c r="T42" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="U42" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="U42" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X42" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y42" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y42" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F43" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="L43" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>40</v>
@@ -5474,34 +5493,34 @@
         <v>33</v>
       </c>
       <c r="X43" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y43" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y43" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J44" s="1" t="s">
+      <c r="L44" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>277</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>48</v>
@@ -5522,34 +5541,34 @@
         <v>33</v>
       </c>
       <c r="X44" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y44" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y44" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J45" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>48</v>
@@ -5558,7 +5577,7 @@
         <v>41</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U45" s="2">
         <v>49</v>
@@ -5570,38 +5589,38 @@
         <v>33</v>
       </c>
       <c r="X45" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y45" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y45" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:25" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
@@ -5615,7 +5634,7 @@
         <v>41</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="U46" s="2">
         <v>75</v>
@@ -5627,34 +5646,34 @@
         <v>33</v>
       </c>
       <c r="X46" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y46" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F47" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="L47" s="6" t="s">
         <v>288</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>289</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>40</v>
@@ -5672,34 +5691,34 @@
         <v>33</v>
       </c>
       <c r="X47" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y47" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y47" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J48" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>291</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>40</v>
@@ -5708,49 +5727,49 @@
         <v>41</v>
       </c>
       <c r="T48" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="U48" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="U48" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X48" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y48" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y48" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J49" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="L49" s="6" t="s">
+      <c r="M49" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="M49" s="7" t="s">
+      <c r="N49" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="R49" s="1" t="s">
         <v>48</v>
@@ -5771,41 +5790,41 @@
         <v>33</v>
       </c>
       <c r="X49" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="Y49" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="Y49" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="J50" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="15" t="s">
         <v>304</v>
-      </c>
-      <c r="L50" s="15" t="s">
-        <v>305</v>
       </c>
       <c r="M50" s="1"/>
       <c r="N50" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>31</v>
@@ -5820,44 +5839,44 @@
         <v>3</v>
       </c>
       <c r="X50" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y50" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="Y50" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="J51" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="K51" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="15" t="s">
         <v>311</v>
-      </c>
-      <c r="L51" s="15" t="s">
-        <v>312</v>
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R51" s="9" t="s">
         <v>48</v>
@@ -5872,37 +5891,37 @@
         <v>3</v>
       </c>
       <c r="X51" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y51" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="Y51" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="52" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J52" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="15" t="s">
         <v>316</v>
-      </c>
-      <c r="L52" s="15" t="s">
-        <v>317</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
@@ -5919,22 +5938,22 @@
         <v>3</v>
       </c>
       <c r="X52" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y52" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="Y52" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>26</v>
@@ -5943,13 +5962,13 @@
         <v>44</v>
       </c>
       <c r="J53" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="15" t="s">
         <v>320</v>
-      </c>
-      <c r="L53" s="15" t="s">
-        <v>321</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
@@ -5969,38 +5988,38 @@
         <v>3</v>
       </c>
       <c r="X53" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y53" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="Y53" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="54" spans="1:25" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="9"/>
       <c r="J54" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M54" s="17"/>
       <c r="N54" s="17"/>
@@ -6026,36 +6045,37 @@
         <v>3</v>
       </c>
       <c r="X54" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y54" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="Y54" s="9" t="s">
-        <v>323</v>
-      </c>
     </row>
     <row r="55" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B55" t="s">
-        <v>323</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="1"/>
+      <c r="D55" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="K55" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="L55" s="15" t="s">
         <v>332</v>
-      </c>
-      <c r="L55" s="15" t="s">
-        <v>333</v>
       </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
@@ -6063,7 +6083,7 @@
         <v>109</v>
       </c>
       <c r="S55" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="T55" s="2">
         <v>53</v>
@@ -6075,41 +6095,42 @@
         <v>3</v>
       </c>
       <c r="X55" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y55" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="Y55" s="1" t="s">
-        <v>323</v>
-      </c>
     </row>
     <row r="56" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B56" t="s">
-        <v>323</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="1"/>
+      <c r="D56" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E56" t="s">
-        <v>26</v>
-      </c>
-      <c r="F56" s="1" t="s">
+      <c r="J56" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="K56" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="15" t="s">
         <v>338</v>
-      </c>
-      <c r="L56" s="15" t="s">
-        <v>339</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="R56" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>41</v>
@@ -6127,36 +6148,37 @@
         <v>3</v>
       </c>
       <c r="X56" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y56" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="Y56" s="1" t="s">
-        <v>323</v>
-      </c>
     </row>
     <row r="57" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B57" t="s">
-        <v>323</v>
-      </c>
-      <c r="D57" t="s">
-        <v>341</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>44</v>
       </c>
       <c r="J57" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="L57" s="15" t="s">
         <v>343</v>
-      </c>
-      <c r="L57" s="15" t="s">
-        <v>344</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
@@ -6179,22 +6201,22 @@
         <v>3</v>
       </c>
       <c r="X57" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y57" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="Y57" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>26</v>
@@ -6203,13 +6225,13 @@
         <v>44</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="6" t="s">
         <v>349</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>350</v>
       </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
@@ -6232,37 +6254,37 @@
         <v>2</v>
       </c>
       <c r="X58" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y58" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="Y58" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="K59" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="J59" s="1" t="s">
+      <c r="L59" s="15" t="s">
         <v>354</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="L59" s="15" t="s">
-        <v>356</v>
       </c>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
@@ -6285,22 +6307,22 @@
         <v>2</v>
       </c>
       <c r="X59" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y59" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="Y59" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>26</v>
@@ -6309,13 +6331,13 @@
         <v>44</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="L60" s="15" t="s">
         <v>358</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="L60" s="15" t="s">
-        <v>360</v>
       </c>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
@@ -6335,37 +6357,37 @@
         <v>2</v>
       </c>
       <c r="X60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y60" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="Y60" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="61" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="L61" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="L61" s="15" t="s">
-        <v>365</v>
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
@@ -6388,22 +6410,22 @@
         <v>2</v>
       </c>
       <c r="X61" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y61" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="Y61" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="62" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>26</v>
@@ -6412,13 +6434,13 @@
         <v>44</v>
       </c>
       <c r="J62" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="L62" s="15" t="s">
         <v>367</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="L62" s="15" t="s">
-        <v>369</v>
       </c>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
@@ -6435,42 +6457,42 @@
         <v>2</v>
       </c>
       <c r="X62" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y62" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="Y62" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="63" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="L63" s="15" t="s">
         <v>371</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="L63" s="15" t="s">
-        <v>373</v>
       </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>99</v>
@@ -6482,33 +6504,39 @@
         <v>2</v>
       </c>
       <c r="X63" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y63" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="Y63" s="2" t="s">
-        <v>346</v>
-      </c>
     </row>
     <row r="64" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>958</v>
+      </c>
       <c r="C64" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J64" s="1" t="s">
+      <c r="L64" s="15" t="s">
         <v>377</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="L64" s="15" t="s">
-        <v>379</v>
       </c>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
@@ -6519,24 +6547,30 @@
         <v>41</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="W64" s="5">
         <v>3</v>
       </c>
       <c r="X64" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="Y64" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="Y64" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>26</v>
@@ -6545,13 +6579,13 @@
         <v>54</v>
       </c>
       <c r="J65" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="L65" s="15" t="s">
         <v>384</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="L65" s="15" t="s">
-        <v>386</v>
       </c>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
@@ -6574,33 +6608,39 @@
         <v>3</v>
       </c>
       <c r="X65" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y65" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>958</v>
+      </c>
       <c r="C66" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="J66" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="L66" s="15" t="s">
         <v>390</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="L66" s="15" t="s">
-        <v>392</v>
       </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
@@ -6617,33 +6657,39 @@
         <v>3</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y66" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>958</v>
+      </c>
       <c r="C67" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="J67" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="L67" s="15" t="s">
         <v>396</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="L67" s="15" t="s">
-        <v>398</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
@@ -6660,43 +6706,43 @@
         <v>3</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J68" s="1" t="s">
+      <c r="L68" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>404</v>
-      </c>
       <c r="R68" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T68" s="2">
         <v>190</v>
@@ -6711,133 +6757,133 @@
         <v>2</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y68" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J69" s="1" t="s">
+      <c r="L69" s="6" t="s">
         <v>406</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="L69" s="6" t="s">
-        <v>408</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="W69" s="4">
         <v>2</v>
       </c>
       <c r="X69" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y69" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="70" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="L70" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="R70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S70" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="L70" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="W70" s="4">
         <v>2</v>
       </c>
       <c r="X70" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y70" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="71" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J71" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F71" s="1" t="s">
+      <c r="K71" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="L71" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="R71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="S71" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L71" s="6" t="s">
+      <c r="T71" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="T71" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="U71" s="2" t="s">
         <v>77</v>
@@ -6846,46 +6892,46 @@
         <v>2</v>
       </c>
       <c r="X71" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y71" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="72" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="K72" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="L72" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>430</v>
-      </c>
       <c r="R72" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T72" s="2">
         <v>600</v>
@@ -6897,85 +6943,85 @@
         <v>2</v>
       </c>
       <c r="X72" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y72" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="73" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F73" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="J73" s="1" t="s">
+      <c r="L73" s="6" t="s">
         <v>432</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="L73" s="6" t="s">
-        <v>434</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="W73" s="4">
         <v>2</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Y73" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="74" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="L74" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="J74" s="1" t="s">
+      <c r="R74" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="L74" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>442</v>
-      </c>
       <c r="S74" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T74" s="2">
         <v>8000</v>
@@ -6984,37 +7030,37 @@
         <v>3</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Y74" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="75" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="J75" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="K75" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="L75" s="15" t="s">
         <v>446</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="L75" s="15" t="s">
-        <v>448</v>
       </c>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
@@ -7022,7 +7068,7 @@
         <v>48</v>
       </c>
       <c r="S75" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T75" s="2">
         <v>150</v>
@@ -7031,37 +7077,37 @@
         <v>3</v>
       </c>
       <c r="X75" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Y75" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="76" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="J76" s="1" t="s">
+      <c r="L76" s="15" t="s">
         <v>451</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="L76" s="15" t="s">
-        <v>453</v>
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
@@ -7069,7 +7115,7 @@
         <v>48</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T76" s="2">
         <v>190</v>
@@ -7078,42 +7124,42 @@
         <v>3</v>
       </c>
       <c r="X76" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Y76" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B77" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D77" t="s">
+        <v>452</v>
+      </c>
+      <c r="E77" t="s">
+        <v>442</v>
+      </c>
+      <c r="F77" t="s">
+        <v>453</v>
+      </c>
+      <c r="J77" t="s">
         <v>454</v>
       </c>
-      <c r="E77" t="s">
-        <v>444</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="K77" t="s">
         <v>455</v>
       </c>
-      <c r="J77" t="s">
+      <c r="L77" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="K77" t="s">
-        <v>457</v>
-      </c>
-      <c r="L77" s="22" t="s">
-        <v>458</v>
-      </c>
       <c r="R77" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="S77" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T77" s="33">
         <v>3250</v>
@@ -7126,37 +7172,37 @@
         <v>3</v>
       </c>
       <c r="X77" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Y77" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="78" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="K78" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J78" s="1" t="s">
+      <c r="L78" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>464</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>48</v>
@@ -7165,7 +7211,7 @@
         <v>99</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U78" s="2">
         <v>92</v>
@@ -7177,49 +7223,49 @@
         <v>33</v>
       </c>
       <c r="X78" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Y78" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="79" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="K79" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="J79" s="1" t="s">
+      <c r="L79" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="M79" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="L79" s="6" t="s">
+      <c r="N79" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="M79" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="N79" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S79" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T79" s="2">
         <v>269</v>
@@ -7228,46 +7274,46 @@
         <v>33</v>
       </c>
       <c r="X79" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Y79" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="80" spans="1:25" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="L80" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="M80" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="L80" s="6" t="s">
+      <c r="N80" s="6" t="s">
         <v>477</v>
-      </c>
-      <c r="M80" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>479</v>
       </c>
       <c r="O80" s="1"/>
       <c r="P80" s="1"/>
@@ -7287,40 +7333,40 @@
         <v>33</v>
       </c>
       <c r="X80" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Y80" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="81" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F81" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L81" s="31" t="s">
         <v>483</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="L81" s="31" t="s">
-        <v>485</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>40</v>
       </c>
       <c r="S81" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T81" s="2">
         <v>600</v>
@@ -7329,45 +7375,45 @@
         <v>2</v>
       </c>
       <c r="X81" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Y81" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B82" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D82" t="s">
+        <v>484</v>
+      </c>
+      <c r="E82" t="s">
+        <v>485</v>
+      </c>
+      <c r="F82" t="s">
         <v>486</v>
       </c>
-      <c r="E82" t="s">
+      <c r="J82" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F82" t="s">
+      <c r="K82" t="s">
         <v>488</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="L82" s="22" t="s">
         <v>489</v>
       </c>
-      <c r="K82" t="s">
+      <c r="R82" t="s">
         <v>490</v>
       </c>
-      <c r="L82" s="22" t="s">
+      <c r="S82" t="s">
         <v>491</v>
       </c>
-      <c r="R82" t="s">
+      <c r="T82" s="32" t="s">
         <v>492</v>
-      </c>
-      <c r="S82" t="s">
-        <v>493</v>
-      </c>
-      <c r="T82" s="32" t="s">
-        <v>494</v>
       </c>
       <c r="U82" s="32"/>
       <c r="V82" s="32"/>
@@ -7375,37 +7421,37 @@
         <v>2</v>
       </c>
       <c r="X82" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="K83" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="J83" s="1" t="s">
+      <c r="L83" s="15" t="s">
         <v>497</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="L83" s="15" t="s">
-        <v>499</v>
       </c>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
@@ -7413,7 +7459,7 @@
         <v>109</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T83" s="2">
         <v>13</v>
@@ -7425,39 +7471,39 @@
         <v>2</v>
       </c>
       <c r="X83" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Y83" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Z83" s="16"/>
       <c r="AA83" s="16"/>
     </row>
     <row r="84" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J84" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L84" s="15" t="s">
         <v>500</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="L84" s="15" t="s">
-        <v>502</v>
       </c>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
@@ -7465,7 +7511,7 @@
         <v>109</v>
       </c>
       <c r="S84" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T84" s="2">
         <v>13</v>
@@ -7477,37 +7523,37 @@
         <v>2</v>
       </c>
       <c r="X84" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="85" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J85" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="L85" s="15" t="s">
         <v>503</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="L85" s="15" t="s">
-        <v>505</v>
       </c>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
@@ -7515,7 +7561,7 @@
         <v>109</v>
       </c>
       <c r="S85" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T85" s="2">
         <v>14</v>
@@ -7527,37 +7573,37 @@
         <v>2</v>
       </c>
       <c r="X85" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Y85" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="86" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="K86" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="L86" s="15" t="s">
         <v>508</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="L86" s="15" t="s">
-        <v>510</v>
       </c>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
@@ -7565,7 +7611,7 @@
         <v>48</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T86" s="2">
         <v>67</v>
@@ -7580,44 +7626,44 @@
         <v>2</v>
       </c>
       <c r="X86" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="87" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K87" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="L87" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>516</v>
       </c>
       <c r="N87" s="1"/>
       <c r="R87" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S87" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T87" s="2">
         <v>27</v>
@@ -7626,40 +7672,40 @@
         <v>2</v>
       </c>
       <c r="X87" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y87" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="88" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="J88" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="J88" s="1" t="s">
+      <c r="L88" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="M88" s="7" t="s">
         <v>522</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="M88" s="7" t="s">
-        <v>524</v>
       </c>
       <c r="N88" s="1"/>
       <c r="R88" s="1" t="s">
@@ -7678,37 +7724,37 @@
         <v>2</v>
       </c>
       <c r="X88" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y88" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="89" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="J89" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="M89" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="N89" s="1"/>
       <c r="R89" s="1" t="s">
@@ -7727,44 +7773,44 @@
         <v>2</v>
       </c>
       <c r="X89" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y89" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="90" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="K90" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="J90" s="1" t="s">
+      <c r="L90" s="6" t="s">
         <v>529</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>531</v>
       </c>
       <c r="N90" s="1"/>
       <c r="R90" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S90" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="T90" s="2">
         <v>105</v>
@@ -7773,53 +7819,53 @@
         <v>2</v>
       </c>
       <c r="X90" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y90" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="91" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G91" s="15" t="s">
         <v>533</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="F91" s="1" t="s">
+      <c r="H91" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="G91" s="15" t="s">
+      <c r="J91" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="K91" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="J91" s="1" t="s">
+      <c r="L91" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="M91" s="7" t="s">
         <v>538</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="M91" s="7" t="s">
-        <v>540</v>
       </c>
       <c r="N91" s="1"/>
       <c r="R91" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="S91" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="T91" s="2">
         <v>380</v>
@@ -7828,97 +7874,97 @@
         <v>2</v>
       </c>
       <c r="X91" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y91" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="92" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G92" s="15" t="s">
         <v>533</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="F92" s="1" t="s">
+      <c r="H92" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="G92" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="H92" s="1" t="s">
+      <c r="J92" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="K92" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="J92" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="K92" s="1" t="s">
+      <c r="L92" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="M92" s="7" t="s">
         <v>538</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="M92" s="7" t="s">
-        <v>540</v>
       </c>
       <c r="N92" s="1"/>
       <c r="R92" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="W92" s="4">
         <v>2</v>
       </c>
       <c r="X92" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y92" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="93" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="J93" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="J93" s="1" t="s">
+      <c r="L93" s="15" t="s">
         <v>550</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="L93" s="15" t="s">
-        <v>552</v>
       </c>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
       <c r="R93" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S93" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="T93" s="2">
         <v>1600</v>
@@ -7930,45 +7976,45 @@
         <v>3</v>
       </c>
       <c r="X93" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Y93" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="94" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="J94" s="1" t="s">
+      <c r="L94" s="15" t="s">
         <v>556</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="L94" s="15" t="s">
-        <v>558</v>
       </c>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
       <c r="R94" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="T94" s="2">
         <v>1440</v>
@@ -7980,45 +8026,45 @@
         <v>3</v>
       </c>
       <c r="X94" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Y94" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="95" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="J95" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="K95" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="J95" s="1" t="s">
+      <c r="L95" s="15" t="s">
         <v>562</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="L95" s="15" t="s">
-        <v>564</v>
       </c>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="R95" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S95" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="T95" s="2">
         <v>1060</v>
@@ -8030,45 +8076,45 @@
         <v>3</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Y95" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="96" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="J96" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="F96" s="1" t="s">
+      <c r="K96" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="J96" s="1" t="s">
+      <c r="L96" s="15" t="s">
         <v>567</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="L96" s="15" t="s">
-        <v>569</v>
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="R96" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S96" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="T96" s="2">
         <v>1150</v>
@@ -8080,90 +8126,90 @@
         <v>3</v>
       </c>
       <c r="X96" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Y96" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="97" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="J97" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="F97" s="1" t="s">
+      <c r="K97" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="J97" s="1" t="s">
+      <c r="L97" s="15" t="s">
         <v>575</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="L97" s="15" t="s">
-        <v>577</v>
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="R97" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="S97" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T97" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="W97" s="4">
         <v>2</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Y97" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="98" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="H98" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="I98" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="J98" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="I98" s="15" t="s">
+      <c r="K98" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="J98" s="1" t="s">
+      <c r="L98" s="15" t="s">
         <v>585</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="L98" s="15" t="s">
-        <v>587</v>
       </c>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
@@ -8174,98 +8220,98 @@
         <v>99</v>
       </c>
       <c r="T98" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="W98" s="4">
         <v>2</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Y98" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="F99" s="1" t="s">
+      <c r="J99" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="K99" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="J99" s="1" t="s">
+      <c r="L99" s="15" t="s">
         <v>592</v>
-      </c>
-      <c r="K99" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="L99" s="15" t="s">
-        <v>594</v>
       </c>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="R99" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="S99" s="1" t="s">
         <v>99</v>
       </c>
       <c r="T99" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="W99" s="4">
         <v>2</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Y99" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="100" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="K100" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="J100" s="1" t="s">
+      <c r="L100" s="15" t="s">
         <v>598</v>
-      </c>
-      <c r="K100" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="L100" s="15" t="s">
-        <v>600</v>
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="R100" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S100" s="1" t="s">
         <v>99</v>
@@ -8277,37 +8323,37 @@
         <v>2</v>
       </c>
       <c r="X100" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Y100" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="101" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J101" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="L101" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="N101" s="12" t="s">
         <v>602</v>
-      </c>
-      <c r="L101" s="12" t="s">
-        <v>603</v>
-      </c>
-      <c r="N101" s="12" t="s">
-        <v>604</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>109</v>
@@ -8328,41 +8374,41 @@
         <v>1</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y101" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="102" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1" t="s">
         <v>124</v>
       </c>
       <c r="E102" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F102" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J102" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="L102" s="12" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N102" s="13"/>
       <c r="R102" s="1" t="s">
-        <v>109</v>
+        <v>959</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="T102" s="2">
         <v>210</v>
@@ -8377,40 +8423,40 @@
         <v>1</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y102" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="103" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="J103" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="G103" s="15" t="s">
+      <c r="L103" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="J103" s="1" t="s">
+      <c r="M103" s="7" t="s">
         <v>610</v>
-      </c>
-      <c r="L103" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="M103" s="7" t="s">
-        <v>612</v>
       </c>
       <c r="N103" s="13"/>
       <c r="R103" s="1" t="s">
@@ -8420,7 +8466,7 @@
         <v>41</v>
       </c>
       <c r="T103" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="U103" s="2">
         <v>182</v>
@@ -8432,41 +8478,41 @@
         <v>1</v>
       </c>
       <c r="X103" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y103" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="104" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J104" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="L104" s="12" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="M104" s="7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="N104" s="13"/>
       <c r="R104" s="1" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="S104" s="1" t="s">
         <v>41</v>
@@ -8484,41 +8530,41 @@
         <v>1</v>
       </c>
       <c r="X104" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y104" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="105" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="J105" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="L105" s="12" t="s">
         <v>617</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="L105" s="12" t="s">
-        <v>619</v>
       </c>
       <c r="N105" s="13"/>
       <c r="R105" s="1" t="s">
         <v>40</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="T105" s="2">
         <v>700</v>
@@ -8533,44 +8579,44 @@
         <v>1</v>
       </c>
       <c r="X105" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y105" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="106" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="J106" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="L106" s="12" t="s">
         <v>623</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="L106" s="12" t="s">
-        <v>625</v>
       </c>
       <c r="N106" s="13"/>
       <c r="R106" s="1" t="s">
         <v>109</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T106" s="2">
         <v>215</v>
@@ -8585,52 +8631,52 @@
         <v>1</v>
       </c>
       <c r="X106" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y106" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="107" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="H107" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="I107" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="J107" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="I107" s="12" t="s">
+      <c r="L107" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="J107" s="1" t="s">
+      <c r="M107" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="L107" s="12" t="s">
+      <c r="N107" s="14" t="s">
         <v>631</v>
-      </c>
-      <c r="M107" s="7" t="s">
-        <v>632</v>
-      </c>
-      <c r="N107" s="14" t="s">
-        <v>633</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>109</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T107" s="2">
         <v>205</v>
@@ -8645,44 +8691,44 @@
         <v>1</v>
       </c>
       <c r="X107" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y107" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="108" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="H108" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="J108" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="L108" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="J108" s="1" t="s">
+      <c r="M108" s="7" t="s">
         <v>637</v>
-      </c>
-      <c r="L108" s="12" t="s">
-        <v>638</v>
-      </c>
-      <c r="M108" s="7" t="s">
-        <v>639</v>
       </c>
       <c r="N108" s="13"/>
       <c r="R108" s="1" t="s">
         <v>109</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T108" s="2">
         <v>80</v>
@@ -8697,45 +8743,45 @@
         <v>1</v>
       </c>
       <c r="X108" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Y108" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="109" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F109" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J109" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="G109" s="1" t="s">
+      <c r="K109" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="J109" s="1" t="s">
+      <c r="L109" s="15" t="s">
         <v>645</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="L109" s="15" t="s">
-        <v>647</v>
       </c>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
       <c r="R109" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="S109" s="1" t="s">
         <v>99</v>
@@ -8744,22 +8790,22 @@
         <v>3</v>
       </c>
       <c r="X109" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Y109" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="110" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>26</v>
@@ -8768,13 +8814,13 @@
         <v>54</v>
       </c>
       <c r="J110" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="L110" s="15" t="s">
         <v>648</v>
-      </c>
-      <c r="K110" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="L110" s="15" t="s">
-        <v>650</v>
       </c>
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
@@ -8794,37 +8840,37 @@
         <v>3</v>
       </c>
       <c r="X110" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Y110" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="111" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E111" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="J111" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="K111" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="J111" s="1" t="s">
+      <c r="L111" s="15" t="s">
         <v>653</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="L111" s="15" t="s">
-        <v>655</v>
       </c>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
@@ -8847,37 +8893,37 @@
         <v>3</v>
       </c>
       <c r="X111" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Y111" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="112" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F112" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="K112" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="J112" s="1" t="s">
+      <c r="L112" s="15" t="s">
         <v>657</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="L112" s="15" t="s">
-        <v>659</v>
       </c>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
@@ -8891,34 +8937,34 @@
         <v>3</v>
       </c>
       <c r="X112" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Y112" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="113" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="J113" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="L113" s="15" t="s">
         <v>664</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="L113" s="15" t="s">
-        <v>666</v>
       </c>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
@@ -8929,55 +8975,55 @@
         <v>99</v>
       </c>
       <c r="T113" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="U113" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="V113" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="U113" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="V113" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="W113" s="4">
         <v>2</v>
       </c>
       <c r="X113" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Y113" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="114" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="J114" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="K114" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="J114" s="1" t="s">
+      <c r="L114" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="K114" s="1" t="s">
+      <c r="M114" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="L114" s="15" t="s">
+      <c r="N114" s="15" t="s">
         <v>675</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="N114" s="15" t="s">
-        <v>677</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>48</v>
@@ -8986,43 +9032,43 @@
         <v>99</v>
       </c>
       <c r="T114" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="W114" s="4">
         <v>2</v>
       </c>
       <c r="X114" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Y114" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="115" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="J115" s="1" t="s">
+      <c r="L115" s="15" t="s">
         <v>680</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="L115" s="15" t="s">
-        <v>682</v>
       </c>
       <c r="M115" s="1"/>
       <c r="N115" s="1"/>
@@ -9045,37 +9091,37 @@
         <v>2</v>
       </c>
       <c r="X115" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Y115" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="116" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="J116" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="L116" s="15" t="s">
         <v>683</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="L116" s="15" t="s">
-        <v>685</v>
       </c>
       <c r="M116" s="1"/>
       <c r="N116" s="1"/>
@@ -9086,7 +9132,7 @@
         <v>99</v>
       </c>
       <c r="T116" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="U116" s="2">
         <v>72</v>
@@ -9098,37 +9144,37 @@
         <v>2</v>
       </c>
       <c r="X116" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Y116" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="117" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="J117" s="1" t="s">
+      <c r="L117" s="15" t="s">
         <v>688</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="L117" s="15" t="s">
-        <v>690</v>
       </c>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
@@ -9139,43 +9185,43 @@
         <v>99</v>
       </c>
       <c r="T117" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="W117" s="4">
         <v>2</v>
       </c>
       <c r="X117" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Y117" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="118" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="K118" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="J118" s="1" t="s">
+      <c r="L118" s="15" t="s">
         <v>693</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="L118" s="15" t="s">
-        <v>695</v>
       </c>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -9186,85 +9232,85 @@
         <v>41</v>
       </c>
       <c r="T118" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="W118" s="4">
         <v>2</v>
       </c>
       <c r="X118" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="Y118" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="119" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="J119" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="L119" s="6" t="s">
         <v>699</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="L119" s="6" t="s">
-        <v>701</v>
       </c>
       <c r="R119" s="1" t="s">
         <v>40</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="W119" s="4">
         <v>2</v>
       </c>
       <c r="X119" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="Y119" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="120" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F120" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="K120" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="J120" s="1" t="s">
+      <c r="L120" s="15" t="s">
         <v>708</v>
       </c>
-      <c r="K120" s="1" t="s">
+      <c r="M120" s="1" t="s">
         <v>709</v>
-      </c>
-      <c r="L120" s="15" t="s">
-        <v>710</v>
-      </c>
-      <c r="M120" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="N120" s="1"/>
       <c r="R120" s="1" t="s">
@@ -9280,43 +9326,43 @@
         <v>3</v>
       </c>
       <c r="X120" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="Y120" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="121" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="J121" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="L121" s="15" t="s">
         <v>712</v>
       </c>
-      <c r="K121" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="L121" s="15" t="s">
-        <v>714</v>
-      </c>
       <c r="M121" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="N121" s="1"/>
       <c r="R121" s="1" t="s">
@@ -9332,40 +9378,40 @@
         <v>3</v>
       </c>
       <c r="X121" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="Y121" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="122" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H122" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="K122" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="J122" s="1" t="s">
+      <c r="L122" s="15" t="s">
         <v>717</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="L122" s="15" t="s">
-        <v>719</v>
       </c>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
@@ -9379,22 +9425,22 @@
         <v>3</v>
       </c>
       <c r="X122" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="Y122" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="123" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>111</v>
@@ -9403,21 +9449,21 @@
         <v>112</v>
       </c>
       <c r="H123" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="J123" s="1" t="s">
+      <c r="L123" s="15" t="s">
         <v>722</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="L123" s="15" t="s">
-        <v>724</v>
       </c>
       <c r="M123" s="1"/>
       <c r="N123" s="1"/>
       <c r="R123" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="S123" s="1" t="s">
         <v>99</v>
@@ -9435,43 +9481,43 @@
         <v>3</v>
       </c>
       <c r="X123" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="Y123" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="124" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="J124" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="G124" s="6" t="s">
+      <c r="L124" s="31" t="s">
         <v>729</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="L124" s="31" t="s">
-        <v>731</v>
       </c>
       <c r="R124" s="1" t="s">
         <v>40</v>
       </c>
       <c r="S124" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="T124" s="2">
         <v>200</v>
@@ -9486,37 +9532,37 @@
         <v>3</v>
       </c>
       <c r="X124" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Y124" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="J125" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="K125" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="J125" s="1" t="s">
+      <c r="L125" s="15" t="s">
         <v>735</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="L125" s="15" t="s">
-        <v>737</v>
       </c>
       <c r="M125" s="1"/>
       <c r="N125" s="1"/>
@@ -9524,7 +9570,7 @@
         <v>40</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="T125" s="2">
         <v>247</v>
@@ -9539,92 +9585,92 @@
         <v>3</v>
       </c>
       <c r="X125" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Y125" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E126" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="J126" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="K126" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="J126" s="1" t="s">
+      <c r="L126" s="15" t="s">
         <v>740</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="L126" s="15" t="s">
-        <v>742</v>
       </c>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
       <c r="R126" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="T126" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="U126" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="W126" s="5">
         <v>3</v>
       </c>
       <c r="X126" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Y126" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="J127" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="E127" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="F127" s="1" t="s">
+      <c r="K127" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="J127" s="1" t="s">
+      <c r="L127" s="15" t="s">
         <v>747</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="L127" s="15" t="s">
-        <v>749</v>
       </c>
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
       <c r="R127" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S127" s="1" t="s">
         <v>41</v>
@@ -9636,43 +9682,43 @@
         <v>3</v>
       </c>
       <c r="X127" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="Y127" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="128" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="L128" s="6" t="s">
         <v>752</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="J128" s="1" t="s">
+      <c r="M128" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="L128" s="6" t="s">
+      <c r="N128" s="6" t="s">
         <v>754</v>
       </c>
-      <c r="M128" s="7" t="s">
+      <c r="P128" s="6" t="s">
         <v>755</v>
-      </c>
-      <c r="N128" s="6" t="s">
-        <v>756</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>757</v>
       </c>
       <c r="R128" s="1" t="s">
         <v>40</v>
@@ -9693,34 +9739,34 @@
         <v>33</v>
       </c>
       <c r="X128" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y128" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="129" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="8">
         <v>1583</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="N129" s="6"/>
       <c r="P129" s="6"/>
@@ -9743,37 +9789,37 @@
         <v>1</v>
       </c>
       <c r="X129" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y129" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="130" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1" t="s">
         <v>138</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F130" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J130" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="L130" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="N130" s="6" t="s">
         <v>759</v>
-      </c>
-      <c r="L130" s="6" t="s">
-        <v>760</v>
-      </c>
-      <c r="N130" s="6" t="s">
-        <v>761</v>
       </c>
       <c r="P130" s="7"/>
       <c r="R130" s="1" t="s">
@@ -9783,7 +9829,7 @@
         <v>41</v>
       </c>
       <c r="T130" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="U130" s="2">
         <v>75</v>
@@ -9795,50 +9841,50 @@
         <v>33</v>
       </c>
       <c r="X130" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y130" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="131" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="8">
         <v>1586</v>
       </c>
       <c r="E131" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J131" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="L131" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="M131" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="L131" s="6" t="s">
+      <c r="N131" s="6" t="s">
         <v>764</v>
-      </c>
-      <c r="M131" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="N131" s="6" t="s">
-        <v>766</v>
       </c>
       <c r="P131" s="7"/>
       <c r="R131" s="1" t="s">
         <v>48</v>
       </c>
       <c r="S131" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="T131" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="U131" s="2">
         <v>120</v>
@@ -9850,80 +9896,80 @@
         <v>33</v>
       </c>
       <c r="X131" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y131" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="132" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="E132" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J132" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="L132" s="6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="P132" s="7"/>
       <c r="R132" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="S132" s="1" t="s">
         <v>41</v>
       </c>
       <c r="T132" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W132" s="3" t="s">
         <v>33</v>
       </c>
       <c r="X132" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y132" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="133" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="L133" s="6" t="s">
         <v>771</v>
       </c>
-      <c r="E133" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="J133" s="1" t="s">
+      <c r="N133" s="6" t="s">
         <v>772</v>
-      </c>
-      <c r="L133" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="N133" s="6" t="s">
-        <v>774</v>
       </c>
       <c r="P133" s="7"/>
       <c r="R133" s="1" t="s">
@@ -9945,34 +9991,34 @@
         <v>33</v>
       </c>
       <c r="X133" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y133" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="134" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E134" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="J134" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="L134" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="P134" s="7"/>
       <c r="R134" s="1" t="s">
@@ -9994,40 +10040,40 @@
         <v>33</v>
       </c>
       <c r="X134" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y134" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="135" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="8">
         <v>1570</v>
       </c>
       <c r="E135" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="J135" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="L135" s="6" t="s">
         <v>778</v>
       </c>
-      <c r="J135" s="1" t="s">
+      <c r="M135" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="L135" s="6" t="s">
+      <c r="N135" s="6" t="s">
         <v>780</v>
-      </c>
-      <c r="M135" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="N135" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="P135" s="7"/>
       <c r="R135" s="1" t="s">
@@ -10049,34 +10095,34 @@
         <v>1</v>
       </c>
       <c r="X135" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y135" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="L136" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="P136" s="7"/>
       <c r="R136" s="1" t="s">
@@ -10098,42 +10144,42 @@
         <v>33</v>
       </c>
       <c r="X136" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Y136" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="J137" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="L137" s="15" t="s">
         <v>789</v>
-      </c>
-      <c r="J137" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="L137" s="15" t="s">
-        <v>791</v>
       </c>
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
       <c r="R137" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S137" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T137" s="2">
         <v>177</v>
@@ -10148,42 +10194,42 @@
         <v>3</v>
       </c>
       <c r="X137" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="Y137" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="J138" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="L138" s="15" t="s">
         <v>793</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="L138" s="15" t="s">
-        <v>795</v>
       </c>
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
       <c r="R138" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="S138" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="T138" s="2">
         <v>180</v>
@@ -10198,42 +10244,42 @@
         <v>3</v>
       </c>
       <c r="X138" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="Y138" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="139" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="J139" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="L139" s="15" t="s">
         <v>800</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="L139" s="15" t="s">
-        <v>802</v>
       </c>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
       <c r="R139" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S139" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="T139" s="2">
         <v>170</v>
@@ -10248,42 +10294,42 @@
         <v>3</v>
       </c>
       <c r="X139" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="Y139" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="140" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F140" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="L140" s="15" t="s">
         <v>804</v>
-      </c>
-      <c r="J140" s="1" t="s">
-        <v>805</v>
-      </c>
-      <c r="L140" s="15" t="s">
-        <v>806</v>
       </c>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
       <c r="R140" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="S140" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="T140" s="2">
         <v>164</v>
@@ -10298,40 +10344,40 @@
         <v>3</v>
       </c>
       <c r="X140" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="Y140" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="141" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="23" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C141" s="23"/>
       <c r="D141" s="23" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E141" s="23" t="s">
         <v>66</v>
       </c>
       <c r="F141" s="23" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G141" s="23"/>
       <c r="H141" s="23"/>
       <c r="I141" s="23"/>
       <c r="J141" s="23" t="s">
+        <v>811</v>
+      </c>
+      <c r="K141" s="23" t="s">
+        <v>812</v>
+      </c>
+      <c r="L141" s="30" t="s">
         <v>813</v>
-      </c>
-      <c r="K141" s="23" t="s">
-        <v>814</v>
-      </c>
-      <c r="L141" s="30" t="s">
-        <v>815</v>
       </c>
       <c r="M141" s="23"/>
       <c r="N141" s="23"/>
@@ -10339,7 +10385,7 @@
       <c r="P141" s="23"/>
       <c r="Q141" s="23"/>
       <c r="R141" s="23" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="S141" s="23" t="s">
         <v>41</v>
@@ -10355,44 +10401,44 @@
         <v>33</v>
       </c>
       <c r="X141" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Y141" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="142" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="J142" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="K142" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="J142" s="1" t="s">
+      <c r="L142" s="15" t="s">
         <v>820</v>
-      </c>
-      <c r="K142" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="L142" s="15" t="s">
-        <v>822</v>
       </c>
       <c r="M142" s="1"/>
       <c r="N142" s="31" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="R142" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S142" s="1" t="s">
         <v>41</v>
@@ -10407,44 +10453,44 @@
         <v>33</v>
       </c>
       <c r="X142" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Y142" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="143" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F143" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="K143" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="J143" s="1" t="s">
+      <c r="L143" s="15" t="s">
         <v>825</v>
-      </c>
-      <c r="K143" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="L143" s="15" t="s">
-        <v>827</v>
       </c>
       <c r="M143" s="1"/>
       <c r="N143" s="31" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S143" s="1" t="s">
         <v>41</v>
@@ -10459,37 +10505,37 @@
         <v>33</v>
       </c>
       <c r="X143" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Y143" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="144" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="K144" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="E144" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="F144" s="1" t="s">
+      <c r="L144" s="15" t="s">
         <v>829</v>
-      </c>
-      <c r="J144" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="K144" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="L144" s="15" t="s">
-        <v>831</v>
       </c>
       <c r="M144" s="1"/>
       <c r="N144" s="1"/>
@@ -10512,37 +10558,37 @@
         <v>33</v>
       </c>
       <c r="X144" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Y144" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="145" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="L145" s="15" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="M145" s="1"/>
       <c r="N145" s="1"/>
@@ -10565,37 +10611,37 @@
         <v>33</v>
       </c>
       <c r="X145" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Y145" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="146" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F146" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="K146" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="J146" s="1" t="s">
+      <c r="L146" s="15" t="s">
         <v>836</v>
-      </c>
-      <c r="K146" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="L146" s="15" t="s">
-        <v>838</v>
       </c>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
@@ -10618,22 +10664,22 @@
         <v>33</v>
       </c>
       <c r="X146" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Y146" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="147" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="23" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B147" s="23" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C147" s="23"/>
       <c r="D147" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E147" s="23" t="s">
         <v>26</v>
@@ -10651,7 +10697,7 @@
         <v>126</v>
       </c>
       <c r="L147" s="24" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="M147" s="25"/>
       <c r="N147" s="25"/>
@@ -10677,37 +10723,37 @@
         <v>33</v>
       </c>
       <c r="X147" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y147" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="148" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F148" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="K148" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="J148" s="1" t="s">
+      <c r="L148" s="6" t="s">
         <v>844</v>
-      </c>
-      <c r="K148" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="L148" s="6" t="s">
-        <v>846</v>
       </c>
       <c r="R148" s="1" t="s">
         <v>48</v>
@@ -10725,40 +10771,40 @@
         <v>33</v>
       </c>
       <c r="X148" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y148" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="149" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F149" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="G149" s="15" t="s">
+        <v>847</v>
+      </c>
+      <c r="J149" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="G149" s="15" t="s">
+      <c r="K149" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="J149" s="1" t="s">
+      <c r="L149" s="6" t="s">
         <v>850</v>
-      </c>
-      <c r="K149" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="L149" s="6" t="s">
-        <v>852</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>48</v>
@@ -10779,40 +10825,40 @@
         <v>33</v>
       </c>
       <c r="X149" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y149" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="150" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="J150" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="L150" s="6" t="s">
         <v>853</v>
-      </c>
-      <c r="K150" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="L150" s="6" t="s">
-        <v>855</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>48</v>
@@ -10833,40 +10879,40 @@
         <v>33</v>
       </c>
       <c r="X150" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y150" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="151" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="J151" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="L151" s="6" t="s">
         <v>856</v>
-      </c>
-      <c r="K151" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="L151" s="6" t="s">
-        <v>858</v>
       </c>
       <c r="R151" s="1" t="s">
         <v>48</v>
@@ -10887,40 +10933,40 @@
         <v>33</v>
       </c>
       <c r="X151" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y151" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="152" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="J152" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="L152" s="6" t="s">
         <v>859</v>
-      </c>
-      <c r="K152" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="L152" s="6" t="s">
-        <v>861</v>
       </c>
       <c r="R152" s="1" t="s">
         <v>48</v>
@@ -10941,28 +10987,28 @@
         <v>33</v>
       </c>
       <c r="X152" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y152" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="153" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>113</v>
@@ -10971,7 +11017,7 @@
         <v>114</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="R153" s="1" t="s">
         <v>48</v>
@@ -10986,40 +11032,40 @@
         <v>33</v>
       </c>
       <c r="X153" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y153" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="154" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="18" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B154" s="18" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C154" s="18"/>
       <c r="D154" s="18" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E154" s="18" t="s">
         <v>81</v>
       </c>
       <c r="F154" s="18" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G154" s="18"/>
       <c r="H154" s="18"/>
       <c r="I154" s="18"/>
       <c r="J154" s="18" t="s">
+        <v>863</v>
+      </c>
+      <c r="K154" s="18" t="s">
+        <v>864</v>
+      </c>
+      <c r="L154" s="19" t="s">
         <v>865</v>
-      </c>
-      <c r="K154" s="18" t="s">
-        <v>866</v>
-      </c>
-      <c r="L154" s="19" t="s">
-        <v>867</v>
       </c>
       <c r="M154" s="20"/>
       <c r="N154" s="20"/>
@@ -11041,34 +11087,34 @@
         <v>33</v>
       </c>
       <c r="X154" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Y154" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="155" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="E155" s="1" t="s">
+      <c r="J155" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="L155" s="15" t="s">
         <v>871</v>
-      </c>
-      <c r="J155" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="L155" s="15" t="s">
-        <v>873</v>
       </c>
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
@@ -11076,7 +11122,7 @@
         <v>40</v>
       </c>
       <c r="S155" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="T155" s="2">
         <v>170</v>
@@ -11091,37 +11137,37 @@
         <v>2</v>
       </c>
       <c r="X155" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y155" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="156" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="J156" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="K156" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="E156" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="J156" s="1" t="s">
+      <c r="L156" s="15" t="s">
         <v>876</v>
-      </c>
-      <c r="K156" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="L156" s="15" t="s">
-        <v>878</v>
       </c>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
@@ -11129,7 +11175,7 @@
         <v>40</v>
       </c>
       <c r="S156" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="T156" s="2">
         <v>155</v>
@@ -11144,37 +11190,37 @@
         <v>2</v>
       </c>
       <c r="X156" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y156" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="157" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C157" s="1"/>
       <c r="D157" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="J157" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="E157" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="F157" s="1" t="s">
+      <c r="K157" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="J157" s="1" t="s">
+      <c r="L157" s="15" t="s">
         <v>882</v>
-      </c>
-      <c r="K157" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="L157" s="15" t="s">
-        <v>884</v>
       </c>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -11182,7 +11228,7 @@
         <v>48</v>
       </c>
       <c r="S157" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="T157" s="2">
         <v>61</v>
@@ -11197,22 +11243,22 @@
         <v>2</v>
       </c>
       <c r="X157" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y157" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="158" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>111</v>
@@ -11221,13 +11267,13 @@
         <v>112</v>
       </c>
       <c r="J158" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="L158" s="15" t="s">
         <v>887</v>
-      </c>
-      <c r="K158" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="L158" s="15" t="s">
-        <v>889</v>
       </c>
       <c r="M158" s="1"/>
       <c r="N158" s="1"/>
@@ -11235,7 +11281,7 @@
         <v>48</v>
       </c>
       <c r="S158" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="T158" s="2">
         <v>62</v>
@@ -11250,37 +11296,37 @@
         <v>2</v>
       </c>
       <c r="X158" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y158" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="159" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C159" s="1"/>
       <c r="D159" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="F159" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="E159" s="1" t="s">
+      <c r="J159" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F159" s="1" t="s">
+      <c r="K159" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="J159" s="1" t="s">
+      <c r="L159" s="15" t="s">
         <v>894</v>
-      </c>
-      <c r="K159" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="L159" s="15" t="s">
-        <v>896</v>
       </c>
       <c r="M159" s="1"/>
       <c r="N159" s="1"/>
@@ -11288,7 +11334,7 @@
         <v>48</v>
       </c>
       <c r="S159" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="T159" s="11">
         <v>224</v>
@@ -11303,37 +11349,37 @@
         <v>2</v>
       </c>
       <c r="X159" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y159" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="160" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>893</v>
-      </c>
       <c r="J160" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="L160" s="15" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
@@ -11341,7 +11387,7 @@
         <v>48</v>
       </c>
       <c r="S160" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="T160" s="2">
         <v>140</v>
@@ -11350,37 +11396,37 @@
         <v>2</v>
       </c>
       <c r="X160" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="Y160" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="161" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="E161" s="1" t="s">
+      <c r="J161" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="F161" s="1" t="s">
+      <c r="K161" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="J161" s="1" t="s">
+      <c r="L161" s="15" t="s">
         <v>904</v>
-      </c>
-      <c r="K161" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="L161" s="15" t="s">
-        <v>906</v>
       </c>
       <c r="M161" s="1"/>
       <c r="N161" s="1"/>
@@ -11397,37 +11443,37 @@
         <v>3</v>
       </c>
       <c r="X161" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="Y161" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="162" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C162" s="1"/>
       <c r="D162" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F162" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="K162" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="J162" s="1" t="s">
+      <c r="L162" s="15" t="s">
         <v>909</v>
-      </c>
-      <c r="K162" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="L162" s="15" t="s">
-        <v>911</v>
       </c>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
@@ -11435,7 +11481,7 @@
         <v>57</v>
       </c>
       <c r="S162" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="T162" s="2">
         <v>250</v>
@@ -11444,22 +11490,22 @@
         <v>3</v>
       </c>
       <c r="X162" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="Y162" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="163" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C163" s="1"/>
       <c r="D163" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>26</v>
@@ -11468,13 +11514,13 @@
         <v>44</v>
       </c>
       <c r="J163" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="L163" s="15" t="s">
         <v>914</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="L163" s="15" t="s">
-        <v>916</v>
       </c>
       <c r="M163" s="1"/>
       <c r="N163" s="1"/>
@@ -11482,7 +11528,7 @@
         <v>48</v>
       </c>
       <c r="S163" s="1" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="T163" s="2">
         <v>198</v>
@@ -11491,22 +11537,22 @@
         <v>3</v>
       </c>
       <c r="X163" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="Y163" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="164" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C164" s="1"/>
       <c r="D164" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>26</v>
@@ -11515,18 +11561,18 @@
         <v>44</v>
       </c>
       <c r="J164" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="L164" s="15" t="s">
         <v>918</v>
-      </c>
-      <c r="K164" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="L164" s="15" t="s">
-        <v>920</v>
       </c>
       <c r="M164" s="1"/>
       <c r="N164" s="1"/>
       <c r="R164" s="1" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="S164" s="1" t="s">
         <v>76</v>
@@ -11538,34 +11584,34 @@
         <v>3</v>
       </c>
       <c r="X164" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="Y164" s="1" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="165" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F165" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="L165" s="6" t="s">
         <v>925</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="L165" s="6" t="s">
-        <v>927</v>
       </c>
       <c r="R165" s="1" t="s">
         <v>40</v>
@@ -11577,40 +11623,40 @@
         <v>2</v>
       </c>
       <c r="X165" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="Y165" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="166" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C166" s="1"/>
       <c r="D166" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F166" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="K166" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="J166" s="1" t="s">
+      <c r="L166" s="6" t="s">
         <v>930</v>
       </c>
-      <c r="K166" s="1" t="s">
+      <c r="N166" s="6" t="s">
         <v>931</v>
-      </c>
-      <c r="L166" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="N166" s="6" t="s">
-        <v>933</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>48</v>
@@ -11619,46 +11665,46 @@
         <v>41</v>
       </c>
       <c r="T166" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="W166" s="4">
         <v>2</v>
       </c>
       <c r="X166" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="Y166" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="167" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="L167" s="6" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N167" s="6" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>48</v>
@@ -11667,43 +11713,43 @@
         <v>41</v>
       </c>
       <c r="T167" s="2" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="W167" s="4">
         <v>2</v>
       </c>
       <c r="X167" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="Y167" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="168" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="F168" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="E168" s="1" t="s">
+      <c r="J168" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="K168" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="L168" s="6" t="s">
         <v>938</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="K168" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="L168" s="6" t="s">
-        <v>940</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>48</v>
@@ -11712,43 +11758,43 @@
         <v>41</v>
       </c>
       <c r="T168" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="W168" s="4">
         <v>2</v>
       </c>
       <c r="X168" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="Y168" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="169" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F169" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="K169" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="J169" s="1" t="s">
+      <c r="L169" s="6" t="s">
         <v>943</v>
-      </c>
-      <c r="K169" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="L169" s="6" t="s">
-        <v>945</v>
       </c>
       <c r="R169" s="1" t="s">
         <v>48</v>
@@ -11757,7 +11803,7 @@
         <v>41</v>
       </c>
       <c r="T169" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="U169" s="2">
         <v>60</v>
@@ -11769,37 +11815,37 @@
         <v>2</v>
       </c>
       <c r="X169" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="Y169" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="170" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>81</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J170" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="K170" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="L170" s="6" t="s">
         <v>948</v>
-      </c>
-      <c r="K170" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="L170" s="6" t="s">
-        <v>950</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>48</v>
@@ -11820,10 +11866,10 @@
         <v>2</v>
       </c>
       <c r="X170" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="Y170" s="1" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -5925,7 +5925,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Segovie</t>
+          <t>Ségovie</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8318F41-A130-432E-BED9-D19AB8AE7991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E641B639-2604-43D2-AAB0-0EDFACF23F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="1000">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1406,9 +1406,6 @@
   </si>
   <si>
     <t>Bois polychromé et doré</t>
-  </si>
-  <si>
-    <t>1100</t>
   </si>
   <si>
     <t>900</t>
@@ -7172,11 +7169,11 @@
       <c r="S79" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="T79" s="4" t="s">
+      <c r="T79" s="4">
+        <v>1100</v>
+      </c>
+      <c r="U79" s="4" t="s">
         <v>462</v>
-      </c>
-      <c r="U79" s="4" t="s">
-        <v>463</v>
       </c>
       <c r="V79" s="4">
         <v>130</v>
@@ -7194,25 +7191,25 @@
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="H80" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="J80" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J80" s="2" t="s">
+      <c r="K80" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="K80" s="2" t="s">
+      <c r="L80" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>166</v>
@@ -7248,16 +7245,16 @@
         <v>159</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J81" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="K81" s="2" t="s">
+      <c r="L81" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="R81" s="2" t="s">
         <v>77</v>
@@ -7266,7 +7263,7 @@
         <v>172</v>
       </c>
       <c r="T81" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="U81" s="4">
         <v>80</v>
@@ -7280,26 +7277,26 @@
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>177</v>
       </c>
       <c r="J82" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="L82" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>481</v>
       </c>
       <c r="R82" s="2" t="s">
         <v>57</v>
@@ -7308,13 +7305,13 @@
         <v>243</v>
       </c>
       <c r="T82" s="4">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="U82" s="4">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="V82" s="4">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="W82" s="4">
         <v>3</v>
@@ -7322,29 +7319,29 @@
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="F83" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="J83" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="J83" s="2" t="s">
+      <c r="K83" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="L83" s="13" t="s">
         <v>486</v>
-      </c>
-      <c r="L83" s="13" t="s">
-        <v>487</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -7369,29 +7366,29 @@
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F84" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="J84" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="J84" s="2" t="s">
+      <c r="K84" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="K84" s="2" t="s">
+      <c r="L84" s="13" t="s">
         <v>490</v>
-      </c>
-      <c r="L84" s="13" t="s">
-        <v>491</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -7416,28 +7413,28 @@
     </row>
     <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>477</v>
-      </c>
       <c r="D85" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F85" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="F85" s="5" t="s">
+      <c r="J85" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="J85" s="5" t="s">
+      <c r="K85" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="K85" s="5" t="s">
+      <c r="L85" s="15" t="s">
         <v>495</v>
-      </c>
-      <c r="L85" s="15" t="s">
-        <v>496</v>
       </c>
       <c r="R85" s="5" t="s">
         <v>57</v>
@@ -7460,14 +7457,14 @@
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>254</v>
@@ -7476,13 +7473,13 @@
         <v>255</v>
       </c>
       <c r="J86" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="K86" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="L86" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="R86" s="8" t="s">
         <v>47</v>
@@ -7505,35 +7502,35 @@
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="J87" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="K87" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="L87" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="L87" s="3" t="s">
+      <c r="M87" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="M87" s="6" t="s">
+      <c r="N87" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="R87" s="8" t="s">
         <v>47</v>
@@ -7556,35 +7553,35 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="J88" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="J88" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="L88" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="M88" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="M88" s="6" t="s">
+      <c r="N88" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="R88" s="8" t="s">
         <v>47</v>
@@ -7607,30 +7604,30 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="B89" s="18" t="s">
         <v>517</v>
-      </c>
-      <c r="B89" s="18" t="s">
-        <v>518</v>
       </c>
       <c r="C89" s="18"/>
       <c r="D89" s="18" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E89" s="18" t="s">
         <v>66</v>
       </c>
       <c r="F89" s="18" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G89" s="18"/>
       <c r="H89" s="18"/>
       <c r="I89" s="18"/>
       <c r="J89" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K89" s="18"/>
       <c r="L89" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M89" s="19"/>
       <c r="N89" s="19"/>
@@ -7641,7 +7638,7 @@
         <v>71</v>
       </c>
       <c r="S89" s="18" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T89" s="10">
         <v>600</v>
@@ -7658,37 +7655,37 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="B90" s="5" t="s">
-        <v>518</v>
-      </c>
       <c r="D90" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="E90" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="F90" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="J90" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="J90" s="2" t="s">
+      <c r="K90" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="K90" s="5" t="s">
+      <c r="L90" s="15" t="s">
         <v>528</v>
-      </c>
-      <c r="L90" s="15" t="s">
-        <v>529</v>
       </c>
       <c r="R90" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S90" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="T90" s="17" t="s">
         <v>530</v>
-      </c>
-      <c r="T90" s="17" t="s">
-        <v>531</v>
       </c>
       <c r="U90" s="17">
         <v>75</v>
@@ -7702,29 +7699,29 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="J91" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="J91" s="2" t="s">
+      <c r="K91" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="K91" s="2" t="s">
+      <c r="L91" s="13" t="s">
         <v>536</v>
-      </c>
-      <c r="L91" s="13" t="s">
-        <v>537</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -7746,29 +7743,29 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="E92" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="J92" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="K92" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="K92" s="2" t="s">
+      <c r="L92" s="13" t="s">
         <v>539</v>
-      </c>
-      <c r="L92" s="13" t="s">
-        <v>540</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -7790,29 +7787,29 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="E93" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="J93" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="K93" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="K93" s="2" t="s">
+      <c r="L93" s="13" t="s">
         <v>542</v>
-      </c>
-      <c r="L93" s="13" t="s">
-        <v>543</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -7834,29 +7831,29 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="F94" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="J94" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="J94" s="2" t="s">
+      <c r="K94" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="K94" s="2" t="s">
+      <c r="L94" s="13" t="s">
         <v>548</v>
-      </c>
-      <c r="L94" s="13" t="s">
-        <v>549</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -7864,7 +7861,7 @@
         <v>77</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T94" s="4">
         <v>67</v>
@@ -7881,36 +7878,36 @@
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E95" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>187</v>
       </c>
       <c r="K95" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="L95" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>555</v>
       </c>
       <c r="N95" s="2"/>
       <c r="R95" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="T95" s="4">
         <v>27</v>
@@ -7927,32 +7924,32 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="F96" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="J96" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="K96" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="K96" s="2" t="s">
+      <c r="L96" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="6" t="s">
         <v>562</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="R96" s="2" t="s">
@@ -7973,29 +7970,29 @@
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>559</v>
-      </c>
       <c r="J97" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="L97" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="L97" s="3" t="s">
-        <v>565</v>
-      </c>
       <c r="M97" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N97" s="2"/>
       <c r="R97" s="2" t="s">
@@ -8016,36 +8013,36 @@
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="J98" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="J98" s="2" t="s">
+      <c r="K98" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="K98" s="2" t="s">
+      <c r="L98" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="N98" s="2"/>
       <c r="R98" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="T98" s="4">
         <v>105</v>
@@ -8062,45 +8059,45 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F99" s="2" t="s">
+      <c r="G99" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="G99" s="13" t="s">
+      <c r="H99" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="J99" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="J99" s="2" t="s">
+      <c r="K99" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="K99" s="2" t="s">
+      <c r="L99" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="L99" s="3" t="s">
+      <c r="M99" s="6" t="s">
         <v>578</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>579</v>
       </c>
       <c r="N99" s="2"/>
       <c r="R99" s="2" t="s">
         <v>57</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T99" s="4">
         <v>380</v>
@@ -8111,45 +8108,45 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F100" s="2" t="s">
+      <c r="G100" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="G100" s="13" t="s">
+      <c r="H100" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="H100" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="J100" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K100" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="M100" s="6" t="s">
         <v>578</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>579</v>
       </c>
       <c r="N100" s="2"/>
       <c r="R100" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="S100" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="W100" s="4">
         <v>2</v>
@@ -8157,29 +8154,29 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="J101" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="J101" s="2" t="s">
+      <c r="K101" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="K101" s="2" t="s">
+      <c r="L101" s="13" t="s">
         <v>590</v>
-      </c>
-      <c r="L101" s="13" t="s">
-        <v>591</v>
       </c>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -8187,7 +8184,7 @@
         <v>166</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T101" s="4">
         <v>1600</v>
@@ -8201,29 +8198,29 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
         <v>287</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="J102" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="J102" s="2" t="s">
+      <c r="K102" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="K102" s="2" t="s">
+      <c r="L102" s="13" t="s">
         <v>596</v>
-      </c>
-      <c r="L102" s="13" t="s">
-        <v>597</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -8231,7 +8228,7 @@
         <v>166</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T102" s="4">
         <v>1440</v>
@@ -8245,29 +8242,29 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="J103" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="J103" s="2" t="s">
+      <c r="K103" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="K103" s="2" t="s">
+      <c r="L103" s="13" t="s">
         <v>602</v>
-      </c>
-      <c r="L103" s="13" t="s">
-        <v>603</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -8275,7 +8272,7 @@
         <v>166</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T103" s="4">
         <v>1060</v>
@@ -8289,29 +8286,29 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="J104" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="J104" s="2" t="s">
+      <c r="K104" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="K104" s="2" t="s">
+      <c r="L104" s="13" t="s">
         <v>607</v>
-      </c>
-      <c r="L104" s="13" t="s">
-        <v>608</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -8319,7 +8316,7 @@
         <v>166</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="T104" s="4">
         <v>1150</v>
@@ -8333,29 +8330,29 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F105" s="2" t="s">
+      <c r="J105" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="J105" s="2" t="s">
+      <c r="K105" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="K105" s="6" t="s">
+      <c r="L105" s="13" t="s">
         <v>615</v>
-      </c>
-      <c r="L105" s="13" t="s">
-        <v>616</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
@@ -8366,7 +8363,7 @@
         <v>100</v>
       </c>
       <c r="T105" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="W105" s="4">
         <v>2</v>
@@ -8374,35 +8371,35 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="F106" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="H106" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="I106" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="I106" s="13" t="s">
+      <c r="J106" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="J106" s="2" t="s">
+      <c r="K106" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="K106" s="6" t="s">
+      <c r="L106" s="13" t="s">
         <v>624</v>
-      </c>
-      <c r="L106" s="13" t="s">
-        <v>625</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -8413,7 +8410,7 @@
         <v>100</v>
       </c>
       <c r="T106" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="U106" s="4">
         <v>200</v>
@@ -8427,32 +8424,32 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F107" s="2" t="s">
+      <c r="H107" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="J107" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="J107" s="2" t="s">
+      <c r="K107" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="K107" s="6" t="s">
+      <c r="L107" s="13" t="s">
         <v>631</v>
-      </c>
-      <c r="L107" s="13" t="s">
-        <v>632</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -8463,7 +8460,7 @@
         <v>100</v>
       </c>
       <c r="T107" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="W107" s="4">
         <v>2</v>
@@ -8471,29 +8468,29 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="J108" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="J108" s="2" t="s">
+      <c r="K108" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="K108" s="6" t="s">
+      <c r="L108" s="13" t="s">
         <v>636</v>
-      </c>
-      <c r="L108" s="13" t="s">
-        <v>637</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -8521,7 +8518,7 @@
         <v>198</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
@@ -8534,13 +8531,13 @@
         <v>255</v>
       </c>
       <c r="J109" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="L109" s="20" t="s">
         <v>639</v>
       </c>
-      <c r="L109" s="20" t="s">
+      <c r="N109" s="20" t="s">
         <v>640</v>
-      </c>
-      <c r="N109" s="20" t="s">
-        <v>641</v>
       </c>
       <c r="R109" s="2" t="s">
         <v>380</v>
@@ -8566,7 +8563,7 @@
         <v>198</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
@@ -8579,17 +8576,17 @@
         <v>255</v>
       </c>
       <c r="J110" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="L110" s="20" t="s">
         <v>642</v>
-      </c>
-      <c r="L110" s="20" t="s">
-        <v>643</v>
       </c>
       <c r="N110" s="21"/>
       <c r="R110" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="S110" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="S110" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="T110" s="4">
         <v>210</v>
@@ -8609,11 +8606,11 @@
         <v>198</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>254</v>
@@ -8622,16 +8619,16 @@
         <v>255</v>
       </c>
       <c r="G111" s="13" t="s">
+        <v>646</v>
+      </c>
+      <c r="J111" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="J111" s="2" t="s">
+      <c r="L111" s="20" t="s">
         <v>648</v>
       </c>
-      <c r="L111" s="20" t="s">
+      <c r="M111" s="6" t="s">
         <v>649</v>
-      </c>
-      <c r="M111" s="6" t="s">
-        <v>650</v>
       </c>
       <c r="N111" s="21"/>
       <c r="R111" s="2" t="s">
@@ -8641,7 +8638,7 @@
         <v>40</v>
       </c>
       <c r="T111" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="U111" s="4">
         <v>182</v>
@@ -8658,11 +8655,11 @@
         <v>198</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>254</v>
@@ -8671,13 +8668,13 @@
         <v>255</v>
       </c>
       <c r="J112" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="L112" s="20" t="s">
         <v>652</v>
       </c>
-      <c r="L112" s="20" t="s">
-        <v>653</v>
-      </c>
       <c r="M112" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="N112" s="21"/>
       <c r="R112" s="2" t="s">
@@ -8704,30 +8701,30 @@
         <v>198</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="F113" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="J113" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="J113" s="2" t="s">
+      <c r="L113" s="20" t="s">
         <v>657</v>
-      </c>
-      <c r="L113" s="20" t="s">
-        <v>658</v>
       </c>
       <c r="N113" s="21"/>
       <c r="R113" s="2" t="s">
         <v>380</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="T113" s="4">
         <v>700</v>
@@ -8747,26 +8744,26 @@
         <v>198</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>254</v>
       </c>
       <c r="F114" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="H114" s="2" t="s">
+      <c r="J114" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="J114" s="2" t="s">
+      <c r="L114" s="20" t="s">
         <v>663</v>
-      </c>
-      <c r="L114" s="20" t="s">
-        <v>664</v>
       </c>
       <c r="N114" s="21"/>
       <c r="R114" s="2" t="s">
@@ -8793,35 +8790,35 @@
         <v>198</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>254</v>
       </c>
       <c r="F115" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="I115" s="20" t="s">
         <v>667</v>
       </c>
-      <c r="I115" s="20" t="s">
+      <c r="J115" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="J115" s="2" t="s">
+      <c r="L115" s="20" t="s">
         <v>669</v>
       </c>
-      <c r="L115" s="20" t="s">
+      <c r="M115" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="M115" s="6" t="s">
+      <c r="N115" s="22" t="s">
         <v>671</v>
-      </c>
-      <c r="N115" s="22" t="s">
-        <v>672</v>
       </c>
       <c r="R115" s="2" t="s">
         <v>380</v>
@@ -8847,29 +8844,29 @@
         <v>198</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E116" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="F116" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="H116" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="J116" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="J116" s="2" t="s">
+      <c r="L116" s="20" t="s">
         <v>677</v>
       </c>
-      <c r="L116" s="20" t="s">
+      <c r="M116" s="6" t="s">
         <v>678</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>679</v>
       </c>
       <c r="N116" s="21"/>
       <c r="R116" s="2" t="s">
@@ -8893,29 +8890,29 @@
     </row>
     <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F117" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="J117" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="J117" s="2" t="s">
+      <c r="K117" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="K117" s="2" t="s">
+      <c r="L117" s="13" t="s">
         <v>685</v>
-      </c>
-      <c r="L117" s="13" t="s">
-        <v>686</v>
       </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
@@ -8940,10 +8937,10 @@
     </row>
     <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
@@ -8956,13 +8953,13 @@
         <v>54</v>
       </c>
       <c r="J118" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="K118" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="K118" s="2" t="s">
+      <c r="L118" s="13" t="s">
         <v>688</v>
-      </c>
-      <c r="L118" s="13" t="s">
-        <v>689</v>
       </c>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
@@ -8984,29 +8981,29 @@
     </row>
     <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
         <v>213</v>
       </c>
       <c r="E119" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="F119" s="2" t="s">
+      <c r="J119" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="J119" s="2" t="s">
+      <c r="K119" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="K119" s="2" t="s">
+      <c r="L119" s="13" t="s">
         <v>693</v>
-      </c>
-      <c r="L119" s="13" t="s">
-        <v>694</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -9031,10 +9028,10 @@
     </row>
     <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
@@ -9044,16 +9041,16 @@
         <v>66</v>
       </c>
       <c r="F120" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="J120" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="J120" s="2" t="s">
+      <c r="K120" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="K120" s="2" t="s">
+      <c r="L120" s="13" t="s">
         <v>697</v>
-      </c>
-      <c r="L120" s="13" t="s">
-        <v>698</v>
       </c>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
@@ -9069,14 +9066,14 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>300</v>
@@ -9085,10 +9082,10 @@
         <v>301</v>
       </c>
       <c r="J121" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="L121" s="13" t="s">
         <v>702</v>
-      </c>
-      <c r="L121" s="13" t="s">
-        <v>703</v>
       </c>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
@@ -9099,13 +9096,13 @@
         <v>100</v>
       </c>
       <c r="T121" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="U121" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="U121" s="4" t="s">
+      <c r="V121" s="4" t="s">
         <v>705</v>
-      </c>
-      <c r="V121" s="4" t="s">
-        <v>706</v>
       </c>
       <c r="W121" s="4">
         <v>2</v>
@@ -9113,35 +9110,35 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="F122" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="J122" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="J122" s="2" t="s">
+      <c r="K122" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="L122" s="13" t="s">
         <v>711</v>
       </c>
-      <c r="L122" s="13" t="s">
+      <c r="M122" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="M122" s="2" t="s">
+      <c r="N122" s="13" t="s">
         <v>713</v>
-      </c>
-      <c r="N122" s="13" t="s">
-        <v>714</v>
       </c>
       <c r="R122" s="2" t="s">
         <v>77</v>
@@ -9150,7 +9147,7 @@
         <v>100</v>
       </c>
       <c r="T122" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="U122" s="4">
         <v>143</v>
@@ -9164,29 +9161,29 @@
     </row>
     <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="J123" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="J123" s="2" t="s">
+      <c r="K123" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="K123" s="2" t="s">
+      <c r="L123" s="13" t="s">
         <v>718</v>
-      </c>
-      <c r="L123" s="13" t="s">
-        <v>719</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -9211,29 +9208,29 @@
     </row>
     <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E124" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="F124" s="2" t="s">
-        <v>709</v>
-      </c>
       <c r="J124" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="K124" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="K124" s="2" t="s">
+      <c r="L124" s="13" t="s">
         <v>721</v>
-      </c>
-      <c r="L124" s="13" t="s">
-        <v>722</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -9244,7 +9241,7 @@
         <v>100</v>
       </c>
       <c r="T124" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="U124" s="4">
         <v>72</v>
@@ -9258,29 +9255,29 @@
     </row>
     <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="J125" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="J125" s="2" t="s">
+      <c r="K125" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="K125" s="2" t="s">
+      <c r="L125" s="13" t="s">
         <v>726</v>
-      </c>
-      <c r="L125" s="13" t="s">
-        <v>727</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -9291,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="T125" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="U125" s="4">
         <v>60</v>
@@ -9305,29 +9302,29 @@
     </row>
     <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E126" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="F126" s="2" t="s">
-        <v>709</v>
-      </c>
       <c r="J126" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="K126" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="K126" s="2" t="s">
+      <c r="L126" s="13" t="s">
         <v>730</v>
-      </c>
-      <c r="L126" s="13" t="s">
-        <v>731</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -9338,7 +9335,7 @@
         <v>40</v>
       </c>
       <c r="T126" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="U126" s="4">
         <v>53</v>
@@ -9352,14 +9349,14 @@
     </row>
     <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="23" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C127" s="23"/>
       <c r="D127" s="23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>322</v>
@@ -9371,11 +9368,11 @@
       <c r="H127" s="23"/>
       <c r="I127" s="23"/>
       <c r="J127" s="23" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K127" s="23"/>
       <c r="L127" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M127" s="25"/>
       <c r="N127" s="25"/>
@@ -9386,7 +9383,7 @@
         <v>47</v>
       </c>
       <c r="S127" s="23" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="T127" s="11"/>
       <c r="U127" s="11"/>
@@ -9397,14 +9394,14 @@
     </row>
     <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>322</v>
@@ -9418,13 +9415,13 @@
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="K128" s="8" t="s">
         <v>739</v>
       </c>
-      <c r="K128" s="8" t="s">
+      <c r="L128" s="12" t="s">
         <v>740</v>
-      </c>
-      <c r="L128" s="12" t="s">
-        <v>741</v>
       </c>
       <c r="M128" s="8"/>
       <c r="N128" s="8"/>
@@ -9435,7 +9432,7 @@
         <v>47</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="T128" s="9"/>
       <c r="U128" s="9"/>
@@ -9446,32 +9443,32 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="E129" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="E129" s="8" t="s">
+      <c r="F129" s="8" t="s">
         <v>743</v>
-      </c>
-      <c r="F129" s="8" t="s">
-        <v>744</v>
       </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
       <c r="I129" s="8"/>
       <c r="J129" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="K129" s="8" t="s">
         <v>745</v>
       </c>
-      <c r="K129" s="8" t="s">
+      <c r="L129" s="12" t="s">
         <v>746</v>
-      </c>
-      <c r="L129" s="12" t="s">
-        <v>747</v>
       </c>
       <c r="M129" s="8"/>
       <c r="N129" s="8"/>
@@ -9482,7 +9479,7 @@
         <v>71</v>
       </c>
       <c r="S129" s="8" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T129" s="9">
         <v>600</v>
@@ -9499,30 +9496,30 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="8">
         <v>1572</v>
       </c>
       <c r="E130" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="F130" s="8" t="s">
         <v>708</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>709</v>
       </c>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
       <c r="I130" s="8"/>
       <c r="J130" s="8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K130" s="8"/>
       <c r="L130" s="12" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="M130" s="8"/>
       <c r="N130" s="8"/>
@@ -9533,7 +9530,7 @@
         <v>77</v>
       </c>
       <c r="S130" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="T130" s="9">
         <v>182</v>
@@ -9550,35 +9547,35 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F131" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="H131" s="2" t="s">
+      <c r="J131" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="K131" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="K131" s="2" t="s">
+      <c r="L131" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="L131" s="13" t="s">
+      <c r="M131" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="M131" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="N131" s="2"/>
       <c r="R131" s="2" t="s">
@@ -9602,35 +9599,35 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F132" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="H132" s="2" t="s">
-        <v>755</v>
-      </c>
       <c r="J132" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="K132" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="K132" s="2" t="s">
+      <c r="L132" s="13" t="s">
         <v>761</v>
       </c>
-      <c r="L132" s="13" t="s">
-        <v>762</v>
-      </c>
       <c r="M132" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N132" s="2"/>
       <c r="R132" s="2" t="s">
@@ -9654,14 +9651,14 @@
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>26</v>
@@ -9670,16 +9667,16 @@
         <v>348</v>
       </c>
       <c r="H133" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="J133" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="J133" s="2" t="s">
+      <c r="K133" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="K133" s="2" t="s">
+      <c r="L133" s="13" t="s">
         <v>766</v>
-      </c>
-      <c r="L133" s="13" t="s">
-        <v>767</v>
       </c>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
@@ -9687,7 +9684,7 @@
         <v>47</v>
       </c>
       <c r="S133" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="W133" s="4">
         <v>3</v>
@@ -9695,14 +9692,14 @@
     </row>
     <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>111</v>
@@ -9711,16 +9708,16 @@
         <v>112</v>
       </c>
       <c r="H134" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="J134" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="J134" s="2" t="s">
+      <c r="K134" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="K134" s="2" t="s">
+      <c r="L134" s="13" t="s">
         <v>772</v>
-      </c>
-      <c r="L134" s="13" t="s">
-        <v>773</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
@@ -9745,35 +9742,35 @@
     </row>
     <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G135" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="G135" s="3" t="s">
+      <c r="J135" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="L135" s="12" t="s">
         <v>778</v>
-      </c>
-      <c r="L135" s="12" t="s">
-        <v>779</v>
       </c>
       <c r="R135" s="2" t="s">
         <v>71</v>
       </c>
       <c r="S135" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="T135" s="4">
         <v>200</v>
@@ -9790,29 +9787,29 @@
     </row>
     <row r="136" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E136" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="J136" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="J136" s="2" t="s">
+      <c r="K136" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="K136" s="2" t="s">
+      <c r="L136" s="13" t="s">
         <v>784</v>
-      </c>
-      <c r="L136" s="13" t="s">
-        <v>785</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -9820,7 +9817,7 @@
         <v>71</v>
       </c>
       <c r="S136" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="T136" s="4">
         <v>247</v>
@@ -9837,29 +9834,29 @@
     </row>
     <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E137" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="F137" s="2" t="s">
+      <c r="J137" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="J137" s="2" t="s">
+      <c r="K137" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="K137" s="2" t="s">
+      <c r="L137" s="13" t="s">
         <v>790</v>
-      </c>
-      <c r="L137" s="13" t="s">
-        <v>791</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
@@ -9867,13 +9864,13 @@
         <v>109</v>
       </c>
       <c r="S137" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="T137" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="U137" s="4" t="s">
         <v>792</v>
-      </c>
-      <c r="U137" s="4" t="s">
-        <v>793</v>
       </c>
       <c r="W137" s="4">
         <v>3</v>
@@ -9881,29 +9878,29 @@
     </row>
     <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F138" s="2" t="s">
+      <c r="J138" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="J138" s="2" t="s">
+      <c r="K138" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="K138" s="2" t="s">
+      <c r="L138" s="13" t="s">
         <v>797</v>
-      </c>
-      <c r="L138" s="13" t="s">
-        <v>798</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
@@ -9928,14 +9925,14 @@
     </row>
     <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>246</v>
@@ -9944,19 +9941,19 @@
         <v>247</v>
       </c>
       <c r="J139" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="L139" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="L139" s="3" t="s">
+      <c r="M139" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="M139" s="6" t="s">
+      <c r="N139" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="N139" s="3" t="s">
+      <c r="P139" s="3" t="s">
         <v>805</v>
-      </c>
-      <c r="P139" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="R139" s="2" t="s">
         <v>71</v>
@@ -9979,10 +9976,10 @@
     </row>
     <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="26">
@@ -9995,10 +9992,10 @@
         <v>247</v>
       </c>
       <c r="J140" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="L140" s="3" t="s">
         <v>807</v>
-      </c>
-      <c r="L140" s="3" t="s">
-        <v>808</v>
       </c>
       <c r="N140" s="3"/>
       <c r="P140" s="3"/>
@@ -10023,10 +10020,10 @@
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
@@ -10039,13 +10036,13 @@
         <v>255</v>
       </c>
       <c r="J141" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="L141" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="L141" s="3" t="s">
+      <c r="N141" s="3" t="s">
         <v>810</v>
-      </c>
-      <c r="N141" s="3" t="s">
-        <v>811</v>
       </c>
       <c r="P141" s="6"/>
       <c r="R141" s="2" t="s">
@@ -10055,7 +10052,7 @@
         <v>40</v>
       </c>
       <c r="T141" s="4" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="U141" s="4">
         <v>75</v>
@@ -10069,10 +10066,10 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="26">
@@ -10085,26 +10082,26 @@
         <v>255</v>
       </c>
       <c r="J142" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="L142" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="L142" s="3" t="s">
+      <c r="M142" s="6" t="s">
         <v>814</v>
       </c>
-      <c r="M142" s="6" t="s">
+      <c r="N142" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="N142" s="3" t="s">
-        <v>816</v>
       </c>
       <c r="P142" s="6"/>
       <c r="R142" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S142" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="T142" s="4" t="s">
         <v>817</v>
-      </c>
-      <c r="T142" s="4" t="s">
-        <v>818</v>
       </c>
       <c r="U142" s="4">
         <v>120</v>
@@ -10118,14 +10115,14 @@
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>254</v>
@@ -10134,10 +10131,10 @@
         <v>255</v>
       </c>
       <c r="J143" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="L143" s="3" t="s">
         <v>820</v>
-      </c>
-      <c r="L143" s="3" t="s">
-        <v>821</v>
       </c>
       <c r="P143" s="6"/>
       <c r="R143" s="8" t="s">
@@ -10161,14 +10158,14 @@
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>254</v>
@@ -10177,13 +10174,13 @@
         <v>255</v>
       </c>
       <c r="J144" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="L144" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="L144" s="3" t="s">
+      <c r="N144" s="3" t="s">
         <v>824</v>
-      </c>
-      <c r="N144" s="3" t="s">
-        <v>825</v>
       </c>
       <c r="P144" s="6"/>
       <c r="R144" s="2" t="s">
@@ -10207,10 +10204,10 @@
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
@@ -10223,10 +10220,10 @@
         <v>255</v>
       </c>
       <c r="J145" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="L145" s="3" t="s">
         <v>826</v>
-      </c>
-      <c r="L145" s="3" t="s">
-        <v>827</v>
       </c>
       <c r="P145" s="6"/>
       <c r="R145" s="2" t="s">
@@ -10250,32 +10247,32 @@
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>800</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="26">
         <v>1570</v>
       </c>
       <c r="E146" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="F146" s="2" t="s">
+      <c r="J146" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="L146" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="L146" s="3" t="s">
+      <c r="M146" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="M146" s="6" t="s">
+      <c r="N146" s="3" t="s">
         <v>832</v>
-      </c>
-      <c r="N146" s="3" t="s">
-        <v>833</v>
       </c>
       <c r="P146" s="6"/>
       <c r="R146" s="2" t="s">
@@ -10299,26 +10296,26 @@
     </row>
     <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="F147" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="J147" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="J147" s="2" t="s">
+      <c r="L147" s="13" t="s">
         <v>839</v>
-      </c>
-      <c r="L147" s="13" t="s">
-        <v>840</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -10343,26 +10340,26 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="E148" s="2" t="s">
+      <c r="F148" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="J148" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="F148" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="J148" s="2" t="s">
+      <c r="L148" s="13" t="s">
         <v>843</v>
-      </c>
-      <c r="L148" s="13" t="s">
-        <v>844</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -10370,7 +10367,7 @@
         <v>47</v>
       </c>
       <c r="S148" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="T148" s="4">
         <v>180</v>
@@ -10387,26 +10384,26 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="F149" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="F149" s="2" t="s">
+      <c r="J149" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="J149" s="2" t="s">
+      <c r="L149" s="13" t="s">
         <v>849</v>
-      </c>
-      <c r="L149" s="13" t="s">
-        <v>850</v>
       </c>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
@@ -10414,7 +10411,7 @@
         <v>166</v>
       </c>
       <c r="S149" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="T149" s="4">
         <v>170</v>
@@ -10431,26 +10428,26 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="J150" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="J150" s="2" t="s">
+      <c r="L150" s="13" t="s">
         <v>853</v>
-      </c>
-      <c r="L150" s="13" t="s">
-        <v>854</v>
       </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
@@ -10458,7 +10455,7 @@
         <v>47</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="T150" s="4">
         <v>164</v>
@@ -10475,32 +10472,32 @@
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
+        <v>855</v>
+      </c>
+      <c r="B151" s="18" t="s">
         <v>856</v>
-      </c>
-      <c r="B151" s="18" t="s">
-        <v>857</v>
       </c>
       <c r="C151" s="18"/>
       <c r="D151" s="18" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E151" s="18" t="s">
         <v>66</v>
       </c>
       <c r="F151" s="18" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G151" s="18"/>
       <c r="H151" s="18"/>
       <c r="I151" s="18"/>
       <c r="J151" s="18" t="s">
+        <v>859</v>
+      </c>
+      <c r="K151" s="18" t="s">
         <v>860</v>
       </c>
-      <c r="K151" s="18" t="s">
+      <c r="L151" s="27" t="s">
         <v>861</v>
-      </c>
-      <c r="L151" s="27" t="s">
-        <v>862</v>
       </c>
       <c r="M151" s="18"/>
       <c r="N151" s="18"/>
@@ -10508,7 +10505,7 @@
       <c r="P151" s="18"/>
       <c r="Q151" s="18"/>
       <c r="R151" s="18" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="S151" s="18" t="s">
         <v>40</v>
@@ -10526,33 +10523,33 @@
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="F152" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="J152" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="J152" s="2" t="s">
+      <c r="K152" s="2" t="s">
         <v>867</v>
       </c>
-      <c r="K152" s="2" t="s">
+      <c r="L152" s="13" t="s">
         <v>868</v>
-      </c>
-      <c r="L152" s="13" t="s">
-        <v>869</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="R152" s="2" t="s">
         <v>109</v>
@@ -10572,33 +10569,33 @@
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="E153" s="2" t="s">
+      <c r="F153" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="F153" s="2" t="s">
-        <v>866</v>
-      </c>
       <c r="J153" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="K153" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="K153" s="2" t="s">
+      <c r="L153" s="13" t="s">
         <v>872</v>
-      </c>
-      <c r="L153" s="13" t="s">
-        <v>873</v>
       </c>
       <c r="M153" s="2"/>
       <c r="N153" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="R153" s="2" t="s">
         <v>109</v>
@@ -10618,14 +10615,14 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>429</v>
@@ -10634,13 +10631,13 @@
         <v>398</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K154" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="L154" s="13" t="s">
         <v>875</v>
-      </c>
-      <c r="L154" s="13" t="s">
-        <v>876</v>
       </c>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
@@ -10665,14 +10662,14 @@
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>429</v>
@@ -10684,10 +10681,10 @@
         <v>447</v>
       </c>
       <c r="K155" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="L155" s="13" t="s">
         <v>877</v>
-      </c>
-      <c r="L155" s="13" t="s">
-        <v>878</v>
       </c>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
@@ -10712,29 +10709,29 @@
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>856</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>857</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F156" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="J156" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="J156" s="2" t="s">
+      <c r="K156" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="K156" s="2" t="s">
+      <c r="L156" s="13" t="s">
         <v>882</v>
-      </c>
-      <c r="L156" s="13" t="s">
-        <v>883</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -10759,14 +10756,14 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B157" s="8" t="s">
         <v>856</v>
-      </c>
-      <c r="B157" s="8" t="s">
-        <v>857</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>26</v>
@@ -10778,13 +10775,13 @@
       <c r="H157" s="8"/>
       <c r="I157" s="8"/>
       <c r="J157" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="K157" s="8" t="s">
         <v>885</v>
       </c>
-      <c r="K157" s="8" t="s">
+      <c r="L157" s="12" t="s">
         <v>886</v>
-      </c>
-      <c r="L157" s="12" t="s">
-        <v>887</v>
       </c>
       <c r="M157" s="8"/>
       <c r="N157" s="8"/>
@@ -10795,7 +10792,7 @@
         <v>71</v>
       </c>
       <c r="S157" s="8" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="T157" s="9">
         <v>240</v>
@@ -10812,32 +10809,32 @@
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B158" s="8" t="s">
         <v>856</v>
-      </c>
-      <c r="B158" s="8" t="s">
-        <v>857</v>
       </c>
       <c r="C158" s="8"/>
       <c r="D158" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E158" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G158" s="8"/>
       <c r="H158" s="8"/>
       <c r="I158" s="8"/>
       <c r="J158" s="8" t="s">
+        <v>887</v>
+      </c>
+      <c r="K158" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="8" t="s">
+      <c r="L158" s="12" t="s">
         <v>889</v>
-      </c>
-      <c r="L158" s="12" t="s">
-        <v>890</v>
       </c>
       <c r="M158" s="8"/>
       <c r="N158" s="8"/>
@@ -10865,14 +10862,14 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C159" s="18"/>
       <c r="D159" s="18" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E159" s="18" t="s">
         <v>26</v>
@@ -10890,7 +10887,7 @@
         <v>126</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="M159" s="19"/>
       <c r="N159" s="19"/>
@@ -10918,29 +10915,29 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F160" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="J160" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="J160" s="2" t="s">
+      <c r="K160" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="K160" s="2" t="s">
+      <c r="L160" s="3" t="s">
         <v>897</v>
-      </c>
-      <c r="L160" s="3" t="s">
-        <v>898</v>
       </c>
       <c r="R160" s="2" t="s">
         <v>77</v>
@@ -10960,32 +10957,32 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F161" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="G161" s="13" t="s">
         <v>900</v>
       </c>
-      <c r="G161" s="13" t="s">
+      <c r="J161" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="J161" s="2" t="s">
+      <c r="K161" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="K161" s="2" t="s">
+      <c r="L161" s="3" t="s">
         <v>903</v>
-      </c>
-      <c r="L161" s="3" t="s">
-        <v>904</v>
       </c>
       <c r="R161" s="2" t="s">
         <v>77</v>
@@ -11008,32 +11005,32 @@
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F162" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="G162" s="13" t="s">
         <v>900</v>
       </c>
-      <c r="G162" s="13" t="s">
-        <v>901</v>
-      </c>
       <c r="J162" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="K162" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="K162" s="2" t="s">
+      <c r="L162" s="3" t="s">
         <v>906</v>
-      </c>
-      <c r="L162" s="3" t="s">
-        <v>907</v>
       </c>
       <c r="R162" s="2" t="s">
         <v>77</v>
@@ -11056,32 +11053,32 @@
     </row>
     <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F163" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="G163" s="13" t="s">
         <v>900</v>
       </c>
-      <c r="G163" s="13" t="s">
-        <v>901</v>
-      </c>
       <c r="J163" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="K163" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="K163" s="2" t="s">
+      <c r="L163" s="3" t="s">
         <v>909</v>
-      </c>
-      <c r="L163" s="3" t="s">
-        <v>910</v>
       </c>
       <c r="R163" s="2" t="s">
         <v>77</v>
@@ -11104,32 +11101,32 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F164" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="G164" s="13" t="s">
         <v>900</v>
       </c>
-      <c r="G164" s="13" t="s">
-        <v>901</v>
-      </c>
       <c r="J164" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="K164" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="K164" s="2" t="s">
+      <c r="L164" s="3" t="s">
         <v>912</v>
-      </c>
-      <c r="L164" s="3" t="s">
-        <v>913</v>
       </c>
       <c r="R164" s="2" t="s">
         <v>77</v>
@@ -11152,20 +11149,20 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>113</v>
@@ -11174,7 +11171,7 @@
         <v>114</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="R165" s="2" t="s">
         <v>77</v>
@@ -11197,32 +11194,32 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="23" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C166" s="23"/>
       <c r="D166" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E166" s="23" t="s">
         <v>83</v>
       </c>
       <c r="F166" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G166" s="23"/>
       <c r="H166" s="23"/>
       <c r="I166" s="23"/>
       <c r="J166" s="23" t="s">
+        <v>916</v>
+      </c>
+      <c r="K166" s="23" t="s">
         <v>917</v>
       </c>
-      <c r="K166" s="23" t="s">
+      <c r="L166" s="24" t="s">
         <v>918</v>
-      </c>
-      <c r="L166" s="24" t="s">
-        <v>919</v>
       </c>
       <c r="M166" s="25"/>
       <c r="N166" s="25"/>
@@ -11250,26 +11247,26 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="E167" s="2" t="s">
+      <c r="F167" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="F167" s="2" t="s">
+      <c r="J167" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="J167" s="2" t="s">
+      <c r="L167" s="13" t="s">
         <v>925</v>
-      </c>
-      <c r="L167" s="13" t="s">
-        <v>926</v>
       </c>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
@@ -11277,7 +11274,7 @@
         <v>71</v>
       </c>
       <c r="S167" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="T167" s="4">
         <v>170</v>
@@ -11294,29 +11291,29 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="J168" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="E168" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="J168" s="2" t="s">
+      <c r="K168" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="K168" s="2" t="s">
+      <c r="L168" s="13" t="s">
         <v>930</v>
-      </c>
-      <c r="L168" s="13" t="s">
-        <v>931</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -11324,7 +11321,7 @@
         <v>71</v>
       </c>
       <c r="S168" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="T168" s="4">
         <v>155</v>
@@ -11341,29 +11338,29 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="F169" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="E169" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="F169" s="2" t="s">
+      <c r="J169" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="J169" s="2" t="s">
+      <c r="K169" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="K169" s="2" t="s">
+      <c r="L169" s="13" t="s">
         <v>936</v>
-      </c>
-      <c r="L169" s="13" t="s">
-        <v>937</v>
       </c>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
@@ -11371,7 +11368,7 @@
         <v>77</v>
       </c>
       <c r="S169" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="T169" s="4">
         <v>61</v>
@@ -11388,14 +11385,14 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>111</v>
@@ -11404,13 +11401,13 @@
         <v>112</v>
       </c>
       <c r="J170" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K170" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="2" t="s">
+      <c r="L170" s="13" t="s">
         <v>941</v>
-      </c>
-      <c r="L170" s="13" t="s">
-        <v>942</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -11418,7 +11415,7 @@
         <v>77</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="T170" s="4">
         <v>62</v>
@@ -11435,29 +11432,29 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="E171" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="E171" s="2" t="s">
+      <c r="F171" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="F171" s="2" t="s">
+      <c r="J171" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="J171" s="2" t="s">
+      <c r="K171" s="2" t="s">
         <v>947</v>
       </c>
-      <c r="K171" s="2" t="s">
+      <c r="L171" s="13" t="s">
         <v>948</v>
-      </c>
-      <c r="L171" s="13" t="s">
-        <v>949</v>
       </c>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
@@ -11465,7 +11462,7 @@
         <v>77</v>
       </c>
       <c r="S171" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="T171" s="4">
         <v>224</v>
@@ -11482,29 +11479,29 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>920</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>921</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="E172" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="E172" s="2" t="s">
+      <c r="F172" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="F172" s="2" t="s">
-        <v>946</v>
-      </c>
       <c r="J172" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K172" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="L172" s="13" t="s">
         <v>950</v>
-      </c>
-      <c r="L172" s="13" t="s">
-        <v>951</v>
       </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
@@ -11512,7 +11509,7 @@
         <v>77</v>
       </c>
       <c r="S172" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="T172" s="4">
         <v>140</v>
@@ -11529,29 +11526,29 @@
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="E173" s="2" t="s">
+      <c r="F173" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="F173" s="2" t="s">
+      <c r="J173" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="J173" s="2" t="s">
+      <c r="K173" s="2" t="s">
         <v>957</v>
       </c>
-      <c r="K173" s="2" t="s">
+      <c r="L173" s="13" t="s">
         <v>958</v>
-      </c>
-      <c r="L173" s="13" t="s">
-        <v>959</v>
       </c>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
@@ -11576,29 +11573,29 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="J174" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="J174" s="2" t="s">
+      <c r="K174" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="K174" s="2" t="s">
+      <c r="L174" s="13" t="s">
         <v>963</v>
-      </c>
-      <c r="L174" s="13" t="s">
-        <v>964</v>
       </c>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
@@ -11606,7 +11603,7 @@
         <v>223</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="T174" s="4">
         <v>250</v>
@@ -11623,14 +11620,14 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>26</v>
@@ -11639,13 +11636,13 @@
         <v>43</v>
       </c>
       <c r="J175" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="K175" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="K175" s="2" t="s">
+      <c r="L175" s="13" t="s">
         <v>968</v>
-      </c>
-      <c r="L175" s="13" t="s">
-        <v>969</v>
       </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
@@ -11653,7 +11650,7 @@
         <v>77</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="T175" s="4">
         <v>198</v>
@@ -11670,14 +11667,14 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>953</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>26</v>
@@ -11686,18 +11683,18 @@
         <v>43</v>
       </c>
       <c r="J176" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="K176" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="K176" s="2" t="s">
+      <c r="L176" s="13" t="s">
         <v>972</v>
-      </c>
-      <c r="L176" s="13" t="s">
-        <v>973</v>
       </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="R176" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="S176" s="2" t="s">
         <v>78</v>
@@ -11714,26 +11711,26 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F177" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="J177" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="J177" s="2" t="s">
+      <c r="L177" s="3" t="s">
         <v>979</v>
-      </c>
-      <c r="L177" s="3" t="s">
-        <v>980</v>
       </c>
       <c r="R177" s="2" t="s">
         <v>71</v>
@@ -11756,10 +11753,10 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2">
@@ -11772,16 +11769,16 @@
         <v>95</v>
       </c>
       <c r="J178" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="K178" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="K178" s="2" t="s">
+      <c r="L178" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="L178" s="3" t="s">
+      <c r="N178" s="3" t="s">
         <v>983</v>
-      </c>
-      <c r="N178" s="3" t="s">
-        <v>984</v>
       </c>
       <c r="R178" s="2" t="s">
         <v>77</v>
@@ -11804,14 +11801,14 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>83</v>
@@ -11823,13 +11820,13 @@
         <v>187</v>
       </c>
       <c r="K179" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="L179" s="3" t="s">
         <v>986</v>
       </c>
-      <c r="L179" s="3" t="s">
-        <v>987</v>
-      </c>
       <c r="N179" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="R179" s="2" t="s">
         <v>77</v>
@@ -11852,29 +11849,29 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2">
         <v>1583</v>
       </c>
       <c r="E180" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>989</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>447</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="R180" s="2" t="s">
         <v>77</v>
@@ -11897,29 +11894,29 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F181" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="J181" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="J181" s="2" t="s">
+      <c r="K181" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="K181" s="2" t="s">
+      <c r="L181" s="3" t="s">
         <v>994</v>
-      </c>
-      <c r="L181" s="3" t="s">
-        <v>995</v>
       </c>
       <c r="R181" s="2" t="s">
         <v>77</v>
@@ -11928,7 +11925,7 @@
         <v>40</v>
       </c>
       <c r="T181" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="U181" s="4">
         <v>60</v>
@@ -11942,29 +11939,29 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>976</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="J182" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="K182" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="K182" s="2" t="s">
+      <c r="L182" s="3" t="s">
         <v>999</v>
-      </c>
-      <c r="L182" s="3" t="s">
-        <v>1000</v>
       </c>
       <c r="R182" s="2" t="s">
         <v>77</v>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E641B639-2604-43D2-AAB0-0EDFACF23F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD54509-6A29-454C-8081-8273C684B322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2992,9 +2992,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/c/c8/Alessandro_vittoria%2C_san_giovanni_battista%2C_1565_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>158environ</t>
-  </si>
-  <si>
     <t>Basilique des Saints Jean et Paul</t>
   </si>
   <si>
@@ -3020,6 +3017,9 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1b/Alessandro_Vittoria%2C_San_Zaccaria_%281543%29.jpg/960px-Alessandro_Vittoria%2C_San_Zaccaria_%281543%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1576-1577</t>
   </si>
 </sst>
 </file>
@@ -11901,22 +11901,22 @@
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F181" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="J181" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="J181" s="2" t="s">
+      <c r="K181" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="K181" s="2" t="s">
+      <c r="L181" s="3" t="s">
         <v>993</v>
-      </c>
-      <c r="L181" s="3" t="s">
-        <v>994</v>
       </c>
       <c r="R181" s="2" t="s">
         <v>77</v>
@@ -11925,7 +11925,7 @@
         <v>40</v>
       </c>
       <c r="T181" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="U181" s="4">
         <v>60</v>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>83</v>
@@ -11955,13 +11955,13 @@
         <v>977</v>
       </c>
       <c r="J182" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="K182" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="K182" s="2" t="s">
+      <c r="L182" s="3" t="s">
         <v>998</v>
-      </c>
-      <c r="L182" s="3" t="s">
-        <v>999</v>
       </c>
       <c r="R182" s="2" t="s">
         <v>77</v>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD54509-6A29-454C-8081-8273C684B322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB4834B-9902-46E4-B51E-77154B5211FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="1001">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -703,18 +703,12 @@
     <t>1594</t>
   </si>
   <si>
-    <t>Statue équestre de Cosme Ier de Médicis</t>
-  </si>
-  <si>
     <t>Monumento equestre a Cosimo I de' Medici</t>
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>450(statue) 350 (socle)</t>
-  </si>
-  <si>
     <t>1567-1570</t>
   </si>
   <si>
@@ -937,9 +931,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/3/39/Saliera_Cellini_Vienna_18_04_2013_01_B.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Objet d'art</t>
-  </si>
-  <si>
     <t>Or, émail, ébène, ivoire</t>
   </si>
   <si>
@@ -3020,6 +3011,18 @@
   </si>
   <si>
     <t>1576-1577</t>
+  </si>
+  <si>
+    <t>450 pour la statue, 350 pour le socle</t>
+  </si>
+  <si>
+    <t>Bronze (ronde-bosse et bas-relief) et marbre (socle)</t>
+  </si>
+  <si>
+    <t>Monument équestre ,avec ronde-bosse et bas-relief, intégralement conçu par l'artiste.</t>
+  </si>
+  <si>
+    <t>Monument équestre de Cosme Ier de Médicis</t>
   </si>
 </sst>
 </file>
@@ -3527,8 +3530,8 @@
     <col min="21" max="21" width="8.140625" style="4" customWidth="1"/>
     <col min="22" max="22" width="5.42578125" style="4" customWidth="1"/>
     <col min="23" max="23" width="5.28515625" style="4" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" customWidth="1"/>
     <col min="25" max="25" width="17.140625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3600,6 +3603,11 @@
       </c>
       <c r="W1" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5064,22 +5072,24 @@
         <v>27</v>
       </c>
       <c r="J34" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="L34" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="L34" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>211</v>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument équestre, avec ronde-bosse et bas-relief, intégralement conçu par l'artiste.</t>
+        </is>
       </c>
       <c r="S34" s="2" t="s">
-        <v>100</v>
+        <v>998</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>230</v>
+        <v>997</v>
       </c>
       <c r="U34" s="4">
         <v>400</v>
@@ -5100,7 +5110,7 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>26</v>
@@ -5109,13 +5119,13 @@
         <v>43</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="R35" s="8" t="s">
         <v>47</v>
@@ -5124,7 +5134,7 @@
         <v>40</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="U35" s="4">
         <v>100</v>
@@ -5145,7 +5155,7 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>26</v>
@@ -5160,7 +5170,7 @@
         <v>126</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R36" s="8" t="s">
         <v>47</v>
@@ -5190,7 +5200,7 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>26</v>
@@ -5199,13 +5209,13 @@
         <v>201</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="R37" s="2" t="s">
         <v>77</v>
@@ -5214,7 +5224,7 @@
         <v>40</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U37" s="4">
         <v>130</v>
@@ -5228,26 +5238,26 @@
     </row>
     <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="J38" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="L38" s="13" t="s">
         <v>247</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="L38" s="13" t="s">
-        <v>249</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -5269,26 +5279,26 @@
     </row>
     <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="L39" s="13" t="s">
         <v>250</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="L39" s="13" t="s">
-        <v>252</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -5307,26 +5317,26 @@
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="J40" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="L40" s="13" t="s">
         <v>255</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="L40" s="13" t="s">
-        <v>257</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -5334,7 +5344,7 @@
         <v>71</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="T40" s="4">
         <v>145</v>
@@ -5351,26 +5361,26 @@
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L41" s="13" t="s">
         <v>259</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="L41" s="13" t="s">
-        <v>261</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5395,26 +5405,26 @@
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="R42" s="2" t="s">
         <v>77</v>
@@ -5437,26 +5447,26 @@
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="L43" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="R43" s="2" t="s">
         <v>77</v>
@@ -5479,26 +5489,26 @@
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="R44" s="2" t="s">
         <v>71</v>
@@ -5518,26 +5528,26 @@
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="R45" s="2" t="s">
         <v>77</v>
@@ -5560,26 +5570,26 @@
     </row>
     <row r="46" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="R46" s="2" t="s">
         <v>77</v>
@@ -5588,7 +5598,7 @@
         <v>40</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="U46" s="4">
         <v>49</v>
@@ -5602,26 +5612,26 @@
     </row>
     <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="R47" s="2" t="s">
         <v>77</v>
@@ -5630,7 +5640,7 @@
         <v>40</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U47" s="4">
         <v>75</v>
@@ -5644,26 +5654,26 @@
     </row>
     <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>71</v>
@@ -5683,32 +5693,32 @@
     </row>
     <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="M49" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="N49" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>77</v>
@@ -5731,32 +5741,32 @@
     </row>
     <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>299</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>301</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="L50" s="12" t="s">
         <v>302</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>304</v>
       </c>
       <c r="M50" s="8"/>
       <c r="N50" s="8"/>
@@ -5764,10 +5774,10 @@
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
       <c r="R50" s="8" t="s">
-        <v>305</v>
+        <v>47</v>
       </c>
       <c r="S50" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="T50" s="9">
         <v>26</v>
@@ -5784,14 +5794,14 @@
     </row>
     <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>26</v>
@@ -5803,13 +5813,13 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="M51" s="8"/>
       <c r="N51" s="8"/>
@@ -5823,7 +5833,7 @@
         <v>100</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="U51" s="9">
         <v>132</v>
@@ -5837,32 +5847,32 @@
     </row>
     <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
       <c r="J52" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L52" s="12" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M52" s="8"/>
       <c r="N52" s="8"/>
@@ -5890,14 +5900,14 @@
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>26</v>
@@ -5909,13 +5919,13 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L53" s="14" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
@@ -5926,7 +5936,7 @@
         <v>77</v>
       </c>
       <c r="S53" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="T53" s="9">
         <v>110</v>
@@ -5943,34 +5953,34 @@
     </row>
     <row r="54" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G54" s="8"/>
       <c r="H54" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="L54" s="12" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
@@ -5981,7 +5991,7 @@
         <v>77</v>
       </c>
       <c r="S54" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="T54" s="9">
         <v>274</v>
@@ -5998,32 +6008,32 @@
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="L55" s="14" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="M55" s="8"/>
       <c r="N55" s="8"/>
@@ -6031,7 +6041,7 @@
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
       <c r="R55" s="8" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="S55" s="8" t="s">
         <v>100</v>
@@ -6051,14 +6061,14 @@
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>26</v>
@@ -6070,13 +6080,13 @@
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
       <c r="J56" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="L56" s="12" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="M56" s="8"/>
       <c r="N56" s="8"/>
@@ -6087,7 +6097,7 @@
         <v>77</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="T56" s="9">
         <v>105</v>
@@ -6104,14 +6114,14 @@
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>26</v>
@@ -6123,13 +6133,13 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="L57" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="M57" s="8"/>
       <c r="N57" s="8"/>
@@ -6157,33 +6167,33 @@
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F58" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L58" s="13" t="s">
         <v>348</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="L58" s="13" t="s">
-        <v>351</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="13" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="R58" s="2" t="s">
         <v>211</v>
@@ -6206,36 +6216,36 @@
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F59" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="K59" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="L59" s="13" t="s">
         <v>355</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="L59" s="13" t="s">
-        <v>358</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="13" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="R59" s="2" t="s">
         <v>77</v>
@@ -6258,29 +6268,29 @@
     </row>
     <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -6305,14 +6315,14 @@
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>26</v>
@@ -6321,13 +6331,13 @@
         <v>43</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="L61" s="13" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
@@ -6349,26 +6359,26 @@
     </row>
     <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="R62" s="2" t="s">
         <v>77</v>
@@ -6391,34 +6401,34 @@
     </row>
     <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J63" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="L63" s="13" t="s">
         <v>376</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="L63" s="13" t="s">
-        <v>379</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="R63" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S63" s="2" t="s">
         <v>40</v>
@@ -6435,29 +6445,29 @@
     </row>
     <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F64" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="L64" s="13" t="s">
         <v>382</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="L64" s="13" t="s">
-        <v>385</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -6482,14 +6492,14 @@
     </row>
     <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>26</v>
@@ -6498,13 +6508,13 @@
         <v>43</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="L65" s="13" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -6529,14 +6539,14 @@
     </row>
     <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>26</v>
@@ -6545,13 +6555,13 @@
         <v>43</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -6576,29 +6586,29 @@
     </row>
     <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J67" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="K67" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="L67" s="13" t="s">
         <v>398</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="L67" s="13" t="s">
-        <v>401</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -6623,14 +6633,14 @@
     </row>
     <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>26</v>
@@ -6639,18 +6649,18 @@
         <v>43</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
       <c r="R68" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S68" s="2" t="s">
         <v>100</v>
@@ -6667,14 +6677,14 @@
     </row>
     <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>26</v>
@@ -6683,13 +6693,13 @@
         <v>147</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="L69" s="13" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -6714,14 +6724,14 @@
     </row>
     <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>26</v>
@@ -6730,13 +6740,13 @@
         <v>43</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -6761,29 +6771,29 @@
     </row>
     <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="L71" s="13" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -6808,31 +6818,31 @@
     </row>
     <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J72" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="K72" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="L72" s="13" t="s">
         <v>420</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="L72" s="13" t="s">
-        <v>423</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -6857,16 +6867,16 @@
     </row>
     <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>26</v>
@@ -6875,13 +6885,13 @@
         <v>54</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="L73" s="13" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -6906,31 +6916,31 @@
     </row>
     <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J74" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="K74" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="L74" s="13" t="s">
         <v>430</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L74" s="13" t="s">
-        <v>433</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -6955,31 +6965,31 @@
     </row>
     <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J75" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="K75" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="L75" s="13" t="s">
         <v>436</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="L75" s="13" t="s">
-        <v>439</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -7004,14 +7014,14 @@
     </row>
     <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>159</v>
@@ -7020,13 +7030,13 @@
         <v>160</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="R76" s="2" t="s">
         <v>166</v>
@@ -7049,14 +7059,14 @@
     </row>
     <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>159</v>
@@ -7065,13 +7075,13 @@
         <v>160</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="R77" s="2" t="s">
         <v>77</v>
@@ -7094,35 +7104,35 @@
     </row>
     <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J78" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="L78" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="L78" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="R78" s="2" t="s">
         <v>166</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="T78" s="4">
         <v>600</v>
@@ -7139,41 +7149,41 @@
     </row>
     <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>159</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>195</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="R79" s="2" t="s">
         <v>166</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="T79" s="4">
         <v>1100</v>
       </c>
       <c r="U79" s="4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="V79" s="4">
         <v>130</v>
@@ -7184,32 +7194,32 @@
     </row>
     <row r="80" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="J80" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="K80" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="L80" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>166</v>
@@ -7232,10 +7242,10 @@
     </row>
     <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
@@ -7245,16 +7255,16 @@
         <v>159</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="R81" s="2" t="s">
         <v>77</v>
@@ -7263,7 +7273,7 @@
         <v>172</v>
       </c>
       <c r="T81" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="U81" s="4">
         <v>80</v>
@@ -7277,32 +7287,32 @@
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>177</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="R82" s="2" t="s">
         <v>57</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T82" s="4">
         <v>800</v>
@@ -7319,29 +7329,29 @@
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J83" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="K83" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="L83" s="13" t="s">
         <v>483</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="L83" s="13" t="s">
-        <v>486</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -7366,29 +7376,29 @@
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F84" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="L84" s="13" t="s">
         <v>487</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="L84" s="13" t="s">
-        <v>490</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -7413,34 +7423,34 @@
     </row>
     <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D85" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="K85" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="F85" s="5" t="s">
+      <c r="L85" s="15" t="s">
         <v>492</v>
-      </c>
-      <c r="J85" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="K85" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="L85" s="15" t="s">
-        <v>495</v>
       </c>
       <c r="R85" s="5" t="s">
         <v>57</v>
       </c>
       <c r="S85" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T85" s="16">
         <v>3250</v>
@@ -7457,29 +7467,29 @@
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="L86" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="R86" s="8" t="s">
         <v>47</v>
@@ -7488,7 +7498,7 @@
         <v>100</v>
       </c>
       <c r="T86" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="U86" s="4">
         <v>92</v>
@@ -7502,35 +7512,35 @@
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="J87" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="K87" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="L87" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="M87" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="N87" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="R87" s="8" t="s">
         <v>47</v>
@@ -7553,35 +7563,35 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="L88" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="J88" s="2" t="s">
+      <c r="M88" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="N88" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>515</v>
       </c>
       <c r="R88" s="8" t="s">
         <v>47</v>
@@ -7604,30 +7614,30 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="18" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C89" s="18"/>
       <c r="D89" s="18" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E89" s="18" t="s">
         <v>66</v>
       </c>
       <c r="F89" s="18" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="G89" s="18"/>
       <c r="H89" s="18"/>
       <c r="I89" s="18"/>
       <c r="J89" s="18" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K89" s="18"/>
       <c r="L89" s="12" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="M89" s="19"/>
       <c r="N89" s="19"/>
@@ -7638,7 +7648,7 @@
         <v>71</v>
       </c>
       <c r="S89" s="18" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="T89" s="10">
         <v>600</v>
@@ -7655,37 +7665,37 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D90" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="J90" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="K90" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="L90" s="15" t="s">
         <v>525</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="L90" s="15" t="s">
-        <v>528</v>
       </c>
       <c r="R90" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S90" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="T90" s="17" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="U90" s="17">
         <v>75</v>
@@ -7699,34 +7709,34 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="J91" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="K91" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="L91" s="13" t="s">
         <v>533</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="L91" s="13" t="s">
-        <v>536</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="R91" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S91" s="2" t="s">
         <v>100</v>
@@ -7743,34 +7753,34 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="L92" s="13" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="R92" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S92" s="2" t="s">
         <v>100</v>
@@ -7787,34 +7797,34 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="L93" s="13" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="R93" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S93" s="2" t="s">
         <v>100</v>
@@ -7831,29 +7841,29 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="J94" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="K94" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="L94" s="13" t="s">
         <v>545</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="L94" s="13" t="s">
-        <v>548</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -7861,7 +7871,7 @@
         <v>77</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="T94" s="4">
         <v>67</v>
@@ -7878,36 +7888,36 @@
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>187</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="N95" s="2"/>
       <c r="R95" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="T95" s="4">
         <v>27</v>
@@ -7924,36 +7934,36 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="J96" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="K96" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="L96" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="M96" s="6" t="s">
         <v>559</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>562</v>
       </c>
       <c r="N96" s="2"/>
       <c r="R96" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S96" s="2" t="s">
         <v>100</v>
@@ -7970,33 +7980,33 @@
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="N97" s="2"/>
       <c r="R97" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S97" s="2" t="s">
         <v>100</v>
@@ -8013,36 +8023,36 @@
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K98" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="L98" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="N98" s="2"/>
       <c r="R98" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="T98" s="4">
         <v>105</v>
@@ -8059,45 +8069,45 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G99" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F99" s="2" t="s">
+      <c r="J99" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="G99" s="13" t="s">
+      <c r="K99" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="L99" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="J99" s="2" t="s">
+      <c r="M99" s="6" t="s">
         <v>575</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>578</v>
       </c>
       <c r="N99" s="2"/>
       <c r="R99" s="2" t="s">
         <v>57</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="T99" s="4">
         <v>380</v>
@@ -8108,45 +8118,45 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="G100" s="13" t="s">
+      <c r="J100" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="K100" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="L100" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="J100" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="K100" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>577</v>
-      </c>
       <c r="M100" s="6" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="N100" s="2"/>
       <c r="R100" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="W100" s="4">
         <v>2</v>
@@ -8154,29 +8164,29 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="J101" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="K101" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="L101" s="13" t="s">
         <v>587</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="L101" s="13" t="s">
-        <v>590</v>
       </c>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -8184,7 +8194,7 @@
         <v>166</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="T101" s="4">
         <v>1600</v>
@@ -8198,29 +8208,29 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="K102" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="L102" s="13" t="s">
         <v>593</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="L102" s="13" t="s">
-        <v>596</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -8228,7 +8238,7 @@
         <v>166</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="T102" s="4">
         <v>1440</v>
@@ -8242,29 +8252,29 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="J103" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="K103" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="L103" s="13" t="s">
         <v>599</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="L103" s="13" t="s">
-        <v>602</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -8272,7 +8282,7 @@
         <v>166</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="T103" s="4">
         <v>1060</v>
@@ -8286,29 +8296,29 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="K104" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="L104" s="13" t="s">
         <v>604</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="L104" s="13" t="s">
-        <v>607</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -8316,7 +8326,7 @@
         <v>166</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="T104" s="4">
         <v>1150</v>
@@ -8330,29 +8340,29 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="K105" s="6" t="s">
         <v>611</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F105" s="2" t="s">
+      <c r="L105" s="13" t="s">
         <v>612</v>
-      </c>
-      <c r="J105" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>614</v>
-      </c>
-      <c r="L105" s="13" t="s">
-        <v>615</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
@@ -8363,7 +8373,7 @@
         <v>100</v>
       </c>
       <c r="T105" s="4" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="W105" s="4">
         <v>2</v>
@@ -8371,35 +8381,35 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="I106" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="J106" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="K106" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="I106" s="13" t="s">
+      <c r="L106" s="13" t="s">
         <v>621</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="L106" s="13" t="s">
-        <v>624</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -8410,7 +8420,7 @@
         <v>100</v>
       </c>
       <c r="T106" s="4" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="U106" s="4">
         <v>200</v>
@@ -8424,32 +8434,32 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="J107" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F107" s="2" t="s">
+      <c r="K107" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="L107" s="13" t="s">
         <v>628</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="L107" s="13" t="s">
-        <v>631</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -8460,7 +8470,7 @@
         <v>100</v>
       </c>
       <c r="T107" s="4" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="W107" s="4">
         <v>2</v>
@@ -8468,29 +8478,29 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="L108" s="13" t="s">
         <v>633</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>635</v>
-      </c>
-      <c r="L108" s="13" t="s">
-        <v>636</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -8518,29 +8528,29 @@
         <v>198</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
         <v>124</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="L109" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="N109" s="20" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="R109" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S109" s="2" t="s">
         <v>40</v>
@@ -8563,30 +8573,30 @@
         <v>198</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
         <v>124</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="L110" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="N110" s="21"/>
       <c r="R110" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="T110" s="4">
         <v>210</v>
@@ -8606,39 +8616,39 @@
         <v>198</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="L111" s="20" t="s">
         <v>645</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G111" s="13" t="s">
+      <c r="M111" s="6" t="s">
         <v>646</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="L111" s="20" t="s">
-        <v>648</v>
-      </c>
-      <c r="M111" s="6" t="s">
-        <v>649</v>
       </c>
       <c r="N111" s="21"/>
       <c r="R111" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S111" s="2" t="s">
         <v>40</v>
       </c>
       <c r="T111" s="4" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="U111" s="4">
         <v>182</v>
@@ -8655,30 +8665,30 @@
         <v>198</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="L112" s="20" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="N112" s="21"/>
       <c r="R112" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S112" s="2" t="s">
         <v>40</v>
@@ -8701,30 +8711,30 @@
         <v>198</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="J113" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="L113" s="20" t="s">
         <v>654</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="L113" s="20" t="s">
-        <v>657</v>
       </c>
       <c r="N113" s="21"/>
       <c r="R113" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="T113" s="4">
         <v>700</v>
@@ -8744,33 +8754,33 @@
         <v>198</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="J114" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F114" s="2" t="s">
+      <c r="L114" s="20" t="s">
         <v>660</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="L114" s="20" t="s">
-        <v>663</v>
       </c>
       <c r="N114" s="21"/>
       <c r="R114" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T114" s="4">
         <v>215</v>
@@ -8790,41 +8800,41 @@
         <v>198</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="I115" s="20" t="s">
         <v>664</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F115" s="2" t="s">
+      <c r="J115" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="L115" s="20" t="s">
         <v>666</v>
       </c>
-      <c r="I115" s="20" t="s">
+      <c r="M115" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="J115" s="2" t="s">
+      <c r="N115" s="22" t="s">
         <v>668</v>
       </c>
-      <c r="L115" s="20" t="s">
-        <v>669</v>
-      </c>
-      <c r="M115" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="N115" s="22" t="s">
-        <v>671</v>
-      </c>
       <c r="R115" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T115" s="4">
         <v>205</v>
@@ -8844,36 +8854,36 @@
         <v>198</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="J116" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="L116" s="20" t="s">
         <v>674</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="M116" s="6" t="s">
         <v>675</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="L116" s="20" t="s">
-        <v>677</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>678</v>
       </c>
       <c r="N116" s="21"/>
       <c r="R116" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T116" s="4">
         <v>80</v>
@@ -8890,29 +8900,29 @@
     </row>
     <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F117" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="L117" s="13" t="s">
         <v>682</v>
-      </c>
-      <c r="J117" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="L117" s="13" t="s">
-        <v>685</v>
       </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
@@ -8937,14 +8947,14 @@
     </row>
     <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>26</v>
@@ -8953,13 +8963,13 @@
         <v>54</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="L118" s="13" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
@@ -8981,29 +8991,29 @@
     </row>
     <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
         <v>213</v>
       </c>
       <c r="E119" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="K119" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="F119" s="2" t="s">
+      <c r="L119" s="13" t="s">
         <v>690</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="L119" s="13" t="s">
-        <v>693</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -9028,29 +9038,29 @@
     </row>
     <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F120" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="L120" s="13" t="s">
         <v>694</v>
-      </c>
-      <c r="J120" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="L120" s="13" t="s">
-        <v>697</v>
       </c>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
@@ -9066,26 +9076,26 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="L121" s="13" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
@@ -9096,13 +9106,13 @@
         <v>100</v>
       </c>
       <c r="T121" s="4" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="U121" s="4" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="V121" s="4" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="W121" s="4">
         <v>2</v>
@@ -9110,35 +9120,35 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="J122" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="K122" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="L122" s="13" t="s">
         <v>708</v>
       </c>
-      <c r="J122" s="2" t="s">
+      <c r="M122" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="N122" s="13" t="s">
         <v>710</v>
-      </c>
-      <c r="L122" s="13" t="s">
-        <v>711</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="N122" s="13" t="s">
-        <v>713</v>
       </c>
       <c r="R122" s="2" t="s">
         <v>77</v>
@@ -9147,7 +9157,7 @@
         <v>100</v>
       </c>
       <c r="T122" s="4" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="U122" s="4">
         <v>143</v>
@@ -9161,29 +9171,29 @@
     </row>
     <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="L123" s="13" t="s">
         <v>715</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="L123" s="13" t="s">
-        <v>718</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -9208,29 +9218,29 @@
     </row>
     <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="L124" s="13" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -9241,7 +9251,7 @@
         <v>100</v>
       </c>
       <c r="T124" s="4" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="U124" s="4">
         <v>72</v>
@@ -9255,29 +9265,29 @@
     </row>
     <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="L125" s="13" t="s">
         <v>723</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="L125" s="13" t="s">
-        <v>726</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -9288,7 +9298,7 @@
         <v>100</v>
       </c>
       <c r="T125" s="4" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="U125" s="4">
         <v>60</v>
@@ -9302,29 +9312,29 @@
     </row>
     <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="L126" s="13" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -9335,7 +9345,7 @@
         <v>40</v>
       </c>
       <c r="T126" s="4" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="U126" s="4">
         <v>53</v>
@@ -9349,30 +9359,30 @@
     </row>
     <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="23" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C127" s="23"/>
       <c r="D127" s="23" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F127" s="23" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G127" s="23"/>
       <c r="H127" s="23"/>
       <c r="I127" s="23"/>
       <c r="J127" s="23" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="K127" s="23"/>
       <c r="L127" s="24" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="M127" s="25"/>
       <c r="N127" s="25"/>
@@ -9383,7 +9393,7 @@
         <v>47</v>
       </c>
       <c r="S127" s="23" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="T127" s="11"/>
       <c r="U127" s="11"/>
@@ -9394,34 +9404,34 @@
     </row>
     <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G128" s="8"/>
       <c r="H128" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="8" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="K128" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="L128" s="12" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="M128" s="8"/>
       <c r="N128" s="8"/>
@@ -9432,7 +9442,7 @@
         <v>47</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="T128" s="9"/>
       <c r="U128" s="9"/>
@@ -9443,32 +9453,32 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="8" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
       <c r="I129" s="8"/>
       <c r="J129" s="8" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="K129" s="8" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="L129" s="12" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="M129" s="8"/>
       <c r="N129" s="8"/>
@@ -9479,7 +9489,7 @@
         <v>71</v>
       </c>
       <c r="S129" s="8" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="T129" s="9">
         <v>600</v>
@@ -9496,30 +9506,30 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="8">
         <v>1572</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
       <c r="I130" s="8"/>
       <c r="J130" s="8" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="K130" s="8"/>
       <c r="L130" s="12" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="M130" s="8"/>
       <c r="N130" s="8"/>
@@ -9530,7 +9540,7 @@
         <v>77</v>
       </c>
       <c r="S130" s="8" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="T130" s="9">
         <v>182</v>
@@ -9547,35 +9557,35 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F131" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="K131" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="H131" s="2" t="s">
+      <c r="L131" s="13" t="s">
         <v>754</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="M131" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="K131" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="L131" s="13" t="s">
-        <v>757</v>
-      </c>
-      <c r="M131" s="2" t="s">
-        <v>758</v>
       </c>
       <c r="N131" s="2"/>
       <c r="R131" s="2" t="s">
@@ -9599,35 +9609,35 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="L132" s="13" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="N132" s="2"/>
       <c r="R132" s="2" t="s">
@@ -9651,32 +9661,32 @@
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H133" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="L133" s="13" t="s">
         <v>763</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="L133" s="13" t="s">
-        <v>766</v>
       </c>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
@@ -9684,7 +9694,7 @@
         <v>47</v>
       </c>
       <c r="S133" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="W133" s="4">
         <v>3</v>
@@ -9692,14 +9702,14 @@
     </row>
     <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>111</v>
@@ -9708,16 +9718,16 @@
         <v>112</v>
       </c>
       <c r="H134" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="L134" s="13" t="s">
         <v>769</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="L134" s="13" t="s">
-        <v>772</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
@@ -9742,35 +9752,35 @@
     </row>
     <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="L135" s="12" t="s">
         <v>775</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="G135" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="L135" s="12" t="s">
-        <v>778</v>
       </c>
       <c r="R135" s="2" t="s">
         <v>71</v>
       </c>
       <c r="S135" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="T135" s="4">
         <v>200</v>
@@ -9787,29 +9797,29 @@
     </row>
     <row r="136" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E136" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="K136" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="L136" s="13" t="s">
         <v>781</v>
-      </c>
-      <c r="J136" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="L136" s="13" t="s">
-        <v>784</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -9817,7 +9827,7 @@
         <v>71</v>
       </c>
       <c r="S136" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="T136" s="4">
         <v>247</v>
@@ -9834,29 +9844,29 @@
     </row>
     <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E137" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="K137" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="F137" s="2" t="s">
+      <c r="L137" s="13" t="s">
         <v>787</v>
-      </c>
-      <c r="J137" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="L137" s="13" t="s">
-        <v>790</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
@@ -9864,13 +9874,13 @@
         <v>109</v>
       </c>
       <c r="S137" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="T137" s="4" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="U137" s="4" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="W137" s="4">
         <v>3</v>
@@ -9878,29 +9888,29 @@
     </row>
     <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="K138" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F138" s="2" t="s">
+      <c r="L138" s="13" t="s">
         <v>794</v>
-      </c>
-      <c r="J138" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="K138" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="L138" s="13" t="s">
-        <v>797</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
@@ -9925,35 +9935,35 @@
     </row>
     <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="M139" s="6" t="s">
         <v>800</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="J139" s="2" t="s">
+      <c r="N139" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="L139" s="3" t="s">
+      <c r="P139" s="3" t="s">
         <v>802</v>
-      </c>
-      <c r="M139" s="6" t="s">
-        <v>803</v>
-      </c>
-      <c r="N139" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="P139" s="3" t="s">
-        <v>805</v>
       </c>
       <c r="R139" s="2" t="s">
         <v>71</v>
@@ -9976,26 +9986,26 @@
     </row>
     <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="26">
         <v>1583</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="N140" s="3"/>
       <c r="P140" s="3"/>
@@ -10020,29 +10030,29 @@
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
         <v>137</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="N141" s="3" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="P141" s="6"/>
       <c r="R141" s="2" t="s">
@@ -10052,7 +10062,7 @@
         <v>40</v>
       </c>
       <c r="T141" s="4" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="U141" s="4">
         <v>75</v>
@@ -10066,42 +10076,42 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="26">
         <v>1586</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J142" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="M142" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="N142" s="3" t="s">
         <v>812</v>
-      </c>
-      <c r="L142" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="M142" s="6" t="s">
-        <v>814</v>
-      </c>
-      <c r="N142" s="3" t="s">
-        <v>815</v>
       </c>
       <c r="P142" s="6"/>
       <c r="R142" s="2" t="s">
         <v>77</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="T142" s="4" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="U142" s="4">
         <v>120</v>
@@ -10115,26 +10125,26 @@
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="P143" s="6"/>
       <c r="R143" s="8" t="s">
@@ -10144,7 +10154,7 @@
         <v>40</v>
       </c>
       <c r="T143" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="U143" s="4">
         <v>190</v>
@@ -10158,29 +10168,29 @@
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="N144" s="3" t="s">
         <v>821</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="L144" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="N144" s="3" t="s">
-        <v>824</v>
       </c>
       <c r="P144" s="6"/>
       <c r="R144" s="2" t="s">
@@ -10204,26 +10214,26 @@
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="P145" s="6"/>
       <c r="R145" s="2" t="s">
@@ -10247,32 +10257,32 @@
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="26">
         <v>1570</v>
       </c>
       <c r="E146" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="L146" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="F146" s="2" t="s">
+      <c r="M146" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="N146" s="3" t="s">
         <v>829</v>
-      </c>
-      <c r="L146" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="M146" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="N146" s="3" t="s">
-        <v>832</v>
       </c>
       <c r="P146" s="6"/>
       <c r="R146" s="2" t="s">
@@ -10296,26 +10306,26 @@
     </row>
     <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="J147" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="L147" s="13" t="s">
         <v>836</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="L147" s="13" t="s">
-        <v>839</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -10323,7 +10333,7 @@
         <v>166</v>
       </c>
       <c r="S147" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T147" s="4">
         <v>177</v>
@@ -10340,26 +10350,26 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="L148" s="13" t="s">
         <v>840</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="L148" s="13" t="s">
-        <v>843</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -10367,7 +10377,7 @@
         <v>47</v>
       </c>
       <c r="S148" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="T148" s="4">
         <v>180</v>
@@ -10384,26 +10394,26 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="J149" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="L149" s="13" t="s">
         <v>846</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="J149" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="L149" s="13" t="s">
-        <v>849</v>
       </c>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
@@ -10411,7 +10421,7 @@
         <v>166</v>
       </c>
       <c r="S149" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="T149" s="4">
         <v>170</v>
@@ -10428,26 +10438,26 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="L150" s="13" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
@@ -10455,7 +10465,7 @@
         <v>47</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="T150" s="4">
         <v>164</v>
@@ -10472,32 +10482,32 @@
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C151" s="18"/>
       <c r="D151" s="18" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="E151" s="18" t="s">
         <v>66</v>
       </c>
       <c r="F151" s="18" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="G151" s="18"/>
       <c r="H151" s="18"/>
       <c r="I151" s="18"/>
       <c r="J151" s="18" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="K151" s="18" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="L151" s="27" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="M151" s="18"/>
       <c r="N151" s="18"/>
@@ -10505,7 +10515,7 @@
       <c r="P151" s="18"/>
       <c r="Q151" s="18"/>
       <c r="R151" s="18" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="S151" s="18" t="s">
         <v>40</v>
@@ -10523,33 +10533,33 @@
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="J152" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="K152" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="L152" s="13" t="s">
         <v>865</v>
-      </c>
-      <c r="J152" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="L152" s="13" t="s">
-        <v>868</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="12" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="R152" s="2" t="s">
         <v>109</v>
@@ -10569,33 +10579,33 @@
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="L153" s="13" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="M153" s="2"/>
       <c r="N153" s="12" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="R153" s="2" t="s">
         <v>109</v>
@@ -10615,29 +10625,29 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="L154" s="13" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
@@ -10662,29 +10672,29 @@
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="K155" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="E155" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="J155" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="K155" s="2" t="s">
-        <v>876</v>
-      </c>
       <c r="L155" s="13" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
@@ -10709,29 +10719,29 @@
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F156" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="L156" s="13" t="s">
         <v>879</v>
-      </c>
-      <c r="J156" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>881</v>
-      </c>
-      <c r="L156" s="13" t="s">
-        <v>882</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -10756,32 +10766,32 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="8" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
       <c r="I157" s="8"/>
       <c r="J157" s="8" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="K157" s="8" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="L157" s="12" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="M157" s="8"/>
       <c r="N157" s="8"/>
@@ -10792,7 +10802,7 @@
         <v>71</v>
       </c>
       <c r="S157" s="8" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="T157" s="9">
         <v>240</v>
@@ -10809,32 +10819,32 @@
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C158" s="8"/>
       <c r="D158" s="8" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="E158" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="G158" s="8"/>
       <c r="H158" s="8"/>
       <c r="I158" s="8"/>
       <c r="J158" s="8" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="K158" s="8" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="L158" s="12" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="M158" s="8"/>
       <c r="N158" s="8"/>
@@ -10862,14 +10872,14 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C159" s="18"/>
       <c r="D159" s="18" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="E159" s="18" t="s">
         <v>26</v>
@@ -10887,7 +10897,7 @@
         <v>126</v>
       </c>
       <c r="L159" s="28" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="M159" s="19"/>
       <c r="N159" s="19"/>
@@ -10915,29 +10925,29 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F160" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="L160" s="3" t="s">
         <v>894</v>
-      </c>
-      <c r="J160" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="K160" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="L160" s="3" t="s">
-        <v>897</v>
       </c>
       <c r="R160" s="2" t="s">
         <v>77</v>
@@ -10957,32 +10967,32 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F161" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="G161" s="13" t="s">
+        <v>897</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="K161" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="G161" s="13" t="s">
+      <c r="L161" s="3" t="s">
         <v>900</v>
-      </c>
-      <c r="J161" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="K161" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="L161" s="3" t="s">
-        <v>903</v>
       </c>
       <c r="R161" s="2" t="s">
         <v>77</v>
@@ -11005,32 +11015,32 @@
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="L162" s="3" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="R162" s="2" t="s">
         <v>77</v>
@@ -11053,32 +11063,32 @@
     </row>
     <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="R163" s="2" t="s">
         <v>77</v>
@@ -11101,32 +11111,32 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="L164" s="3" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="R164" s="2" t="s">
         <v>77</v>
@@ -11149,20 +11159,20 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>113</v>
@@ -11171,7 +11181,7 @@
         <v>114</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="R165" s="2" t="s">
         <v>77</v>
@@ -11194,32 +11204,32 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="23" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B166" s="23" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C166" s="23"/>
       <c r="D166" s="23" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="E166" s="23" t="s">
         <v>83</v>
       </c>
       <c r="F166" s="23" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="G166" s="23"/>
       <c r="H166" s="23"/>
       <c r="I166" s="23"/>
       <c r="J166" s="23" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="K166" s="23" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="L166" s="24" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="M166" s="25"/>
       <c r="N166" s="25"/>
@@ -11247,26 +11257,26 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="J167" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="E167" s="2" t="s">
+      <c r="L167" s="13" t="s">
         <v>922</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="J167" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="L167" s="13" t="s">
-        <v>925</v>
       </c>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
@@ -11274,7 +11284,7 @@
         <v>71</v>
       </c>
       <c r="S167" s="2" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="T167" s="4">
         <v>170</v>
@@ -11291,29 +11301,29 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="L168" s="13" t="s">
         <v>927</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="J168" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="K168" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="L168" s="13" t="s">
-        <v>930</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -11321,7 +11331,7 @@
         <v>71</v>
       </c>
       <c r="S168" s="2" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="T168" s="4">
         <v>155</v>
@@ -11338,29 +11348,29 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="K169" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="E169" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="F169" s="2" t="s">
+      <c r="L169" s="13" t="s">
         <v>933</v>
-      </c>
-      <c r="J169" s="2" t="s">
-        <v>934</v>
-      </c>
-      <c r="K169" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="L169" s="13" t="s">
-        <v>936</v>
       </c>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
@@ -11368,7 +11378,7 @@
         <v>77</v>
       </c>
       <c r="S169" s="2" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="T169" s="4">
         <v>61</v>
@@ -11385,14 +11395,14 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>111</v>
@@ -11401,13 +11411,13 @@
         <v>112</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="L170" s="13" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -11415,7 +11425,7 @@
         <v>77</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="T170" s="4">
         <v>62</v>
@@ -11432,29 +11442,29 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="J171" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="E171" s="2" t="s">
+      <c r="K171" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="F171" s="2" t="s">
+      <c r="L171" s="13" t="s">
         <v>945</v>
-      </c>
-      <c r="J171" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="K171" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="L171" s="13" t="s">
-        <v>948</v>
       </c>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
@@ -11462,7 +11472,7 @@
         <v>77</v>
       </c>
       <c r="S171" s="2" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="T171" s="4">
         <v>224</v>
@@ -11479,29 +11489,29 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="L172" s="13" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
@@ -11509,7 +11519,7 @@
         <v>77</v>
       </c>
       <c r="S172" s="2" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="T172" s="4">
         <v>140</v>
@@ -11526,29 +11536,29 @@
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="J173" s="2" t="s">
         <v>953</v>
       </c>
-      <c r="E173" s="2" t="s">
+      <c r="K173" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="F173" s="2" t="s">
+      <c r="L173" s="13" t="s">
         <v>955</v>
-      </c>
-      <c r="J173" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="K173" s="2" t="s">
-        <v>957</v>
-      </c>
-      <c r="L173" s="13" t="s">
-        <v>958</v>
       </c>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
@@ -11573,29 +11583,29 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="L174" s="13" t="s">
         <v>960</v>
-      </c>
-      <c r="J174" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="K174" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="L174" s="13" t="s">
-        <v>963</v>
       </c>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
@@ -11603,7 +11613,7 @@
         <v>223</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="T174" s="4">
         <v>250</v>
@@ -11620,14 +11630,14 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>26</v>
@@ -11636,13 +11646,13 @@
         <v>43</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="L175" s="13" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
@@ -11650,7 +11660,7 @@
         <v>77</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="T175" s="4">
         <v>198</v>
@@ -11667,14 +11677,14 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>26</v>
@@ -11683,18 +11693,18 @@
         <v>43</v>
       </c>
       <c r="J176" s="2" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="L176" s="13" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="R176" s="2" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="S176" s="2" t="s">
         <v>78</v>
@@ -11711,26 +11721,26 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="R177" s="2" t="s">
         <v>71</v>
@@ -11753,10 +11763,10 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2">
@@ -11769,16 +11779,16 @@
         <v>95</v>
       </c>
       <c r="J178" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="L178" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="N178" s="3" t="s">
         <v>980</v>
-      </c>
-      <c r="K178" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="L178" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="N178" s="3" t="s">
-        <v>983</v>
       </c>
       <c r="R178" s="2" t="s">
         <v>77</v>
@@ -11801,14 +11811,14 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>83</v>
@@ -11820,13 +11830,13 @@
         <v>187</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="N179" s="3" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="R179" s="2" t="s">
         <v>77</v>
@@ -11849,29 +11859,29 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2">
         <v>1583</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="R180" s="2" t="s">
         <v>77</v>
@@ -11894,29 +11904,29 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F181" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="K181" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="L181" s="3" t="s">
         <v>990</v>
-      </c>
-      <c r="J181" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="K181" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="L181" s="3" t="s">
-        <v>993</v>
       </c>
       <c r="R181" s="2" t="s">
         <v>77</v>
@@ -11925,7 +11935,7 @@
         <v>40</v>
       </c>
       <c r="T181" s="4" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="U181" s="4">
         <v>60</v>
@@ -11939,29 +11949,29 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="R182" s="2" t="s">
         <v>77</v>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -5085,8 +5085,10 @@
           <t xml:space="preserve">Monument équestre, avec ronde-bosse et bas-relief, intégralement conçu par l'artiste.</t>
         </is>
       </c>
-      <c r="S34" s="2" t="s">
-        <v>998</v>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la ronde-bosse et le bas-relief, marbre pour le socle</t>
+        </is>
       </c>
       <c r="T34" s="4" t="s">
         <v>997</v>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -5082,7 +5082,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monument équestre, avec ronde-bosse et bas-relief, intégralement conçu par l'artiste.</t>
+          <t xml:space="preserve">Monument équestre, avec ronde-bosse et bas-relief en bronze, intégralement conçu par l'artiste, sur un socle en marbre.</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB4834B-9902-46E4-B51E-77154B5211FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6480DFB-383C-40FF-A8AE-2139AD9DBA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1895" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="1005">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -3016,13 +3016,25 @@
     <t>450 pour la statue, 350 pour le socle</t>
   </si>
   <si>
-    <t>Bronze (ronde-bosse et bas-relief) et marbre (socle)</t>
-  </si>
-  <si>
-    <t>Monument équestre ,avec ronde-bosse et bas-relief, intégralement conçu par l'artiste.</t>
-  </si>
-  <si>
     <t>Monument équestre de Cosme Ier de Médicis</t>
+  </si>
+  <si>
+    <t>Artiste associé</t>
+  </si>
+  <si>
+    <t>Monument équestre, avec ronde-bosse et bas-relief en bronze, intégralement conçu par l'artiste, sur un socle en marbre.</t>
+  </si>
+  <si>
+    <t>Bronze pour la ronde-bosse et le bas-relief, marbre pour le socle</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/La_petraia%2C_terrazza_superiore_del_giardino_03_fontana_di_fiorenza.jpg/1280px-La_petraia%2C_terrazza_superiore_del_giardino_03_fontana_di_fiorenza.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument entièrement conçu par Nicolas Tribolo. Le bronze représentant Hercule et Antée est de Bartoloméo Ammanati et date de 1560.</t>
   </si>
 </sst>
 </file>
@@ -3530,11 +3542,11 @@
     <col min="21" max="21" width="8.140625" style="4" customWidth="1"/>
     <col min="22" max="22" width="5.42578125" style="4" customWidth="1"/>
     <col min="23" max="23" width="5.28515625" style="4" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
     <col min="25" max="25" width="17.140625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3604,13 +3616,11 @@
       <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artiste associé</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X1" s="4" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -3652,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -3697,7 +3707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -3742,7 +3752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -3787,7 +3797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -3829,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -3865,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -3907,7 +3917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -3952,7 +3962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>80</v>
       </c>
@@ -3997,7 +4007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>80</v>
       </c>
@@ -4042,7 +4052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>80</v>
       </c>
@@ -4090,7 +4100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>80</v>
       </c>
@@ -4138,7 +4148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>80</v>
       </c>
@@ -4181,7 +4191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -4226,7 +4236,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>116</v>
       </c>
@@ -5072,7 +5082,7 @@
         <v>27</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>227</v>
@@ -5080,15 +5090,11 @@
       <c r="L34" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument équestre, avec ronde-bosse et bas-relief en bronze, intégralement conçu par l'artiste, sur un socle en marbre.</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la ronde-bosse et le bas-relief, marbre pour le socle</t>
-        </is>
+      <c r="R34" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>1001</v>
       </c>
       <c r="T34" s="4" t="s">
         <v>997</v>
@@ -11600,19 +11606,25 @@
       <c r="F174" s="2" t="s">
         <v>957</v>
       </c>
+      <c r="G174" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I174" s="13" t="s">
+        <v>960</v>
+      </c>
       <c r="J174" s="2" t="s">
         <v>958</v>
       </c>
       <c r="K174" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="L174" s="13" t="s">
-        <v>960</v>
+      <c r="L174" s="7" t="s">
+        <v>1002</v>
       </c>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="R174" s="2" t="s">
-        <v>223</v>
+        <v>1004</v>
       </c>
       <c r="S174" s="2" t="s">
         <v>961</v>
@@ -12197,7 +12209,7 @@
     <hyperlink ref="L171" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
     <hyperlink ref="L172" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
     <hyperlink ref="L173" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="L174" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="I174" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
     <hyperlink ref="L175" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
     <hyperlink ref="L176" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
     <hyperlink ref="L177" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
@@ -12208,6 +12220,8 @@
     <hyperlink ref="L180" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
     <hyperlink ref="L181" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
     <hyperlink ref="L182" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="L174" r:id="rId213" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG/1280px-Tribolo_e_pierino_da_vinci%2C_Fontana_di_Fiorenza%2C_base_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{19BD4BA0-571B-428C-9D62-52E010785828}"/>
+    <hyperlink ref="G174" r:id="rId214" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/La_petraia%2C_terrazza_superiore_del_giardino_03_fontana_di_fiorenza.jpg/1280px-La_petraia%2C_terrazza_superiore_del_giardino_03_fontana_di_fiorenza.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F5347DD9-B250-4555-B33B-1E2BF3BF97CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e.xlsx
+++ b/quizzes/sculpture-16e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6480DFB-383C-40FF-A8AE-2139AD9DBA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD02FDE8-330A-422C-A9CE-B01F3594BEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="1008">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -106,18 +106,12 @@
     <t>Piazza della Signoria</t>
   </si>
   <si>
-    <t>La Fontaine de Neptune</t>
-  </si>
-  <si>
     <t>Fontana del Nettuno</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg/1280px-%22Urspr%C3%BCnglich_Symbol_f%C3%BCr_die_Macht_der_Medici-Familie%22_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Monument avec rondes-bosses</t>
-  </si>
-  <si>
     <t>Marbre et bronze</t>
   </si>
   <si>
@@ -3035,6 +3029,21 @@
   </si>
   <si>
     <t>Monument entièrement conçu par Nicolas Tribolo. Le bronze représentant Hercule et Antée est de Bartoloméo Ammanati et date de 1560.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Bacchus_fountain_%28Fontana_del_Bacchino%29%2C_Boboli_Gardens%2C_Florence_%2826075488184%29.jpg/960px-Bacchus_fountain_%28Fontana_del_Bacchino%29%2C_Boboli_Gardens%2C_Florence_%2826075488184%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Statue de Neptune</t>
+  </si>
+  <si>
+    <t>Monument avec rondes-bosses, d'abord imaginé par Bacio Bandinelli. Ammanati, à la mort de Bandinelli, a créé la partie centrale de la fontaine, la statue de Neptune et son char-coquille, tiré par quatre chevaux marins. Les autres rondes-bosses en bronze, tritons, nymphes, ont été réalisées par plusieurs autres artistes de son atelier, dont le jeune Giambologna.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/62/Firenze_fontanna_Neptuna.jpg/1280px-Firenze_fontanna_Neptuna.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg/1280px-Fontana_del_Nettuno_%28Florence%29_2_2013_February.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -3617,7 +3626,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3637,20 +3646,26 @@
       <c r="F2" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G2" s="7" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="J2" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="S2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="T2" s="4">
         <v>560</v>
@@ -3671,31 +3686,31 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="T3" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="U3" s="4">
         <v>310</v>
@@ -3716,28 +3731,28 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="R4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="S4" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T4" s="4">
         <v>262</v>
@@ -3761,28 +3776,28 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="R5" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T5" s="4">
         <v>50</v>
@@ -3806,28 +3821,28 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="S6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="U6" s="4">
         <v>10800</v>
@@ -3848,28 +3863,28 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="R7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="W7" s="4">
         <v>1</v>
@@ -3884,28 +3899,28 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="L8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="S8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T8" s="4">
         <v>550</v>
@@ -3926,31 +3941,31 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="L9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="S9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="T9" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="T9" s="4" t="s">
-        <v>79</v>
       </c>
       <c r="U9" s="4">
         <v>250</v>
@@ -3964,38 +3979,38 @@
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="L10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="R10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T10" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T10" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="U10" s="4">
         <v>90</v>
@@ -4009,38 +4024,38 @@
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="L11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="R11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T11" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="U11" s="4">
         <v>90</v>
@@ -4054,38 +4069,38 @@
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="L12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="R12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S12" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="T12" s="4">
         <v>250</v>
@@ -4102,38 +4117,38 @@
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="J13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="R13" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T13" s="4">
         <v>250</v>
@@ -4150,36 +4165,36 @@
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="L14" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="N14" s="3"/>
       <c r="R14" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T14" s="4">
         <v>48</v>
@@ -4193,35 +4208,35 @@
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="L15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="R15" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T15" s="4">
         <v>56</v>
@@ -4238,14 +4253,14 @@
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>26</v>
@@ -4254,25 +4269,25 @@
         <v>27</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="R16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T16" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T16" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="U16" s="4">
         <v>210</v>
@@ -4286,32 +4301,32 @@
     </row>
     <row r="17" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
@@ -4319,10 +4334,10 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T17" s="4">
         <v>224</v>
@@ -4339,38 +4354,38 @@
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="L18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="R18" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T18" s="4">
         <v>250</v>
@@ -4387,32 +4402,32 @@
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T19" s="4">
         <v>78</v>
@@ -4429,35 +4444,35 @@
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="L20" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>141</v>
-      </c>
       <c r="R20" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T20" s="4">
         <v>195</v>
@@ -4474,35 +4489,35 @@
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="R21" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T21" s="4">
         <v>273</v>
@@ -4519,32 +4534,32 @@
     </row>
     <row r="22" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="L22" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
@@ -4552,10 +4567,10 @@
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S22" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T22" s="9">
         <v>213</v>
@@ -4572,32 +4587,32 @@
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="L23" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
@@ -4605,10 +4620,10 @@
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T23" s="9">
         <v>200</v>
@@ -4625,41 +4640,41 @@
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="L24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="M24" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="N24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="R24" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="S24" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="T24" s="4">
         <v>1500</v>
@@ -4673,44 +4688,44 @@
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="J25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="N25" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="R25" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S25" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="N25" s="3" t="s">
+      <c r="T25" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="R25" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="S25" s="2" t="s">
+      <c r="U25" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="T25" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="U25" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="V25" s="4">
         <v>32</v>
@@ -4721,35 +4736,35 @@
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="L26" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="R26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="S26" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="W26" s="4">
         <v>2</v>
@@ -4757,35 +4772,35 @@
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="L27" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="R27" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T27" s="4">
         <v>187</v>
@@ -4802,41 +4817,41 @@
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="J28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="R28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="T28" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="U28" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="T28" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="V28" s="4">
         <v>34</v>
@@ -4847,35 +4862,35 @@
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="L29" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="R29" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="T29" s="4">
         <v>1000</v>
@@ -4892,38 +4907,38 @@
     </row>
     <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="L30" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="R30" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T30" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="R30" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T30" s="4" t="s">
-        <v>205</v>
       </c>
       <c r="U30" s="4">
         <v>130</v>
@@ -4937,38 +4952,38 @@
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="K31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L31" s="3" t="s">
+      <c r="S31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T31" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="T31" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="W31" s="4">
         <v>1</v>
@@ -4976,38 +4991,38 @@
     </row>
     <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J32" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="R32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T32" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="T32" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="U32" s="4">
         <v>57</v>
@@ -5021,38 +5036,38 @@
     </row>
     <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="L33" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="R33" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="L33" s="3" t="s">
+      <c r="S33" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="R33" s="2" t="s">
+      <c r="T33" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="T33" s="4" t="s">
-        <v>225</v>
       </c>
       <c r="U33" s="4">
         <v>1200</v>
@@ -5066,14 +5081,14 @@
     </row>
     <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>26</v>
@@ -5082,22 +5097,22 @@
         <v>27</v>
       </c>
       <c r="J34" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="R34" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>1000</v>
-      </c>
       <c r="S34" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="U34" s="4">
         <v>400</v>
@@ -5111,38 +5126,38 @@
     </row>
     <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="R35" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T35" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="R35" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T35" s="4" t="s">
-        <v>233</v>
       </c>
       <c r="U35" s="4">
         <v>100</v>
@@ -5156,35 +5171,35 @@
     </row>
     <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T36" s="4">
         <v>235</v>
@@ -5201,38 +5216,38 @@
     </row>
     <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="R37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T37" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T37" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="U37" s="4">
         <v>130</v>
@@ -5246,34 +5261,34 @@
     </row>
     <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="J38" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="L38" s="13" t="s">
         <v>245</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L38" s="13" t="s">
-        <v>247</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="R38" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T38" s="4">
         <v>83</v>
@@ -5287,34 +5302,34 @@
     </row>
     <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L39" s="13" t="s">
         <v>248</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="L39" s="13" t="s">
-        <v>250</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="R39" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T39" s="4">
         <v>230</v>
@@ -5325,34 +5340,34 @@
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="J40" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="L40" s="13" t="s">
         <v>253</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="L40" s="13" t="s">
-        <v>255</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="R40" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="T40" s="4">
         <v>145</v>
@@ -5369,34 +5384,34 @@
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="L41" s="13" t="s">
         <v>257</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="L41" s="13" t="s">
-        <v>259</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="R41" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T41" s="4">
         <v>64</v>
@@ -5413,32 +5428,32 @@
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="R42" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T42" s="4">
         <v>517</v>
@@ -5455,32 +5470,32 @@
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="L43" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="J43" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="R43" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T43" s="4">
         <v>128</v>
@@ -5497,32 +5512,32 @@
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J44" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="L44" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="R44" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T44" s="4">
         <v>780</v>
@@ -5536,32 +5551,32 @@
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="R45" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T45" s="4">
         <v>228</v>
@@ -5578,35 +5593,35 @@
     </row>
     <row r="46" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J46" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T46" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="R46" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S46" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T46" s="4" t="s">
-        <v>279</v>
       </c>
       <c r="U46" s="4">
         <v>49</v>
@@ -5620,35 +5635,35 @@
     </row>
     <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J47" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="L47" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="R47" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T47" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T47" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="U47" s="4">
         <v>75</v>
@@ -5662,32 +5677,32 @@
     </row>
     <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="J48" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="R48" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T48" s="4">
         <v>650</v>
@@ -5701,38 +5716,38 @@
     </row>
     <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="M49" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="N49" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="M49" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="R49" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T49" s="4">
         <v>277</v>
@@ -5749,32 +5764,32 @@
     </row>
     <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>299</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="L50" s="12" t="s">
         <v>300</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>302</v>
       </c>
       <c r="M50" s="8"/>
       <c r="N50" s="8"/>
@@ -5782,10 +5797,10 @@
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
       <c r="R50" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S50" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="T50" s="9">
         <v>26</v>
@@ -5802,32 +5817,32 @@
     </row>
     <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C51" s="8"/>
       <c r="D51" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="L51" s="12" t="s">
         <v>305</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="L51" s="12" t="s">
-        <v>307</v>
       </c>
       <c r="M51" s="8"/>
       <c r="N51" s="8"/>
@@ -5835,13 +5850,13 @@
       <c r="P51" s="8"/>
       <c r="Q51" s="8"/>
       <c r="R51" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T51" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="U51" s="9">
         <v>132</v>
@@ -5855,32 +5870,32 @@
     </row>
     <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
       <c r="J52" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="L52" s="12" t="s">
         <v>310</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="L52" s="12" t="s">
-        <v>312</v>
       </c>
       <c r="M52" s="8"/>
       <c r="N52" s="8"/>
@@ -5888,10 +5903,10 @@
       <c r="P52" s="8"/>
       <c r="Q52" s="8"/>
       <c r="R52" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S52" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T52" s="9">
         <v>205</v>
@@ -5908,32 +5923,32 @@
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="L53" s="14" t="s">
         <v>314</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="14" t="s">
-        <v>316</v>
       </c>
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
@@ -5941,10 +5956,10 @@
       <c r="P53" s="8"/>
       <c r="Q53" s="8"/>
       <c r="R53" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S53" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="T53" s="9">
         <v>110</v>
@@ -5961,34 +5976,34 @@
     </row>
     <row r="54" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>320</v>
       </c>
       <c r="G54" s="8"/>
       <c r="H54" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="L54" s="12" t="s">
         <v>322</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="L54" s="12" t="s">
-        <v>324</v>
       </c>
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
@@ -5996,10 +6011,10 @@
       <c r="P54" s="8"/>
       <c r="Q54" s="8"/>
       <c r="R54" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S54" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="T54" s="9">
         <v>274</v>
@@ -6016,32 +6031,32 @@
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>326</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>328</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="L55" s="14" t="s">
         <v>329</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="L55" s="14" t="s">
-        <v>331</v>
       </c>
       <c r="M55" s="8"/>
       <c r="N55" s="8"/>
@@ -6049,10 +6064,10 @@
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
       <c r="R55" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="S55" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T55" s="9">
         <v>105</v>
@@ -6069,32 +6084,32 @@
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
       <c r="J56" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="L56" s="12" t="s">
         <v>334</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="L56" s="12" t="s">
-        <v>336</v>
       </c>
       <c r="M56" s="8"/>
       <c r="N56" s="8"/>
@@ -6102,10 +6117,10 @@
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
       <c r="R56" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="T56" s="9">
         <v>105</v>
@@ -6122,32 +6137,32 @@
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="L57" s="12" t="s">
         <v>339</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="L57" s="12" t="s">
-        <v>341</v>
       </c>
       <c r="M57" s="8"/>
       <c r="N57" s="8"/>
@@ -6155,10 +6170,10 @@
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
       <c r="R57" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T57" s="9">
         <v>149</v>
@@ -6175,39 +6190,42 @@
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F58" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="K58" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="L58" s="13" t="s">
         <v>346</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="L58" s="13" t="s">
-        <v>348</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T58" s="4">
         <v>116</v>
@@ -6224,42 +6242,42 @@
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F59" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="L59" s="13" t="s">
         <v>353</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="L59" s="13" t="s">
-        <v>355</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T59" s="4">
         <v>145</v>
@@ -6276,37 +6294,37 @@
     </row>
     <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J60" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="L60" s="13" t="s">
         <v>358</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="L60" s="13" t="s">
-        <v>360</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="R60" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T60" s="4">
         <v>98</v>
@@ -6323,37 +6341,37 @@
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J61" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="L61" s="13" t="s">
         <v>362</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="L61" s="13" t="s">
-        <v>364</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="R61" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T61" s="4">
         <v>71</v>
@@ -6367,32 +6385,32 @@
     </row>
     <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F62" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="J62" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="R62" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T62" s="4">
         <v>215</v>
@@ -6409,37 +6427,37 @@
     </row>
     <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="J63" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="L63" s="13" t="s">
         <v>374</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="L63" s="13" t="s">
-        <v>376</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="R63" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T63" s="4">
         <v>53</v>
@@ -6453,37 +6471,37 @@
     </row>
     <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F64" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="K64" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="J64" s="2" t="s">
+      <c r="L64" s="13" t="s">
         <v>380</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="L64" s="13" t="s">
-        <v>382</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="R64" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T64" s="4">
         <v>30</v>
@@ -6500,37 +6518,37 @@
     </row>
     <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J65" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="L65" s="13" t="s">
         <v>384</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="L65" s="13" t="s">
-        <v>386</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="R65" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T65" s="4">
         <v>76</v>
@@ -6547,37 +6565,37 @@
     </row>
     <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J66" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>392</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="R66" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T66" s="4">
         <v>187</v>
@@ -6594,37 +6612,37 @@
     </row>
     <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="J67" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="K67" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="L67" s="13" t="s">
         <v>396</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="L67" s="13" t="s">
-        <v>398</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="R67" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T67" s="4">
         <v>265</v>
@@ -6641,37 +6659,37 @@
     </row>
     <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J68" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="L68" s="13" t="s">
         <v>400</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="L68" s="13" t="s">
-        <v>402</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
       <c r="R68" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T68" s="4">
         <v>82</v>
@@ -6685,37 +6703,37 @@
     </row>
     <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J69" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="L69" s="13" t="s">
         <v>404</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="L69" s="13" t="s">
-        <v>406</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="R69" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T69" s="4">
         <v>120</v>
@@ -6732,37 +6750,37 @@
     </row>
     <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J70" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="L70" s="13" t="s">
         <v>408</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="L70" s="13" t="s">
-        <v>410</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="R70" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T70" s="4">
         <v>280</v>
@@ -6779,37 +6797,37 @@
     </row>
     <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J71" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="L71" s="13" t="s">
         <v>412</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="L71" s="13" t="s">
-        <v>414</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="R71" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T71" s="4">
         <v>243</v>
@@ -6826,39 +6844,39 @@
     </row>
     <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="E72" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J72" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="K72" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J72" s="2" t="s">
+      <c r="L72" s="13" t="s">
         <v>418</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="L72" s="13" t="s">
-        <v>420</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="R72" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T72" s="4">
         <v>179</v>
@@ -6875,39 +6893,39 @@
     </row>
     <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J73" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="L73" s="13" t="s">
         <v>422</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="L73" s="13" t="s">
-        <v>424</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="R73" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T73" s="4">
         <v>190</v>
@@ -6924,39 +6942,39 @@
     </row>
     <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="J74" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="K74" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="J74" s="2" t="s">
+      <c r="L74" s="13" t="s">
         <v>428</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="L74" s="13" t="s">
-        <v>430</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="R74" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T74" s="4">
         <v>232</v>
@@ -6973,39 +6991,39 @@
     </row>
     <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="J75" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="K75" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="L75" s="13" t="s">
         <v>434</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="L75" s="13" t="s">
-        <v>436</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="R75" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T75" s="4">
         <v>160</v>
@@ -7022,35 +7040,35 @@
     </row>
     <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="K76" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J76" s="2" t="s">
+      <c r="L76" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="R76" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T76" s="4">
         <v>190</v>
@@ -7067,35 +7085,35 @@
     </row>
     <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="K77" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J77" s="2" t="s">
+      <c r="L77" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="K77" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>446</v>
-      </c>
       <c r="R77" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T77" s="4">
         <v>117</v>
@@ -7112,35 +7130,35 @@
     </row>
     <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="J78" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="L78" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="R78" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="S78" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="L78" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="R78" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="T78" s="4">
         <v>600</v>
@@ -7157,41 +7175,41 @@
     </row>
     <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K79" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F79" s="2" t="s">
+      <c r="L79" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="J79" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="K79" s="2" t="s">
+      <c r="R79" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="S79" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="R79" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="T79" s="4">
         <v>1100</v>
       </c>
       <c r="U79" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="V79" s="4">
         <v>130</v>
@@ -7202,38 +7220,38 @@
     </row>
     <row r="80" spans="1:23" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="E80" s="2" t="s">
+      <c r="H80" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="J80" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="K80" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="J80" s="2" t="s">
+      <c r="L80" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>466</v>
-      </c>
       <c r="R80" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T80" s="4">
         <v>600</v>
@@ -7250,38 +7268,38 @@
     </row>
     <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="K81" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="L81" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="K81" s="2" t="s">
+      <c r="R81" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="T81" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="R81" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S81" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="T81" s="4" t="s">
-        <v>471</v>
       </c>
       <c r="U81" s="4">
         <v>80</v>
@@ -7295,32 +7313,32 @@
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J82" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="L82" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="R82" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T82" s="4">
         <v>800</v>
@@ -7337,37 +7355,37 @@
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="J83" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="K83" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="J83" s="2" t="s">
+      <c r="L83" s="13" t="s">
         <v>481</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="L83" s="13" t="s">
-        <v>483</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="R83" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T83" s="4">
         <v>116</v>
@@ -7384,37 +7402,37 @@
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F84" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="K84" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="J84" s="2" t="s">
+      <c r="L84" s="13" t="s">
         <v>485</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="L84" s="13" t="s">
-        <v>487</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="R84" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T84" s="4">
         <v>190</v>
@@ -7431,34 +7449,34 @@
     </row>
     <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D85" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="J85" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="F85" s="5" t="s">
+      <c r="K85" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="J85" s="5" t="s">
+      <c r="L85" s="15" t="s">
         <v>490</v>
       </c>
-      <c r="K85" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="L85" s="15" t="s">
-        <v>492</v>
-      </c>
       <c r="R85" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="S85" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T85" s="16">
         <v>3250</v>
@@ -7475,38 +7493,38 @@
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="K86" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J86" s="2" t="s">
+      <c r="L86" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>498</v>
-      </c>
       <c r="R86" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T86" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="U86" s="4">
         <v>92</v>
@@ -7520,41 +7538,41 @@
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="J87" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="K87" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="L87" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="M87" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="L87" s="3" t="s">
+      <c r="N87" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="M87" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>506</v>
-      </c>
       <c r="R87" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T87" s="4">
         <v>269</v>
@@ -7571,41 +7589,41 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="K88" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="J88" s="2" t="s">
+      <c r="L88" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="M88" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="N88" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="M88" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>512</v>
-      </c>
       <c r="R88" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T88" s="4">
         <v>347</v>
@@ -7622,30 +7640,30 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="18" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C89" s="18"/>
       <c r="D89" s="18" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F89" s="18" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G89" s="18"/>
       <c r="H89" s="18"/>
       <c r="I89" s="18"/>
       <c r="J89" s="18" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K89" s="18"/>
       <c r="L89" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M89" s="19"/>
       <c r="N89" s="19"/>
@@ -7653,10 +7671,10 @@
       <c r="P89" s="18"/>
       <c r="Q89" s="18"/>
       <c r="R89" s="18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S89" s="18" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="T89" s="10">
         <v>600</v>
@@ -7673,37 +7691,37 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D90" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="J90" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="K90" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="J90" s="2" t="s">
+      <c r="L90" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="K90" s="5" t="s">
+      <c r="R90" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S90" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="L90" s="15" t="s">
+      <c r="T90" s="17" t="s">
         <v>525</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S90" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="T90" s="17" t="s">
-        <v>527</v>
       </c>
       <c r="U90" s="17">
         <v>75</v>
@@ -7717,37 +7735,37 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="E91" s="2" t="s">
+      <c r="J91" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="K91" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="J91" s="2" t="s">
+      <c r="L91" s="13" t="s">
         <v>531</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="L91" s="13" t="s">
-        <v>533</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="R91" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T91" s="4">
         <v>13</v>
@@ -7761,37 +7779,37 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="J92" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="L92" s="13" t="s">
         <v>534</v>
-      </c>
-      <c r="K92" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="L92" s="13" t="s">
-        <v>536</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="R92" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T92" s="4">
         <v>13</v>
@@ -7805,37 +7823,37 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="J93" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="L93" s="13" t="s">
         <v>537</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="L93" s="13" t="s">
-        <v>539</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="R93" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T93" s="4">
         <v>14</v>
@@ -7849,37 +7867,37 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="E94" s="2" t="s">
+      <c r="J94" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="K94" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="J94" s="2" t="s">
+      <c r="L94" s="13" t="s">
         <v>543</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="L94" s="13" t="s">
-        <v>545</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="R94" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="T94" s="4">
         <v>67</v>
@@ -7896,36 +7914,36 @@
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E95" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K95" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="L95" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="N95" s="2"/>
       <c r="R95" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="T95" s="4">
         <v>27</v>
@@ -7942,39 +7960,39 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="E96" s="2" t="s">
+      <c r="J96" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="K96" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="L96" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="K96" s="2" t="s">
+      <c r="M96" s="6" t="s">
         <v>557</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>559</v>
       </c>
       <c r="N96" s="2"/>
       <c r="R96" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T96" s="4">
         <v>8</v>
@@ -7988,36 +8006,36 @@
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="J97" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="N97" s="2"/>
       <c r="R97" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T97" s="4">
         <v>8</v>
@@ -8031,36 +8049,36 @@
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="J98" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="K98" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="J98" s="2" t="s">
+      <c r="L98" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>566</v>
       </c>
       <c r="N98" s="2"/>
       <c r="R98" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="T98" s="4">
         <v>105</v>
@@ -8077,45 +8095,45 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="G99" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F99" s="2" t="s">
+      <c r="H99" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="G99" s="13" t="s">
+      <c r="J99" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="K99" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="J99" s="2" t="s">
+      <c r="L99" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="K99" s="2" t="s">
+      <c r="M99" s="6" t="s">
         <v>573</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>575</v>
       </c>
       <c r="N99" s="2"/>
       <c r="R99" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="T99" s="4">
         <v>380</v>
@@ -8126,45 +8144,45 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="G100" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F100" s="2" t="s">
+      <c r="H100" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="G100" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="H100" s="2" t="s">
+      <c r="J100" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="K100" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="J100" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="K100" s="2" t="s">
+      <c r="L100" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="M100" s="6" t="s">
         <v>573</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>575</v>
       </c>
       <c r="N100" s="2"/>
       <c r="R100" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="W100" s="4">
         <v>2</v>
@@ -8172,37 +8190,37 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="E101" s="2" t="s">
+      <c r="J101" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="K101" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="J101" s="2" t="s">
+      <c r="L101" s="13" t="s">
         <v>585</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="L101" s="13" t="s">
-        <v>587</v>
       </c>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="R101" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="T101" s="4">
         <v>1600</v>
@@ -8216,37 +8234,37 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="J102" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="K102" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="J102" s="2" t="s">
+      <c r="L102" s="13" t="s">
         <v>591</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="L102" s="13" t="s">
-        <v>593</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="R102" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="T102" s="4">
         <v>1440</v>
@@ -8260,37 +8278,37 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E103" s="2" t="s">
+      <c r="J103" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="K103" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="J103" s="2" t="s">
+      <c r="L103" s="13" t="s">
         <v>597</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="L103" s="13" t="s">
-        <v>599</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="R103" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="T103" s="4">
         <v>1060</v>
@@ -8304,37 +8322,37 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J104" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="K104" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="J104" s="2" t="s">
+      <c r="L104" s="13" t="s">
         <v>602</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="L104" s="13" t="s">
-        <v>604</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="R104" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="T104" s="4">
         <v>1150</v>
@@ -8348,40 +8366,40 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="J105" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F105" s="2" t="s">
+      <c r="K105" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="J105" s="2" t="s">
+      <c r="L105" s="13" t="s">
         <v>610</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="L105" s="13" t="s">
-        <v>612</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="R105" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S105" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T105" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="W105" s="4">
         <v>2</v>
@@ -8389,46 +8407,46 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="H106" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="I106" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="J106" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="I106" s="13" t="s">
+      <c r="K106" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="J106" s="2" t="s">
+      <c r="L106" s="13" t="s">
         <v>619</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="L106" s="13" t="s">
-        <v>621</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="R106" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S106" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T106" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="U106" s="4">
         <v>200</v>
@@ -8442,43 +8460,43 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F107" s="2" t="s">
+      <c r="J107" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="K107" s="6" t="s">
         <v>625</v>
       </c>
-      <c r="J107" s="2" t="s">
+      <c r="L107" s="13" t="s">
         <v>626</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="L107" s="13" t="s">
-        <v>628</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="R107" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S107" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T107" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="W107" s="4">
         <v>2</v>
@@ -8486,37 +8504,37 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="K108" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="J108" s="2" t="s">
+      <c r="L108" s="13" t="s">
         <v>631</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="L108" s="13" t="s">
-        <v>633</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="R108" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T108" s="4">
         <v>180</v>
@@ -8533,35 +8551,35 @@
     </row>
     <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J109" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="L109" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="N109" s="20" t="s">
         <v>635</v>
       </c>
-      <c r="L109" s="20" t="s">
-        <v>636</v>
-      </c>
-      <c r="N109" s="20" t="s">
-        <v>637</v>
-      </c>
       <c r="R109" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S109" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T109" s="4">
         <v>73</v>
@@ -8578,33 +8596,33 @@
     </row>
     <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="L110" s="20" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="N110" s="21"/>
       <c r="R110" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="T110" s="4">
         <v>210</v>
@@ -8621,42 +8639,42 @@
     </row>
     <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>641</v>
+      </c>
+      <c r="J111" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G111" s="13" t="s">
+      <c r="L111" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="J111" s="2" t="s">
+      <c r="M111" s="6" t="s">
         <v>644</v>
-      </c>
-      <c r="L111" s="20" t="s">
-        <v>645</v>
-      </c>
-      <c r="M111" s="6" t="s">
-        <v>646</v>
       </c>
       <c r="N111" s="21"/>
       <c r="R111" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T111" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="U111" s="4">
         <v>182</v>
@@ -8670,36 +8688,36 @@
     </row>
     <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="L112" s="20" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="N112" s="21"/>
       <c r="R112" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T112" s="4">
         <v>79</v>
@@ -8716,33 +8734,33 @@
     </row>
     <row r="113" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="J113" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="L113" s="20" t="s">
         <v>652</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="L113" s="20" t="s">
-        <v>654</v>
       </c>
       <c r="N113" s="21"/>
       <c r="R113" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="T113" s="4">
         <v>700</v>
@@ -8759,36 +8777,36 @@
     </row>
     <row r="114" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F114" s="2" t="s">
+      <c r="J114" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="H114" s="2" t="s">
+      <c r="L114" s="20" t="s">
         <v>658</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="L114" s="20" t="s">
-        <v>660</v>
       </c>
       <c r="N114" s="21"/>
       <c r="R114" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T114" s="4">
         <v>215</v>
@@ -8805,44 +8823,44 @@
     </row>
     <row r="115" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F115" s="2" t="s">
+      <c r="I115" s="20" t="s">
         <v>662</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="J115" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="I115" s="20" t="s">
+      <c r="L115" s="20" t="s">
         <v>664</v>
       </c>
-      <c r="J115" s="2" t="s">
+      <c r="M115" s="6" t="s">
         <v>665</v>
       </c>
-      <c r="L115" s="20" t="s">
+      <c r="N115" s="22" t="s">
         <v>666</v>
       </c>
-      <c r="M115" s="6" t="s">
-        <v>667</v>
-      </c>
-      <c r="N115" s="22" t="s">
-        <v>668</v>
-      </c>
       <c r="R115" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T115" s="4">
         <v>205</v>
@@ -8859,39 +8877,39 @@
     </row>
     <row r="116" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="H116" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="J116" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="L116" s="20" t="s">
         <v>672</v>
       </c>
-      <c r="J116" s="2" t="s">
+      <c r="M116" s="6" t="s">
         <v>673</v>
-      </c>
-      <c r="L116" s="20" t="s">
-        <v>674</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>675</v>
       </c>
       <c r="N116" s="21"/>
       <c r="R116" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T116" s="4">
         <v>80</v>
@@ -8908,37 +8926,37 @@
     </row>
     <row r="117" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="J117" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F117" s="2" t="s">
+      <c r="K117" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="J117" s="2" t="s">
+      <c r="L117" s="13" t="s">
         <v>680</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="L117" s="13" t="s">
-        <v>682</v>
       </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="R117" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T117" s="4">
         <v>140</v>
@@ -8955,37 +8973,37 @@
     </row>
     <row r="118" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J118" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="L118" s="13" t="s">
         <v>683</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="L118" s="13" t="s">
-        <v>685</v>
       </c>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="R118" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T118" s="4">
         <v>230</v>
@@ -8999,37 +9017,37 @@
     </row>
     <row r="119" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E119" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="J119" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="F119" s="2" t="s">
+      <c r="K119" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="J119" s="2" t="s">
+      <c r="L119" s="13" t="s">
         <v>688</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="L119" s="13" t="s">
-        <v>690</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="R119" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S119" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T119" s="4">
         <v>76</v>
@@ -9046,37 +9064,37 @@
     </row>
     <row r="120" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F120" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="K120" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="J120" s="2" t="s">
+      <c r="L120" s="13" t="s">
         <v>692</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="L120" s="13" t="s">
-        <v>694</v>
       </c>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
       <c r="R120" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="W120" s="4">
         <v>3</v>
@@ -9084,43 +9102,43 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="L121" s="13" t="s">
         <v>697</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J121" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="L121" s="13" t="s">
-        <v>699</v>
       </c>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
       <c r="R121" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S121" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T121" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="U121" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="V121" s="4" t="s">
         <v>700</v>
-      </c>
-      <c r="U121" s="4" t="s">
-        <v>701</v>
-      </c>
-      <c r="V121" s="4" t="s">
-        <v>702</v>
       </c>
       <c r="W121" s="4">
         <v>2</v>
@@ -9128,44 +9146,44 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="J122" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="K122" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="J122" s="2" t="s">
+      <c r="L122" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="K122" s="2" t="s">
+      <c r="M122" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="L122" s="13" t="s">
+      <c r="N122" s="13" t="s">
         <v>708</v>
       </c>
-      <c r="M122" s="2" t="s">
+      <c r="R122" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T122" s="4" t="s">
         <v>709</v>
-      </c>
-      <c r="N122" s="13" t="s">
-        <v>710</v>
-      </c>
-      <c r="R122" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S122" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="T122" s="4" t="s">
-        <v>711</v>
       </c>
       <c r="U122" s="4">
         <v>143</v>
@@ -9179,37 +9197,37 @@
     </row>
     <row r="123" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="K123" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="J123" s="2" t="s">
+      <c r="L123" s="13" t="s">
         <v>713</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="L123" s="13" t="s">
-        <v>715</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="R123" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S123" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T123" s="4">
         <v>182</v>
@@ -9226,40 +9244,40 @@
     </row>
     <row r="124" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="J124" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="L124" s="13" t="s">
         <v>716</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="L124" s="13" t="s">
-        <v>718</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="R124" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S124" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T124" s="4" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="U124" s="4">
         <v>72</v>
@@ -9273,40 +9291,40 @@
     </row>
     <row r="125" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="K125" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="J125" s="2" t="s">
+      <c r="L125" s="13" t="s">
         <v>721</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="L125" s="13" t="s">
-        <v>723</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
       <c r="R125" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S125" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T125" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="U125" s="4">
         <v>60</v>
@@ -9320,40 +9338,40 @@
     </row>
     <row r="126" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="J126" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="L126" s="13" t="s">
         <v>725</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="L126" s="13" t="s">
-        <v>727</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
       <c r="R126" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S126" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T126" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="U126" s="4">
         <v>53</v>
@@ -9367,30 +9385,30 @@
     </row>
     <row r="127" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="23" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C127" s="23"/>
       <c r="D127" s="23" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F127" s="23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G127" s="23"/>
       <c r="H127" s="23"/>
       <c r="I127" s="23"/>
       <c r="J127" s="23" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="K127" s="23"/>
       <c r="L127" s="24" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="M127" s="25"/>
       <c r="N127" s="25"/>
@@ -9398,10 +9416,10 @@
       <c r="P127" s="23"/>
       <c r="Q127" s="23"/>
       <c r="R127" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S127" s="23" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="T127" s="11"/>
       <c r="U127" s="11"/>
@@ -9412,34 +9430,34 @@
     </row>
     <row r="128" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G128" s="8"/>
       <c r="H128" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="K128" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="L128" s="12" t="s">
         <v>735</v>
-      </c>
-      <c r="K128" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="L128" s="12" t="s">
-        <v>737</v>
       </c>
       <c r="M128" s="8"/>
       <c r="N128" s="8"/>
@@ -9447,10 +9465,10 @@
       <c r="P128" s="8"/>
       <c r="Q128" s="8"/>
       <c r="R128" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S128" s="8" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="T128" s="9"/>
       <c r="U128" s="9"/>
@@ -9461,32 +9479,32 @@
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C129" s="8"/>
       <c r="D129" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="F129" s="8" t="s">
         <v>738</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="F129" s="8" t="s">
-        <v>740</v>
       </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
       <c r="I129" s="8"/>
       <c r="J129" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="L129" s="12" t="s">
         <v>741</v>
-      </c>
-      <c r="K129" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="L129" s="12" t="s">
-        <v>743</v>
       </c>
       <c r="M129" s="8"/>
       <c r="N129" s="8"/>
@@ -9494,10 +9512,10 @@
       <c r="P129" s="8"/>
       <c r="Q129" s="8"/>
       <c r="R129" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S129" s="8" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="T129" s="9">
         <v>600</v>
@@ -9514,30 +9532,30 @@
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="8">
         <v>1572</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
       <c r="I130" s="8"/>
       <c r="J130" s="8" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="K130" s="8"/>
       <c r="L130" s="12" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="M130" s="8"/>
       <c r="N130" s="8"/>
@@ -9545,10 +9563,10 @@
       <c r="P130" s="8"/>
       <c r="Q130" s="8"/>
       <c r="R130" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S130" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="T130" s="9">
         <v>182</v>
@@ -9565,42 +9583,42 @@
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F131" s="2" t="s">
+      <c r="J131" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="H131" s="2" t="s">
+      <c r="K131" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="J131" s="2" t="s">
+      <c r="L131" s="13" t="s">
         <v>752</v>
       </c>
-      <c r="K131" s="2" t="s">
+      <c r="M131" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="L131" s="13" t="s">
-        <v>754</v>
-      </c>
-      <c r="M131" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="N131" s="2"/>
       <c r="R131" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S131" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T131" s="4">
         <v>350</v>
@@ -9617,42 +9635,42 @@
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>751</v>
-      </c>
       <c r="J132" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="L132" s="13" t="s">
         <v>756</v>
       </c>
-      <c r="K132" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="L132" s="13" t="s">
-        <v>758</v>
-      </c>
       <c r="M132" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="N132" s="2"/>
       <c r="R132" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S132" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="T132" s="4">
         <v>350</v>
@@ -9669,40 +9687,40 @@
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H133" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="K133" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="J133" s="2" t="s">
+      <c r="L133" s="13" t="s">
         <v>761</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="L133" s="13" t="s">
-        <v>763</v>
       </c>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
       <c r="R133" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S133" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="W133" s="4">
         <v>3</v>
@@ -9710,40 +9728,40 @@
     </row>
     <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="J134" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H134" s="2" t="s">
+      <c r="K134" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="J134" s="2" t="s">
+      <c r="L134" s="13" t="s">
         <v>767</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="L134" s="13" t="s">
-        <v>769</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
       <c r="R134" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S134" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T134" s="4">
         <v>25</v>
@@ -9760,35 +9778,35 @@
     </row>
     <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="J135" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="G135" s="3" t="s">
+      <c r="L135" s="12" t="s">
         <v>773</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="R135" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="S135" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="L135" s="12" t="s">
-        <v>775</v>
-      </c>
-      <c r="R135" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="S135" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="T135" s="4">
         <v>200</v>
@@ -9805,37 +9823,37 @@
     </row>
     <row r="136" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E136" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="J136" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="K136" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="J136" s="2" t="s">
+      <c r="L136" s="13" t="s">
         <v>779</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="L136" s="13" t="s">
-        <v>781</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
       <c r="R136" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S136" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="T136" s="4">
         <v>247</v>
@@ -9852,43 +9870,43 @@
     </row>
     <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E137" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="J137" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="F137" s="2" t="s">
+      <c r="K137" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="J137" s="2" t="s">
+      <c r="L137" s="13" t="s">
         <v>785</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="L137" s="13" t="s">
-        <v>787</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
       <c r="R137" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S137" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="T137" s="4" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="U137" s="4" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="W137" s="4">
         <v>3</v>
@@ -9896,37 +9914,37 @@
     </row>
     <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="J138" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F138" s="2" t="s">
+      <c r="K138" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="J138" s="2" t="s">
+      <c r="L138" s="13" t="s">
         <v>792</v>
-      </c>
-      <c r="K138" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="L138" s="13" t="s">
-        <v>794</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="R138" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S138" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T138" s="4">
         <v>500</v>
@@ -9943,41 +9961,41 @@
     </row>
     <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="L139" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J139" s="2" t="s">
+      <c r="M139" s="6" t="s">
         <v>798</v>
       </c>
-      <c r="L139" s="3" t="s">
+      <c r="N139" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="M139" s="6" t="s">
+      <c r="P139" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="N139" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="P139" s="3" t="s">
-        <v>802</v>
-      </c>
       <c r="R139" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S139" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="T139" s="4">
         <v>450</v>
@@ -9994,34 +10012,34 @@
     </row>
     <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="26">
         <v>1583</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="N140" s="3"/>
       <c r="P140" s="3"/>
       <c r="R140" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S140" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T140" s="4">
         <v>90</v>
@@ -10038,39 +10056,39 @@
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J141" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="N141" s="3" t="s">
         <v>805</v>
-      </c>
-      <c r="L141" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="N141" s="3" t="s">
-        <v>807</v>
       </c>
       <c r="P141" s="6"/>
       <c r="R141" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S141" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T141" s="4" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="U141" s="4">
         <v>75</v>
@@ -10084,42 +10102,42 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="26">
         <v>1586</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J142" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="M142" s="6" t="s">
         <v>809</v>
       </c>
-      <c r="L142" s="3" t="s">
+      <c r="N142" s="3" t="s">
         <v>810</v>
-      </c>
-      <c r="M142" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="N142" s="3" t="s">
-        <v>812</v>
       </c>
       <c r="P142" s="6"/>
       <c r="R142" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="T142" s="4" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="U142" s="4">
         <v>120</v>
@@ -10133,36 +10151,36 @@
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="L143" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J143" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="L143" s="3" t="s">
-        <v>817</v>
       </c>
       <c r="P143" s="6"/>
       <c r="R143" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S143" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T143" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="U143" s="4">
         <v>190</v>
@@ -10176,36 +10194,36 @@
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="L144" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="E144" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J144" s="2" t="s">
+      <c r="N144" s="3" t="s">
         <v>819</v>
-      </c>
-      <c r="L144" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="N144" s="3" t="s">
-        <v>821</v>
       </c>
       <c r="P144" s="6"/>
       <c r="R144" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S144" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T144" s="4">
         <v>83</v>
@@ -10222,33 +10240,33 @@
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="P145" s="6"/>
       <c r="R145" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S145" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T145" s="4">
         <v>140</v>
@@ -10265,39 +10283,39 @@
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="26">
         <v>1570</v>
       </c>
       <c r="E146" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="J146" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="F146" s="2" t="s">
+      <c r="L146" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="J146" s="2" t="s">
+      <c r="M146" s="6" t="s">
         <v>826</v>
       </c>
-      <c r="L146" s="3" t="s">
+      <c r="N146" s="3" t="s">
         <v>827</v>
-      </c>
-      <c r="M146" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="N146" s="3" t="s">
-        <v>829</v>
       </c>
       <c r="P146" s="6"/>
       <c r="R146" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S146" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T146" s="4">
         <v>96</v>
@@ -10314,34 +10332,34 @@
     </row>
     <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="E147" s="2" t="s">
+      <c r="J147" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="L147" s="13" t="s">
         <v>834</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="L147" s="13" t="s">
-        <v>836</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
       <c r="R147" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S147" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="T147" s="4">
         <v>177</v>
@@ -10358,34 +10376,34 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="J148" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="E148" s="2" t="s">
+      <c r="L148" s="13" t="s">
         <v>838</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="L148" s="13" t="s">
-        <v>840</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
       <c r="R148" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S148" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="T148" s="4">
         <v>180</v>
@@ -10402,34 +10420,34 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="E149" s="2" t="s">
+      <c r="J149" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="F149" s="2" t="s">
+      <c r="L149" s="13" t="s">
         <v>844</v>
-      </c>
-      <c r="J149" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="L149" s="13" t="s">
-        <v>846</v>
       </c>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
       <c r="R149" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S149" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="T149" s="4">
         <v>170</v>
@@ -10446,34 +10464,34 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="L150" s="13" t="s">
         <v>848</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="J150" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="L150" s="13" t="s">
-        <v>850</v>
       </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
       <c r="R150" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="T150" s="4">
         <v>164</v>
@@ -10490,32 +10508,32 @@
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C151" s="18"/>
       <c r="D151" s="18" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E151" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F151" s="18" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G151" s="18"/>
       <c r="H151" s="18"/>
       <c r="I151" s="18"/>
       <c r="J151" s="18" t="s">
+        <v>854</v>
+      </c>
+      <c r="K151" s="18" t="s">
+        <v>855</v>
+      </c>
+      <c r="L151" s="27" t="s">
         <v>856</v>
-      </c>
-      <c r="K151" s="18" t="s">
-        <v>857</v>
-      </c>
-      <c r="L151" s="27" t="s">
-        <v>858</v>
       </c>
       <c r="M151" s="18"/>
       <c r="N151" s="18"/>
@@ -10523,10 +10541,10 @@
       <c r="P151" s="18"/>
       <c r="Q151" s="18"/>
       <c r="R151" s="18" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="S151" s="18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T151" s="10">
         <v>130</v>
@@ -10541,39 +10559,39 @@
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="J152" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="K152" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="J152" s="2" t="s">
+      <c r="L152" s="13" t="s">
         <v>863</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="L152" s="13" t="s">
-        <v>865</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="R152" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S152" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T152" s="4">
         <v>185</v>
@@ -10587,39 +10605,39 @@
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="E153" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>862</v>
-      </c>
       <c r="J153" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="L153" s="13" t="s">
         <v>867</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="L153" s="13" t="s">
-        <v>869</v>
       </c>
       <c r="M153" s="2"/>
       <c r="N153" s="12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="R153" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S153" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T153" s="4">
         <v>150</v>
@@ -10633,37 +10651,37 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="L154" s="13" t="s">
         <v>870</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="J154" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="L154" s="13" t="s">
-        <v>872</v>
       </c>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
       <c r="R154" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T154" s="4">
         <v>180</v>
@@ -10680,37 +10698,37 @@
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="L155" s="13" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="R155" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="S155" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T155" s="4">
         <v>175</v>
@@ -10727,37 +10745,37 @@
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="J156" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="E156" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="K156" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="J156" s="2" t="s">
+      <c r="L156" s="13" t="s">
         <v>877</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="L156" s="13" t="s">
-        <v>879</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
       <c r="R156" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S156" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="T156" s="4">
         <v>800</v>
@@ -10774,32 +10792,32 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="8" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E157" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
       <c r="I157" s="8"/>
       <c r="J157" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="K157" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="L157" s="12" t="s">
         <v>881</v>
-      </c>
-      <c r="K157" s="8" t="s">
-        <v>882</v>
-      </c>
-      <c r="L157" s="12" t="s">
-        <v>883</v>
       </c>
       <c r="M157" s="8"/>
       <c r="N157" s="8"/>
@@ -10807,10 +10825,10 @@
       <c r="P157" s="8"/>
       <c r="Q157" s="8"/>
       <c r="R157" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S157" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="T157" s="9">
         <v>240</v>
@@ -10827,32 +10845,32 @@
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
-        